--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Game Log Season 3'!$A$2:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Player Adjusted Ranks'!$A$1:$L$9</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <pivotCaches>
     <pivotCache cacheId="5" r:id="rId7"/>
   </pivotCaches>
@@ -26624,22 +26624,253 @@
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-      <c r="E51" s="3"/>
-      <c r="M51" s="48"/>
-      <c r="X51" s="3"/>
+      <c r="A51" s="1">
+        <v>46236</v>
+      </c>
+      <c r="B51" s="7">
+        <v>14</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" s="3">
+        <v>2.3</v>
+      </c>
+      <c r="F51" s="7">
+        <v>1</v>
+      </c>
+      <c r="G51" s="7">
+        <v>1</v>
+      </c>
+      <c r="H51" s="7">
+        <v>3</v>
+      </c>
+      <c r="I51" s="7">
+        <v>2</v>
+      </c>
+      <c r="J51" s="7">
+        <f>F51-(1/H51)</f>
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="K51" s="7">
+        <f>((I51-((H51-1)/H51))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.4333333333333334</v>
+      </c>
+      <c r="L51" s="7">
+        <f>E51-((E52+E53)/2)</f>
+        <v>-0.75</v>
+      </c>
+      <c r="M51" s="48">
+        <f>0.5+(L51*0.09)</f>
+        <v>0.4325</v>
+      </c>
+      <c r="N51" s="7">
+        <f>((H51-(G51-1))/H51)*(IF(I51&lt;&gt;0,(I51+H51)/H51,1))</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="O51" s="8">
+        <f>(N51-(1/6))/(10/6)</f>
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="P51" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q51" s="8">
+        <f>IF(F51=1,(((1-((P51-3)/15))*0.5)+0.5),((P51/18)*0.5))</f>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="R51" s="7">
+        <v>1</v>
+      </c>
+      <c r="S51" s="7">
+        <v>0</v>
+      </c>
+      <c r="T51" s="7">
+        <v>0</v>
+      </c>
+      <c r="U51" s="8">
+        <f>IFERROR(T51/S51, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V51" s="10">
+        <v>0</v>
+      </c>
+      <c r="W51" s="14">
+        <v>2</v>
+      </c>
+      <c r="X51" s="3">
+        <f>((O51*0.3)+(Q51*0.175)+(R51*0.175)+(U51*0.175)+((1-V51)*0.175))+W51</f>
+        <v>2.9408333333333334</v>
+      </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-      <c r="E52" s="3"/>
-      <c r="M52" s="48"/>
-      <c r="X52" s="3"/>
+      <c r="A52" s="1">
+        <v>46236</v>
+      </c>
+      <c r="B52" s="7">
+        <v>14</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="F52" s="7">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7">
+        <v>2</v>
+      </c>
+      <c r="H52" s="7">
+        <v>3</v>
+      </c>
+      <c r="I52" s="7">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7">
+        <f>F52-(1/H52)</f>
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="K52" s="7">
+        <f>((I52-((H52-1)/H52))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.03333333333333335</v>
+      </c>
+      <c r="L52" s="7">
+        <f>E52-((E51+E53)/2)</f>
+        <v>-0.4500000000000002</v>
+      </c>
+      <c r="M52" s="48">
+        <f>0.5+(L52*0.09)</f>
+        <v>0.45949999999999996</v>
+      </c>
+      <c r="N52" s="7">
+        <f>((H52-(G52-1))/H52)*(IF(I52&lt;&gt;0,(I52+H52)/H52,1))</f>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O52" s="8">
+        <f>(N52-(1/6))/(10/6)</f>
+        <v>0.3</v>
+      </c>
+      <c r="P52" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="8">
+        <f>IF(F52=1,(((1-((P52-3)/15))*0.5)+0.5),((P52/18)*0.5))</f>
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="R52" s="7">
+        <v>0</v>
+      </c>
+      <c r="S52" s="7">
+        <v>1</v>
+      </c>
+      <c r="T52" s="7">
+        <v>0</v>
+      </c>
+      <c r="U52" s="8">
+        <f>IFERROR(T52/S52, 1)</f>
+        <v>0.0</v>
+      </c>
+      <c r="V52" s="10">
+        <v>0</v>
+      </c>
+      <c r="W52" s="14">
+        <v>2</v>
+      </c>
+      <c r="X52" s="3">
+        <f>((O52*0.3)+(Q52*0.175)+(R52*0.175)+(U52*0.175)+((1-V52)*0.175))+W52</f>
+        <v>2.303888888888889</v>
+      </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="E53" s="3"/>
-      <c r="M53" s="48"/>
-      <c r="X53" s="3"/>
+      <c r="A53" s="1">
+        <v>46236</v>
+      </c>
+      <c r="B53" s="7">
+        <v>14</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E53" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="F53" s="7">
+        <v>0</v>
+      </c>
+      <c r="G53" s="7">
+        <v>3</v>
+      </c>
+      <c r="H53" s="7">
+        <v>3</v>
+      </c>
+      <c r="I53" s="7">
+        <v>0</v>
+      </c>
+      <c r="J53" s="7">
+        <f>F53-(1/H53)</f>
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="K53" s="7">
+        <f>((I53-((H53-1)/H53))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.03333333333333335</v>
+      </c>
+      <c r="L53" s="7">
+        <f>E53-((E51+E52)/2)</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="M53" s="48">
+        <f>0.5+(L53*0.09)</f>
+        <v>0.608</v>
+      </c>
+      <c r="N53" s="7">
+        <f>((H53-(G53-1))/H53)*(IF(I53&lt;&gt;0,(I53+H53)/H53,1))</f>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O53" s="8">
+        <f>(N53-(1/6))/(10/6)</f>
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="P53" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q53" s="8">
+        <f>IF(F53=1,(((1-((P53-3)/15))*0.5)+0.5),((P53/18)*0.5))</f>
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="R53" s="7">
+        <v>0</v>
+      </c>
+      <c r="S53" s="7">
+        <v>1</v>
+      </c>
+      <c r="T53" s="7">
+        <v>0</v>
+      </c>
+      <c r="U53" s="8">
+        <f>IFERROR(T53/S53, 1)</f>
+        <v>0.0</v>
+      </c>
+      <c r="V53" s="10">
+        <v>0</v>
+      </c>
+      <c r="W53" s="14">
+        <v>3</v>
+      </c>
+      <c r="X53" s="3">
+        <f>((O53*0.3)+(Q53*0.175)+(R53*0.175)+(U53*0.175)+((1-V53)*0.175))+W53</f>
+        <v>3.239027777777778</v>
+      </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -28602,7 +28602,7 @@
       </c>
       <c r="B3" s="36">
         <f t="shared" si="0"/>
-        <v>0.27472520353960433</v>
+        <v>0.24978876904265432</v>
       </c>
       <c r="C3">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28610,11 +28610,11 @@
       </c>
       <c r="D3">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="36">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="F3">
         <f>SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28622,15 +28622,15 @@
       </c>
       <c r="G3">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D3,0)</f>
-        <v>5.0500000000000007</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="H3" s="36">
         <f t="shared" si="2"/>
-        <v>0.29698375870069604</v>
+        <v>0.2717622080679406</v>
       </c>
       <c r="I3" s="36">
         <f>IF(C3&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.20300000000000007</v>
+        <v>0.1875757575757576</v>
       </c>
       <c r="J3">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C3, 0)</f>
@@ -28638,11 +28638,11 @@
       </c>
       <c r="K3">
         <f>IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D3, 0)</f>
-        <v>7.1994999999999996</v>
+        <v>8.307500000000001</v>
       </c>
       <c r="L3" s="36">
         <f t="shared" si="3"/>
-        <v>0.29006015185879103</v>
+        <v>0.26148991021424123</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -28700,11 +28700,11 @@
       </c>
       <c r="B5" s="36">
         <f t="shared" si="0"/>
-        <v>0.20924751206541659</v>
+        <v>0.2596530147667175</v>
       </c>
       <c r="C5">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
@@ -28712,35 +28712,35 @@
       </c>
       <c r="E5" s="36">
         <f t="shared" si="1"/>
-        <v>0.23076923076923078</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F5">
         <f>SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
-        <v>2.166666666666667</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="G5">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D5,0)</f>
-        <v>7.1833333333333327</v>
+        <v>7.183333333333334</v>
       </c>
       <c r="H5" s="36">
         <f t="shared" si="2"/>
-        <v>0.23172905525846707</v>
+        <v>0.2828618968386023</v>
       </c>
       <c r="I5" s="36">
         <f>IF(C5&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.14589743589743592</v>
+        <v>0.16642857142857145</v>
       </c>
       <c r="J5">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C5, 0)</f>
-        <v>2.7330000000000001</v>
+        <v>3.8005</v>
       </c>
       <c r="K5">
         <f>IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D5, 0)</f>
-        <v>9.6280000000000001</v>
+        <v>9.628</v>
       </c>
       <c r="L5" s="36">
         <f t="shared" si="3"/>
-        <v>0.22109861661677857</v>
+        <v>0.283017462858845</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Game Log Season 3'!$A$2:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Player Adjusted Ranks'!$A$1:$L$9</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="5" r:id="rId7"/>
   </pivotCaches>
@@ -26624,253 +26624,22 @@
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
-        <v>46236</v>
-      </c>
-      <c r="B51" s="7">
-        <v>14</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E51" s="3">
-        <v>2.3</v>
-      </c>
-      <c r="F51" s="7">
-        <v>1</v>
-      </c>
-      <c r="G51" s="7">
-        <v>1</v>
-      </c>
-      <c r="H51" s="7">
-        <v>3</v>
-      </c>
-      <c r="I51" s="7">
-        <v>2</v>
-      </c>
-      <c r="J51" s="7">
-        <f>F51-(1/H51)</f>
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="K51" s="7">
-        <f>((I51-((H51-1)/H51))-(-5/6))/((5-(5/6))-(-5/6))</f>
-        <v>0.4333333333333334</v>
-      </c>
-      <c r="L51" s="7">
-        <f>E51-((E52+E53)/2)</f>
-        <v>-0.75</v>
-      </c>
-      <c r="M51" s="48">
-        <f>0.5+(L51*0.09)</f>
-        <v>0.4325</v>
-      </c>
-      <c r="N51" s="7">
-        <f>((H51-(G51-1))/H51)*(IF(I51&lt;&gt;0,(I51+H51)/H51,1))</f>
-        <v>1.6666666666666667</v>
-      </c>
-      <c r="O51" s="8">
-        <f>(N51-(1/6))/(10/6)</f>
-        <v>0.8999999999999999</v>
-      </c>
-      <c r="P51" s="7">
-        <v>8</v>
-      </c>
-      <c r="Q51" s="8">
-        <f>IF(F51=1,(((1-((P51-3)/15))*0.5)+0.5),((P51/18)*0.5))</f>
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="R51" s="7">
-        <v>1</v>
-      </c>
-      <c r="S51" s="7">
-        <v>0</v>
-      </c>
-      <c r="T51" s="7">
-        <v>0</v>
-      </c>
-      <c r="U51" s="8">
-        <f>IFERROR(T51/S51, 1)</f>
-        <v>1</v>
-      </c>
-      <c r="V51" s="10">
-        <v>0</v>
-      </c>
-      <c r="W51" s="14">
-        <v>2</v>
-      </c>
-      <c r="X51" s="3">
-        <f>((O51*0.3)+(Q51*0.175)+(R51*0.175)+(U51*0.175)+((1-V51)*0.175))+W51</f>
-        <v>2.9408333333333334</v>
-      </c>
+      <c r="A51" s="1"/>
+      <c r="E51" s="3"/>
+      <c r="M51" s="48"/>
+      <c r="X51" s="3"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
-        <v>46236</v>
-      </c>
-      <c r="B52" s="7">
-        <v>14</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="F52" s="7">
-        <v>0</v>
-      </c>
-      <c r="G52" s="7">
-        <v>2</v>
-      </c>
-      <c r="H52" s="7">
-        <v>3</v>
-      </c>
-      <c r="I52" s="7">
-        <v>0</v>
-      </c>
-      <c r="J52" s="7">
-        <f>F52-(1/H52)</f>
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="K52" s="7">
-        <f>((I52-((H52-1)/H52))-(-5/6))/((5-(5/6))-(-5/6))</f>
-        <v>0.03333333333333335</v>
-      </c>
-      <c r="L52" s="7">
-        <f>E52-((E51+E53)/2)</f>
-        <v>-0.4500000000000002</v>
-      </c>
-      <c r="M52" s="48">
-        <f>0.5+(L52*0.09)</f>
-        <v>0.45949999999999996</v>
-      </c>
-      <c r="N52" s="7">
-        <f>((H52-(G52-1))/H52)*(IF(I52&lt;&gt;0,(I52+H52)/H52,1))</f>
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="O52" s="8">
-        <f>(N52-(1/6))/(10/6)</f>
-        <v>0.3</v>
-      </c>
-      <c r="P52" s="7">
-        <v>8</v>
-      </c>
-      <c r="Q52" s="8">
-        <f>IF(F52=1,(((1-((P52-3)/15))*0.5)+0.5),((P52/18)*0.5))</f>
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="R52" s="7">
-        <v>0</v>
-      </c>
-      <c r="S52" s="7">
-        <v>1</v>
-      </c>
-      <c r="T52" s="7">
-        <v>0</v>
-      </c>
-      <c r="U52" s="8">
-        <f>IFERROR(T52/S52, 1)</f>
-        <v>0.0</v>
-      </c>
-      <c r="V52" s="10">
-        <v>0</v>
-      </c>
-      <c r="W52" s="14">
-        <v>2</v>
-      </c>
-      <c r="X52" s="3">
-        <f>((O52*0.3)+(Q52*0.175)+(R52*0.175)+(U52*0.175)+((1-V52)*0.175))+W52</f>
-        <v>2.303888888888889</v>
-      </c>
+      <c r="A52" s="1"/>
+      <c r="E52" s="3"/>
+      <c r="M52" s="48"/>
+      <c r="X52" s="3"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
-        <v>46236</v>
-      </c>
-      <c r="B53" s="7">
-        <v>14</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E53" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="F53" s="7">
-        <v>0</v>
-      </c>
-      <c r="G53" s="7">
-        <v>3</v>
-      </c>
-      <c r="H53" s="7">
-        <v>3</v>
-      </c>
-      <c r="I53" s="7">
-        <v>0</v>
-      </c>
-      <c r="J53" s="7">
-        <f>F53-(1/H53)</f>
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="K53" s="7">
-        <f>((I53-((H53-1)/H53))-(-5/6))/((5-(5/6))-(-5/6))</f>
-        <v>0.03333333333333335</v>
-      </c>
-      <c r="L53" s="7">
-        <f>E53-((E51+E52)/2)</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="M53" s="48">
-        <f>0.5+(L53*0.09)</f>
-        <v>0.608</v>
-      </c>
-      <c r="N53" s="7">
-        <f>((H53-(G53-1))/H53)*(IF(I53&lt;&gt;0,(I53+H53)/H53,1))</f>
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="O53" s="8">
-        <f>(N53-(1/6))/(10/6)</f>
-        <v>0.09999999999999999</v>
-      </c>
-      <c r="P53" s="7">
-        <v>7</v>
-      </c>
-      <c r="Q53" s="8">
-        <f>IF(F53=1,(((1-((P53-3)/15))*0.5)+0.5),((P53/18)*0.5))</f>
-        <v>0.19444444444444445</v>
-      </c>
-      <c r="R53" s="7">
-        <v>0</v>
-      </c>
-      <c r="S53" s="7">
-        <v>1</v>
-      </c>
-      <c r="T53" s="7">
-        <v>0</v>
-      </c>
-      <c r="U53" s="8">
-        <f>IFERROR(T53/S53, 1)</f>
-        <v>0.0</v>
-      </c>
-      <c r="V53" s="10">
-        <v>0</v>
-      </c>
-      <c r="W53" s="14">
-        <v>3</v>
-      </c>
-      <c r="X53" s="3">
-        <f>((O53*0.3)+(Q53*0.175)+(R53*0.175)+(U53*0.175)+((1-V53)*0.175))+W53</f>
-        <v>3.239027777777778</v>
-      </c>
+      <c r="A53" s="1"/>
+      <c r="E53" s="3"/>
+      <c r="M53" s="48"/>
+      <c r="X53" s="3"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -28602,7 +28371,7 @@
       </c>
       <c r="B3" s="36">
         <f t="shared" si="0"/>
-        <v>0.24978876904265432</v>
+        <v>0.27472520353960433</v>
       </c>
       <c r="C3">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28610,11 +28379,11 @@
       </c>
       <c r="D3">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="36">
         <f t="shared" si="1"/>
-        <v>0.2727272727272727</v>
+        <v>0.3</v>
       </c>
       <c r="F3">
         <f>SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28622,15 +28391,15 @@
       </c>
       <c r="G3">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D3,0)</f>
-        <v>5.716666666666667</v>
+        <v>5.0500000000000007</v>
       </c>
       <c r="H3" s="36">
         <f t="shared" si="2"/>
-        <v>0.2717622080679406</v>
+        <v>0.29698375870069604</v>
       </c>
       <c r="I3" s="36">
         <f>IF(C3&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.1875757575757576</v>
+        <v>0.20300000000000007</v>
       </c>
       <c r="J3">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C3, 0)</f>
@@ -28638,11 +28407,11 @@
       </c>
       <c r="K3">
         <f>IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D3, 0)</f>
-        <v>8.307500000000001</v>
+        <v>7.1994999999999996</v>
       </c>
       <c r="L3" s="36">
         <f t="shared" si="3"/>
-        <v>0.26148991021424123</v>
+        <v>0.29006015185879103</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -28700,11 +28469,11 @@
       </c>
       <c r="B5" s="36">
         <f t="shared" si="0"/>
-        <v>0.2596530147667175</v>
+        <v>0.20924751206541659</v>
       </c>
       <c r="C5">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
@@ -28712,35 +28481,35 @@
       </c>
       <c r="E5" s="36">
         <f t="shared" si="1"/>
-        <v>0.2857142857142857</v>
+        <v>0.23076923076923078</v>
       </c>
       <c r="F5">
         <f>SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
-        <v>2.8333333333333335</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="G5">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D5,0)</f>
-        <v>7.183333333333334</v>
+        <v>7.1833333333333327</v>
       </c>
       <c r="H5" s="36">
         <f t="shared" si="2"/>
-        <v>0.2828618968386023</v>
+        <v>0.23172905525846707</v>
       </c>
       <c r="I5" s="36">
         <f>IF(C5&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.16642857142857145</v>
+        <v>0.14589743589743592</v>
       </c>
       <c r="J5">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C5, 0)</f>
-        <v>3.8005</v>
+        <v>2.7330000000000001</v>
       </c>
       <c r="K5">
         <f>IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D5, 0)</f>
-        <v>9.628</v>
+        <v>9.6280000000000001</v>
       </c>
       <c r="L5" s="36">
         <f t="shared" si="3"/>
-        <v>0.283017462858845</v>
+        <v>0.22109861661677857</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Game Log Season 3'!$A$2:$X$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Player Adjusted Ranks'!$A$1:$L$9</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <pivotCaches>
     <pivotCache cacheId="5" r:id="rId7"/>
   </pivotCaches>
@@ -26624,22 +26624,253 @@
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-      <c r="E51" s="3"/>
-      <c r="M51" s="48"/>
-      <c r="X51" s="3"/>
+      <c r="A51" s="1">
+        <v>46236</v>
+      </c>
+      <c r="B51" s="7">
+        <v>14</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" s="3">
+        <v>2.3</v>
+      </c>
+      <c r="F51" s="7">
+        <v>1</v>
+      </c>
+      <c r="G51" s="7">
+        <v>1</v>
+      </c>
+      <c r="H51" s="7">
+        <v>3</v>
+      </c>
+      <c r="I51" s="7">
+        <v>2</v>
+      </c>
+      <c r="J51" s="7">
+        <f>F51-(1/H51)</f>
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="K51" s="7">
+        <f>((I51-((H51-1)/H51))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.4333333333333334</v>
+      </c>
+      <c r="L51" s="7">
+        <f>E51-((E52+E53)/2)</f>
+        <v>-0.75</v>
+      </c>
+      <c r="M51" s="48">
+        <f>0.5+(L51*0.09)</f>
+        <v>0.4325</v>
+      </c>
+      <c r="N51" s="7">
+        <f>((H51-(G51-1))/H51)*(IF(I51&lt;&gt;0,(I51+H51)/H51,1))</f>
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="O51" s="8">
+        <f>(N51-(1/6))/(10/6)</f>
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="P51" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q51" s="8">
+        <f>IF(F51=1,(((1-((P51-3)/15))*0.5)+0.5),((P51/18)*0.5))</f>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="R51" s="7">
+        <v>1</v>
+      </c>
+      <c r="S51" s="7">
+        <v>0</v>
+      </c>
+      <c r="T51" s="7">
+        <v>0</v>
+      </c>
+      <c r="U51" s="8">
+        <f>IFERROR(T51/S51, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V51" s="10">
+        <v>0</v>
+      </c>
+      <c r="W51" s="14">
+        <v>2</v>
+      </c>
+      <c r="X51" s="3">
+        <f>((O51*0.3)+(Q51*0.175)+(R51*0.175)+(U51*0.175)+((1-V51)*0.175))+W51</f>
+        <v>2.9408333333333334</v>
+      </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-      <c r="E52" s="3"/>
-      <c r="M52" s="48"/>
-      <c r="X52" s="3"/>
+      <c r="A52" s="1">
+        <v>46236</v>
+      </c>
+      <c r="B52" s="7">
+        <v>14</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="F52" s="7">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7">
+        <v>2</v>
+      </c>
+      <c r="H52" s="7">
+        <v>3</v>
+      </c>
+      <c r="I52" s="7">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7">
+        <f>F52-(1/H52)</f>
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="K52" s="7">
+        <f>((I52-((H52-1)/H52))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.03333333333333335</v>
+      </c>
+      <c r="L52" s="7">
+        <f>E52-((E51+E53)/2)</f>
+        <v>-0.4500000000000002</v>
+      </c>
+      <c r="M52" s="48">
+        <f>0.5+(L52*0.09)</f>
+        <v>0.45949999999999996</v>
+      </c>
+      <c r="N52" s="7">
+        <f>((H52-(G52-1))/H52)*(IF(I52&lt;&gt;0,(I52+H52)/H52,1))</f>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="O52" s="8">
+        <f>(N52-(1/6))/(10/6)</f>
+        <v>0.3</v>
+      </c>
+      <c r="P52" s="7">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="8">
+        <f>IF(F52=1,(((1-((P52-3)/15))*0.5)+0.5),((P52/18)*0.5))</f>
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="R52" s="7">
+        <v>0</v>
+      </c>
+      <c r="S52" s="7">
+        <v>1</v>
+      </c>
+      <c r="T52" s="7">
+        <v>0</v>
+      </c>
+      <c r="U52" s="8">
+        <f>IFERROR(T52/S52, 1)</f>
+        <v>0.0</v>
+      </c>
+      <c r="V52" s="10">
+        <v>0</v>
+      </c>
+      <c r="W52" s="14">
+        <v>2</v>
+      </c>
+      <c r="X52" s="3">
+        <f>((O52*0.3)+(Q52*0.175)+(R52*0.175)+(U52*0.175)+((1-V52)*0.175))+W52</f>
+        <v>2.303888888888889</v>
+      </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="E53" s="3"/>
-      <c r="M53" s="48"/>
-      <c r="X53" s="3"/>
+      <c r="A53" s="1">
+        <v>46236</v>
+      </c>
+      <c r="B53" s="7">
+        <v>14</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E53" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="F53" s="7">
+        <v>0</v>
+      </c>
+      <c r="G53" s="7">
+        <v>3</v>
+      </c>
+      <c r="H53" s="7">
+        <v>3</v>
+      </c>
+      <c r="I53" s="7">
+        <v>0</v>
+      </c>
+      <c r="J53" s="7">
+        <f>F53-(1/H53)</f>
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="K53" s="7">
+        <f>((I53-((H53-1)/H53))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.03333333333333335</v>
+      </c>
+      <c r="L53" s="7">
+        <f>E53-((E51+E52)/2)</f>
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="M53" s="48">
+        <f>0.5+(L53*0.09)</f>
+        <v>0.608</v>
+      </c>
+      <c r="N53" s="7">
+        <f>((H53-(G53-1))/H53)*(IF(I53&lt;&gt;0,(I53+H53)/H53,1))</f>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="O53" s="8">
+        <f>(N53-(1/6))/(10/6)</f>
+        <v>0.1</v>
+      </c>
+      <c r="P53" s="7">
+        <v>7</v>
+      </c>
+      <c r="Q53" s="8">
+        <f>IF(F53=1,(((1-((P53-3)/15))*0.5)+0.5),((P53/18)*0.5))</f>
+        <v>0.19444444444444445</v>
+      </c>
+      <c r="R53" s="7">
+        <v>0</v>
+      </c>
+      <c r="S53" s="7">
+        <v>1</v>
+      </c>
+      <c r="T53" s="7">
+        <v>0</v>
+      </c>
+      <c r="U53" s="8">
+        <f>IFERROR(T53/S53, 1)</f>
+        <v>0.0</v>
+      </c>
+      <c r="V53" s="10">
+        <v>0</v>
+      </c>
+      <c r="W53" s="14">
+        <v>3</v>
+      </c>
+      <c r="X53" s="3">
+        <f>((O53*0.3)+(Q53*0.175)+(R53*0.175)+(U53*0.175)+((1-V53)*0.175))+W53</f>
+        <v>3.239027777777778</v>
+      </c>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
@@ -28371,7 +28602,7 @@
       </c>
       <c r="B3" s="36">
         <f t="shared" si="0"/>
-        <v>0.27472520353960433</v>
+        <v>0.24978876904265432</v>
       </c>
       <c r="C3">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28379,11 +28610,11 @@
       </c>
       <c r="D3">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="36">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="F3">
         <f>SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28391,15 +28622,15 @@
       </c>
       <c r="G3">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D3,0)</f>
-        <v>5.0500000000000007</v>
+        <v>5.716666666666667</v>
       </c>
       <c r="H3" s="36">
         <f t="shared" si="2"/>
-        <v>0.29698375870069604</v>
+        <v>0.271762</v>
       </c>
       <c r="I3" s="36">
         <f>IF(C3&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.20300000000000007</v>
+        <v>0.187576</v>
       </c>
       <c r="J3">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C3, 0)</f>
@@ -28407,11 +28638,11 @@
       </c>
       <c r="K3">
         <f>IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D3, 0)</f>
-        <v>7.1994999999999996</v>
+        <v>8.3075</v>
       </c>
       <c r="L3" s="36">
         <f t="shared" si="3"/>
-        <v>0.29006015185879103</v>
+        <v>0.26149</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -28469,11 +28700,11 @@
       </c>
       <c r="B5" s="36">
         <f t="shared" si="0"/>
-        <v>0.20924751206541659</v>
+        <v>0.2596530147667175</v>
       </c>
       <c r="C5">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <f>COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
@@ -28481,35 +28712,35 @@
       </c>
       <c r="E5" s="36">
         <f t="shared" si="1"/>
-        <v>0.23076923076923078</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F5">
         <f>SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
-        <v>2.166666666666667</v>
+        <v>2.8333333333333335</v>
       </c>
       <c r="G5">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D5,0)</f>
-        <v>7.1833333333333327</v>
+        <v>7.183333333333334</v>
       </c>
       <c r="H5" s="36">
         <f t="shared" si="2"/>
-        <v>0.23172905525846707</v>
+        <v>0.282862</v>
       </c>
       <c r="I5" s="36">
         <f>IF(C5&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.14589743589743592</v>
+        <v>0.16642857142857143</v>
       </c>
       <c r="J5">
         <f>IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C5, 0)</f>
-        <v>2.7330000000000001</v>
+        <v>3.8005</v>
       </c>
       <c r="K5">
         <f>IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D5, 0)</f>
-        <v>9.6280000000000001</v>
+        <v>9.628</v>
       </c>
       <c r="L5" s="36">
         <f t="shared" si="3"/>
-        <v>0.22109861661677857</v>
+        <v>0.283017</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -27267,15 +27267,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E89CEC-EE00-4ADE-80BD-C35FB118BE4C}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.44140625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="51" t="s">
         <v>95</v>
       </c>
@@ -27283,6 +27284,11 @@
         <v>96</v>
       </c>
       <c r="C1" s="57"/>
+      <c r="D1" s="51" t="inlineStr">
+        <is>
+          <t>Baseline (used until a game is logged)</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="50" t="s">
@@ -27290,47 +27296,63 @@
       </c>
       <c r="B2" s="52">
         <f>AVERAGE(B3:B6)</f>
-        <v>2.7249999999999996</v>
+        <v>2.7228819444444445</v>
       </c>
       <c r="C2" s="57"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="41" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A3)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D3)</f>
+        <v>2.403888888888889</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="41">
         <v>2.4</v>
       </c>
-      <c r="C3" s="57"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="41" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A4)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D4)</f>
         <v>3.7</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="41">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="41" t="s">
         <v>90</v>
       </c>
       <c r="B5" s="41">
-        <v>2.2999999999999998</v>
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A5)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D5)</f>
+        <v>2.303888888888889</v>
       </c>
       <c r="C5" s="57"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="41">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
         <v>117</v>
       </c>
       <c r="B6" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A6)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D6)</f>
+        <v>2.48375</v>
+      </c>
+      <c r="C6" s="57"/>
+      <c r="D6" s="41">
         <v>2.5</v>
       </c>
-      <c r="C6" s="57"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="50" t="s">
@@ -27338,103 +27360,143 @@
       </c>
       <c r="B7" s="52">
         <f>AVERAGE(B8:B17)</f>
-        <v>3.22</v>
+        <v>3.2838194444444446</v>
       </c>
       <c r="C7" s="57"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
         <v>86</v>
       </c>
       <c r="B8" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A8)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D8)</f>
+        <v>3.8391666666666664</v>
+      </c>
+      <c r="C8" s="57"/>
+      <c r="D8" s="41">
         <v>3.8</v>
       </c>
-      <c r="C8" s="57"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="41" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A9)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D9)</f>
         <v>3.9</v>
       </c>
       <c r="C9" s="57"/>
-    </row>
-    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D9" s="41">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="41" t="s">
         <v>83</v>
       </c>
       <c r="B10" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A10)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D10)</f>
         <v>3.4</v>
       </c>
       <c r="C10" s="57" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="41">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="41" t="s">
         <v>101</v>
       </c>
       <c r="B11" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A11)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D11)</f>
         <v>2.6</v>
       </c>
       <c r="C11" s="57"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="41">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
         <v>44</v>
       </c>
       <c r="B12" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A12)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D12)</f>
         <v>3.5</v>
       </c>
       <c r="C12" s="57" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="41">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="41" t="s">
         <v>109</v>
       </c>
       <c r="B13" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A13)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D13)</f>
+        <v>2.653888888888889</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="41">
         <v>2.7</v>
       </c>
-      <c r="C13" s="57"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="41" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A14)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D14)</f>
         <v>2.6</v>
       </c>
       <c r="C14" s="57"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="41">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="41" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A15)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D15)</f>
+        <v>3.9108333333333336</v>
+      </c>
+      <c r="C15" s="57"/>
+      <c r="D15" s="41">
         <v>3.9</v>
       </c>
-      <c r="C15" s="57"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="41" t="s">
         <v>113</v>
       </c>
       <c r="B16" s="41">
-        <v>2.2999999999999998</v>
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A16)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D16)</f>
+        <v>2.9408333333333334</v>
       </c>
       <c r="C16" s="57"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" s="41">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="41" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A17)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D17)</f>
+        <v>3.493472222222222</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="41">
         <v>3.5</v>
       </c>
-      <c r="C17" s="57"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="50" t="s">
@@ -27442,141 +27504,197 @@
       </c>
       <c r="B18" s="52">
         <f>AVERAGE(B19:B32)</f>
-        <v>3.3142857142857141</v>
+        <v>3.3146428571428572</v>
       </c>
       <c r="C18" s="57"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="41" t="s">
         <v>88</v>
       </c>
       <c r="B19" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
         <v>2.4</v>
       </c>
       <c r="C19" s="57"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" s="41">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="41" t="s">
         <v>82</v>
       </c>
       <c r="B20" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
         <v>2.6</v>
       </c>
       <c r="C20" s="57"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" s="41">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="41" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
+        <v>3.574027777777778</v>
+      </c>
+      <c r="C21" s="57"/>
+      <c r="D21" s="41">
         <v>3.6</v>
       </c>
-      <c r="C21" s="57"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="41" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
         <v>3.6</v>
       </c>
       <c r="C22" s="57"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" s="41">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="41" t="s">
         <v>89</v>
       </c>
       <c r="B23" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
         <v>2.9</v>
       </c>
       <c r="C23" s="57"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" s="41">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="41" t="s">
         <v>71</v>
       </c>
       <c r="B24" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
         <v>3.9</v>
       </c>
       <c r="C24" s="57" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D24" s="41">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="41" t="s">
         <v>98</v>
       </c>
       <c r="B25" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
         <v>2.8</v>
       </c>
       <c r="C25" s="57"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D25" s="41">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="41" t="s">
         <v>100</v>
       </c>
       <c r="B26" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
         <v>2.6</v>
       </c>
       <c r="C26" s="57"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D26" s="41">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="41" t="s">
         <v>103</v>
       </c>
       <c r="B27" s="41">
-        <v>3.6</v>
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
+        <v>3.59875</v>
       </c>
       <c r="C27" s="57" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D27" s="41">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="41" t="s">
         <v>46</v>
       </c>
       <c r="B28" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
+        <v>3.9408333333333334</v>
+      </c>
+      <c r="C28" s="57"/>
+      <c r="D28" s="41">
         <v>3.9</v>
       </c>
-      <c r="C28" s="57"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="41" t="s">
         <v>111</v>
       </c>
       <c r="B29" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
+        <v>3.653888888888889</v>
+      </c>
+      <c r="C29" s="57"/>
+      <c r="D29" s="41">
         <v>3.7</v>
       </c>
-      <c r="C29" s="57"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="41" t="s">
         <v>45</v>
       </c>
       <c r="B30" s="53">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
+        <v>3.9558333333333335</v>
+      </c>
+      <c r="C30" s="57"/>
+      <c r="D30" s="53">
         <v>4</v>
       </c>
-      <c r="C30" s="57"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="41" t="s">
         <v>114</v>
       </c>
       <c r="B31" s="53">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
+        <v>2.9466666666666668</v>
+      </c>
+      <c r="C31" s="57"/>
+      <c r="D31" s="53">
         <v>2.9</v>
       </c>
-      <c r="C31" s="57"/>
-    </row>
-    <row r="32" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="53">
-        <v>3.9</v>
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
+        <v>3.935</v>
       </c>
       <c r="C32" s="57" t="s">
         <v>112</v>
       </c>
+      <c r="D32" s="53">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="50" t="s">
@@ -27584,108 +27702,152 @@
       </c>
       <c r="B33" s="52">
         <f>AVERAGE(B34:B44)</f>
-        <v>3.290909090909091</v>
+        <v>3.2627550505050507</v>
       </c>
       <c r="C33" s="57"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="41" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
         <v>3.5</v>
       </c>
       <c r="C34" s="57"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" s="41">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="41" t="s">
         <v>76</v>
       </c>
       <c r="B35" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
+        <v>3.430888888888889</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="41">
         <v>3.4</v>
       </c>
-      <c r="C35" s="57"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="41" t="s">
         <v>26</v>
       </c>
       <c r="B36" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
         <v>3.7</v>
       </c>
       <c r="C36" s="57"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D36" s="41">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="41" t="s">
         <v>75</v>
       </c>
       <c r="B37" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
         <v>2.6</v>
       </c>
       <c r="C37" s="57"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D37" s="41">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="41" t="s">
         <v>37</v>
       </c>
       <c r="B38" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
+        <v>3.7781666666666665</v>
+      </c>
+      <c r="C38" s="57"/>
+      <c r="D38" s="41">
         <v>3.8</v>
       </c>
-      <c r="C38" s="57"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="41" t="s">
         <v>97</v>
       </c>
       <c r="B39" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
+        <v>2.593888888888889</v>
+      </c>
+      <c r="C39" s="57"/>
+      <c r="D39" s="41">
         <v>2.6</v>
       </c>
-      <c r="C39" s="57"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="41" t="s">
         <v>52</v>
       </c>
       <c r="B40" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
+        <v>3.239027777777778</v>
+      </c>
+      <c r="C40" s="57"/>
+      <c r="D40" s="41">
         <v>3.6</v>
       </c>
-      <c r="C40" s="57"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="41" t="s">
         <v>108</v>
       </c>
       <c r="B41" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
         <v>2.6</v>
       </c>
       <c r="C41" s="57"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D41" s="41">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="41" t="s">
         <v>110</v>
       </c>
       <c r="B42" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
+        <v>3.5841666666666665</v>
+      </c>
+      <c r="C42" s="57"/>
+      <c r="D42" s="41">
         <v>3.6</v>
       </c>
-      <c r="C42" s="57"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="41" t="s">
         <v>116</v>
       </c>
       <c r="B43" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
+        <v>2.9408333333333334</v>
+      </c>
+      <c r="C43" s="57"/>
+      <c r="D43" s="41">
         <v>2.9</v>
       </c>
-      <c r="C43" s="57"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="41" t="s">
         <v>119</v>
       </c>
       <c r="B44" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
+        <v>3.9233333333333333</v>
+      </c>
+      <c r="C44" s="57"/>
+      <c r="D44" s="41">
         <v>3.9</v>
       </c>
-      <c r="C44" s="57"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="50" t="s">
@@ -27693,60 +27855,80 @@
       </c>
       <c r="B45" s="52">
         <f>AVERAGE(B46:B50)</f>
-        <v>3.2800000000000002</v>
+        <v>3.2865</v>
       </c>
       <c r="C45" s="57"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="41" t="s">
         <v>85</v>
       </c>
       <c r="B46" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
         <v>3.6</v>
       </c>
       <c r="C46" s="57" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D46" s="41">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="41" t="s">
         <v>71</v>
       </c>
       <c r="B47" s="41">
-        <v>3.3</v>
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
+        <v>3.3376111111111113</v>
       </c>
       <c r="C47" s="57" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D47" s="41">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="41" t="s">
         <v>93</v>
       </c>
       <c r="B48" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
         <v>3.2</v>
       </c>
       <c r="C48" s="57"/>
-    </row>
-    <row r="49" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D48" s="41">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="41" t="s">
         <v>105</v>
       </c>
       <c r="B49" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
         <v>3.9</v>
       </c>
       <c r="C49" s="57" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D49" s="41">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="41" t="s">
         <v>115</v>
       </c>
       <c r="B50" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
+        <v>2.3948888888888886</v>
+      </c>
+      <c r="C50" s="57"/>
+      <c r="D50" s="41">
         <v>2.4</v>
       </c>
-      <c r="C50" s="57"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="50" t="s">
@@ -27754,54 +27936,74 @@
       </c>
       <c r="B51" s="52">
         <f>AVERAGE(B52:B56)</f>
-        <v>3.4200000000000004</v>
+        <v>3.4280700000000004</v>
       </c>
       <c r="C51" s="57"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="41" t="s">
         <v>47</v>
       </c>
       <c r="B52" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
         <v>3.6</v>
       </c>
       <c r="C52" s="57"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D52" s="41">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="41" t="s">
         <v>91</v>
       </c>
       <c r="B53" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
         <v>3.8</v>
       </c>
       <c r="C53" s="57"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D53" s="41">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="41" t="s">
         <v>92</v>
       </c>
       <c r="B54" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
         <v>2.7</v>
       </c>
       <c r="C54" s="57"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D54" s="41">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="41" t="s">
         <v>80</v>
       </c>
       <c r="B55" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
         <v>3.3</v>
       </c>
       <c r="C55" s="57"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D55" s="41">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="41" t="s">
         <v>79</v>
       </c>
       <c r="B56" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
+        <v>3.7403500000000003</v>
+      </c>
+      <c r="C56" s="57"/>
+      <c r="D56" s="41">
         <v>3.7</v>
       </c>
-      <c r="C56" s="57"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="50" t="s">
@@ -27813,32 +28015,44 @@
       </c>
       <c r="C57" s="57"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="41" t="s">
         <v>26</v>
       </c>
       <c r="B58" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
         <v>2.7</v>
       </c>
       <c r="C58" s="57"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D58" s="41">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="41" t="s">
         <v>84</v>
       </c>
       <c r="B59" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
         <v>3.4</v>
       </c>
       <c r="C59" s="57"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D59" s="41">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="41" t="s">
         <v>104</v>
       </c>
       <c r="B60" s="53">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
         <v>1</v>
       </c>
       <c r="C60" s="57"/>
+      <c r="D60" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="50" t="s">
@@ -27846,33 +28060,45 @@
       </c>
       <c r="B61" s="52">
         <f>AVERAGE(B62:B63)</f>
-        <v>2.35</v>
+        <v>2.2519444444444447</v>
       </c>
       <c r="C61" s="57"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="41" t="s">
         <v>50</v>
       </c>
       <c r="B62" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
+        <v>2.303888888888889</v>
+      </c>
+      <c r="C62" s="57"/>
+      <c r="D62" s="41">
         <v>2.5</v>
       </c>
-      <c r="C62" s="57"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="41" t="s">
         <v>106</v>
       </c>
       <c r="B63" s="41">
-        <v>2.2000000000000002</v>
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
+        <v>2.2</v>
       </c>
       <c r="C63" s="57"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D63" s="41">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="41" t="s">
         <v>118</v>
       </c>
       <c r="B64" s="41">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
+        <v>2.4306944444444443</v>
+      </c>
+      <c r="D64" s="41">
         <v>2.4</v>
       </c>
     </row>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -27,9 +27,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Player Adjusted Ranks'!$A$1:$L$9</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
-  <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId7"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -924,1591 +921,6 @@
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Ryan Munden" refreshedDate="46229.755866898151" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{8056E9D3-2684-4CF2-9B4C-2A704DDBBC90}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A2:X50" sheet="Game Log Season 3"/>
-  </cacheSource>
-  <cacheFields count="24">
-    <cacheField name="Game Date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-07-01T00:00:00" maxDate="2026-07-26T00:00:00"/>
-    </cacheField>
-    <cacheField name="Game #" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="13"/>
-    </cacheField>
-    <cacheField name="Player Name" numFmtId="0">
-      <sharedItems count="7">
-        <s v="Becca"/>
-        <s v="Mateo"/>
-        <s v="Manny"/>
-        <s v="Ryan"/>
-        <s v="Kristy"/>
-        <s v="Michelle"/>
-        <s v="Joseph"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Commander" numFmtId="0">
-      <sharedItems count="27">
-        <s v="Ms. Bumbleflower"/>
-        <s v="Captain America, Team Leader"/>
-        <s v="Kruphix, God of Horizons"/>
-        <s v="Fire Lord Zuko"/>
-        <s v="Auntie Ool, Cursewretch"/>
-        <s v="Teval, the Balanced Scale"/>
-        <s v="The Wise Mothman"/>
-        <s v="Killian, Decisive Mentor"/>
-        <s v="Galadriel, Light of Valinor"/>
-        <s v="Zurgo Stormrender"/>
-        <s v="Ureni of the Unwritten"/>
-        <s v="Zada, Hedron Grinder"/>
-        <s v="Rootha, Mastering the Moment"/>
-        <s v="Kratos, God of War"/>
-        <s v="Ultima, Origin of Oblivion"/>
-        <s v="Ashling, The Limitless"/>
-        <s v="Doctor Doom, King of Latveria"/>
-        <s v="Aragorn, the Uniter"/>
-        <s v="Arna Kennerud, Skycaptain"/>
-        <s v="Eshki, Temur's Roar (Manny's)"/>
-        <s v="Witherbloom, The Balancer"/>
-        <s v="Preston Garvey, Minuteman"/>
-        <s v="Lucy MacLean, Positively Armed"/>
-        <s v="Chatterfang, Squirrel General"/>
-        <s v="Namor the Sub-Mariner"/>
-        <s v="Avatar Aang"/>
-        <s v="Yuna, Grand Summoner"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Commander Strength" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2" maxValue="3.9"/>
-    </cacheField>
-    <cacheField name="Game Result" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Place" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
-    </cacheField>
-    <cacheField name="Pod Size" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="5"/>
-    </cacheField>
-    <cacheField name="Knockouts" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="4"/>
-    </cacheField>
-    <cacheField name="Adjusted Pod Size Win/Loss Score" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.33333333333333331" maxValue="0.8"/>
-    </cacheField>
-    <cacheField name="Knockout Score" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.6666666666666654E-3" maxValue="0.80666666666666664"/>
-    </cacheField>
-    <cacheField name="Deck Strength Comparison Differential" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-1.4750000000000001" maxValue="1.2000000000000002"/>
-    </cacheField>
-    <cacheField name="Win Probability based on Deck Strength" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.36724999999999997" maxValue="0.60799999999999998"/>
-    </cacheField>
-    <cacheField name="Player Score" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2" maxValue="1.8"/>
-    </cacheField>
-    <cacheField name="Normalized Player Score" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.0000000000000011E-2" maxValue="0.98"/>
-    </cacheField>
-    <cacheField name="TOV" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="6" maxValue="14"/>
-    </cacheField>
-    <cacheField name="Normalized TOV" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.16666666666666666" maxValue="0.8666666666666667"/>
-    </cacheField>
-    <cacheField name="Pop-Off" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Disruptions" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="5"/>
-    </cacheField>
-    <cacheField name="Successful Recoveries" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="3"/>
-    </cacheField>
-    <cacheField name="Deck Resilience Score" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Games Clearly Behind" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Current Deck Bracket" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="3"/>
-    </cacheField>
-    <cacheField name="Game Calculated Deck Strength" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2.2848611111111112" maxValue="3.9558333333333335"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="48">
-  <r>
-    <d v="2026-07-01T00:00:00"/>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="2.9"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="-0.2"/>
-    <n v="6.6666666666666654E-3"/>
-    <n v="-0.35000000000000009"/>
-    <n v="0.46849999999999997"/>
-    <n v="0.8"/>
-    <n v="0.38"/>
-    <n v="10"/>
-    <n v="0.27777777777777779"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.5126111111111111"/>
-  </r>
-  <r>
-    <d v="2026-07-01T00:00:00"/>
-    <n v="1"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="3.7"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="-0.2"/>
-    <n v="6.6666666666666654E-3"/>
-    <n v="0.64999999999999991"/>
-    <n v="0.5585"/>
-    <n v="0.8"/>
-    <n v="0.38"/>
-    <n v="10"/>
-    <n v="0.27777777777777779"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.687611111111111"/>
-  </r>
-  <r>
-    <d v="2026-07-01T00:00:00"/>
-    <n v="1"/>
-    <x v="2"/>
-    <x v="2"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="-0.2"/>
-    <n v="6.6666666666666654E-3"/>
-    <n v="-1.4750000000000001"/>
-    <n v="0.36724999999999997"/>
-    <n v="0.8"/>
-    <n v="0.38"/>
-    <n v="10"/>
-    <n v="0.27777777777777779"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.687611111111111"/>
-  </r>
-  <r>
-    <d v="2026-07-01T00:00:00"/>
-    <n v="1"/>
-    <x v="3"/>
-    <x v="3"/>
-    <n v="3.9"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-    <n v="4"/>
-    <n v="0.8"/>
-    <n v="0.80666666666666664"/>
-    <n v="0.89999999999999991"/>
-    <n v="0.58099999999999996"/>
-    <n v="1.8"/>
-    <n v="0.98"/>
-    <n v="10"/>
-    <n v="0.76666666666666661"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.7781666666666665"/>
-  </r>
-  <r>
-    <d v="2026-07-01T00:00:00"/>
-    <n v="1"/>
-    <x v="4"/>
-    <x v="4"/>
-    <n v="3.4"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="-0.2"/>
-    <n v="6.6666666666666654E-3"/>
-    <n v="0.27499999999999991"/>
-    <n v="0.52474999999999994"/>
-    <n v="0.8"/>
-    <n v="0.38"/>
-    <n v="10"/>
-    <n v="0.27777777777777779"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.3376111111111113"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="2"/>
-    <x v="1"/>
-    <x v="5"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0.75"/>
-    <n v="0.6166666666666667"/>
-    <n v="0"/>
-    <n v="0.5"/>
-    <n v="1.75"/>
-    <n v="0.95"/>
-    <n v="8"/>
-    <n v="0.83333333333333337"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.9558333333333335"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="2"/>
-    <x v="5"/>
-    <x v="6"/>
-    <n v="2.7"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="-0.39999999999999991"/>
-    <n v="0.46400000000000002"/>
-    <n v="0.75"/>
-    <n v="0.35000000000000003"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.6688888888888886"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="2"/>
-    <x v="0"/>
-    <x v="7"/>
-    <n v="2.7"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="-0.39999999999999991"/>
-    <n v="0.46400000000000002"/>
-    <n v="0.75"/>
-    <n v="0.35000000000000003"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.4938888888888888"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="2"/>
-    <x v="2"/>
-    <x v="8"/>
-    <n v="3.6"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="0.79999999999999982"/>
-    <n v="0.57199999999999995"/>
-    <n v="0.75"/>
-    <n v="0.35000000000000003"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="3.318888888888889"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="3"/>
-    <x v="0"/>
-    <x v="7"/>
-    <n v="2.5"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="0.75"/>
-    <n v="0.2166666666666667"/>
-    <n v="-0.80000000000000027"/>
-    <n v="0.42799999999999999"/>
-    <n v="1.25"/>
-    <n v="0.64999999999999991"/>
-    <n v="9"/>
-    <n v="0.8"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.8600000000000003"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="3"/>
-    <x v="2"/>
-    <x v="8"/>
-    <n v="3.3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="-0.25"/>
-    <n v="0.2166666666666667"/>
-    <n v="0.26666666666666661"/>
-    <n v="0.52400000000000002"/>
-    <n v="0.9375"/>
-    <n v="0.46250000000000002"/>
-    <n v="9"/>
-    <n v="0.25"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="3.3574999999999999"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="3"/>
-    <x v="5"/>
-    <x v="6"/>
-    <n v="2.7"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="-0.25"/>
-    <n v="0.2166666666666667"/>
-    <n v="-0.53333333333333277"/>
-    <n v="0.45200000000000007"/>
-    <n v="0.625"/>
-    <n v="0.27500000000000002"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.4713888888888889"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="3"/>
-    <x v="1"/>
-    <x v="9"/>
-    <n v="3.9"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="1.0666666666666664"/>
-    <n v="0.59599999999999997"/>
-    <n v="0.25"/>
-    <n v="0.05"/>
-    <n v="7"/>
-    <n v="0.19444444444444445"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.5740277777777778"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="4"/>
-    <x v="1"/>
-    <x v="10"/>
-    <n v="3.8"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0.66666666666666674"/>
-    <n v="0.4333333333333334"/>
-    <n v="1.0999999999999996"/>
-    <n v="0.59899999999999998"/>
-    <n v="1.6666666666666667"/>
-    <n v="0.89999999999999991"/>
-    <n v="8"/>
-    <n v="0.83333333333333337"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.9408333333333334"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="4"/>
-    <x v="0"/>
-    <x v="7"/>
-    <n v="2.9"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="-0.25"/>
-    <n v="0.47749999999999998"/>
-    <n v="0.66666666666666663"/>
-    <n v="0.3"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.3038888888888889"/>
-  </r>
-  <r>
-    <d v="2026-07-03T00:00:00"/>
-    <n v="4"/>
-    <x v="2"/>
-    <x v="11"/>
-    <n v="2.5"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="-0.84999999999999964"/>
-    <n v="0.42350000000000004"/>
-    <n v="0.66666666666666663"/>
-    <n v="0.3"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.3038888888888889"/>
-  </r>
-  <r>
-    <d v="2026-07-08T00:00:00"/>
-    <n v="5"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="2.5"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="0.75"/>
-    <n v="0.2166666666666667"/>
-    <n v="-0.86666666666666714"/>
-    <n v="0.42199999999999993"/>
-    <n v="1.25"/>
-    <n v="0.64999999999999991"/>
-    <n v="14"/>
-    <n v="0.6333333333333333"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0.66666666666666663"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.7725"/>
-  </r>
-  <r>
-    <d v="2026-07-08T00:00:00"/>
-    <n v="5"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="3.7"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="-0.25"/>
-    <n v="0.41666666666666669"/>
-    <n v="0.73333333333333339"/>
-    <n v="0.56600000000000006"/>
-    <n v="1.125"/>
-    <n v="0.57499999999999996"/>
-    <n v="14"/>
-    <n v="0.3888888888888889"/>
-    <n v="1"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="0.4"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.6605555555555558"/>
-  </r>
-  <r>
-    <d v="2026-07-08T00:00:00"/>
-    <n v="5"/>
-    <x v="3"/>
-    <x v="12"/>
-    <n v="3.7"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="0.73333333333333339"/>
-    <n v="0.56600000000000006"/>
-    <n v="0.5"/>
-    <n v="0.2"/>
-    <n v="14"/>
-    <n v="0.3888888888888889"/>
-    <n v="1"/>
-    <n v="5"/>
-    <n v="3"/>
-    <n v="0.6"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.5830555555555552"/>
-  </r>
-  <r>
-    <d v="2026-07-08T00:00:00"/>
-    <n v="5"/>
-    <x v="2"/>
-    <x v="2"/>
-    <n v="2.7"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="-0.60000000000000009"/>
-    <n v="0.44600000000000001"/>
-    <n v="0.25"/>
-    <n v="0.05"/>
-    <n v="12"/>
-    <n v="0.33333333333333331"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.5983333333333336"/>
-  </r>
-  <r>
-    <d v="2026-07-17T00:00:00"/>
-    <n v="6"/>
-    <x v="1"/>
-    <x v="13"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="0.8"/>
-    <n v="0.40666666666666662"/>
-    <n v="-0.77499999999999991"/>
-    <n v="0.43025000000000002"/>
-    <n v="1.4"/>
-    <n v="0.73999999999999988"/>
-    <n v="9"/>
-    <n v="0.8"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.887"/>
-  </r>
-  <r>
-    <d v="2026-07-17T00:00:00"/>
-    <n v="6"/>
-    <x v="6"/>
-    <x v="14"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="5"/>
-    <n v="2"/>
-    <n v="-0.2"/>
-    <n v="0.40666666666666662"/>
-    <n v="0.47500000000000009"/>
-    <n v="0.54274999999999995"/>
-    <n v="1.1199999999999999"/>
-    <n v="0.57199999999999995"/>
-    <n v="9"/>
-    <n v="0.25"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.7403500000000003"/>
-  </r>
-  <r>
-    <d v="2026-07-17T00:00:00"/>
-    <n v="6"/>
-    <x v="2"/>
-    <x v="2"/>
-    <n v="2.6"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="-0.2"/>
-    <n v="6.6666666666666654E-3"/>
-    <n v="-2.4999999999999911E-2"/>
-    <n v="0.49775000000000003"/>
-    <n v="0.6"/>
-    <n v="0.26"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.4668888888888887"/>
-  </r>
-  <r>
-    <d v="2026-07-17T00:00:00"/>
-    <n v="6"/>
-    <x v="3"/>
-    <x v="15"/>
-    <n v="3.5"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="-0.2"/>
-    <n v="6.6666666666666654E-3"/>
-    <n v="1.1000000000000001"/>
-    <n v="0.59899999999999998"/>
-    <n v="0.4"/>
-    <n v="0.14000000000000001"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.4308888888888891"/>
-  </r>
-  <r>
-    <d v="2026-07-17T00:00:00"/>
-    <n v="6"/>
-    <x v="4"/>
-    <x v="16"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="5"/>
-    <n v="5"/>
-    <n v="0"/>
-    <n v="-0.2"/>
-    <n v="6.6666666666666654E-3"/>
-    <n v="-0.77499999999999991"/>
-    <n v="0.43025000000000002"/>
-    <n v="0.2"/>
-    <n v="2.0000000000000011E-2"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.3948888888888886"/>
-  </r>
-  <r>
-    <d v="2026-07-17T00:00:00"/>
-    <n v="7"/>
-    <x v="2"/>
-    <x v="17"/>
-    <n v="3.5"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="2"/>
-    <n v="0.75"/>
-    <n v="0.41666666666666669"/>
-    <n v="0.66666666666666652"/>
-    <n v="0.55999999999999994"/>
-    <n v="1.5"/>
-    <n v="0.79999999999999993"/>
-    <n v="8"/>
-    <n v="0.83333333333333337"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.9108333333333336"/>
-  </r>
-  <r>
-    <d v="2026-07-17T00:00:00"/>
-    <n v="7"/>
-    <x v="3"/>
-    <x v="18"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="1"/>
-    <n v="-0.25"/>
-    <n v="0.2166666666666667"/>
-    <n v="-1.3333333333333335"/>
-    <n v="0.38"/>
-    <n v="0.9375"/>
-    <n v="0.46250000000000002"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.702638888888889"/>
-  </r>
-  <r>
-    <d v="2026-07-17T00:00:00"/>
-    <n v="7"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="3.7"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="0.93333333333333313"/>
-    <n v="0.58399999999999996"/>
-    <n v="0.75"/>
-    <n v="0.35000000000000003"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.4938888888888888"/>
-  </r>
-  <r>
-    <d v="2026-07-17T00:00:00"/>
-    <n v="7"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="2.8"/>
-    <n v="0"/>
-    <n v="4"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="-0.26666666666666661"/>
-    <n v="0.47599999999999998"/>
-    <n v="0.25"/>
-    <n v="0.05"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.403888888888889"/>
-  </r>
-  <r>
-    <d v="2026-07-22T00:00:00"/>
-    <n v="8"/>
-    <x v="2"/>
-    <x v="8"/>
-    <n v="3.4"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0.66666666666666674"/>
-    <n v="0.4333333333333334"/>
-    <n v="1.1999999999999997"/>
-    <n v="0.60799999999999998"/>
-    <n v="1.6666666666666667"/>
-    <n v="0.89999999999999991"/>
-    <n v="9"/>
-    <n v="0.8"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.9350000000000001"/>
-  </r>
-  <r>
-    <d v="2026-07-22T00:00:00"/>
-    <n v="8"/>
-    <x v="0"/>
-    <x v="19"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="-0.89999999999999991"/>
-    <n v="0.41900000000000004"/>
-    <n v="0.66666666666666663"/>
-    <n v="0.3"/>
-    <n v="9"/>
-    <n v="0.25"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.4837500000000001"/>
-  </r>
-  <r>
-    <d v="2026-07-22T00:00:00"/>
-    <n v="8"/>
-    <x v="3"/>
-    <x v="20"/>
-    <n v="2.4"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="-0.30000000000000027"/>
-    <n v="0.47299999999999998"/>
-    <n v="0.33333333333333331"/>
-    <n v="9.9999999999999992E-2"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.5938888888888889"/>
-  </r>
-  <r>
-    <d v="2026-07-24T00:00:00"/>
-    <n v="9"/>
-    <x v="2"/>
-    <x v="8"/>
-    <n v="3.9"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="4"/>
-    <n v="3"/>
-    <n v="0.75"/>
-    <n v="0.6166666666666667"/>
-    <n v="1.0999999999999996"/>
-    <n v="0.59899999999999998"/>
-    <n v="1.75"/>
-    <n v="0.95"/>
-    <n v="13"/>
-    <n v="0.66666666666666674"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0.5"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.8391666666666664"/>
-  </r>
-  <r>
-    <d v="2026-07-24T00:00:00"/>
-    <n v="9"/>
-    <x v="3"/>
-    <x v="21"/>
-    <n v="3.5"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="0.56666666666666643"/>
-    <n v="0.55099999999999993"/>
-    <n v="0.75"/>
-    <n v="0.35000000000000003"/>
-    <n v="13"/>
-    <n v="0.3611111111111111"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0.5"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.6056944444444445"/>
-  </r>
-  <r>
-    <d v="2026-07-24T00:00:00"/>
-    <n v="9"/>
-    <x v="1"/>
-    <x v="13"/>
-    <n v="2.9"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="-0.23333333333333339"/>
-    <n v="0.47899999999999998"/>
-    <n v="0.75"/>
-    <n v="0.35000000000000003"/>
-    <n v="13"/>
-    <n v="0.3611111111111111"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0.66666666666666663"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2.2848611111111112"/>
-  </r>
-  <r>
-    <d v="2026-07-24T00:00:00"/>
-    <n v="9"/>
-    <x v="5"/>
-    <x v="22"/>
-    <n v="2"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="4"/>
-    <n v="0"/>
-    <n v="-0.25"/>
-    <n v="1.6666666666666673E-2"/>
-    <n v="-1.4333333333333336"/>
-    <n v="0.371"/>
-    <n v="0.75"/>
-    <n v="0.35000000000000003"/>
-    <n v="13"/>
-    <n v="0.3611111111111111"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="1"/>
-    <n v="0.5"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.4306944444444443"/>
-  </r>
-  <r>
-    <d v="2026-07-24T00:00:00"/>
-    <n v="10"/>
-    <x v="1"/>
-    <x v="23"/>
-    <n v="3"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0.66666666666666674"/>
-    <n v="0.4333333333333334"/>
-    <n v="0.25"/>
-    <n v="0.52249999999999996"/>
-    <n v="1.6666666666666667"/>
-    <n v="0.89999999999999991"/>
-    <n v="9"/>
-    <n v="0.8"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.9350000000000001"/>
-  </r>
-  <r>
-    <d v="2026-07-24T00:00:00"/>
-    <n v="10"/>
-    <x v="2"/>
-    <x v="2"/>
-    <n v="2.5"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="-0.5"/>
-    <n v="0.45500000000000002"/>
-    <n v="0.66666666666666663"/>
-    <n v="0.3"/>
-    <n v="9"/>
-    <n v="0.25"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.4837500000000001"/>
-  </r>
-  <r>
-    <d v="2026-07-24T00:00:00"/>
-    <n v="10"/>
-    <x v="3"/>
-    <x v="24"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="0.25"/>
-    <n v="0.52249999999999996"/>
-    <n v="0.66666666666666663"/>
-    <n v="0.3"/>
-    <n v="9"/>
-    <n v="0.25"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="3.3087499999999999"/>
-  </r>
-  <r>
-    <d v="2026-07-25T00:00:00"/>
-    <n v="11"/>
-    <x v="3"/>
-    <x v="18"/>
-    <n v="2.7"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0.66666666666666674"/>
-    <n v="0.4333333333333334"/>
-    <n v="-0.19999999999999973"/>
-    <n v="0.48200000000000004"/>
-    <n v="1.6666666666666667"/>
-    <n v="0.89999999999999991"/>
-    <n v="8"/>
-    <n v="0.83333333333333337"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.9408333333333334"/>
-  </r>
-  <r>
-    <d v="2026-07-25T00:00:00"/>
-    <n v="11"/>
-    <x v="2"/>
-    <x v="11"/>
-    <n v="2.2999999999999998"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="-0.80000000000000027"/>
-    <n v="0.42799999999999999"/>
-    <n v="0.66666666666666663"/>
-    <n v="0.3"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.653888888888889"/>
-  </r>
-  <r>
-    <d v="2026-07-25T00:00:00"/>
-    <n v="11"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="3.5"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="1"/>
-    <n v="0.59"/>
-    <n v="0.66666666666666663"/>
-    <n v="0.3"/>
-    <n v="8"/>
-    <n v="0.22222222222222221"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.653888888888889"/>
-  </r>
-  <r>
-    <d v="2026-07-25T00:00:00"/>
-    <n v="12"/>
-    <x v="1"/>
-    <x v="13"/>
-    <n v="2.2999999999999998"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0.66666666666666674"/>
-    <n v="0.4333333333333334"/>
-    <n v="-0.75"/>
-    <n v="0.4325"/>
-    <n v="1.6666666666666667"/>
-    <n v="0.89999999999999991"/>
-    <n v="7"/>
-    <n v="0.8666666666666667"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="2.9466666666666668"/>
-  </r>
-  <r>
-    <d v="2026-07-25T00:00:00"/>
-    <n v="12"/>
-    <x v="2"/>
-    <x v="2"/>
-    <n v="2.5"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="-0.45000000000000018"/>
-    <n v="0.45949999999999996"/>
-    <n v="0.66666666666666663"/>
-    <n v="0.3"/>
-    <n v="7"/>
-    <n v="0.19444444444444445"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="2"/>
-    <n v="2.2990277777777779"/>
-  </r>
-  <r>
-    <d v="2026-07-25T00:00:00"/>
-    <n v="12"/>
-    <x v="3"/>
-    <x v="12"/>
-    <n v="3.6"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="1.2000000000000002"/>
-    <n v="0.60799999999999998"/>
-    <n v="0.33333333333333331"/>
-    <n v="9.9999999999999992E-2"/>
-    <n v="6"/>
-    <n v="0.16666666666666666"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.5841666666666665"/>
-  </r>
-  <r>
-    <d v="2026-07-25T00:00:00"/>
-    <n v="13"/>
-    <x v="3"/>
-    <x v="24"/>
-    <n v="3.3"/>
-    <n v="1"/>
-    <n v="1"/>
-    <n v="3"/>
-    <n v="2"/>
-    <n v="0.66666666666666674"/>
-    <n v="0.4333333333333334"/>
-    <n v="-5.0000000000000266E-2"/>
-    <n v="0.4955"/>
-    <n v="1.6666666666666667"/>
-    <n v="0.89999999999999991"/>
-    <n v="11"/>
-    <n v="0.73333333333333339"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.9233333333333333"/>
-  </r>
-  <r>
-    <d v="2026-07-25T00:00:00"/>
-    <n v="13"/>
-    <x v="2"/>
-    <x v="25"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="2"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="-0.5"/>
-    <n v="0.45500000000000002"/>
-    <n v="0.66666666666666663"/>
-    <n v="0.3"/>
-    <n v="11"/>
-    <n v="0.30555555555555558"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.4934722222222221"/>
-  </r>
-  <r>
-    <d v="2026-07-25T00:00:00"/>
-    <n v="13"/>
-    <x v="1"/>
-    <x v="26"/>
-    <n v="3.7"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3"/>
-    <n v="0"/>
-    <n v="-0.33333333333333331"/>
-    <n v="3.3333333333333347E-2"/>
-    <n v="0.55000000000000027"/>
-    <n v="0.54949999999999999"/>
-    <n v="0.33333333333333331"/>
-    <n v="9.9999999999999992E-2"/>
-    <n v="9"/>
-    <n v="0.25"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="3"/>
-    <n v="3.5987499999999999"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5EA05A64-BCF0-4340-B4AC-DDB207BCA579}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A1:C36" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="24">
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="8">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="28">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="9" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-  </pivotFields>
-  <rowFields count="2">
-    <field x="2"/>
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="35">
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="17"/>
-    </i>
-    <i r="1">
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="13"/>
-    </i>
-    <i r="1">
-      <x v="23"/>
-    </i>
-    <i r="1">
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="15"/>
-    </i>
-    <i r="1">
-      <x v="18"/>
-    </i>
-    <i r="1">
-      <x v="20"/>
-    </i>
-    <i r="1">
-      <x v="21"/>
-    </i>
-    <i r="1">
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="14"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Count of Game Result" fld="5" subtotal="count" baseField="2" baseItem="0"/>
-    <dataField name="Sum of Game Result" fld="5" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -28109,7 +26521,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78721C01-74C8-4B39-8A98-A9995A31B797}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -28118,598 +26530,1224 @@
     <col min="4" max="4" width="23.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>Player / Deck</t>
+        </is>
+      </c>
+      <c r="B1" s="51" t="inlineStr">
+        <is>
+          <t>Games Played</t>
+        </is>
+      </c>
+      <c r="C1" s="51" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+      <c r="D1" s="51" t="inlineStr">
+        <is>
+          <t>Win Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="50" t="inlineStr">
+        <is>
+          <t>Becca</t>
+        </is>
+      </c>
+      <c r="B2" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A2)</f>
+        <v>7</v>
+      </c>
+      <c r="C2" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A2,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>2</v>
+      </c>
+      <c r="D2" s="52">
+        <f>IFERROR(C2/B2,0)</f>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>Ms. Bumbleflower</t>
+        </is>
+      </c>
+      <c r="B3" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A3)</f>
+        <v>3</v>
+      </c>
+      <c r="C3" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A3,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="41">
+        <f>IFERROR(C3/B3,0)</f>
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>Aminatou, Veil Piercer</t>
+        </is>
+      </c>
+      <c r="B4" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A4)</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A4,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="41">
+        <f>IFERROR(C4/B4,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>Killian, Decisive Mentor</t>
+        </is>
+      </c>
+      <c r="B5" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A5)</f>
+        <v>3</v>
+      </c>
+      <c r="C5" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A5,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="41">
+        <f>IFERROR(C5/B5,0)</f>
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>Eshki, Temur's Roar (Manny's)</t>
+        </is>
+      </c>
+      <c r="B6" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A6)</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A6,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="41">
+        <f>IFERROR(C6/B6,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="50" t="inlineStr">
+        <is>
+          <t>Manny</t>
+        </is>
+      </c>
+      <c r="B7" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7)</f>
+        <v>14</v>
+      </c>
+      <c r="C7" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>4</v>
+      </c>
+      <c r="D7" s="52">
+        <f>IFERROR(C7/B7,0)</f>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>Galadriel, Light of Valinor</t>
+        </is>
+      </c>
+      <c r="B8" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8)</f>
+        <v>4</v>
+      </c>
+      <c r="C8" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="41">
+        <f>IFERROR(C8/B8,0)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>Atraxa, Praetor's Voice</t>
+        </is>
+      </c>
+      <c r="B9" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="41">
+        <f>IFERROR(C9/B9,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>Athreos, God of Passage</t>
+        </is>
+      </c>
+      <c r="B10" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A10)</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A10,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="41">
+        <f>IFERROR(C10/B10,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>Fynn, the Fangbearer</t>
+        </is>
+      </c>
+      <c r="B11" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A11)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A11,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="41">
+        <f>IFERROR(C11/B11,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>Frodo, Adventurous Hobbit/Sam, Loyal Attendant</t>
+        </is>
+      </c>
+      <c r="B12" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A12)</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A12,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="41">
+        <f>IFERROR(C12/B12,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>Zada, Hedron Grinder</t>
+        </is>
+      </c>
+      <c r="B13" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13)</f>
+        <v>2</v>
+      </c>
+      <c r="C13" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="41">
+        <f>IFERROR(C13/B13,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>Ureni of the Unwritten</t>
+        </is>
+      </c>
+      <c r="B14" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14)</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="41">
+        <f>IFERROR(C14/B14,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>Aragorn, the Uniter</t>
+        </is>
+      </c>
+      <c r="B15" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15)</f>
+        <v>1</v>
+      </c>
+      <c r="C15" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D15" s="41">
+        <f>IFERROR(C15/B15,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>Kruphix, God of Horizons</t>
+        </is>
+      </c>
+      <c r="B16" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16)</f>
+        <v>6</v>
+      </c>
+      <c r="C16" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="41">
+        <f>IFERROR(C16/B16,0)</f>
+        <v>0.16666666666666666</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>Avatar Aang</t>
+        </is>
+      </c>
+      <c r="B17" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17)</f>
+        <v>1</v>
+      </c>
+      <c r="C17" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="41">
+        <f>IFERROR(C17/B17,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="50" t="inlineStr">
+        <is>
+          <t>Mateo</t>
+        </is>
+      </c>
+      <c r="B18" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
+        <v>12</v>
+      </c>
+      <c r="C18" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>2</v>
-      </c>
-      <c r="D2" s="45">
-        <f t="shared" ref="D2:D36" si="0">C2/B2</f>
-        <v>0.2857142857142857</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="44" t="s">
+      <c r="D18" s="52">
+        <f>IFERROR(C18/B18,0)</f>
+        <v>0.4166666666666667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>High Perfect Morcant</t>
+        </is>
+      </c>
+      <c r="B19" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="41">
+        <f>IFERROR(C19/B19,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>Leonardo, the Balance/Michelangelo, the Heart</t>
+        </is>
+      </c>
+      <c r="B20" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
+        <v>0</v>
+      </c>
+      <c r="C20" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="41">
+        <f>IFERROR(C20/B20,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>Zurgo Stormrender</t>
+        </is>
+      </c>
+      <c r="B21" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
+        <v>1</v>
+      </c>
+      <c r="C21" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="41">
+        <f>IFERROR(C21/B21,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>Fire Lord Azula</t>
+        </is>
+      </c>
+      <c r="B22" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="41">
+        <f>IFERROR(C22/B22,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>Quintorius, History Chaser</t>
+        </is>
+      </c>
+      <c r="B23" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="41">
+        <f>IFERROR(C23/B23,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>Auntie Ool, Cursewretch</t>
+        </is>
+      </c>
+      <c r="B24" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="41">
+        <f>IFERROR(C24/B24,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>Killian, Decisive Mentor (Becca's)</t>
+        </is>
+      </c>
+      <c r="B25" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
+        <v>0</v>
+      </c>
+      <c r="C25" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="41">
+        <f>IFERROR(C25/B25,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>Noctis, Heir Apparent</t>
+        </is>
+      </c>
+      <c r="B26" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="41">
+        <f>IFERROR(C26/B26,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>Yuna, Grand Summoner</t>
+        </is>
+      </c>
+      <c r="B27" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
+        <v>1</v>
+      </c>
+      <c r="C27" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="41">
+        <f>IFERROR(C27/B27,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="41" t="inlineStr">
+        <is>
+          <t>Ureni of the Unwritten</t>
+        </is>
+      </c>
+      <c r="B28" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
+        <v>1</v>
+      </c>
+      <c r="C28" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D28" s="41">
+        <f>IFERROR(C28/B28,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Captain America, Team Leader</t>
+        </is>
+      </c>
+      <c r="B29" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
+        <v>4</v>
+      </c>
+      <c r="C29" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="41">
+        <f>IFERROR(C29/B29,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>Teval, the Balanced Scale</t>
+        </is>
+      </c>
+      <c r="B30" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
+        <v>1</v>
+      </c>
+      <c r="C30" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D30" s="41">
+        <f>IFERROR(C30/B30,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>Kratos, God of War</t>
+        </is>
+      </c>
+      <c r="B31" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
+        <v>3</v>
+      </c>
+      <c r="C31" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>2</v>
+      </c>
+      <c r="D31" s="41">
+        <f>IFERROR(C31/B31,0)</f>
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>Chatterfang, Squirrel General</t>
+        </is>
+      </c>
+      <c r="B32" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
+        <v>1</v>
+      </c>
+      <c r="C32" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D32" s="41">
+        <f>IFERROR(C32/B32,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="50" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B33" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
         <v>11</v>
       </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="36">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="36">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" s="45">
-        <f t="shared" si="0"/>
-        <v>0.23076923076923078</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8">
+      <c r="C33" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D33" s="52">
+        <f>IFERROR(C33/B33,0)</f>
+        <v>0.2727272727272727</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>Eowyn, Shieldmaiden</t>
+        </is>
+      </c>
+      <c r="B34" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="41">
+        <f>IFERROR(C34/B34,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>Ashling, The Limitless</t>
+        </is>
+      </c>
+      <c r="B35" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
+        <v>1</v>
+      </c>
+      <c r="C35" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="41">
+        <f>IFERROR(C35/B35,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>Cloud, Ex-SOLDIER</t>
+        </is>
+      </c>
+      <c r="B36" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="41">
+        <f>IFERROR(C36/B36,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>Kratos, Stoic Father/Atreus, Impulsive Son</t>
+        </is>
+      </c>
+      <c r="B37" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="41">
+        <f>IFERROR(C37/B37,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>Fire Lord Zuko</t>
+        </is>
+      </c>
+      <c r="B38" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
+        <v>1</v>
+      </c>
+      <c r="C38" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D38" s="41">
+        <f>IFERROR(C38/B38,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="41" t="inlineStr">
+        <is>
+          <t>Witherbloom, The Balancer</t>
+        </is>
+      </c>
+      <c r="B39" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
+        <v>1</v>
+      </c>
+      <c r="C39" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="41">
+        <f>IFERROR(C39/B39,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="41" t="inlineStr">
+        <is>
+          <t>Preston Garvey, Minuteman</t>
+        </is>
+      </c>
+      <c r="B40" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
+        <v>2</v>
+      </c>
+      <c r="C40" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="41">
+        <f>IFERROR(C40/B40,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>Giada, Font of Hope</t>
+        </is>
+      </c>
+      <c r="B41" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
+        <v>0</v>
+      </c>
+      <c r="C41" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="41">
+        <f>IFERROR(C41/B41,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>Rootha, Mastering the Moment</t>
+        </is>
+      </c>
+      <c r="B42" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
+        <v>2</v>
+      </c>
+      <c r="C42" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="41">
+        <f>IFERROR(C42/B42,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>Arna Kennerud, Skycaptain</t>
+        </is>
+      </c>
+      <c r="B43" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
+        <v>2</v>
+      </c>
+      <c r="C43" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D43" s="41">
+        <f>IFERROR(C43/B43,0)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="41" t="inlineStr">
+        <is>
+          <t>Namor the Sub-Mariner</t>
+        </is>
+      </c>
+      <c r="B44" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
+        <v>2</v>
+      </c>
+      <c r="C44" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D44" s="41">
+        <f>IFERROR(C44/B44,0)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="50" t="inlineStr">
+        <is>
+          <t>Kristy</t>
+        </is>
+      </c>
+      <c r="B45" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
+        <v>2</v>
+      </c>
+      <c r="C45" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="52">
+        <f>IFERROR(C45/B45,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>Edgar Markov</t>
+        </is>
+      </c>
+      <c r="B46" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="41">
+        <f>IFERROR(C46/B46,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="41" t="inlineStr">
+        <is>
+          <t>Auntie Ool, Cursewretch</t>
+        </is>
+      </c>
+      <c r="B47" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
+        <v>1</v>
+      </c>
+      <c r="C47" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="41">
+        <f>IFERROR(C47/B47,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="41" t="inlineStr">
+        <is>
+          <t>Dina, Essence Brewer</t>
+        </is>
+      </c>
+      <c r="B48" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
+        <v>0</v>
+      </c>
+      <c r="C48" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="41">
+        <f>IFERROR(C48/B48,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="41" t="inlineStr">
+        <is>
+          <t>Niv-Mizzet, Parun</t>
+        </is>
+      </c>
+      <c r="B49" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
+        <v>0</v>
+      </c>
+      <c r="C49" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="41">
+        <f>IFERROR(C49/B49,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>Doctor Doom, King of Latveria</t>
+        </is>
+      </c>
+      <c r="B50" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
+        <v>1</v>
+      </c>
+      <c r="C50" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="41">
+        <f>IFERROR(C50/B50,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="50" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="B51" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="52">
+        <f>IFERROR(C51/B51,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="41" t="inlineStr">
+        <is>
+          <t>Valgavoth, Harrower of Souls</t>
+        </is>
+      </c>
+      <c r="B52" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
+        <v>0</v>
+      </c>
+      <c r="C52" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="41">
+        <f>IFERROR(C52/B52,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>Zimone, Infinite Analyst</t>
+        </is>
+      </c>
+      <c r="B53" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
+        <v>0</v>
+      </c>
+      <c r="C53" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D53" s="41">
+        <f>IFERROR(C53/B53,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>Super Shredder</t>
+        </is>
+      </c>
+      <c r="B54" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="41">
+        <f>IFERROR(C54/B54,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>Hei Bai, Forest Guardian</t>
+        </is>
+      </c>
+      <c r="B55" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
+        <v>0</v>
+      </c>
+      <c r="C55" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="41">
+        <f>IFERROR(C55/B55,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>Ultima, Origin of Oblivion</t>
+        </is>
+      </c>
+      <c r="B56" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
+        <v>1</v>
+      </c>
+      <c r="C56" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="41">
+        <f>IFERROR(C56/B56,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="50" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="B57" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
+        <v>0</v>
+      </c>
+      <c r="C57" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="52">
+        <f>IFERROR(C57/B57,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>Cloud, Ex-SOLDIER</t>
+        </is>
+      </c>
+      <c r="B58" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
+        <v>0</v>
+      </c>
+      <c r="C58" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="41">
+        <f>IFERROR(C58/B58,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>Squall, SeeD Mercenary</t>
+        </is>
+      </c>
+      <c r="B59" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="41">
+        <f>IFERROR(C59/B59,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>Sanar, Innovative First-Year</t>
+        </is>
+      </c>
+      <c r="B60" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
+        <v>0</v>
+      </c>
+      <c r="C60" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="41">
+        <f>IFERROR(C60/B60,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="50" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B61" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
         <v>4</v>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8" s="36">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="44" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" s="36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12">
-        <v>12</v>
-      </c>
-      <c r="C12">
-        <v>5</v>
-      </c>
-      <c r="D12" s="45">
-        <f t="shared" si="0"/>
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="44" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" s="36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17">
-        <v>3</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17" s="36">
-        <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" s="36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="43" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20">
-        <v>10</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20" s="45">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" s="36">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-      <c r="D24" s="36">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" s="36">
-        <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
-      </c>
-      <c r="D29" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31">
-        <v>3</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-      <c r="D31" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="44" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32">
-        <v>2</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33">
-        <v>0</v>
-      </c>
-      <c r="D33" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36">
-        <v>48</v>
-      </c>
-      <c r="C36">
-        <v>13</v>
-      </c>
-      <c r="D36" s="46">
-        <f t="shared" si="0"/>
-        <v>0.27083333333333331</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D37" s="54"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D38" s="48"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D39" s="48"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D40" s="48"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D41" s="48"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D42" s="54"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D43" s="48"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D44" s="48"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D45" s="48"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D46" s="48"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D47" s="54"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D48" s="48"/>
-    </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D49" s="48"/>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D50" s="48"/>
-    </row>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D51" s="54"/>
-    </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D52" s="48"/>
-    </row>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D53" s="48"/>
-    </row>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D54" s="55"/>
+      <c r="C61" s="52">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="52">
+        <f>IFERROR(C61/B61,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="41" t="inlineStr">
+        <is>
+          <t>The Wise Mothman</t>
+        </is>
+      </c>
+      <c r="B62" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
+        <v>3</v>
+      </c>
+      <c r="C62" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="41">
+        <f>IFERROR(C62/B62,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="41" t="inlineStr">
+        <is>
+          <t>Szarel, Genesis Shepard</t>
+        </is>
+      </c>
+      <c r="B63" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
+        <v>0</v>
+      </c>
+      <c r="C63" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="41">
+        <f>IFERROR(C63/B63,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="41" t="inlineStr">
+        <is>
+          <t>Lucy MacLean, Positively Armed</t>
+        </is>
+      </c>
+      <c r="B64" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
+        <v>1</v>
+      </c>
+      <c r="C64" s="41">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="41">
+        <f>IFERROR(C64/B64,0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25670,7 +25670,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.33"/>
@@ -26501,6 +26501,48 @@
       </c>
       <c r="D64" s="48" t="n">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="46" t="inlineStr">
+        <is>
+          <t>ZZTestPlayer</t>
+        </is>
+      </c>
+      <c r="B65" s="47">
+        <f>AVERAGE(B66:B67)</f>
+        <v>2.8</v>
+      </c>
+      <c r="C65" s="45"/>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="48" t="inlineStr">
+        <is>
+          <t>Test Commander One</t>
+        </is>
+      </c>
+      <c r="B66" s="48">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer")*('Game Log Season 3'!$D$3:$D$1000=A66)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D66)</f>
+        <v>3.1</v>
+      </c>
+      <c r="C66" s="45"/>
+      <c r="D66" s="48">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="48" t="inlineStr">
+        <is>
+          <t>Test Commander Two</t>
+        </is>
+      </c>
+      <c r="B67" s="48">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
+        <v>2.5</v>
+      </c>
+      <c r="C67" s="45"/>
+      <c r="D67" s="48">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -26519,7 +26561,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.89"/>
@@ -27610,6 +27652,63 @@
       </c>
       <c r="D64" s="48" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="46" t="inlineStr">
+        <is>
+          <t>ZZTestPlayer</t>
+        </is>
+      </c>
+      <c r="B65" s="47">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A65)</f>
+        <v>0</v>
+      </c>
+      <c r="C65" s="47">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="47">
+        <f>IFERROR(C65/B65,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="48" t="inlineStr">
+        <is>
+          <t>Test Commander One</t>
+        </is>
+      </c>
+      <c r="B66" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer",'Game Log Season 3'!$D$3:$D$1000,A66)</f>
+        <v>0</v>
+      </c>
+      <c r="C66" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer",'Game Log Season 3'!$D$3:$D$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="48">
+        <f>IFERROR(C66/B66,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="48" t="inlineStr">
+        <is>
+          <t>Test Commander Two</t>
+        </is>
+      </c>
+      <c r="B67" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="48">
+        <f>IFERROR(C67/B67,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25670,7 +25670,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.33"/>
@@ -25696,7 +25696,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="47" t="n">
-        <f aca="false">AVERAGE(B3:B6)</f>
+        <f aca="false">AVERAGE(B3:B7)</f>
         <v>2.72288194444444</v>
       </c>
       <c r="C2" s="45"/>
@@ -25755,206 +25755,208 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="46" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t>ZZ Test New Deck</t>
+        </is>
+      </c>
+      <c r="B7" s="48">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
+        <v>2.9</v>
+      </c>
+      <c r="C7" s="45"/>
+      <c r="D7" s="48">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="47" t="n">
-        <f aca="false">AVERAGE(B8:B17)</f>
+      <c r="B8" s="47" t="n">
+        <f aca="false">AVERAGE(B9:B18)</f>
         <v>3.28381944444444</v>
       </c>
-      <c r="C7" s="45"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A8)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D8)</f>
-        <v>3.83916666666667</v>
-      </c>
       <c r="C8" s="45"/>
-      <c r="D8" s="48" t="n">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B9" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A9)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D9)</f>
-        <v>3.9</v>
+        <v>3.83916666666667</v>
       </c>
       <c r="C9" s="45"/>
       <c r="D9" s="48" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="48" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B10" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A10)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D10)</f>
-        <v>3.4</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>102</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="C10" s="45"/>
       <c r="D10" s="48" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B11" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A11)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D11)</f>
-        <v>2.6</v>
-      </c>
-      <c r="C11" s="45"/>
+        <v>3.4</v>
+      </c>
+      <c r="C11" s="45" t="s">
+        <v>102</v>
+      </c>
       <c r="D11" s="48" t="n">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B12" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A12)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D12)</f>
-        <v>3.5</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>101</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="C12" s="45"/>
       <c r="D12" s="48" t="n">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B13" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A13)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D13)</f>
-        <v>2.65388888888889</v>
-      </c>
-      <c r="C13" s="45"/>
+        <v>3.5</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>101</v>
+      </c>
       <c r="D13" s="48" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="48" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B14" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A14)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D14)</f>
-        <v>2.6</v>
+        <v>2.65388888888889</v>
       </c>
       <c r="C14" s="45"/>
       <c r="D14" s="48" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A15)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D15)</f>
-        <v>3.91083333333333</v>
+        <v>2.6</v>
       </c>
       <c r="C15" s="45"/>
       <c r="D15" s="48" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="48" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="B16" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A16)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D16)</f>
-        <v>2.94083333333333</v>
+        <v>3.91083333333333</v>
       </c>
       <c r="C16" s="45"/>
       <c r="D16" s="48" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B17" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A17)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D17)</f>
-        <v>3.49347222222222</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C17" s="45"/>
       <c r="D17" s="48" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="48" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
+        <v>3.49347222222222</v>
+      </c>
+      <c r="C18" s="45"/>
+      <c r="D18" s="48" t="n">
         <v>3.5</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="46" t="s">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="47" t="n">
-        <f aca="false">AVERAGE(B19:B32)</f>
+      <c r="B19" s="47" t="n">
+        <f aca="false">AVERAGE(B20:B33)</f>
         <v>3.31464285714286</v>
       </c>
-      <c r="C18" s="45"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
-        <v>2.4</v>
-      </c>
       <c r="C19" s="45"/>
-      <c r="D19" s="48" t="n">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="C20" s="45"/>
       <c r="D20" s="48" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="48" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B21" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
-        <v>3.57402777777778</v>
+        <v>2.6</v>
       </c>
       <c r="C21" s="45"/>
       <c r="D21" s="48" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
-        <v>3.6</v>
+        <v>3.57402777777778</v>
       </c>
       <c r="C22" s="45"/>
       <c r="D22" s="48" t="n">
@@ -25963,543 +25965,556 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="48" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B23" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="C23" s="45"/>
       <c r="D23" s="48" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="48" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B24" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C24" s="45" t="s">
-        <v>101</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="C24" s="45"/>
       <c r="D24" s="48" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="48" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B25" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
-        <v>2.8</v>
-      </c>
-      <c r="C25" s="45"/>
+        <v>3.9</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>101</v>
+      </c>
       <c r="D25" s="48" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="48" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
-        <v>3.59875</v>
-      </c>
-      <c r="C27" s="45" t="s">
-        <v>103</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="C27" s="45"/>
       <c r="D27" s="48" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="48" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B28" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
-        <v>3.94083333333333</v>
-      </c>
-      <c r="C28" s="45"/>
+        <v>3.59875</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>103</v>
+      </c>
       <c r="D28" s="48" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="48" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B29" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>3.65388888888889</v>
+        <v>3.94083333333333</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="48" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="49" t="n">
+        <v>90</v>
+      </c>
+      <c r="B30" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
-        <v>3.95583333333333</v>
+        <v>3.65388888888889</v>
       </c>
       <c r="C30" s="45"/>
-      <c r="D30" s="49" t="n">
-        <v>4</v>
+      <c r="D30" s="48" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="48" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
-        <v>2.94666666666667</v>
+        <v>3.95583333333333</v>
       </c>
       <c r="C31" s="45"/>
       <c r="D31" s="49" t="n">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="48" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
+        <v>2.94666666666667</v>
+      </c>
+      <c r="C32" s="45"/>
+      <c r="D32" s="49" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
         <v>3.935</v>
       </c>
-      <c r="C32" s="45" t="s">
+      <c r="C33" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="49" t="n">
+      <c r="D33" s="49" t="n">
         <v>3.9</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="46" t="s">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="47" t="n">
-        <f aca="false">AVERAGE(B34:B44)</f>
+      <c r="B34" s="47" t="n">
+        <f aca="false">AVERAGE(B35:B45)</f>
         <v>3.26275505050505</v>
       </c>
-      <c r="C33" s="45"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
-        <v>3.5</v>
-      </c>
       <c r="C34" s="45"/>
-      <c r="D34" s="48" t="n">
-        <v>3.5</v>
-      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="48" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B35" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
-        <v>3.43088888888889</v>
+        <v>3.5</v>
       </c>
       <c r="C35" s="45"/>
       <c r="D35" s="48" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.7</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C36" s="45"/>
       <c r="D36" s="48" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="48" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B37" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="C37" s="45"/>
       <c r="D37" s="48" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>3.77816666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C38" s="45"/>
       <c r="D38" s="48" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="48" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B39" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>2.59388888888889</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C39" s="45"/>
       <c r="D39" s="48" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="48" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B40" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>3.23902777777778</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C40" s="45"/>
       <c r="D40" s="48" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="48" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B41" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>2.6</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C41" s="45"/>
       <c r="D41" s="48" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="48" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>3.58416666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C42" s="45"/>
       <c r="D42" s="48" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="48" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B43" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>2.94083333333333</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C43" s="45"/>
       <c r="D43" s="48" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B44" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>3.92333333333333</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C44" s="45"/>
       <c r="D44" s="48" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
+        <v>3.92333333333333</v>
+      </c>
+      <c r="C45" s="45"/>
+      <c r="D45" s="48" t="n">
         <v>3.9</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="46" t="s">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="47" t="n">
-        <f aca="false">AVERAGE(B46:B50)</f>
+      <c r="B46" s="47" t="n">
+        <f aca="false">AVERAGE(B47:B51)</f>
         <v>3.2865</v>
       </c>
-      <c r="C45" s="45"/>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
-        <v>3.6</v>
-      </c>
-      <c r="C46" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="48" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="C46" s="45"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="48" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B47" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.33761111111111</v>
+        <v>3.6</v>
       </c>
       <c r="C47" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D47" s="48" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="48" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B48" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C48" s="45"/>
+        <v>3.33761111111111</v>
+      </c>
+      <c r="C48" s="45" t="s">
+        <v>103</v>
+      </c>
       <c r="D48" s="48" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="48" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B49" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C49" s="45" t="s">
-        <v>104</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C49" s="45"/>
       <c r="D49" s="48" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="48" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B50" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C50" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="48" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="48" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
         <v>2.39488888888889</v>
       </c>
-      <c r="C50" s="45"/>
-      <c r="D50" s="48" t="n">
+      <c r="C51" s="45"/>
+      <c r="D51" s="48" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="46" t="s">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="47" t="n">
-        <f aca="false">AVERAGE(B52:B56)</f>
+      <c r="B52" s="47" t="n">
+        <f aca="false">AVERAGE(B53:B57)</f>
         <v>3.42807</v>
       </c>
-      <c r="C51" s="45"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
-        <v>3.6</v>
-      </c>
       <c r="C52" s="45"/>
-      <c r="D52" s="48" t="n">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="48" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B53" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="C53" s="45"/>
       <c r="D53" s="48" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="C54" s="45"/>
       <c r="D54" s="48" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="48" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B55" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="C55" s="45"/>
       <c r="D55" s="48" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.74035</v>
+        <v>3.3</v>
       </c>
       <c r="C56" s="45"/>
       <c r="D56" s="48" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="48" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
+        <v>3.74035</v>
+      </c>
+      <c r="C57" s="45"/>
+      <c r="D57" s="48" t="n">
         <v>3.7</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="46" t="s">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="47" t="n">
-        <f aca="false">AVERAGE(B58:B59)</f>
+      <c r="B58" s="47" t="n">
+        <f aca="false">AVERAGE(B59:B60)</f>
         <v>3.05</v>
       </c>
-      <c r="C57" s="45"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
-        <v>2.7</v>
-      </c>
       <c r="C58" s="45"/>
-      <c r="D58" s="48" t="n">
-        <v>2.7</v>
-      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="48" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B59" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="C59" s="45"/>
       <c r="D59" s="48" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="48" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
+        <v>3.4</v>
+      </c>
+      <c r="C60" s="45"/>
+      <c r="D60" s="48" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="B60" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>1</v>
-      </c>
-      <c r="C60" s="45"/>
-      <c r="D60" s="49" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="46" t="s">
+      <c r="B61" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
+        <v>1</v>
+      </c>
+      <c r="C61" s="45"/>
+      <c r="D61" s="49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="47" t="n">
-        <f aca="false">AVERAGE(B62:B63)</f>
+      <c r="B62" s="47" t="n">
+        <f aca="false">AVERAGE(B63:B64)</f>
         <v>2.25194444444444</v>
       </c>
-      <c r="C61" s="45"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
-        <v>2.30388888888889</v>
-      </c>
       <c r="C62" s="45"/>
-      <c r="D62" s="48" t="n">
-        <v>2.5</v>
-      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="48" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B63" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>2.2</v>
+        <v>2.30388888888889</v>
       </c>
       <c r="C63" s="45"/>
       <c r="D63" s="48" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="48" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B64" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
+        <v>2.2</v>
+      </c>
+      <c r="C64" s="45"/>
+      <c r="D64" s="48" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="48" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
         <v>2.43069444444444</v>
       </c>
-      <c r="D64" s="48" t="n">
+      <c r="D65" s="48" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -26519,7 +26534,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.89"/>
@@ -26627,60 +26642,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="46" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="48" t="inlineStr">
+        <is>
+          <t>ZZ Test New Deck</t>
+        </is>
+      </c>
+      <c r="B7" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="48">
+        <f>IFERROR(C7/B7,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7)</f>
+      <c r="B8" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8)</f>
         <v>14</v>
       </c>
-      <c r="C7" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+      <c r="C8" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>4</v>
       </c>
-      <c r="D7" s="47" t="n">
-        <f aca="false">IFERROR(C7/B7,0)</f>
+      <c r="D8" s="47" t="n">
+        <f aca="false">IFERROR(C8/B8,0)</f>
         <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8)</f>
-        <v>4</v>
-      </c>
-      <c r="C8" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
-      </c>
-      <c r="D8" s="48" t="n">
-        <f aca="false">IFERROR(C8/B8,0)</f>
-        <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B9" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="48" t="n">
         <f aca="false">IFERROR(C9/B9,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="48" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B10" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A10)</f>
@@ -26697,7 +26714,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B11" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A11)</f>
@@ -26714,7 +26731,7 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B12" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A12)</f>
@@ -26731,11 +26748,11 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B13" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -26748,11 +26765,11 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="48" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B14" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -26765,28 +26782,28 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="48" t="n">
         <f aca="false">IFERROR(C15/B15,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="48" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="B16" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C16" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -26794,63 +26811,63 @@
       </c>
       <c r="D16" s="48" t="n">
         <f aca="false">IFERROR(C16/B16,0)</f>
-        <v>0.166666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B17" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="48" t="n">
         <f aca="false">IFERROR(C17/B17,0)</f>
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
+        <v>1</v>
+      </c>
+      <c r="C18" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="48" t="n">
+        <f aca="false">IFERROR(C18/B18,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
+      <c r="B19" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19)</f>
         <v>12</v>
       </c>
-      <c r="C18" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+      <c r="C19" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>5</v>
       </c>
-      <c r="D18" s="47" t="n">
-        <f aca="false">IFERROR(C18/B18,0)</f>
+      <c r="D19" s="47" t="n">
+        <f aca="false">IFERROR(C19/B19,0)</f>
         <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="48" t="n">
-        <f aca="false">IFERROR(C19/B19,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -26867,11 +26884,11 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="48" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B21" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -26884,11 +26901,11 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -26901,7 +26918,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="48" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B23" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
@@ -26918,7 +26935,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="48" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B24" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
@@ -26935,7 +26952,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="48" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B25" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
@@ -26952,7 +26969,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="48" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
@@ -26969,11 +26986,11 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -26986,7 +27003,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="48" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B28" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
@@ -26994,122 +27011,122 @@
       </c>
       <c r="C28" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="48" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="48" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B29" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="48" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="48" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="B30" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="48" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="48" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B31" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="48" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="48" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B32" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="48" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="46" t="s">
+      <c r="A33" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
+        <v>1</v>
+      </c>
+      <c r="C33" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D33" s="48" t="n">
+        <f aca="false">IFERROR(C33/B33,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
+      <c r="B34" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34)</f>
         <v>11</v>
       </c>
-      <c r="C33" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D33" s="47" t="n">
-        <f aca="false">IFERROR(C33/B33,0)</f>
+      <c r="C34" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D34" s="47" t="n">
+        <f aca="false">IFERROR(C34/B34,0)</f>
         <v>0.272727272727273</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="48" t="n">
-        <f aca="false">IFERROR(C34/B34,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="48" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B35" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27122,11 +27139,11 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27139,7 +27156,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="48" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B37" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
@@ -27156,24 +27173,24 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="48" t="n">
         <f aca="false">IFERROR(C38/B38,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="48" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B39" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
@@ -27181,20 +27198,20 @@
       </c>
       <c r="C39" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" s="48" t="n">
         <f aca="false">IFERROR(C39/B39,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="48" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B40" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27207,11 +27224,11 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="48" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B41" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27224,11 +27241,11 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="48" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C42" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27241,7 +27258,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="48" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B43" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
@@ -27249,16 +27266,16 @@
       </c>
       <c r="C43" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="48" t="n">
         <f aca="false">IFERROR(C43/B43,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="48" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B44" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
@@ -27274,46 +27291,46 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="46" t="s">
+      <c r="A45" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
+        <v>2</v>
+      </c>
+      <c r="C45" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="48" t="n">
+        <f aca="false">IFERROR(C45/B45,0)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
-        <v>2</v>
-      </c>
-      <c r="C45" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="47" t="n">
-        <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
-        <v>0</v>
-      </c>
-      <c r="C46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="48" t="n">
+      <c r="B46" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46)</f>
+        <v>2</v>
+      </c>
+      <c r="C46" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="47" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="48" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B47" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27326,11 +27343,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="48" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B48" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27343,7 +27360,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="48" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B49" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
@@ -27360,11 +27377,11 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="48" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B50" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27376,42 +27393,42 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="46" t="s">
+      <c r="A51" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="48" t="n">
+        <f aca="false">IFERROR(C51/B51,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="47" t="n">
-        <f aca="false">IFERROR(C51/B51,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
-        <v>0</v>
-      </c>
-      <c r="C52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="48" t="n">
+      <c r="B52" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52)</f>
+        <v>1</v>
+      </c>
+      <c r="C52" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="47" t="n">
         <f aca="false">IFERROR(C52/B52,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="48" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B53" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -27428,7 +27445,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -27445,7 +27462,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="48" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B55" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
@@ -27462,11 +27479,11 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27478,42 +27495,42 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="46" t="s">
+      <c r="A57" s="48" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
+        <v>1</v>
+      </c>
+      <c r="C57" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="48" t="n">
+        <f aca="false">IFERROR(C57/B57,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
-        <v>0</v>
-      </c>
-      <c r="C57" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="47" t="n">
-        <f aca="false">IFERROR(C57/B57,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
-        <v>0</v>
-      </c>
-      <c r="C58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="48" t="n">
+      <c r="B58" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58)</f>
+        <v>0</v>
+      </c>
+      <c r="C58" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="47" t="n">
         <f aca="false">IFERROR(C58/B58,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="48" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B59" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
@@ -27530,7 +27547,7 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="48" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B60" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
@@ -27546,46 +27563,46 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="46" t="s">
+      <c r="A61" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="48" t="n">
+        <f aca="false">IFERROR(C61/B61,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+      <c r="B62" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62)</f>
         <v>4</v>
       </c>
-      <c r="C61" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="47" t="n">
-        <f aca="false">IFERROR(C61/B61,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
-        <v>3</v>
-      </c>
-      <c r="C62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="48" t="n">
+      <c r="C62" s="47" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="47" t="n">
         <f aca="false">IFERROR(C62/B62,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="48" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B63" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C63" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27598,11 +27615,11 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="48" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B64" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27610,6 +27627,23 @@
       </c>
       <c r="D64" s="48" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
+        <v>1</v>
+      </c>
+      <c r="C65" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="48" t="n">
+        <f aca="false">IFERROR(C65/B65,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Game Log Season 1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Game Log Season 2" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Game Log Season 3" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Game Log Season 4" sheetId="7" r:id="rId10"/>
     <sheet name="Current Deck Strength" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Deck Win Rates" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Player Adjusted Ranks" sheetId="6" state="visible" r:id="rId8"/>
@@ -25706,12 +25707,12 @@
         <v>45</v>
       </c>
       <c r="B3" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A3)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D3)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Becca")*('Game Log Season 4'!$D$3:$D$1000=A3)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D3)</f>
         <v>2.40388888888889</v>
       </c>
       <c r="C3" s="45"/>
       <c r="D3" s="48" t="n">
-        <v>2.4</v>
+        <v>2.40388888888889</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25719,7 +25720,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A4)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D4)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Becca")*('Game Log Season 4'!$D$3:$D$1000=A4)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D4)</f>
         <v>3.7</v>
       </c>
       <c r="C4" s="45" t="s">
@@ -25734,12 +25735,12 @@
         <v>75</v>
       </c>
       <c r="B5" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A5)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D5)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Becca")*('Game Log Season 4'!$D$3:$D$1000=A5)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D5)</f>
         <v>2.30388888888889</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="48" t="n">
-        <v>2.3</v>
+        <v>2.30388888888889</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25747,12 +25748,12 @@
         <v>95</v>
       </c>
       <c r="B6" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A6)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D6)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Becca")*('Game Log Season 4'!$D$3:$D$1000=A6)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D6)</f>
         <v>2.48375</v>
       </c>
       <c r="C6" s="45"/>
       <c r="D6" s="48" t="n">
-        <v>2.5</v>
+        <v>2.48375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25770,12 +25771,12 @@
         <v>68</v>
       </c>
       <c r="B8" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A8)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D8)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A8)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D8)</f>
         <v>3.83916666666667</v>
       </c>
       <c r="C8" s="45"/>
       <c r="D8" s="48" t="n">
-        <v>3.8</v>
+        <v>3.83916666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25783,7 +25784,7 @@
         <v>42</v>
       </c>
       <c r="B9" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A9)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D9)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A9)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D9)</f>
         <v>3.9</v>
       </c>
       <c r="C9" s="45"/>
@@ -25796,7 +25797,7 @@
         <v>67</v>
       </c>
       <c r="B10" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A10)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D10)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A10)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D10)</f>
         <v>3.4</v>
       </c>
       <c r="C10" s="45" t="s">
@@ -25811,7 +25812,7 @@
         <v>82</v>
       </c>
       <c r="B11" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A11)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D11)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A11)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D11)</f>
         <v>2.6</v>
       </c>
       <c r="C11" s="45"/>
@@ -25824,7 +25825,7 @@
         <v>44</v>
       </c>
       <c r="B12" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A12)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D12)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A12)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D12)</f>
         <v>3.5</v>
       </c>
       <c r="C12" s="45" t="s">
@@ -25839,12 +25840,12 @@
         <v>88</v>
       </c>
       <c r="B13" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A13)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D13)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A13)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D13)</f>
         <v>2.65388888888889</v>
       </c>
       <c r="C13" s="45"/>
       <c r="D13" s="48" t="n">
-        <v>2.7</v>
+        <v>2.65388888888889</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25852,7 +25853,7 @@
         <v>48</v>
       </c>
       <c r="B14" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A14)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D14)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A14)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D14)</f>
         <v>2.6</v>
       </c>
       <c r="C14" s="45"/>
@@ -25865,12 +25866,12 @@
         <v>37</v>
       </c>
       <c r="B15" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A15)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D15)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A15)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D15)</f>
         <v>3.91083333333333</v>
       </c>
       <c r="C15" s="45"/>
       <c r="D15" s="48" t="n">
-        <v>3.9</v>
+        <v>3.91083333333333</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25878,12 +25879,12 @@
         <v>91</v>
       </c>
       <c r="B16" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A16)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D16)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A16)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D16)</f>
         <v>2.94083333333333</v>
       </c>
       <c r="C16" s="45"/>
       <c r="D16" s="48" t="n">
-        <v>2.3</v>
+        <v>2.94083333333333</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25891,12 +25892,12 @@
         <v>47</v>
       </c>
       <c r="B17" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A17)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D17)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Manny")*('Game Log Season 4'!$D$3:$D$1000=A17)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D17)</f>
         <v>3.49347222222222</v>
       </c>
       <c r="C17" s="45"/>
       <c r="D17" s="48" t="n">
-        <v>3.5</v>
+        <v>3.49347222222222</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25914,7 +25915,7 @@
         <v>73</v>
       </c>
       <c r="B19" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A19)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D19)</f>
         <v>2.4</v>
       </c>
       <c r="C19" s="45"/>
@@ -25927,7 +25928,7 @@
         <v>66</v>
       </c>
       <c r="B20" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A20)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D20)</f>
         <v>2.6</v>
       </c>
       <c r="C20" s="45"/>
@@ -25940,12 +25941,12 @@
         <v>31</v>
       </c>
       <c r="B21" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A21)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D21)</f>
         <v>3.57402777777778</v>
       </c>
       <c r="C21" s="45"/>
       <c r="D21" s="48" t="n">
-        <v>3.6</v>
+        <v>3.57402777777778</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25953,7 +25954,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A22)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D22)</f>
         <v>3.6</v>
       </c>
       <c r="C22" s="45"/>
@@ -25966,7 +25967,7 @@
         <v>74</v>
       </c>
       <c r="B23" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A23)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D23)</f>
         <v>2.9</v>
       </c>
       <c r="C23" s="45"/>
@@ -25979,7 +25980,7 @@
         <v>57</v>
       </c>
       <c r="B24" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A24)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D24)</f>
         <v>3.9</v>
       </c>
       <c r="C24" s="45" t="s">
@@ -25994,7 +25995,7 @@
         <v>80</v>
       </c>
       <c r="B25" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A25)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D25)</f>
         <v>2.8</v>
       </c>
       <c r="C25" s="45"/>
@@ -26007,7 +26008,7 @@
         <v>81</v>
       </c>
       <c r="B26" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A26)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D26)</f>
         <v>2.6</v>
       </c>
       <c r="C26" s="45"/>
@@ -26020,14 +26021,14 @@
         <v>83</v>
       </c>
       <c r="B27" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A27)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D27)</f>
         <v>3.59875</v>
       </c>
       <c r="C27" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D27" s="48" t="n">
-        <v>3.6</v>
+        <v>3.59875</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26035,12 +26036,12 @@
         <v>48</v>
       </c>
       <c r="B28" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A28)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D28)</f>
         <v>3.94083333333333</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="48" t="n">
-        <v>3.9</v>
+        <v>3.94083333333333</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26048,12 +26049,12 @@
         <v>90</v>
       </c>
       <c r="B29" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A29)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D29)</f>
         <v>3.65388888888889</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="48" t="n">
-        <v>3.7</v>
+        <v>3.65388888888889</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26061,12 +26062,12 @@
         <v>46</v>
       </c>
       <c r="B30" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A30)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D30)</f>
         <v>3.95583333333333</v>
       </c>
       <c r="C30" s="45"/>
       <c r="D30" s="49" t="n">
-        <v>4</v>
+        <v>3.95583333333333</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26074,12 +26075,12 @@
         <v>92</v>
       </c>
       <c r="B31" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A31)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D31)</f>
         <v>2.94666666666667</v>
       </c>
       <c r="C31" s="45"/>
       <c r="D31" s="49" t="n">
-        <v>2.9</v>
+        <v>2.94666666666667</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26087,14 +26088,14 @@
         <v>40</v>
       </c>
       <c r="B32" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Mateo")*('Game Log Season 4'!$D$3:$D$1000=A32)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D32)</f>
         <v>3.935</v>
       </c>
       <c r="C32" s="45" t="s">
         <v>104</v>
       </c>
       <c r="D32" s="49" t="n">
-        <v>3.9</v>
+        <v>3.935</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26112,7 +26113,7 @@
         <v>36</v>
       </c>
       <c r="B34" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A34)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D34)</f>
         <v>3.5</v>
       </c>
       <c r="C34" s="45"/>
@@ -26125,12 +26126,12 @@
         <v>62</v>
       </c>
       <c r="B35" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A35)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D35)</f>
         <v>3.43088888888889</v>
       </c>
       <c r="C35" s="45"/>
       <c r="D35" s="48" t="n">
-        <v>3.4</v>
+        <v>3.43088888888889</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26138,7 +26139,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A36)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D36)</f>
         <v>3.7</v>
       </c>
       <c r="C36" s="45"/>
@@ -26151,7 +26152,7 @@
         <v>61</v>
       </c>
       <c r="B37" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A37)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D37)</f>
         <v>2.6</v>
       </c>
       <c r="C37" s="45"/>
@@ -26164,12 +26165,12 @@
         <v>41</v>
       </c>
       <c r="B38" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A38)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D38)</f>
         <v>3.77816666666667</v>
       </c>
       <c r="C38" s="45"/>
       <c r="D38" s="48" t="n">
-        <v>3.8</v>
+        <v>3.77816666666667</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26177,12 +26178,12 @@
         <v>79</v>
       </c>
       <c r="B39" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A39)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D39)</f>
         <v>2.59388888888889</v>
       </c>
       <c r="C39" s="45"/>
       <c r="D39" s="48" t="n">
-        <v>2.6</v>
+        <v>2.59388888888889</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26190,12 +26191,12 @@
         <v>54</v>
       </c>
       <c r="B40" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A40)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D40)</f>
         <v>3.23902777777778</v>
       </c>
       <c r="C40" s="45"/>
       <c r="D40" s="48" t="n">
-        <v>3.6</v>
+        <v>3.23902777777778</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26203,7 +26204,7 @@
         <v>87</v>
       </c>
       <c r="B41" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A41)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D41)</f>
         <v>2.6</v>
       </c>
       <c r="C41" s="45"/>
@@ -26216,12 +26217,12 @@
         <v>89</v>
       </c>
       <c r="B42" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A42)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D42)</f>
         <v>3.58416666666667</v>
       </c>
       <c r="C42" s="45"/>
       <c r="D42" s="48" t="n">
-        <v>3.6</v>
+        <v>3.58416666666667</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26229,12 +26230,12 @@
         <v>94</v>
       </c>
       <c r="B43" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A43)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D43)</f>
         <v>2.94083333333333</v>
       </c>
       <c r="C43" s="45"/>
       <c r="D43" s="48" t="n">
-        <v>2.9</v>
+        <v>2.94083333333333</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26242,12 +26243,12 @@
         <v>97</v>
       </c>
       <c r="B44" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Ryan")*('Game Log Season 4'!$D$3:$D$1000=A44)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D44)</f>
         <v>3.92333333333333</v>
       </c>
       <c r="C44" s="45"/>
       <c r="D44" s="48" t="n">
-        <v>3.9</v>
+        <v>3.92333333333333</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26265,7 +26266,7 @@
         <v>71</v>
       </c>
       <c r="B46" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Kristy")*('Game Log Season 4'!$D$3:$D$1000=A46)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D46)</f>
         <v>3.6</v>
       </c>
       <c r="C46" s="45" t="s">
@@ -26280,14 +26281,14 @@
         <v>57</v>
       </c>
       <c r="B47" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Kristy")*('Game Log Season 4'!$D$3:$D$1000=A47)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D47)</f>
         <v>3.33761111111111</v>
       </c>
       <c r="C47" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D47" s="48" t="n">
-        <v>3.3</v>
+        <v>3.33761111111111</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26295,7 +26296,7 @@
         <v>78</v>
       </c>
       <c r="B48" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Kristy")*('Game Log Season 4'!$D$3:$D$1000=A48)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D48)</f>
         <v>3.2</v>
       </c>
       <c r="C48" s="45"/>
@@ -26308,7 +26309,7 @@
         <v>85</v>
       </c>
       <c r="B49" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Kristy")*('Game Log Season 4'!$D$3:$D$1000=A49)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D49)</f>
         <v>3.9</v>
       </c>
       <c r="C49" s="45" t="s">
@@ -26323,12 +26324,12 @@
         <v>93</v>
       </c>
       <c r="B50" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Kristy")*('Game Log Season 4'!$D$3:$D$1000=A50)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D50)</f>
         <v>2.39488888888889</v>
       </c>
       <c r="C50" s="45"/>
       <c r="D50" s="48" t="n">
-        <v>2.4</v>
+        <v>2.39488888888889</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26346,7 +26347,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Joseph")*('Game Log Season 4'!$D$3:$D$1000=A52)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D52)</f>
         <v>3.6</v>
       </c>
       <c r="C52" s="45"/>
@@ -26359,7 +26360,7 @@
         <v>76</v>
       </c>
       <c r="B53" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Joseph")*('Game Log Season 4'!$D$3:$D$1000=A53)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D53)</f>
         <v>3.8</v>
       </c>
       <c r="C53" s="45"/>
@@ -26372,7 +26373,7 @@
         <v>77</v>
       </c>
       <c r="B54" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Joseph")*('Game Log Season 4'!$D$3:$D$1000=A54)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D54)</f>
         <v>2.7</v>
       </c>
       <c r="C54" s="45"/>
@@ -26385,7 +26386,7 @@
         <v>64</v>
       </c>
       <c r="B55" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Joseph")*('Game Log Season 4'!$D$3:$D$1000=A55)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D55)</f>
         <v>3.3</v>
       </c>
       <c r="C55" s="45"/>
@@ -26398,12 +26399,12 @@
         <v>63</v>
       </c>
       <c r="B56" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Joseph")*('Game Log Season 4'!$D$3:$D$1000=A56)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D56)</f>
         <v>3.74035</v>
       </c>
       <c r="C56" s="45"/>
       <c r="D56" s="48" t="n">
-        <v>3.7</v>
+        <v>3.74035</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26421,7 +26422,7 @@
         <v>33</v>
       </c>
       <c r="B58" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Red")*('Game Log Season 4'!$D$3:$D$1000=A58)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D58)</f>
         <v>2.7</v>
       </c>
       <c r="C58" s="45"/>
@@ -26434,7 +26435,7 @@
         <v>69</v>
       </c>
       <c r="B59" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Red")*('Game Log Season 4'!$D$3:$D$1000=A59)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D59)</f>
         <v>3.4</v>
       </c>
       <c r="C59" s="45"/>
@@ -26447,7 +26448,7 @@
         <v>84</v>
       </c>
       <c r="B60" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Red")*('Game Log Season 4'!$D$3:$D$1000=A60)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D60)</f>
         <v>1</v>
       </c>
       <c r="C60" s="45"/>
@@ -26470,12 +26471,12 @@
         <v>52</v>
       </c>
       <c r="B62" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Michelle")*('Game Log Season 4'!$D$3:$D$1000=A62)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D62)</f>
         <v>2.30388888888889</v>
       </c>
       <c r="C62" s="45"/>
       <c r="D62" s="48" t="n">
-        <v>2.5</v>
+        <v>2.30388888888889</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26483,7 +26484,7 @@
         <v>86</v>
       </c>
       <c r="B63" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Michelle")*('Game Log Season 4'!$D$3:$D$1000=A63)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D63)</f>
         <v>2.2</v>
       </c>
       <c r="C63" s="45"/>
@@ -26496,11 +26497,11 @@
         <v>96</v>
       </c>
       <c r="B64" s="48" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 4'!$C$3:$C$1000="Michelle")*('Game Log Season 4'!$D$3:$D$1000=A64)*('Game Log Season 4'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 4'!$X$3:$X$1000), D64)</f>
         <v>2.43069444444444</v>
       </c>
       <c r="D64" s="48" t="n">
-        <v>2.4</v>
+        <v>2.43069444444444</v>
       </c>
     </row>
   </sheetData>
@@ -26547,11 +26548,11 @@
         <v>26</v>
       </c>
       <c r="B2" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A2)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A2)</f>
         <v>7</v>
       </c>
       <c r="C2" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A2,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A2,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>2</v>
       </c>
       <c r="D2" s="47" t="n">
@@ -26564,11 +26565,11 @@
         <v>45</v>
       </c>
       <c r="B3" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A3)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Becca",'Game Log Season 4'!$D$3:$D$1000,A3)</f>
         <v>3</v>
       </c>
       <c r="C3" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A3,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Becca",'Game Log Season 4'!$D$3:$D$1000,A3,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D3" s="48" t="n">
@@ -26581,11 +26582,11 @@
         <v>27</v>
       </c>
       <c r="B4" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A4)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Becca",'Game Log Season 4'!$D$3:$D$1000,A4)</f>
         <v>0</v>
       </c>
       <c r="C4" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A4,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Becca",'Game Log Season 4'!$D$3:$D$1000,A4,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D4" s="48" t="n">
@@ -26598,11 +26599,11 @@
         <v>75</v>
       </c>
       <c r="B5" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A5)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Becca",'Game Log Season 4'!$D$3:$D$1000,A5)</f>
         <v>3</v>
       </c>
       <c r="C5" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A5,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Becca",'Game Log Season 4'!$D$3:$D$1000,A5,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D5" s="48" t="n">
@@ -26615,11 +26616,11 @@
         <v>95</v>
       </c>
       <c r="B6" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A6)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Becca",'Game Log Season 4'!$D$3:$D$1000,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A6,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Becca",'Game Log Season 4'!$D$3:$D$1000,A6,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D6" s="48" t="n">
@@ -26632,11 +26633,11 @@
         <v>28</v>
       </c>
       <c r="B7" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A7)</f>
         <v>14</v>
       </c>
       <c r="C7" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A7,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>4</v>
       </c>
       <c r="D7" s="47" t="n">
@@ -26649,11 +26650,11 @@
         <v>68</v>
       </c>
       <c r="B8" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A8)</f>
         <v>4</v>
       </c>
       <c r="C8" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A8,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>2</v>
       </c>
       <c r="D8" s="48" t="n">
@@ -26666,11 +26667,11 @@
         <v>42</v>
       </c>
       <c r="B9" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A9)</f>
         <v>0</v>
       </c>
       <c r="C9" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A9,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D9" s="48" t="n">
@@ -26683,11 +26684,11 @@
         <v>67</v>
       </c>
       <c r="B10" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A10)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A10)</f>
         <v>0</v>
       </c>
       <c r="C10" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A10,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A10,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D10" s="48" t="n">
@@ -26700,11 +26701,11 @@
         <v>82</v>
       </c>
       <c r="B11" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A11)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A11)</f>
         <v>0</v>
       </c>
       <c r="C11" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A11,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A11,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D11" s="48" t="n">
@@ -26717,11 +26718,11 @@
         <v>44</v>
       </c>
       <c r="B12" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A12)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A12)</f>
         <v>0</v>
       </c>
       <c r="C12" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A12,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A12,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D12" s="48" t="n">
@@ -26734,11 +26735,11 @@
         <v>88</v>
       </c>
       <c r="B13" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A13)</f>
         <v>2</v>
       </c>
       <c r="C13" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A13,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D13" s="48" t="n">
@@ -26751,11 +26752,11 @@
         <v>48</v>
       </c>
       <c r="B14" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A14)</f>
         <v>0</v>
       </c>
       <c r="C14" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A14,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D14" s="48" t="n">
@@ -26768,11 +26769,11 @@
         <v>37</v>
       </c>
       <c r="B15" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A15)</f>
         <v>1</v>
       </c>
       <c r="C15" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A15,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D15" s="48" t="n">
@@ -26785,11 +26786,11 @@
         <v>91</v>
       </c>
       <c r="B16" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A16)</f>
         <v>6</v>
       </c>
       <c r="C16" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A16,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D16" s="48" t="n">
@@ -26802,11 +26803,11 @@
         <v>47</v>
       </c>
       <c r="B17" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A17)</f>
         <v>1</v>
       </c>
       <c r="C17" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Manny",'Game Log Season 4'!$D$3:$D$1000,A17,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D17" s="48" t="n">
@@ -26819,11 +26820,11 @@
         <v>30</v>
       </c>
       <c r="B18" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A18)</f>
         <v>12</v>
       </c>
       <c r="C18" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A18,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>5</v>
       </c>
       <c r="D18" s="47" t="n">
@@ -26836,11 +26837,11 @@
         <v>73</v>
       </c>
       <c r="B19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A19,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D19" s="48" t="n">
@@ -26853,11 +26854,11 @@
         <v>66</v>
       </c>
       <c r="B20" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A20,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D20" s="48" t="n">
@@ -26870,11 +26871,11 @@
         <v>31</v>
       </c>
       <c r="B21" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A21)</f>
         <v>1</v>
       </c>
       <c r="C21" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A21,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D21" s="48" t="n">
@@ -26887,11 +26888,11 @@
         <v>34</v>
       </c>
       <c r="B22" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A22)</f>
         <v>0</v>
       </c>
       <c r="C22" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A22,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D22" s="48" t="n">
@@ -26904,11 +26905,11 @@
         <v>74</v>
       </c>
       <c r="B23" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A23)</f>
         <v>0</v>
       </c>
       <c r="C23" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A23,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D23" s="48" t="n">
@@ -26921,11 +26922,11 @@
         <v>57</v>
       </c>
       <c r="B24" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A24)</f>
         <v>0</v>
       </c>
       <c r="C24" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A24,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D24" s="48" t="n">
@@ -26938,11 +26939,11 @@
         <v>80</v>
       </c>
       <c r="B25" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A25)</f>
         <v>0</v>
       </c>
       <c r="C25" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A25,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D25" s="48" t="n">
@@ -26955,11 +26956,11 @@
         <v>81</v>
       </c>
       <c r="B26" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A26)</f>
         <v>0</v>
       </c>
       <c r="C26" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A26,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D26" s="48" t="n">
@@ -26972,11 +26973,11 @@
         <v>83</v>
       </c>
       <c r="B27" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A27)</f>
         <v>1</v>
       </c>
       <c r="C27" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A27,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D27" s="48" t="n">
@@ -26989,11 +26990,11 @@
         <v>48</v>
       </c>
       <c r="B28" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A28)</f>
         <v>1</v>
       </c>
       <c r="C28" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A28,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D28" s="48" t="n">
@@ -27006,11 +27007,11 @@
         <v>90</v>
       </c>
       <c r="B29" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A29)</f>
         <v>4</v>
       </c>
       <c r="C29" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A29,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D29" s="48" t="n">
@@ -27023,11 +27024,11 @@
         <v>46</v>
       </c>
       <c r="B30" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A30)</f>
         <v>1</v>
       </c>
       <c r="C30" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A30,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D30" s="48" t="n">
@@ -27040,11 +27041,11 @@
         <v>92</v>
       </c>
       <c r="B31" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A31)</f>
         <v>3</v>
       </c>
       <c r="C31" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A31,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>2</v>
       </c>
       <c r="D31" s="48" t="n">
@@ -27057,11 +27058,11 @@
         <v>40</v>
       </c>
       <c r="B32" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A32)</f>
         <v>1</v>
       </c>
       <c r="C32" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Mateo",'Game Log Season 4'!$D$3:$D$1000,A32,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D32" s="48" t="n">
@@ -27074,11 +27075,11 @@
         <v>32</v>
       </c>
       <c r="B33" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A33)</f>
         <v>11</v>
       </c>
       <c r="C33" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A33,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>3</v>
       </c>
       <c r="D33" s="47" t="n">
@@ -27091,11 +27092,11 @@
         <v>36</v>
       </c>
       <c r="B34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A34,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D34" s="48" t="n">
@@ -27108,11 +27109,11 @@
         <v>62</v>
       </c>
       <c r="B35" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A35)</f>
         <v>1</v>
       </c>
       <c r="C35" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A35,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D35" s="48" t="n">
@@ -27125,11 +27126,11 @@
         <v>33</v>
       </c>
       <c r="B36" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A36)</f>
         <v>0</v>
       </c>
       <c r="C36" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A36,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D36" s="48" t="n">
@@ -27142,11 +27143,11 @@
         <v>61</v>
       </c>
       <c r="B37" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A37)</f>
         <v>0</v>
       </c>
       <c r="C37" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A37,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D37" s="48" t="n">
@@ -27159,11 +27160,11 @@
         <v>41</v>
       </c>
       <c r="B38" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A38)</f>
         <v>1</v>
       </c>
       <c r="C38" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A38,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D38" s="48" t="n">
@@ -27176,11 +27177,11 @@
         <v>79</v>
       </c>
       <c r="B39" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A39)</f>
         <v>1</v>
       </c>
       <c r="C39" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A39,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D39" s="48" t="n">
@@ -27193,11 +27194,11 @@
         <v>54</v>
       </c>
       <c r="B40" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A40)</f>
         <v>2</v>
       </c>
       <c r="C40" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A40,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D40" s="48" t="n">
@@ -27210,11 +27211,11 @@
         <v>87</v>
       </c>
       <c r="B41" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A41)</f>
         <v>0</v>
       </c>
       <c r="C41" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A41,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D41" s="48" t="n">
@@ -27227,11 +27228,11 @@
         <v>89</v>
       </c>
       <c r="B42" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A42)</f>
         <v>2</v>
       </c>
       <c r="C42" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A42,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D42" s="48" t="n">
@@ -27244,11 +27245,11 @@
         <v>94</v>
       </c>
       <c r="B43" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A43)</f>
         <v>2</v>
       </c>
       <c r="C43" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A43,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D43" s="48" t="n">
@@ -27261,11 +27262,11 @@
         <v>97</v>
       </c>
       <c r="B44" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A44)</f>
         <v>2</v>
       </c>
       <c r="C44" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Ryan",'Game Log Season 4'!$D$3:$D$1000,A44,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>1</v>
       </c>
       <c r="D44" s="48" t="n">
@@ -27278,11 +27279,11 @@
         <v>70</v>
       </c>
       <c r="B45" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A45)</f>
         <v>2</v>
       </c>
       <c r="C45" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A45,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D45" s="47" t="n">
@@ -27295,11 +27296,11 @@
         <v>71</v>
       </c>
       <c r="B46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A46)</f>
         <v>0</v>
       </c>
       <c r="C46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A46,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D46" s="48" t="n">
@@ -27312,11 +27313,11 @@
         <v>57</v>
       </c>
       <c r="B47" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A47)</f>
         <v>1</v>
       </c>
       <c r="C47" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A47,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D47" s="48" t="n">
@@ -27329,11 +27330,11 @@
         <v>78</v>
       </c>
       <c r="B48" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A48)</f>
         <v>0</v>
       </c>
       <c r="C48" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A48,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D48" s="48" t="n">
@@ -27346,11 +27347,11 @@
         <v>85</v>
       </c>
       <c r="B49" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A49)</f>
         <v>0</v>
       </c>
       <c r="C49" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A49,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D49" s="48" t="n">
@@ -27363,11 +27364,11 @@
         <v>93</v>
       </c>
       <c r="B50" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A50)</f>
         <v>1</v>
       </c>
       <c r="C50" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Kristy",'Game Log Season 4'!$D$3:$D$1000,A50,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D50" s="48" t="n">
@@ -27380,11 +27381,11 @@
         <v>38</v>
       </c>
       <c r="B51" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A51)</f>
         <v>1</v>
       </c>
       <c r="C51" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A51,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D51" s="47" t="n">
@@ -27397,11 +27398,11 @@
         <v>49</v>
       </c>
       <c r="B52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A52)</f>
         <v>0</v>
       </c>
       <c r="C52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A52,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D52" s="48" t="n">
@@ -27414,11 +27415,11 @@
         <v>76</v>
       </c>
       <c r="B53" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A53)</f>
         <v>0</v>
       </c>
       <c r="C53" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A53,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D53" s="48" t="n">
@@ -27431,11 +27432,11 @@
         <v>77</v>
       </c>
       <c r="B54" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A54)</f>
         <v>0</v>
       </c>
       <c r="C54" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A54,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D54" s="48" t="n">
@@ -27448,11 +27449,11 @@
         <v>64</v>
       </c>
       <c r="B55" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A55)</f>
         <v>0</v>
       </c>
       <c r="C55" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A55,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D55" s="48" t="n">
@@ -27465,11 +27466,11 @@
         <v>63</v>
       </c>
       <c r="B56" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A56)</f>
         <v>1</v>
       </c>
       <c r="C56" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Joseph",'Game Log Season 4'!$D$3:$D$1000,A56,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D56" s="48" t="n">
@@ -27482,11 +27483,11 @@
         <v>59</v>
       </c>
       <c r="B57" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A57)</f>
         <v>0</v>
       </c>
       <c r="C57" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A57,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D57" s="47" t="n">
@@ -27499,11 +27500,11 @@
         <v>33</v>
       </c>
       <c r="B58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Red",'Game Log Season 4'!$D$3:$D$1000,A58)</f>
         <v>0</v>
       </c>
       <c r="C58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Red",'Game Log Season 4'!$D$3:$D$1000,A58,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D58" s="48" t="n">
@@ -27516,11 +27517,11 @@
         <v>69</v>
       </c>
       <c r="B59" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Red",'Game Log Season 4'!$D$3:$D$1000,A59)</f>
         <v>0</v>
       </c>
       <c r="C59" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Red",'Game Log Season 4'!$D$3:$D$1000,A59,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D59" s="48" t="n">
@@ -27533,11 +27534,11 @@
         <v>84</v>
       </c>
       <c r="B60" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Red",'Game Log Season 4'!$D$3:$D$1000,A60)</f>
         <v>0</v>
       </c>
       <c r="C60" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Red",'Game Log Season 4'!$D$3:$D$1000,A60,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D60" s="48" t="n">
@@ -27550,11 +27551,11 @@
         <v>51</v>
       </c>
       <c r="B61" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A61)</f>
         <v>4</v>
       </c>
       <c r="C61" s="47" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,A61,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D61" s="47" t="n">
@@ -27567,11 +27568,11 @@
         <v>52</v>
       </c>
       <c r="B62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Michelle",'Game Log Season 4'!$D$3:$D$1000,A62)</f>
         <v>3</v>
       </c>
       <c r="C62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Michelle",'Game Log Season 4'!$D$3:$D$1000,A62,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D62" s="48" t="n">
@@ -27584,11 +27585,11 @@
         <v>86</v>
       </c>
       <c r="B63" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Michelle",'Game Log Season 4'!$D$3:$D$1000,A63)</f>
         <v>0</v>
       </c>
       <c r="C63" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Michelle",'Game Log Season 4'!$D$3:$D$1000,A63,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D63" s="48" t="n">
@@ -27601,11 +27602,11 @@
         <v>96</v>
       </c>
       <c r="B64" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Michelle",'Game Log Season 4'!$D$3:$D$1000,A64)</f>
         <v>1</v>
       </c>
       <c r="C64" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$1000,"Michelle",'Game Log Season 4'!$D$3:$D$1000,A64,'Game Log Season 4'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D64" s="48" t="n">
@@ -27693,11 +27694,11 @@
         <v>0.371988902467902</v>
       </c>
       <c r="C2" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Mateo", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>5</v>
       </c>
       <c r="D2" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Mateo", 'Game Log Season 4'!$F$3:$F$126, 0)</f>
         <v>7</v>
       </c>
       <c r="E2" s="17" t="n">
@@ -27705,11 +27706,11 @@
         <v>0.416666666666667</v>
       </c>
       <c r="F2" s="14" t="n">
-        <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">SUMIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Mateo", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>3.55</v>
       </c>
       <c r="G2" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D2,0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Mateo", 'Game Log Season 4'!$F$3:$F$126, 0)*-1))*D2,0)</f>
         <v>5.13333333333333</v>
       </c>
       <c r="H2" s="17" t="n">
@@ -27717,15 +27718,15 @@
         <v>0.408829174664108</v>
       </c>
       <c r="I2" s="17" t="n">
-        <f aca="false">IF(C2&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$K$3:$K$126),0)</f>
+        <f aca="false">IF(C2&lt;&gt;0,AVERAGEIF('Game Log Season 4'!$C$3:$C$126, "Mateo", 'Game Log Season 4'!$K$3:$K$126),0)</f>
         <v>0.238611111111111</v>
       </c>
       <c r="J2" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C2, 0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Mateo", 'Game Log Season 4'!$F$3:$F$126, 1)-0.5))*C2, 0)</f>
         <v>5.01575</v>
       </c>
       <c r="K2" s="14" t="n">
-        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D2, 0)</f>
+        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Mateo", 'Game Log Season 4'!$F$3:$F$126, 0)-0.5))*D2, 0)</f>
         <v>7.423</v>
       </c>
       <c r="L2" s="17" t="n">
@@ -27742,11 +27743,11 @@
         <v>0.249788769042654</v>
       </c>
       <c r="C3" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Ryan", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>3</v>
       </c>
       <c r="D3" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Ryan", 'Game Log Season 4'!$F$3:$F$126, 0)</f>
         <v>8</v>
       </c>
       <c r="E3" s="17" t="n">
@@ -27754,11 +27755,11 @@
         <v>0.272727272727273</v>
       </c>
       <c r="F3" s="14" t="n">
-        <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">SUMIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Ryan", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>2.13333333333333</v>
       </c>
       <c r="G3" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D3,0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Ryan", 'Game Log Season 4'!$F$3:$F$126, 0)*-1))*D3,0)</f>
         <v>5.71666666666667</v>
       </c>
       <c r="H3" s="17" t="n">
@@ -27766,15 +27767,15 @@
         <v>0.271762208067941</v>
       </c>
       <c r="I3" s="17" t="n">
-        <f aca="false">IF(C3&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$K$3:$K$126),0)</f>
+        <f aca="false">IF(C3&lt;&gt;0,AVERAGEIF('Game Log Season 4'!$C$3:$C$126, "Ryan", 'Game Log Season 4'!$K$3:$K$126),0)</f>
         <v>0.187575757575758</v>
       </c>
       <c r="J3" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C3, 0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Ryan", 'Game Log Season 4'!$F$3:$F$126, 1)-0.5))*C3, 0)</f>
         <v>2.9415</v>
       </c>
       <c r="K3" s="14" t="n">
-        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D3, 0)</f>
+        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Ryan", 'Game Log Season 4'!$F$3:$F$126, 0)-0.5))*D3, 0)</f>
         <v>8.3075</v>
       </c>
       <c r="L3" s="17" t="n">
@@ -27791,11 +27792,11 @@
         <v>0.257655970198026</v>
       </c>
       <c r="C4" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Becca", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>2</v>
       </c>
       <c r="D4" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Becca", 'Game Log Season 4'!$F$3:$F$126, 0)</f>
         <v>5</v>
       </c>
       <c r="E4" s="17" t="n">
@@ -27803,11 +27804,11 @@
         <v>0.285714285714286</v>
       </c>
       <c r="F4" s="14" t="n">
-        <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">SUMIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Becca", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>1.5</v>
       </c>
       <c r="G4" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D4,0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Becca", 'Game Log Season 4'!$F$3:$F$126, 0)*-1))*D4,0)</f>
         <v>3.63333333333333</v>
       </c>
       <c r="H4" s="17" t="n">
@@ -27815,15 +27816,15 @@
         <v>0.292207792207792</v>
       </c>
       <c r="I4" s="17" t="n">
-        <f aca="false">IF(C4&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$K$3:$K$126),0)</f>
+        <f aca="false">IF(C4&lt;&gt;0,AVERAGEIF('Game Log Season 4'!$C$3:$C$126, "Becca", 'Game Log Season 4'!$K$3:$K$126),0)</f>
         <v>0.0771428571428572</v>
       </c>
       <c r="J4" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C4, 0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Becca", 'Game Log Season 4'!$F$3:$F$126, 1)-0.5))*C4, 0)</f>
         <v>2.15</v>
       </c>
       <c r="K4" s="14" t="n">
-        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D4, 0)</f>
+        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Becca", 'Game Log Season 4'!$F$3:$F$126, 0)-0.5))*D4, 0)</f>
         <v>4.805</v>
       </c>
       <c r="L4" s="17" t="n">
@@ -27840,11 +27841,11 @@
         <v>0.259653014766718</v>
       </c>
       <c r="C5" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Manny", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>4</v>
       </c>
       <c r="D5" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Manny", 'Game Log Season 4'!$F$3:$F$126, 0)</f>
         <v>10</v>
       </c>
       <c r="E5" s="17" t="n">
@@ -27852,11 +27853,11 @@
         <v>0.285714285714286</v>
       </c>
       <c r="F5" s="14" t="n">
-        <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">SUMIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Manny", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>2.83333333333333</v>
       </c>
       <c r="G5" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D5,0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Manny", 'Game Log Season 4'!$F$3:$F$126, 0)*-1))*D5,0)</f>
         <v>7.18333333333333</v>
       </c>
       <c r="H5" s="17" t="n">
@@ -27864,15 +27865,15 @@
         <v>0.282861896838602</v>
       </c>
       <c r="I5" s="17" t="n">
-        <f aca="false">IF(C5&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$K$3:$K$126),0)</f>
+        <f aca="false">IF(C5&lt;&gt;0,AVERAGEIF('Game Log Season 4'!$C$3:$C$126, "Manny", 'Game Log Season 4'!$K$3:$K$126),0)</f>
         <v>0.166428571428571</v>
       </c>
       <c r="J5" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C5, 0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Manny", 'Game Log Season 4'!$F$3:$F$126, 1)-0.5))*C5, 0)</f>
         <v>3.8005</v>
       </c>
       <c r="K5" s="14" t="n">
-        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D5, 0)</f>
+        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Manny", 'Game Log Season 4'!$F$3:$F$126, 0)-0.5))*D5, 0)</f>
         <v>9.628</v>
       </c>
       <c r="L5" s="17" t="n">
@@ -27889,11 +27890,11 @@
         <v>0</v>
       </c>
       <c r="C6" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Kristy", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Kristy", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>0</v>
       </c>
       <c r="D6" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Kristy", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Kristy", 'Game Log Season 4'!$F$3:$F$126, 0)</f>
         <v>2</v>
       </c>
       <c r="E6" s="17" t="n">
@@ -27901,11 +27902,11 @@
         <v>0</v>
       </c>
       <c r="F6" s="14" t="n">
-        <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Kristy", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">SUMIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Kristy", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>0</v>
       </c>
       <c r="G6" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Kristy", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D6,0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Kristy", 'Game Log Season 4'!$F$3:$F$126, 0)*-1))*D6,0)</f>
         <v>1.6</v>
       </c>
       <c r="H6" s="17" t="n">
@@ -27913,15 +27914,15 @@
         <v>0</v>
       </c>
       <c r="I6" s="17" t="n">
-        <f aca="false">IF(C6&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Kristy", 'Game Log Season 3'!$K$3:$K$126),0)</f>
+        <f aca="false">IF(C6&lt;&gt;0,AVERAGEIF('Game Log Season 4'!$C$3:$C$126, "Kristy", 'Game Log Season 4'!$K$3:$K$126),0)</f>
         <v>0</v>
       </c>
       <c r="J6" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Kristy", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C6, 0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Kristy", 'Game Log Season 4'!$F$3:$F$126, 1)-0.5))*C6, 0)</f>
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Kristy", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D6, 0)</f>
+        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Kristy", 'Game Log Season 4'!$F$3:$F$126, 0)-0.5))*D6, 0)</f>
         <v>1.955</v>
       </c>
       <c r="L6" s="17" t="n">
@@ -27938,11 +27939,11 @@
         <v>0</v>
       </c>
       <c r="C7" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Joseph", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Joseph", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>0</v>
       </c>
       <c r="D7" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Joseph", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Joseph", 'Game Log Season 4'!$F$3:$F$126, 0)</f>
         <v>1</v>
       </c>
       <c r="E7" s="17" t="n">
@@ -27950,11 +27951,11 @@
         <v>0</v>
       </c>
       <c r="F7" s="14" t="n">
-        <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Joseph", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">SUMIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Joseph", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>0</v>
       </c>
       <c r="G7" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Joseph", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D7,0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Joseph", 'Game Log Season 4'!$F$3:$F$126, 0)*-1))*D7,0)</f>
         <v>0.8</v>
       </c>
       <c r="H7" s="17" t="n">
@@ -27962,15 +27963,15 @@
         <v>0</v>
       </c>
       <c r="I7" s="17" t="n">
-        <f aca="false">IF(C7&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Joseph", 'Game Log Season 3'!$K$3:$K$126),0)</f>
+        <f aca="false">IF(C7&lt;&gt;0,AVERAGEIF('Game Log Season 4'!$C$3:$C$126, "Joseph", 'Game Log Season 4'!$K$3:$K$126),0)</f>
         <v>0</v>
       </c>
       <c r="J7" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Joseph", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C7, 0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Joseph", 'Game Log Season 4'!$F$3:$F$126, 1)-0.5))*C7, 0)</f>
         <v>0</v>
       </c>
       <c r="K7" s="14" t="n">
-        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Joseph", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D7, 0)</f>
+        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Joseph", 'Game Log Season 4'!$F$3:$F$126, 0)-0.5))*D7, 0)</f>
         <v>1.04275</v>
       </c>
       <c r="L7" s="17" t="n">
@@ -27987,11 +27988,11 @@
         <v>0</v>
       </c>
       <c r="C8" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Michelle", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Michelle", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>0</v>
       </c>
       <c r="D8" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Michelle", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Michelle", 'Game Log Season 4'!$F$3:$F$126, 0)</f>
         <v>4</v>
       </c>
       <c r="E8" s="17" t="n">
@@ -27999,11 +28000,11 @@
         <v>0</v>
       </c>
       <c r="F8" s="14" t="n">
-        <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Michelle", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">SUMIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Michelle", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>0</v>
       </c>
       <c r="G8" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Michelle", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D8,0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Michelle", 'Game Log Season 4'!$F$3:$F$126, 0)*-1))*D8,0)</f>
         <v>2.91666666666667</v>
       </c>
       <c r="H8" s="17" t="n">
@@ -28011,15 +28012,15 @@
         <v>0</v>
       </c>
       <c r="I8" s="17" t="n">
-        <f aca="false">IF(C8&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Michelle", 'Game Log Season 3'!$K$3:$K$126),0)</f>
+        <f aca="false">IF(C8&lt;&gt;0,AVERAGEIF('Game Log Season 4'!$C$3:$C$126, "Michelle", 'Game Log Season 4'!$K$3:$K$126),0)</f>
         <v>0</v>
       </c>
       <c r="J8" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Michelle", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C8, 0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Michelle", 'Game Log Season 4'!$F$3:$F$126, 1)-0.5))*C8, 0)</f>
         <v>0</v>
       </c>
       <c r="K8" s="14" t="n">
-        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Michelle", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D8, 0)</f>
+        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Michelle", 'Game Log Season 4'!$F$3:$F$126, 0)-0.5))*D8, 0)</f>
         <v>3.7465</v>
       </c>
       <c r="L8" s="17" t="n">
@@ -28036,11 +28037,11 @@
         <v>0</v>
       </c>
       <c r="C9" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Red", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Red", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>0</v>
       </c>
       <c r="D9" s="14" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Red", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
+        <f aca="false">COUNTIFS('Game Log Season 4'!$C$3:$C$126, "Red", 'Game Log Season 4'!$F$3:$F$126, 0)</f>
         <v>0</v>
       </c>
       <c r="E9" s="17" t="n">
@@ -28048,11 +28049,11 @@
         <v>0</v>
       </c>
       <c r="F9" s="14" t="n">
-        <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Red", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
+        <f aca="false">SUMIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Red", 'Game Log Season 4'!$F$3:$F$126, 1)</f>
         <v>0</v>
       </c>
       <c r="G9" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Red", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D9,0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$J$3:$J$126, 'Game Log Season 4'!$C$3:$C$126, "Red", 'Game Log Season 4'!$F$3:$F$126, 0)*-1))*D9,0)</f>
         <v>0</v>
       </c>
       <c r="H9" s="17" t="n">
@@ -28060,15 +28061,15 @@
         <v>0</v>
       </c>
       <c r="I9" s="17" t="n">
-        <f aca="false">IF(C9&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Red", 'Game Log Season 3'!$K$3:$K$126),0)</f>
+        <f aca="false">IF(C9&lt;&gt;0,AVERAGEIF('Game Log Season 4'!$C$3:$C$126, "Red", 'Game Log Season 4'!$K$3:$K$126),0)</f>
         <v>0</v>
       </c>
       <c r="J9" s="14" t="n">
-        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Red", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C9, 0)</f>
+        <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Red", 'Game Log Season 4'!$F$3:$F$126, 1)-0.5))*C9, 0)</f>
         <v>0</v>
       </c>
       <c r="K9" s="14" t="n">
-        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Red", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D9, 0)</f>
+        <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 4'!$M$3:$M$126, 'Game Log Season 4'!$C$3:$C$126, "Red", 'Game Log Season 4'!$F$3:$F$126, 0)-0.5))*D9, 0)</f>
         <v>0</v>
       </c>
       <c r="L9" s="17" t="n">
@@ -28085,4 +28086,162 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="48.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="28.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="32.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="29.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="20.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="0" width="19.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="22" style="0" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="26.78"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="X1" s="6"/>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="W2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:X34"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="W1:X1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25670,7 +25670,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.33"/>
@@ -25690,6 +25690,11 @@
       <c r="D1" s="44" t="s">
         <v>100</v>
       </c>
+      <c r="E1" s="46" t="inlineStr">
+        <is>
+          <t>Playgroup Deck ID</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="46" t="s">
@@ -25713,6 +25718,11 @@
       <c r="D3" s="48" t="n">
         <v>2.4</v>
       </c>
+      <c r="E3" s="46" t="inlineStr">
+        <is>
+          <t>560453</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="48" t="s">
@@ -25728,6 +25738,11 @@
       <c r="D4" s="48" t="n">
         <v>3.7</v>
       </c>
+      <c r="E4" s="46" t="inlineStr">
+        <is>
+          <t>560452</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
@@ -25741,6 +25756,11 @@
       <c r="D5" s="48" t="n">
         <v>2.3</v>
       </c>
+      <c r="E5" s="46" t="inlineStr">
+        <is>
+          <t>648625</t>
+        </is>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="48" t="s">
@@ -25777,6 +25797,11 @@
       <c r="D8" s="48" t="n">
         <v>3.8</v>
       </c>
+      <c r="E8" s="46" t="inlineStr">
+        <is>
+          <t>626865</t>
+        </is>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
@@ -25790,6 +25815,11 @@
       <c r="D9" s="48" t="n">
         <v>3.9</v>
       </c>
+      <c r="E9" s="46" t="inlineStr">
+        <is>
+          <t>626866</t>
+        </is>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="48" t="s">
@@ -25805,6 +25835,11 @@
       <c r="D10" s="48" t="n">
         <v>3.4</v>
       </c>
+      <c r="E10" s="46" t="inlineStr">
+        <is>
+          <t>626503</t>
+        </is>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
@@ -25818,6 +25853,11 @@
       <c r="D11" s="48" t="n">
         <v>2.6</v>
       </c>
+      <c r="E11" s="46" t="inlineStr">
+        <is>
+          <t>614179</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="48" t="s">
@@ -25833,6 +25873,11 @@
       <c r="D12" s="48" t="n">
         <v>3.5</v>
       </c>
+      <c r="E12" s="46" t="inlineStr">
+        <is>
+          <t>560532</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
@@ -25846,6 +25891,11 @@
       <c r="D13" s="48" t="n">
         <v>2.7</v>
       </c>
+      <c r="E13" s="46" t="inlineStr">
+        <is>
+          <t>695274</t>
+        </is>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="48" t="s">
@@ -25859,6 +25909,11 @@
       <c r="D14" s="48" t="n">
         <v>2.6</v>
       </c>
+      <c r="E14" s="46" t="inlineStr">
+        <is>
+          <t>703425</t>
+        </is>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
@@ -25872,6 +25927,11 @@
       <c r="D15" s="48" t="n">
         <v>3.9</v>
       </c>
+      <c r="E15" s="46" t="inlineStr">
+        <is>
+          <t>560534</t>
+        </is>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="48" t="s">
@@ -25885,6 +25945,11 @@
       <c r="D16" s="48" t="n">
         <v>2.3</v>
       </c>
+      <c r="E16" s="46" t="inlineStr">
+        <is>
+          <t>713019</t>
+        </is>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
@@ -25898,6 +25963,11 @@
       <c r="D17" s="48" t="n">
         <v>3.5</v>
       </c>
+      <c r="E17" s="46" t="inlineStr">
+        <is>
+          <t>560535</t>
+        </is>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="46" t="s">
@@ -25921,6 +25991,11 @@
       <c r="D19" s="48" t="n">
         <v>2.4</v>
       </c>
+      <c r="E19" s="46" t="inlineStr">
+        <is>
+          <t>639396</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
@@ -25934,6 +26009,11 @@
       <c r="D20" s="48" t="n">
         <v>2.6</v>
       </c>
+      <c r="E20" s="46" t="inlineStr">
+        <is>
+          <t>614175</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="48" t="s">
@@ -25947,6 +26027,11 @@
       <c r="D21" s="48" t="n">
         <v>3.6</v>
       </c>
+      <c r="E21" s="46" t="inlineStr">
+        <is>
+          <t>560454</t>
+        </is>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="48" t="s">
@@ -25960,6 +26045,11 @@
       <c r="D22" s="48" t="n">
         <v>3.6</v>
       </c>
+      <c r="E22" s="46" t="inlineStr">
+        <is>
+          <t>614174</t>
+        </is>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="48" t="s">
@@ -25973,6 +26063,11 @@
       <c r="D23" s="48" t="n">
         <v>2.9</v>
       </c>
+      <c r="E23" s="46" t="inlineStr">
+        <is>
+          <t>648623</t>
+        </is>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="48" t="s">
@@ -25988,6 +26083,11 @@
       <c r="D24" s="48" t="n">
         <v>3.9</v>
       </c>
+      <c r="E24" s="46" t="inlineStr">
+        <is>
+          <t>588726</t>
+        </is>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="48" t="s">
@@ -26014,6 +26114,11 @@
       <c r="D26" s="48" t="n">
         <v>2.6</v>
       </c>
+      <c r="E26" s="46" t="inlineStr">
+        <is>
+          <t>671540</t>
+        </is>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="48" t="s">
@@ -26029,6 +26134,11 @@
       <c r="D27" s="48" t="n">
         <v>3.6</v>
       </c>
+      <c r="E27" s="46" t="inlineStr">
+        <is>
+          <t>677158</t>
+        </is>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="48" t="s">
@@ -26042,6 +26152,11 @@
       <c r="D28" s="48" t="n">
         <v>3.9</v>
       </c>
+      <c r="E28" s="46" t="inlineStr">
+        <is>
+          <t>560457</t>
+        </is>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="48" t="s">
@@ -26055,6 +26170,11 @@
       <c r="D29" s="48" t="n">
         <v>3.7</v>
       </c>
+      <c r="E29" s="46" t="inlineStr">
+        <is>
+          <t>710932</t>
+        </is>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="48" t="s">
@@ -26068,6 +26188,11 @@
       <c r="D30" s="49" t="n">
         <v>4</v>
       </c>
+      <c r="E30" s="46" t="inlineStr">
+        <is>
+          <t>566516</t>
+        </is>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="48" t="s">
@@ -26081,6 +26206,11 @@
       <c r="D31" s="49" t="n">
         <v>2.9</v>
       </c>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>743882</t>
+        </is>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="48" t="s">
@@ -26096,6 +26226,11 @@
       <c r="D32" s="49" t="n">
         <v>3.9</v>
       </c>
+      <c r="E32" s="46" t="inlineStr">
+        <is>
+          <t>566515</t>
+        </is>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="46" t="s">
@@ -26119,6 +26254,11 @@
       <c r="D34" s="48" t="n">
         <v>3.5</v>
       </c>
+      <c r="E34" s="46" t="inlineStr">
+        <is>
+          <t>560264</t>
+        </is>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="48" t="s">
@@ -26132,6 +26272,11 @@
       <c r="D35" s="48" t="n">
         <v>3.4</v>
       </c>
+      <c r="E35" s="46" t="inlineStr">
+        <is>
+          <t>601033</t>
+        </is>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
@@ -26145,6 +26290,11 @@
       <c r="D36" s="48" t="n">
         <v>3.7</v>
       </c>
+      <c r="E36" s="46" t="inlineStr">
+        <is>
+          <t>560262</t>
+        </is>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="48" t="s">
@@ -26158,6 +26308,11 @@
       <c r="D37" s="48" t="n">
         <v>2.6</v>
       </c>
+      <c r="E37" s="46" t="inlineStr">
+        <is>
+          <t>601032</t>
+        </is>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
@@ -26171,6 +26326,11 @@
       <c r="D38" s="48" t="n">
         <v>3.8</v>
       </c>
+      <c r="E38" s="46" t="inlineStr">
+        <is>
+          <t>560261</t>
+        </is>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="48" t="s">
@@ -26184,6 +26344,11 @@
       <c r="D39" s="48" t="n">
         <v>2.6</v>
       </c>
+      <c r="E39" s="46" t="inlineStr">
+        <is>
+          <t>659612</t>
+        </is>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="48" t="s">
@@ -26197,6 +26362,11 @@
       <c r="D40" s="48" t="n">
         <v>3.6</v>
       </c>
+      <c r="E40" s="46" t="inlineStr">
+        <is>
+          <t>560263</t>
+        </is>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="48" t="s">
@@ -26210,6 +26380,11 @@
       <c r="D41" s="48" t="n">
         <v>2.6</v>
       </c>
+      <c r="E41" s="46" t="inlineStr">
+        <is>
+          <t>693262</t>
+        </is>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="48" t="s">
@@ -26236,6 +26411,11 @@
       <c r="D43" s="48" t="n">
         <v>2.9</v>
       </c>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>744133</t>
+        </is>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="48" t="s">
@@ -26249,6 +26429,11 @@
       <c r="D44" s="48" t="n">
         <v>3.9</v>
       </c>
+      <c r="E44" s="46" t="inlineStr">
+        <is>
+          <t>744134</t>
+        </is>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="46" t="s">
@@ -26428,6 +26613,11 @@
       <c r="D58" s="48" t="n">
         <v>2.7</v>
       </c>
+      <c r="E58" s="46" t="inlineStr">
+        <is>
+          <t>595027</t>
+        </is>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="48" t="s">
@@ -26441,6 +26631,11 @@
       <c r="D59" s="48" t="n">
         <v>3.4</v>
       </c>
+      <c r="E59" s="46" t="inlineStr">
+        <is>
+          <t>629604</t>
+        </is>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="48" t="s">
@@ -26454,6 +26649,11 @@
       <c r="D60" s="49" t="n">
         <v>1</v>
       </c>
+      <c r="E60" s="46" t="inlineStr">
+        <is>
+          <t>682763</t>
+        </is>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="46" t="s">
@@ -26489,6 +26689,11 @@
       <c r="C63" s="45"/>
       <c r="D63" s="48" t="n">
         <v>2.2</v>
+      </c>
+      <c r="E63" s="46" t="inlineStr">
+        <is>
+          <t>576574</t>
+        </is>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25781,7 +25781,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -25810,7 +25810,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="48" t="n">
-        <f aca="false">AVERAGE(B3:B6)</f>
+        <f aca="false">AVERAGE(B3:B7)</f>
         <v>2.72288194444444</v>
       </c>
       <c r="C2" s="46"/>
@@ -25878,864 +25878,932 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>ZZ Test Deck With ID</t>
+        </is>
+      </c>
+      <c r="B7" s="49">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
+        <v>2.9</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="49">
+        <v>2.9</v>
+      </c>
+      <c r="E7" s="47" t="inlineStr">
+        <is>
+          <t>999002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="48" t="n">
-        <f aca="false">AVERAGE(B8:B17)</f>
+      <c r="B8" s="48" t="n">
+        <f aca="false">AVERAGE(B9:B18)</f>
         <v>3.28381944444444</v>
       </c>
-      <c r="C7" s="46"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A8)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D8)</f>
-        <v>3.83916666666667</v>
-      </c>
       <c r="C8" s="46"/>
-      <c r="D8" s="49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B9" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A9)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D9)</f>
-        <v>3.9</v>
+        <v>3.83916666666667</v>
       </c>
       <c r="C9" s="46"/>
       <c r="D9" s="49" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="49" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B10" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A10)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D10)</f>
-        <v>3.4</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>108</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="C10" s="46"/>
       <c r="D10" s="49" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B11" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A11)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D11)</f>
-        <v>2.6</v>
-      </c>
-      <c r="C11" s="46"/>
+        <v>3.4</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>108</v>
+      </c>
       <c r="D11" s="49" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="49" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B12" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A12)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D12)</f>
-        <v>3.5</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="C12" s="46"/>
       <c r="D12" s="49" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B13" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A13)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D13)</f>
-        <v>2.65388888888889</v>
-      </c>
-      <c r="C13" s="46"/>
+        <v>3.5</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D13" s="49" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B14" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A14)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D14)</f>
-        <v>2.6</v>
+        <v>2.65388888888889</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="49" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A15)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D15)</f>
-        <v>3.91083333333333</v>
+        <v>2.6</v>
       </c>
       <c r="C15" s="46"/>
       <c r="D15" s="49" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="B16" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A16)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D16)</f>
-        <v>2.94083333333333</v>
+        <v>3.91083333333333</v>
       </c>
       <c r="C16" s="46"/>
       <c r="D16" s="49" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B17" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A17)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D17)</f>
-        <v>3.49347222222222</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C17" s="46"/>
       <c r="D17" s="49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
+        <v>3.49347222222222</v>
+      </c>
+      <c r="C18" s="46"/>
+      <c r="D18" s="49" t="n">
         <v>3.5</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E18" s="47" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="48" t="n">
-        <f aca="false">AVERAGE(B19:B32)</f>
+      <c r="B19" s="48" t="n">
+        <f aca="false">AVERAGE(B20:B33)</f>
         <v>3.31464285714286</v>
       </c>
-      <c r="C18" s="46"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
-        <v>2.4</v>
-      </c>
       <c r="C19" s="46"/>
-      <c r="D19" s="49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="49" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
-        <v>3.57402777777778</v>
+        <v>2.6</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
-        <v>3.6</v>
+        <v>3.57402777777778</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="49" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="C24" s="46"/>
       <c r="D24" s="49" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
-        <v>2.8</v>
-      </c>
-      <c r="C25" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D25" s="49" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>123</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
-        <v>3.59875</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>124</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="C27" s="46"/>
       <c r="D27" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
-        <v>3.94083333333333</v>
-      </c>
-      <c r="C28" s="46"/>
+        <v>3.59875</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>124</v>
+      </c>
       <c r="D28" s="49" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>3.65388888888889</v>
+        <v>3.94083333333333</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="49" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="50" t="n">
+        <v>90</v>
+      </c>
+      <c r="B30" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
-        <v>3.95583333333333</v>
+        <v>3.65388888888889</v>
       </c>
       <c r="C30" s="46"/>
-      <c r="D30" s="50" t="n">
-        <v>4</v>
+      <c r="D30" s="49" t="n">
+        <v>3.7</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B31" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
-        <v>2.94666666666667</v>
+        <v>3.95583333333333</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="50" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B32" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
+        <v>2.94666666666667</v>
+      </c>
+      <c r="C32" s="46"/>
+      <c r="D32" s="50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
         <v>3.935</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C33" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="50" t="n">
+      <c r="D33" s="50" t="n">
         <v>3.9</v>
       </c>
-      <c r="E32" s="47" t="s">
+      <c r="E33" s="47" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="47" t="s">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="48" t="n">
-        <f aca="false">AVERAGE(B34:B44)</f>
+      <c r="B34" s="48" t="n">
+        <f aca="false">AVERAGE(B35:B45)</f>
         <v>3.26275505050505</v>
       </c>
-      <c r="C33" s="46"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
-        <v>3.5</v>
-      </c>
       <c r="C34" s="46"/>
-      <c r="D34" s="49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>132</v>
-      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
-        <v>3.43088888888889</v>
+        <v>3.5</v>
       </c>
       <c r="C35" s="46"/>
       <c r="D35" s="49" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.7</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="49" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="49" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>3.77816666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C38" s="46"/>
       <c r="D38" s="49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>2.59388888888889</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>3.23902777777778</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C40" s="46"/>
       <c r="D40" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>2.6</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C41" s="46"/>
       <c r="D41" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>3.58416666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>2.94083333333333</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E43" s="47" t="s">
-        <v>140</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>3.92333333333333</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
+        <v>3.92333333333333</v>
+      </c>
+      <c r="C45" s="46"/>
+      <c r="D45" s="49" t="n">
         <v>3.9</v>
       </c>
-      <c r="E44" s="47" t="s">
+      <c r="E45" s="47" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="s">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="48" t="n">
-        <f aca="false">AVERAGE(B46:B50)</f>
+      <c r="B46" s="48" t="n">
+        <f aca="false">AVERAGE(B47:B51)</f>
         <v>3.2865</v>
       </c>
-      <c r="C45" s="46"/>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
-        <v>3.6</v>
-      </c>
-      <c r="C46" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" s="49" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="C46" s="46"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.33761111111111</v>
+        <v>3.6</v>
       </c>
       <c r="C47" s="46" t="s">
         <v>124</v>
       </c>
       <c r="D47" s="49" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C48" s="46"/>
+        <v>3.33761111111111</v>
+      </c>
+      <c r="C48" s="46" t="s">
+        <v>124</v>
+      </c>
       <c r="D48" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C49" s="46" t="s">
-        <v>130</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C49" s="46"/>
       <c r="D49" s="49" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C50" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="49" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
         <v>2.39488888888889</v>
       </c>
-      <c r="C50" s="46"/>
-      <c r="D50" s="49" t="n">
+      <c r="C51" s="46"/>
+      <c r="D51" s="49" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47" t="s">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="48" t="n">
-        <f aca="false">AVERAGE(B52:B56)</f>
+      <c r="B52" s="48" t="n">
+        <f aca="false">AVERAGE(B53:B57)</f>
         <v>3.42807</v>
       </c>
-      <c r="C51" s="46"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
-        <v>3.6</v>
-      </c>
       <c r="C52" s="46"/>
-      <c r="D52" s="49" t="n">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="C53" s="46"/>
       <c r="D53" s="49" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="C54" s="46"/>
       <c r="D54" s="49" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="C55" s="46"/>
       <c r="D55" s="49" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.74035</v>
+        <v>3.3</v>
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="49" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
+        <v>3.74035</v>
+      </c>
+      <c r="C57" s="46"/>
+      <c r="D57" s="49" t="n">
         <v>3.7</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="s">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="48" t="n">
-        <f aca="false">AVERAGE(B58:B59)</f>
+      <c r="B58" s="48" t="n">
+        <f aca="false">AVERAGE(B59:B60)</f>
         <v>3.05</v>
       </c>
-      <c r="C57" s="46"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
-        <v>2.7</v>
-      </c>
       <c r="C58" s="46"/>
-      <c r="D58" s="49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E58" s="47" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="49" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
+        <v>3.4</v>
+      </c>
+      <c r="C60" s="46"/>
+      <c r="D60" s="49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E60" s="47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B60" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>1</v>
-      </c>
-      <c r="C60" s="46"/>
-      <c r="D60" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="47" t="s">
+      <c r="B61" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
+        <v>1</v>
+      </c>
+      <c r="C61" s="46"/>
+      <c r="D61" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="47" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">AVERAGE(B62:B63)</f>
+      <c r="B62" s="48" t="n">
+        <f aca="false">AVERAGE(B63:B64)</f>
         <v>2.25194444444444</v>
       </c>
-      <c r="C61" s="46"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
-        <v>2.30388888888889</v>
-      </c>
       <c r="C62" s="46"/>
-      <c r="D62" s="49" t="n">
-        <v>2.5</v>
-      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>2.2</v>
+        <v>2.30388888888889</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E63" s="47" t="s">
-        <v>145</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
+        <v>2.2</v>
+      </c>
+      <c r="C64" s="46"/>
+      <c r="D64" s="49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E64" s="47" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
         <v>2.43069444444444</v>
       </c>
-      <c r="D64" s="49" t="n">
+      <c r="D65" s="49" t="n">
         <v>2.4</v>
       </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="47" t="inlineStr">
+        <is>
+          <t>ZZTestPlayer2</t>
+        </is>
+      </c>
+      <c r="B66" s="48">
+        <f>AVERAGE(B67:B68)</f>
+        <v>2.85</v>
+      </c>
+      <c r="C66" s="46"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="49" t="inlineStr">
+        <is>
+          <t>Test Commander A</t>
+        </is>
+      </c>
+      <c r="B67" s="49">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer2")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
+        <v>3</v>
+      </c>
+      <c r="C67" s="46"/>
+      <c r="D67" s="49">
+        <v>3</v>
+      </c>
+      <c r="E67" s="47" t="inlineStr">
+        <is>
+          <t>999001</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="49" t="inlineStr">
+        <is>
+          <t>Test Commander B</t>
+        </is>
+      </c>
+      <c r="B68" s="49">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer2")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
+        <v>2.7</v>
+      </c>
+      <c r="C68" s="46"/>
+      <c r="D68" s="49">
+        <v>2.7</v>
+      </c>
+      <c r="E68" s="47"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -26753,7 +26821,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26861,60 +26929,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>ZZ Test Deck With ID</t>
+        </is>
+      </c>
+      <c r="B7" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="49">
+        <f>IFERROR(C7/B7,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7)</f>
+      <c r="B8" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8)</f>
         <v>14</v>
       </c>
-      <c r="C7" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+      <c r="C8" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>4</v>
       </c>
-      <c r="D7" s="48" t="n">
-        <f aca="false">IFERROR(C7/B7,0)</f>
+      <c r="D8" s="48" t="n">
+        <f aca="false">IFERROR(C8/B8,0)</f>
         <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8)</f>
-        <v>4</v>
-      </c>
-      <c r="C8" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
-      </c>
-      <c r="D8" s="49" t="n">
-        <f aca="false">IFERROR(C8/B8,0)</f>
-        <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B9" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="49" t="n">
         <f aca="false">IFERROR(C9/B9,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="49" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B10" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A10)</f>
@@ -26931,7 +27001,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B11" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A11)</f>
@@ -26948,7 +27018,7 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="49" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B12" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A12)</f>
@@ -26965,11 +27035,11 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B13" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -26982,11 +27052,11 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B14" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -26999,28 +27069,28 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="49" t="n">
         <f aca="false">IFERROR(C15/B15,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="B16" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C16" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27028,63 +27098,63 @@
       </c>
       <c r="D16" s="49" t="n">
         <f aca="false">IFERROR(C16/B16,0)</f>
-        <v>0.166666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B17" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="49" t="n">
         <f aca="false">IFERROR(C17/B17,0)</f>
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
+        <v>1</v>
+      </c>
+      <c r="C18" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="49" t="n">
+        <f aca="false">IFERROR(C18/B18,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
+      <c r="B19" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19)</f>
         <v>12</v>
       </c>
-      <c r="C18" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+      <c r="C19" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>5</v>
       </c>
-      <c r="D18" s="48" t="n">
-        <f aca="false">IFERROR(C18/B18,0)</f>
+      <c r="D19" s="48" t="n">
+        <f aca="false">IFERROR(C19/B19,0)</f>
         <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="49" t="n">
-        <f aca="false">IFERROR(C19/B19,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -27101,11 +27171,11 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27118,11 +27188,11 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27135,7 +27205,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
@@ -27152,7 +27222,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
@@ -27169,7 +27239,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
@@ -27186,7 +27256,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
@@ -27203,11 +27273,11 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27220,7 +27290,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
@@ -27228,122 +27298,122 @@
       </c>
       <c r="C28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="49" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="49" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="B30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="49" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="49" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="49" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
+        <v>1</v>
+      </c>
+      <c r="C33" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D33" s="49" t="n">
+        <f aca="false">IFERROR(C33/B33,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
+      <c r="B34" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34)</f>
         <v>11</v>
       </c>
-      <c r="C33" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D33" s="48" t="n">
-        <f aca="false">IFERROR(C33/B33,0)</f>
+      <c r="C34" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D34" s="48" t="n">
+        <f aca="false">IFERROR(C34/B34,0)</f>
         <v>0.272727272727273</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="49" t="n">
-        <f aca="false">IFERROR(C34/B34,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27356,11 +27426,11 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27373,7 +27443,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
@@ -27390,24 +27460,24 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="49" t="n">
         <f aca="false">IFERROR(C38/B38,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
@@ -27415,20 +27485,20 @@
       </c>
       <c r="C39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" s="49" t="n">
         <f aca="false">IFERROR(C39/B39,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27441,11 +27511,11 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27458,11 +27528,11 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27475,7 +27545,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
@@ -27483,16 +27553,16 @@
       </c>
       <c r="C43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="49" t="n">
         <f aca="false">IFERROR(C43/B43,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
@@ -27508,46 +27578,46 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="s">
+      <c r="A45" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
+        <v>2</v>
+      </c>
+      <c r="C45" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="49" t="n">
+        <f aca="false">IFERROR(C45/B45,0)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
-        <v>2</v>
-      </c>
-      <c r="C45" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="48" t="n">
-        <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
-        <v>0</v>
-      </c>
-      <c r="C46" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="49" t="n">
+      <c r="B46" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46)</f>
+        <v>2</v>
+      </c>
+      <c r="C46" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="48" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27560,11 +27630,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27577,7 +27647,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
@@ -27594,11 +27664,11 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27610,42 +27680,42 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47" t="s">
+      <c r="A51" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="49" t="n">
+        <f aca="false">IFERROR(C51/B51,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="48" t="n">
-        <f aca="false">IFERROR(C51/B51,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
-        <v>0</v>
-      </c>
-      <c r="C52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="49" t="n">
+      <c r="B52" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52)</f>
+        <v>1</v>
+      </c>
+      <c r="C52" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="48" t="n">
         <f aca="false">IFERROR(C52/B52,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -27662,7 +27732,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -27679,7 +27749,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
@@ -27696,11 +27766,11 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27712,42 +27782,42 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="s">
+      <c r="A57" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
+        <v>1</v>
+      </c>
+      <c r="C57" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="49" t="n">
+        <f aca="false">IFERROR(C57/B57,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
-        <v>0</v>
-      </c>
-      <c r="C57" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="48" t="n">
-        <f aca="false">IFERROR(C57/B57,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
-        <v>0</v>
-      </c>
-      <c r="C58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="49" t="n">
+      <c r="B58" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58)</f>
+        <v>0</v>
+      </c>
+      <c r="C58" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="48" t="n">
         <f aca="false">IFERROR(C58/B58,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
@@ -27764,7 +27834,7 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B60" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
@@ -27780,46 +27850,46 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
+      <c r="A61" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="49" t="n">
+        <f aca="false">IFERROR(C61/B61,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+      <c r="B62" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62)</f>
         <v>4</v>
       </c>
-      <c r="C61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="48" t="n">
-        <f aca="false">IFERROR(C61/B61,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
-        <v>3</v>
-      </c>
-      <c r="C62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="49" t="n">
+      <c r="C62" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="48" t="n">
         <f aca="false">IFERROR(C62/B62,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27832,11 +27902,11 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27844,6 +27914,80 @@
       </c>
       <c r="D64" s="49" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
+        <v>1</v>
+      </c>
+      <c r="C65" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="49" t="n">
+        <f aca="false">IFERROR(C65/B65,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="47" t="inlineStr">
+        <is>
+          <t>ZZTestPlayer2</t>
+        </is>
+      </c>
+      <c r="B66" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
+        <v>0</v>
+      </c>
+      <c r="C66" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="48">
+        <f>IFERROR(C66/B66,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="49" t="inlineStr">
+        <is>
+          <t>Test Commander A</t>
+        </is>
+      </c>
+      <c r="B67" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="49">
+        <f>IFERROR(C67/B67,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="49" t="inlineStr">
+        <is>
+          <t>Test Commander B</t>
+        </is>
+      </c>
+      <c r="B68" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="49">
+        <f>IFERROR(C68/B68,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="167">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -350,6 +350,12 @@
     <t xml:space="preserve">648625</t>
   </si>
   <si>
+    <t xml:space="preserve">ZZ Test Deck With ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">999002</t>
+  </si>
+  <si>
     <t xml:space="preserve">626865</t>
   </si>
   <si>
@@ -468,6 +474,18 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZZTestPlayer2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Commander A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">999001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Commander B</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -25811,7 +25829,7 @@
       </c>
       <c r="B2" s="48" t="n">
         <f aca="false">AVERAGE(B3:B7)</f>
-        <v>2.72288194444444</v>
+        <v>2.75830555555556</v>
       </c>
       <c r="C2" s="46"/>
     </row>
@@ -25878,24 +25896,20 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="49" t="inlineStr">
-        <is>
-          <t>ZZ Test Deck With ID</t>
-        </is>
-      </c>
-      <c r="B7" s="49">
-        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
         <v>2.9</v>
       </c>
       <c r="C7" s="46"/>
-      <c r="D7" s="49">
+      <c r="D7" s="49" t="n">
         <v>2.9</v>
       </c>
-      <c r="E7" s="47" t="inlineStr">
-        <is>
-          <t>999002</t>
-        </is>
+      <c r="E7" s="47" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25921,7 +25935,7 @@
         <v>3.8</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25937,7 +25951,7 @@
         <v>3.9</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25949,13 +25963,13 @@
         <v>3.4</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D11" s="49" t="n">
         <v>3.4</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25971,7 +25985,7 @@
         <v>2.6</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25989,7 +26003,7 @@
         <v>3.5</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26005,7 +26019,7 @@
         <v>2.7</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26021,7 +26035,7 @@
         <v>2.6</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26037,7 +26051,7 @@
         <v>3.9</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26053,7 +26067,7 @@
         <v>2.3</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26069,7 +26083,7 @@
         <v>3.5</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26095,7 +26109,7 @@
         <v>2.4</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26111,7 +26125,7 @@
         <v>2.6</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26127,7 +26141,7 @@
         <v>3.6</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26143,7 +26157,7 @@
         <v>3.6</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26159,7 +26173,7 @@
         <v>2.9</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26177,7 +26191,7 @@
         <v>3.9</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26206,7 +26220,7 @@
         <v>2.6</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26218,13 +26232,13 @@
         <v>3.59875</v>
       </c>
       <c r="C28" s="46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D28" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26240,7 +26254,7 @@
         <v>3.9</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26256,7 +26270,7 @@
         <v>3.7</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26272,7 +26286,7 @@
         <v>4</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26288,7 +26302,7 @@
         <v>2.9</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26300,13 +26314,13 @@
         <v>3.935</v>
       </c>
       <c r="C33" s="46" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D33" s="50" t="n">
         <v>3.9</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26332,7 +26346,7 @@
         <v>3.5</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26348,7 +26362,7 @@
         <v>3.4</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26364,7 +26378,7 @@
         <v>3.7</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26380,7 +26394,7 @@
         <v>2.6</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26396,7 +26410,7 @@
         <v>3.8</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26412,7 +26426,7 @@
         <v>2.6</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26428,7 +26442,7 @@
         <v>3.6</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26444,7 +26458,7 @@
         <v>2.6</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26473,7 +26487,7 @@
         <v>2.9</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26489,7 +26503,7 @@
         <v>3.9</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26511,7 +26525,7 @@
         <v>3.6</v>
       </c>
       <c r="C47" s="46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D47" s="49" t="n">
         <v>3.6</v>
@@ -26526,7 +26540,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C48" s="46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D48" s="49" t="n">
         <v>3.3</v>
@@ -26554,7 +26568,7 @@
         <v>3.9</v>
       </c>
       <c r="C50" s="46" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D50" s="49" t="n">
         <v>3.9</v>
@@ -26671,7 +26685,7 @@
         <v>2.7</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26687,7 +26701,7 @@
         <v>3.4</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26703,7 +26717,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="47" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26742,7 +26756,7 @@
         <v>2.2</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26757,50 +26771,42 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="47" t="inlineStr">
-        <is>
-          <t>ZZTestPlayer2</t>
-        </is>
-      </c>
-      <c r="B66" s="48">
-        <f>AVERAGE(B67:B68)</f>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="48" t="n">
+        <f aca="false">AVERAGE(B67:B68)</f>
         <v>2.85</v>
       </c>
       <c r="C66" s="46"/>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="49" t="inlineStr">
-        <is>
-          <t>Test Commander A</t>
-        </is>
-      </c>
-      <c r="B67" s="49">
-        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer2")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer2")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
         <v>3</v>
       </c>
       <c r="C67" s="46"/>
-      <c r="D67" s="49">
-        <v>3</v>
-      </c>
-      <c r="E67" s="47" t="inlineStr">
-        <is>
-          <t>999001</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="49" t="inlineStr">
-        <is>
-          <t>Test Commander B</t>
-        </is>
-      </c>
-      <c r="B68" s="49">
-        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer2")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
+      <c r="D67" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" s="47" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="B68" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer2")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
         <v>2.7</v>
       </c>
       <c r="C68" s="46"/>
-      <c r="D68" s="49">
+      <c r="D68" s="49" t="n">
         <v>2.7</v>
       </c>
       <c r="E68" s="47"/>
@@ -26832,16 +26838,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26929,22 +26935,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="49" t="inlineStr">
-        <is>
-          <t>ZZ Test Deck With ID</t>
-        </is>
-      </c>
-      <c r="B7" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7)</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="49">
-        <f>IFERROR(C7/B7,0)</f>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="49" t="n">
+        <f aca="false">IFERROR(C7/B7,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -27934,60 +27938,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="47" t="inlineStr">
-        <is>
-          <t>ZZTestPlayer2</t>
-        </is>
-      </c>
-      <c r="B66" s="48">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
-        <v>0</v>
-      </c>
-      <c r="C66" s="48">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="48">
-        <f>IFERROR(C66/B66,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="49" t="inlineStr">
-        <is>
-          <t>Test Commander A</t>
-        </is>
-      </c>
-      <c r="B67" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="49">
-        <f>IFERROR(C67/B67,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="49" t="inlineStr">
-        <is>
-          <t>Test Commander B</t>
-        </is>
-      </c>
-      <c r="B68" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
-        <v>0</v>
-      </c>
-      <c r="C68" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="49">
-        <f>IFERROR(C68/B68,0)</f>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
+        <v>0</v>
+      </c>
+      <c r="C66" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="48" t="n">
+        <f aca="false">IFERROR(C66/B66,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="49" t="n">
+        <f aca="false">IFERROR(C67/B67,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="B68" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="49" t="n">
+        <f aca="false">IFERROR(C68/B68,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -28026,40 +28024,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F1" s="51" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="161">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -350,12 +350,6 @@
     <t xml:space="preserve">648625</t>
   </si>
   <si>
-    <t xml:space="preserve">ZZ Test Deck With ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">999002</t>
-  </si>
-  <si>
     <t xml:space="preserve">626865</t>
   </si>
   <si>
@@ -474,18 +468,6 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZZTestPlayer2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Commander A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">999001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Commander B</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -25799,7 +25781,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -25828,8 +25810,8 @@
         <v>26</v>
       </c>
       <c r="B2" s="48" t="n">
-        <f aca="false">AVERAGE(B3:B7)</f>
-        <v>2.75830555555556</v>
+        <f aca="false">AVERAGE(B3:B6)</f>
+        <v>2.72288194444444</v>
       </c>
       <c r="C2" s="46"/>
     </row>
@@ -25897,327 +25879,329 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
+      <c r="A7" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="48" t="n">
+        <f aca="false">AVERAGE(B8:B17)</f>
+        <v>3.28381944444444</v>
+      </c>
+      <c r="C7" s="46"/>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A8)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D8)</f>
+        <v>3.83916666666667</v>
+      </c>
+      <c r="C8" s="46"/>
+      <c r="D8" s="49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E8" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
-        <v>2.9</v>
-      </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E7" s="47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="48" t="n">
-        <f aca="false">AVERAGE(B9:B18)</f>
-        <v>3.28381944444444</v>
-      </c>
-      <c r="C8" s="46"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="B9" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A9)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D9)</f>
-        <v>3.83916666666667</v>
+        <v>3.9</v>
       </c>
       <c r="C9" s="46"/>
       <c r="D9" s="49" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="49" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B10" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A10)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D10)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C10" s="46"/>
+        <v>3.4</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>108</v>
+      </c>
       <c r="D10" s="49" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="E10" s="47" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B11" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A11)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D11)</f>
-        <v>3.4</v>
-      </c>
-      <c r="C11" s="46" t="s">
+        <v>2.6</v>
+      </c>
+      <c r="C11" s="46"/>
+      <c r="D11" s="49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E11" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="49" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B12" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A12)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D12)</f>
-        <v>2.6</v>
-      </c>
-      <c r="C12" s="46"/>
+        <v>3.5</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D12" s="49" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="B13" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A13)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D13)</f>
-        <v>3.5</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.65388888888889</v>
+      </c>
+      <c r="C13" s="46"/>
       <c r="D13" s="49" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B14" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A14)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D14)</f>
-        <v>2.65388888888889</v>
+        <v>2.6</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="49" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B15" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A15)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D15)</f>
-        <v>2.6</v>
+        <v>3.91083333333333</v>
       </c>
       <c r="C15" s="46"/>
       <c r="D15" s="49" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="B16" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A16)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D16)</f>
-        <v>3.91083333333333</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C16" s="46"/>
       <c r="D16" s="49" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B17" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A17)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D17)</f>
-        <v>2.94083333333333</v>
+        <v>3.49347222222222</v>
       </c>
       <c r="C17" s="46"/>
       <c r="D17" s="49" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="E17" s="47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="48" t="n">
+        <f aca="false">AVERAGE(B19:B32)</f>
+        <v>3.31464285714286</v>
+      </c>
+      <c r="C18" s="46"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
+        <v>2.4</v>
+      </c>
+      <c r="C19" s="46"/>
+      <c r="D19" s="49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E19" s="47" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
-        <v>3.49347222222222</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="48" t="n">
-        <f aca="false">AVERAGE(B20:B33)</f>
-        <v>3.31464285714286</v>
-      </c>
-      <c r="C19" s="46"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="49" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
-        <v>2.6</v>
+        <v>3.57402777777778</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
-        <v>3.57402777777778</v>
+        <v>3.6</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
-        <v>2.9</v>
-      </c>
-      <c r="C24" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D24" s="49" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C25" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="C25" s="46"/>
       <c r="D25" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>124</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="49" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
-        <v>2.6</v>
-      </c>
-      <c r="C27" s="46"/>
+        <v>3.59875</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>124</v>
+      </c>
       <c r="D27" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E27" s="47" t="s">
         <v>125</v>
@@ -26225,591 +26209,533 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
-        <v>3.59875</v>
-      </c>
-      <c r="C28" s="46" t="s">
+        <v>3.94083333333333</v>
+      </c>
+      <c r="C28" s="46"/>
+      <c r="D28" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E28" s="47" t="s">
         <v>126</v>
-      </c>
-      <c r="D28" s="49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>3.94083333333333</v>
+        <v>3.65388888888889</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="49" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="49" t="n">
+        <v>46</v>
+      </c>
+      <c r="B30" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
-        <v>3.65388888888889</v>
+        <v>3.95583333333333</v>
       </c>
       <c r="C30" s="46"/>
-      <c r="D30" s="49" t="n">
-        <v>3.7</v>
+      <c r="D30" s="50" t="n">
+        <v>4</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B31" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
-        <v>3.95583333333333</v>
+        <v>2.94666666666667</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="50" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B32" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
-        <v>2.94666666666667</v>
-      </c>
-      <c r="C32" s="46"/>
+        <v>3.935</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>130</v>
+      </c>
       <c r="D32" s="50" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E32" s="47" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
-        <v>3.935</v>
-      </c>
-      <c r="C33" s="46" t="s">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="48" t="n">
+        <f aca="false">AVERAGE(B34:B44)</f>
+        <v>3.26275505050505</v>
+      </c>
+      <c r="C33" s="46"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
+        <v>3.5</v>
+      </c>
+      <c r="C34" s="46"/>
+      <c r="D34" s="49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E34" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="50" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E33" s="47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="48" t="n">
-        <f aca="false">AVERAGE(B35:B45)</f>
-        <v>3.26275505050505</v>
-      </c>
-      <c r="C34" s="46"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
-        <v>3.5</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C35" s="46"/>
       <c r="D35" s="49" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.43088888888889</v>
+        <v>3.7</v>
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="49" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="49" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>2.6</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C38" s="46"/>
       <c r="D38" s="49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>3.77816666666667</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>2.59388888888889</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C40" s="46"/>
       <c r="D40" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>3.23902777777778</v>
+        <v>2.6</v>
       </c>
       <c r="C41" s="46"/>
       <c r="D41" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>2.6</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E42" s="47" t="s">
-        <v>141</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>3.58416666666667</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>2.94083333333333</v>
+        <v>3.92333333333333</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
-        <v>3.92333333333333</v>
+      <c r="A45" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">AVERAGE(B46:B50)</f>
+        <v>3.2865</v>
       </c>
       <c r="C45" s="46"/>
-      <c r="D45" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E45" s="47" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="48" t="n">
-        <f aca="false">AVERAGE(B47:B51)</f>
-        <v>3.2865</v>
-      </c>
-      <c r="C46" s="46"/>
+      <c r="A46" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
+        <v>3.6</v>
+      </c>
+      <c r="C46" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.6</v>
+        <v>3.33761111111111</v>
       </c>
       <c r="C47" s="46" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D47" s="49" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.33761111111111</v>
-      </c>
-      <c r="C48" s="46" t="s">
-        <v>126</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C48" s="46"/>
       <c r="D48" s="49" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C49" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C49" s="46" t="s">
+        <v>130</v>
+      </c>
       <c r="D49" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C50" s="46" t="s">
-        <v>132</v>
-      </c>
+        <v>2.39488888888889</v>
+      </c>
+      <c r="C50" s="46"/>
       <c r="D50" s="49" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
-        <v>2.39488888888889</v>
+      <c r="A51" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="48" t="n">
+        <f aca="false">AVERAGE(B52:B56)</f>
+        <v>3.42807</v>
       </c>
       <c r="C51" s="46"/>
-      <c r="D51" s="49" t="n">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="48" t="n">
-        <f aca="false">AVERAGE(B53:B57)</f>
-        <v>3.42807</v>
+      <c r="A52" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
+        <v>3.6</v>
       </c>
       <c r="C52" s="46"/>
+      <c r="D52" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="C53" s="46"/>
       <c r="D53" s="49" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="C54" s="46"/>
       <c r="D54" s="49" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="C55" s="46"/>
       <c r="D55" s="49" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.3</v>
+        <v>3.74035</v>
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="49" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
-        <v>3.74035</v>
+      <c r="A57" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="48" t="n">
+        <f aca="false">AVERAGE(B58:B59)</f>
+        <v>3.05</v>
       </c>
       <c r="C57" s="46"/>
-      <c r="D57" s="49" t="n">
-        <v>3.7</v>
-      </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="48" t="n">
-        <f aca="false">AVERAGE(B59:B60)</f>
-        <v>3.05</v>
+      <c r="A58" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
+        <v>2.7</v>
       </c>
       <c r="C58" s="46"/>
+      <c r="D58" s="49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E58" s="47" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="49" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60" s="49" t="n">
+        <v>84</v>
+      </c>
+      <c r="B60" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="C60" s="46"/>
-      <c r="D60" s="49" t="n">
-        <v>3.4</v>
+      <c r="D60" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
-        <v>1</v>
+      <c r="A61" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">AVERAGE(B62:B63)</f>
+        <v>2.25194444444444</v>
       </c>
       <c r="C61" s="46"/>
-      <c r="D61" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="47" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">AVERAGE(B63:B64)</f>
-        <v>2.25194444444444</v>
+      <c r="A62" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
+        <v>2.30388888888889</v>
       </c>
       <c r="C62" s="46"/>
+      <c r="D62" s="49" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>2.30388888888889</v>
+        <v>2.2</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="49" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="E63" s="47" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
-        <v>2.2</v>
-      </c>
-      <c r="C64" s="46"/>
+        <v>2.43069444444444</v>
+      </c>
       <c r="D64" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E64" s="47" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B65" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
-        <v>2.43069444444444</v>
-      </c>
-      <c r="D65" s="49" t="n">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="B66" s="48" t="n">
-        <f aca="false">AVERAGE(B67:B68)</f>
-        <v>2.85</v>
-      </c>
-      <c r="C66" s="46"/>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="B67" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer2")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
-        <v>3</v>
-      </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="E67" s="47" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="B68" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestPlayer2")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
-        <v>2.7</v>
-      </c>
-      <c r="C68" s="46"/>
-      <c r="D68" s="49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E68" s="47"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -26827,7 +26753,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26838,16 +26764,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26936,59 +26862,59 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7)</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="49" t="n">
+      <c r="A7" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7)</f>
+        <v>14</v>
+      </c>
+      <c r="C7" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>4</v>
+      </c>
+      <c r="D7" s="48" t="n">
         <f aca="false">IFERROR(C7/B7,0)</f>
-        <v>0</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8)</f>
-        <v>14</v>
-      </c>
-      <c r="C8" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+      <c r="A8" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8)</f>
         <v>4</v>
       </c>
-      <c r="D8" s="48" t="n">
+      <c r="C8" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="49" t="n">
         <f aca="false">IFERROR(C8/B8,0)</f>
-        <v>0.285714285714286</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="B9" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C9" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="49" t="n">
         <f aca="false">IFERROR(C9/B9,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="49" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B10" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A10)</f>
@@ -27005,7 +26931,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B11" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A11)</f>
@@ -27022,7 +26948,7 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="49" t="s">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="B12" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A12)</f>
@@ -27039,11 +26965,11 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="B13" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27056,11 +26982,11 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="B14" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C14" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27073,28 +26999,28 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B15" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="49" t="n">
         <f aca="false">IFERROR(C15/B15,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="B16" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C16" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27102,63 +27028,63 @@
       </c>
       <c r="D16" s="49" t="n">
         <f aca="false">IFERROR(C16/B16,0)</f>
-        <v>1</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B17" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C17" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="49" t="n">
         <f aca="false">IFERROR(C17/B17,0)</f>
-        <v>0.166666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
-        <v>1</v>
-      </c>
-      <c r="C18" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="49" t="n">
+      <c r="A18" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
+        <v>12</v>
+      </c>
+      <c r="C18" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>5</v>
+      </c>
+      <c r="D18" s="48" t="n">
         <f aca="false">IFERROR(C18/B18,0)</f>
-        <v>0</v>
+        <v>0.416666666666667</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19)</f>
-        <v>12</v>
-      </c>
-      <c r="C19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>5</v>
-      </c>
-      <c r="D19" s="48" t="n">
+      <c r="A19" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="49" t="n">
         <f aca="false">IFERROR(C19/B19,0)</f>
-        <v>0.416666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -27175,11 +27101,11 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27192,11 +27118,11 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27209,7 +27135,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
@@ -27226,7 +27152,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
@@ -27243,7 +27169,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
@@ -27260,7 +27186,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
@@ -27277,11 +27203,11 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27294,7 +27220,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
@@ -27302,122 +27228,122 @@
       </c>
       <c r="C28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="49" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="49" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="B30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="49" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="49" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="49" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
-        <v>1</v>
-      </c>
-      <c r="C33" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
-      </c>
-      <c r="D33" s="49" t="n">
+      <c r="A33" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
+        <v>11</v>
+      </c>
+      <c r="C33" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D33" s="48" t="n">
         <f aca="false">IFERROR(C33/B33,0)</f>
-        <v>1</v>
+        <v>0.272727272727273</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34)</f>
-        <v>11</v>
-      </c>
-      <c r="C34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D34" s="48" t="n">
+      <c r="A34" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="49" t="n">
         <f aca="false">IFERROR(C34/B34,0)</f>
-        <v>0.272727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27430,11 +27356,11 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27447,7 +27373,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
@@ -27464,24 +27390,24 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="49" t="n">
         <f aca="false">IFERROR(C38/B38,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
@@ -27489,20 +27415,20 @@
       </c>
       <c r="C39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="49" t="n">
         <f aca="false">IFERROR(C39/B39,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27515,11 +27441,11 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27532,11 +27458,11 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27549,7 +27475,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
@@ -27557,16 +27483,16 @@
       </c>
       <c r="C43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="49" t="n">
         <f aca="false">IFERROR(C43/B43,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
@@ -27582,46 +27508,46 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
-        <v>2</v>
-      </c>
-      <c r="C45" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
-      </c>
-      <c r="D45" s="49" t="n">
+      <c r="A45" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
+        <v>2</v>
+      </c>
+      <c r="C45" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="48" t="n">
         <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46)</f>
-        <v>2</v>
-      </c>
-      <c r="C46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="48" t="n">
+      <c r="A46" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="49" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27634,11 +27560,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27651,7 +27577,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
@@ -27668,11 +27594,11 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27684,42 +27610,42 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="49" t="n">
+      <c r="A51" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="48" t="n">
         <f aca="false">IFERROR(C51/B51,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52)</f>
-        <v>1</v>
-      </c>
-      <c r="C52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="48" t="n">
+      <c r="A52" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
+        <v>0</v>
+      </c>
+      <c r="C52" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="49" t="n">
         <f aca="false">IFERROR(C52/B52,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -27736,7 +27662,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -27753,7 +27679,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
@@ -27770,11 +27696,11 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27786,42 +27712,42 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
-        <v>1</v>
-      </c>
-      <c r="C57" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="49" t="n">
+      <c r="A57" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
+        <v>0</v>
+      </c>
+      <c r="C57" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="48" t="n">
         <f aca="false">IFERROR(C57/B57,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58)</f>
-        <v>0</v>
-      </c>
-      <c r="C58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="48" t="n">
+      <c r="A58" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
+        <v>0</v>
+      </c>
+      <c r="C58" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49" t="n">
         <f aca="false">IFERROR(C58/B58,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
@@ -27838,7 +27764,7 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B60" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
@@ -27854,46 +27780,46 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
-        <v>0</v>
-      </c>
-      <c r="C61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="49" t="n">
+      <c r="A61" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+        <v>4</v>
+      </c>
+      <c r="C61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="48" t="n">
         <f aca="false">IFERROR(C61/B61,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62)</f>
-        <v>4</v>
-      </c>
-      <c r="C62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="48" t="n">
+      <c r="A62" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
+        <v>3</v>
+      </c>
+      <c r="C62" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="49" t="n">
         <f aca="false">IFERROR(C62/B62,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27906,11 +27832,11 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27918,74 +27844,6 @@
       </c>
       <c r="D64" s="49" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B65" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
-        <v>1</v>
-      </c>
-      <c r="C65" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D65" s="49" t="n">
-        <f aca="false">IFERROR(C65/B65,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="B66" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
-        <v>0</v>
-      </c>
-      <c r="C66" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="48" t="n">
-        <f aca="false">IFERROR(C66/B66,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="B67" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="49" t="n">
-        <f aca="false">IFERROR(C67/B67,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="B68" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
-        <v>0</v>
-      </c>
-      <c r="C68" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestPlayer2",'Game Log Season 3'!$D$3:$D$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="49" t="n">
-        <f aca="false">IFERROR(C68/B68,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -28024,40 +27882,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="I1" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="J1" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="K1" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="51" t="s">
+      <c r="L1" s="51" t="s">
         <v>160</v>
-      </c>
-      <c r="G1" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="J1" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="K1" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="L1" s="51" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25781,7 +25781,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -25883,7 +25883,7 @@
         <v>28</v>
       </c>
       <c r="B7" s="48" t="n">
-        <f aca="false">AVERAGE(B8:B17)</f>
+        <f aca="false">AVERAGE(B8:B18)</f>
         <v>3.28381944444444</v>
       </c>
       <c r="C7" s="46"/>
@@ -26052,689 +26052,761 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="49" t="inlineStr">
+        <is>
+          <t>ZZ Test Batch Deck</t>
+        </is>
+      </c>
+      <c r="B18" s="49">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
+        <v>2.8</v>
+      </c>
+      <c r="C18" s="46"/>
+      <c r="D18" s="49">
+        <v>2.8</v>
+      </c>
+      <c r="E18" s="47" t="inlineStr">
+        <is>
+          <t>999003</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="48" t="n">
-        <f aca="false">AVERAGE(B19:B32)</f>
+      <c r="B19" s="48" t="n">
+        <f aca="false">AVERAGE(B20:B33)</f>
         <v>3.31464285714286</v>
       </c>
-      <c r="C18" s="46"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
-        <v>2.4</v>
-      </c>
       <c r="C19" s="46"/>
-      <c r="D19" s="49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="49" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
-        <v>3.57402777777778</v>
+        <v>2.6</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
-        <v>3.6</v>
+        <v>3.57402777777778</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="49" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="C24" s="46"/>
       <c r="D24" s="49" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
-        <v>2.8</v>
-      </c>
-      <c r="C25" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D25" s="49" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>123</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
-        <v>3.59875</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>124</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="C27" s="46"/>
       <c r="D27" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
-        <v>3.94083333333333</v>
-      </c>
-      <c r="C28" s="46"/>
+        <v>3.59875</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>124</v>
+      </c>
       <c r="D28" s="49" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>3.65388888888889</v>
+        <v>3.94083333333333</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="49" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="50" t="n">
+        <v>90</v>
+      </c>
+      <c r="B30" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
-        <v>3.95583333333333</v>
+        <v>3.65388888888889</v>
       </c>
       <c r="C30" s="46"/>
-      <c r="D30" s="50" t="n">
-        <v>4</v>
+      <c r="D30" s="49" t="n">
+        <v>3.7</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B31" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
-        <v>2.94666666666667</v>
+        <v>3.95583333333333</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="50" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B32" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
+        <v>2.94666666666667</v>
+      </c>
+      <c r="C32" s="46"/>
+      <c r="D32" s="50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
         <v>3.935</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C33" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="50" t="n">
+      <c r="D33" s="50" t="n">
         <v>3.9</v>
       </c>
-      <c r="E32" s="47" t="s">
+      <c r="E33" s="47" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="47" t="s">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="48" t="n">
-        <f aca="false">AVERAGE(B34:B44)</f>
+      <c r="B34" s="48" t="n">
+        <f aca="false">AVERAGE(B35:B45)</f>
         <v>3.26275505050505</v>
       </c>
-      <c r="C33" s="46"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
-        <v>3.5</v>
-      </c>
       <c r="C34" s="46"/>
-      <c r="D34" s="49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>132</v>
-      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
-        <v>3.43088888888889</v>
+        <v>3.5</v>
       </c>
       <c r="C35" s="46"/>
       <c r="D35" s="49" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.7</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="49" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="49" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>3.77816666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C38" s="46"/>
       <c r="D38" s="49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>2.59388888888889</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>3.23902777777778</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C40" s="46"/>
       <c r="D40" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>2.6</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C41" s="46"/>
       <c r="D41" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>3.58416666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>2.94083333333333</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E43" s="47" t="s">
-        <v>140</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>3.92333333333333</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
+        <v>3.92333333333333</v>
+      </c>
+      <c r="C45" s="46"/>
+      <c r="D45" s="49" t="n">
         <v>3.9</v>
       </c>
-      <c r="E44" s="47" t="s">
+      <c r="E45" s="47" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="s">
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="48" t="n">
-        <f aca="false">AVERAGE(B46:B50)</f>
+      <c r="B46" s="48" t="n">
+        <f aca="false">AVERAGE(B47:B51)</f>
         <v>3.2865</v>
       </c>
-      <c r="C45" s="46"/>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
-        <v>3.6</v>
-      </c>
-      <c r="C46" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" s="49" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="C46" s="46"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.33761111111111</v>
+        <v>3.6</v>
       </c>
       <c r="C47" s="46" t="s">
         <v>124</v>
       </c>
       <c r="D47" s="49" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C48" s="46"/>
+        <v>3.33761111111111</v>
+      </c>
+      <c r="C48" s="46" t="s">
+        <v>124</v>
+      </c>
       <c r="D48" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C49" s="46" t="s">
-        <v>130</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C49" s="46"/>
       <c r="D49" s="49" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C50" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="49" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
         <v>2.39488888888889</v>
       </c>
-      <c r="C50" s="46"/>
-      <c r="D50" s="49" t="n">
+      <c r="C51" s="46"/>
+      <c r="D51" s="49" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47" t="s">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="48" t="n">
-        <f aca="false">AVERAGE(B52:B56)</f>
+      <c r="B52" s="48" t="n">
+        <f aca="false">AVERAGE(B53:B57)</f>
         <v>3.42807</v>
       </c>
-      <c r="C51" s="46"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
-        <v>3.6</v>
-      </c>
       <c r="C52" s="46"/>
-      <c r="D52" s="49" t="n">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="C53" s="46"/>
       <c r="D53" s="49" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="C54" s="46"/>
       <c r="D54" s="49" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="C55" s="46"/>
       <c r="D55" s="49" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.74035</v>
+        <v>3.3</v>
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="49" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
+        <v>3.74035</v>
+      </c>
+      <c r="C57" s="46"/>
+      <c r="D57" s="49" t="n">
         <v>3.7</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="s">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="48" t="n">
-        <f aca="false">AVERAGE(B58:B59)</f>
+      <c r="B58" s="48" t="n">
+        <f aca="false">AVERAGE(B59:B60)</f>
         <v>3.05</v>
       </c>
-      <c r="C57" s="46"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
-        <v>2.7</v>
-      </c>
       <c r="C58" s="46"/>
-      <c r="D58" s="49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E58" s="47" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="49" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
+        <v>3.4</v>
+      </c>
+      <c r="C60" s="46"/>
+      <c r="D60" s="49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E60" s="47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B60" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>1</v>
-      </c>
-      <c r="C60" s="46"/>
-      <c r="D60" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="47" t="s">
+      <c r="B61" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
+        <v>1</v>
+      </c>
+      <c r="C61" s="46"/>
+      <c r="D61" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="47" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">AVERAGE(B62:B63)</f>
+      <c r="B62" s="48" t="n">
+        <f aca="false">AVERAGE(B63:B64)</f>
         <v>2.25194444444444</v>
       </c>
-      <c r="C61" s="46"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
-        <v>2.30388888888889</v>
-      </c>
       <c r="C62" s="46"/>
-      <c r="D62" s="49" t="n">
-        <v>2.5</v>
-      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>2.2</v>
+        <v>2.30388888888889</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E63" s="47" t="s">
-        <v>145</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
+        <v>2.2</v>
+      </c>
+      <c r="C64" s="46"/>
+      <c r="D64" s="49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E64" s="47" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
         <v>2.43069444444444</v>
       </c>
-      <c r="D64" s="49" t="n">
+      <c r="D65" s="49" t="n">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="47" t="inlineStr">
+        <is>
+          <t>ZZTestAlex</t>
+        </is>
+      </c>
+      <c r="B66" s="48">
+        <f>AVERAGE(B67:B68)</f>
+        <v>3.1</v>
+      </c>
+      <c r="C66" s="46"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="49" t="inlineStr">
+        <is>
+          <t>Aragorn, the Uniter</t>
+        </is>
+      </c>
+      <c r="B67" s="49">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAlex")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
+        <v>3.2</v>
+      </c>
+      <c r="C67" s="46"/>
+      <c r="D67" s="49">
+        <v>3.2</v>
+      </c>
+      <c r="E67" s="47" t="inlineStr">
+        <is>
+          <t>763457</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="49" t="inlineStr">
+        <is>
+          <t>Kruphix, God of Horizons</t>
+        </is>
+      </c>
+      <c r="B68" s="49">
+        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAlex")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
+        <v>3</v>
+      </c>
+      <c r="C68" s="46"/>
+      <c r="D68" s="49">
+        <v>3</v>
+      </c>
+      <c r="E68" s="47" t="inlineStr">
+        <is>
+          <t>763449</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -26753,7 +26825,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -27048,43 +27120,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
+    <row r="18" spans="1:4">
+      <c r="A18" s="49" t="inlineStr">
+        <is>
+          <t>ZZ Test Batch Deck</t>
+        </is>
+      </c>
+      <c r="B18" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="49">
+        <f>IFERROR(C18/B18,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
+      <c r="B19" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19)</f>
         <v>12</v>
       </c>
-      <c r="C18" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+      <c r="C19" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>5</v>
       </c>
-      <c r="D18" s="48" t="n">
-        <f aca="false">IFERROR(C18/B18,0)</f>
+      <c r="D19" s="48" t="n">
+        <f aca="false">IFERROR(C19/B19,0)</f>
         <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="49" t="n">
-        <f aca="false">IFERROR(C19/B19,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -27101,11 +27175,11 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27118,11 +27192,11 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27135,7 +27209,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
@@ -27152,7 +27226,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
@@ -27169,7 +27243,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
@@ -27186,7 +27260,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
@@ -27203,11 +27277,11 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27220,7 +27294,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
@@ -27228,122 +27302,122 @@
       </c>
       <c r="C28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="49" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="49" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="B30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="49" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="49" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="49" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
+        <v>1</v>
+      </c>
+      <c r="C33" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D33" s="49" t="n">
+        <f aca="false">IFERROR(C33/B33,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
+      <c r="B34" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34)</f>
         <v>11</v>
       </c>
-      <c r="C33" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D33" s="48" t="n">
-        <f aca="false">IFERROR(C33/B33,0)</f>
+      <c r="C34" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D34" s="48" t="n">
+        <f aca="false">IFERROR(C34/B34,0)</f>
         <v>0.272727272727273</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="49" t="n">
-        <f aca="false">IFERROR(C34/B34,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27356,11 +27430,11 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27373,7 +27447,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
@@ -27390,24 +27464,24 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="49" t="n">
         <f aca="false">IFERROR(C38/B38,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
@@ -27415,20 +27489,20 @@
       </c>
       <c r="C39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" s="49" t="n">
         <f aca="false">IFERROR(C39/B39,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27441,11 +27515,11 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27458,11 +27532,11 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27475,7 +27549,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
@@ -27483,16 +27557,16 @@
       </c>
       <c r="C43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="49" t="n">
         <f aca="false">IFERROR(C43/B43,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
@@ -27508,46 +27582,46 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="s">
+      <c r="A45" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
+        <v>2</v>
+      </c>
+      <c r="C45" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="49" t="n">
+        <f aca="false">IFERROR(C45/B45,0)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
-        <v>2</v>
-      </c>
-      <c r="C45" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="48" t="n">
-        <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
-        <v>0</v>
-      </c>
-      <c r="C46" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="49" t="n">
+      <c r="B46" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46)</f>
+        <v>2</v>
+      </c>
+      <c r="C46" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="48" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27560,11 +27634,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27577,7 +27651,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
@@ -27594,11 +27668,11 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27610,42 +27684,42 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47" t="s">
+      <c r="A51" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="49" t="n">
+        <f aca="false">IFERROR(C51/B51,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="48" t="n">
-        <f aca="false">IFERROR(C51/B51,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
-        <v>0</v>
-      </c>
-      <c r="C52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="49" t="n">
+      <c r="B52" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52)</f>
+        <v>1</v>
+      </c>
+      <c r="C52" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="48" t="n">
         <f aca="false">IFERROR(C52/B52,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -27662,7 +27736,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -27679,7 +27753,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
@@ -27696,11 +27770,11 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27712,42 +27786,42 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="s">
+      <c r="A57" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
+        <v>1</v>
+      </c>
+      <c r="C57" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="49" t="n">
+        <f aca="false">IFERROR(C57/B57,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
-        <v>0</v>
-      </c>
-      <c r="C57" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="48" t="n">
-        <f aca="false">IFERROR(C57/B57,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
-        <v>0</v>
-      </c>
-      <c r="C58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="49" t="n">
+      <c r="B58" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58)</f>
+        <v>0</v>
+      </c>
+      <c r="C58" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="48" t="n">
         <f aca="false">IFERROR(C58/B58,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
@@ -27764,7 +27838,7 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B60" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
@@ -27780,46 +27854,46 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
+      <c r="A61" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="49" t="n">
+        <f aca="false">IFERROR(C61/B61,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+      <c r="B62" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62)</f>
         <v>4</v>
       </c>
-      <c r="C61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="48" t="n">
-        <f aca="false">IFERROR(C61/B61,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
-        <v>3</v>
-      </c>
-      <c r="C62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="49" t="n">
+      <c r="C62" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="48" t="n">
         <f aca="false">IFERROR(C62/B62,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27832,11 +27906,11 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27844,6 +27918,80 @@
       </c>
       <c r="D64" s="49" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
+        <v>1</v>
+      </c>
+      <c r="C65" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="49" t="n">
+        <f aca="false">IFERROR(C65/B65,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="47" t="inlineStr">
+        <is>
+          <t>ZZTestAlex</t>
+        </is>
+      </c>
+      <c r="B66" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
+        <v>0</v>
+      </c>
+      <c r="C66" s="48">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="48">
+        <f>IFERROR(C66/B66,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="49" t="inlineStr">
+        <is>
+          <t>Aragorn, the Uniter</t>
+        </is>
+      </c>
+      <c r="B67" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="49">
+        <f>IFERROR(C67/B67,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="49" t="inlineStr">
+        <is>
+          <t>Kruphix, God of Horizons</t>
+        </is>
+      </c>
+      <c r="B68" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="49">
+        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="49">
+        <f>IFERROR(C68/B68,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="166">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -383,6 +383,12 @@
     <t xml:space="preserve">560535</t>
   </si>
   <si>
+    <t xml:space="preserve">ZZ Test Batch Deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">999003</t>
+  </si>
+  <si>
     <t xml:space="preserve">639396</t>
   </si>
   <si>
@@ -468,6 +474,15 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZZTestAlex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763449</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -25884,7 +25899,7 @@
       </c>
       <c r="B7" s="48" t="n">
         <f aca="false">AVERAGE(B8:B18)</f>
-        <v>3.28381944444444</v>
+        <v>3.23983585858586</v>
       </c>
       <c r="C7" s="46"/>
     </row>
@@ -26052,24 +26067,20 @@
         <v>116</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="49" t="inlineStr">
-        <is>
-          <t>ZZ Test Batch Deck</t>
-        </is>
-      </c>
-      <c r="B18" s="49">
-        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
         <v>2.8</v>
       </c>
       <c r="C18" s="46"/>
-      <c r="D18" s="49">
+      <c r="D18" s="49" t="n">
         <v>2.8</v>
       </c>
-      <c r="E18" s="47" t="inlineStr">
-        <is>
-          <t>999003</t>
-        </is>
+      <c r="E18" s="47" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26095,7 +26106,7 @@
         <v>2.4</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26111,7 +26122,7 @@
         <v>2.6</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26127,7 +26138,7 @@
         <v>3.6</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26143,7 +26154,7 @@
         <v>3.6</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26159,7 +26170,7 @@
         <v>2.9</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26177,7 +26188,7 @@
         <v>3.9</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26206,7 +26217,7 @@
         <v>2.6</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26218,13 +26229,13 @@
         <v>3.59875</v>
       </c>
       <c r="C28" s="46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D28" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26240,7 +26251,7 @@
         <v>3.9</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26256,7 +26267,7 @@
         <v>3.7</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26272,7 +26283,7 @@
         <v>4</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26288,7 +26299,7 @@
         <v>2.9</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26300,13 +26311,13 @@
         <v>3.935</v>
       </c>
       <c r="C33" s="46" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D33" s="50" t="n">
         <v>3.9</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26332,7 +26343,7 @@
         <v>3.5</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26348,7 +26359,7 @@
         <v>3.4</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26364,7 +26375,7 @@
         <v>3.7</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26380,7 +26391,7 @@
         <v>2.6</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26396,7 +26407,7 @@
         <v>3.8</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26412,7 +26423,7 @@
         <v>2.6</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26428,7 +26439,7 @@
         <v>3.6</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26444,7 +26455,7 @@
         <v>2.6</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26473,7 +26484,7 @@
         <v>2.9</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26489,7 +26500,7 @@
         <v>3.9</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26511,7 +26522,7 @@
         <v>3.6</v>
       </c>
       <c r="C47" s="46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D47" s="49" t="n">
         <v>3.6</v>
@@ -26526,7 +26537,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C48" s="46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D48" s="49" t="n">
         <v>3.3</v>
@@ -26554,7 +26565,7 @@
         <v>3.9</v>
       </c>
       <c r="C50" s="46" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D50" s="49" t="n">
         <v>3.9</v>
@@ -26671,7 +26682,7 @@
         <v>2.7</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26687,7 +26698,7 @@
         <v>3.4</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26703,7 +26714,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="47" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26742,7 +26753,7 @@
         <v>2.2</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26757,56 +26768,46 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="47" t="inlineStr">
-        <is>
-          <t>ZZTestAlex</t>
-        </is>
-      </c>
-      <c r="B66" s="48">
-        <f>AVERAGE(B67:B68)</f>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="48" t="n">
+        <f aca="false">AVERAGE(B67:B68)</f>
         <v>3.1</v>
       </c>
       <c r="C66" s="46"/>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="49" t="inlineStr">
-        <is>
-          <t>Aragorn, the Uniter</t>
-        </is>
-      </c>
-      <c r="B67" s="49">
-        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAlex")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAlex")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
         <v>3.2</v>
       </c>
       <c r="C67" s="46"/>
-      <c r="D67" s="49">
+      <c r="D67" s="49" t="n">
         <v>3.2</v>
       </c>
-      <c r="E67" s="47" t="inlineStr">
-        <is>
-          <t>763457</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="49" t="inlineStr">
-        <is>
-          <t>Kruphix, God of Horizons</t>
-        </is>
-      </c>
-      <c r="B68" s="49">
-        <f>IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAlex")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
+      <c r="E67" s="47" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAlex")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
         <v>3</v>
       </c>
       <c r="C68" s="46"/>
-      <c r="D68" s="49">
-        <v>3</v>
-      </c>
-      <c r="E68" s="47" t="inlineStr">
-        <is>
-          <t>763449</t>
-        </is>
+      <c r="D68" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="47" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -26836,16 +26837,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27120,22 +27121,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="49" t="inlineStr">
-        <is>
-          <t>ZZ Test Batch Deck</t>
-        </is>
-      </c>
-      <c r="B18" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="49">
-        <f>IFERROR(C18/B18,0)</f>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="49" t="n">
+        <f aca="false">IFERROR(C18/B18,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -27938,60 +27937,54 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="47" t="inlineStr">
-        <is>
-          <t>ZZTestAlex</t>
-        </is>
-      </c>
-      <c r="B66" s="48">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
-        <v>0</v>
-      </c>
-      <c r="C66" s="48">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="48">
-        <f>IFERROR(C66/B66,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="49" t="inlineStr">
-        <is>
-          <t>Aragorn, the Uniter</t>
-        </is>
-      </c>
-      <c r="B67" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="49">
-        <f>IFERROR(C67/B67,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="49" t="inlineStr">
-        <is>
-          <t>Kruphix, God of Horizons</t>
-        </is>
-      </c>
-      <c r="B68" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
-        <v>0</v>
-      </c>
-      <c r="C68" s="49">
-        <f>COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="49">
-        <f>IFERROR(C68/B68,0)</f>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="B66" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
+        <v>0</v>
+      </c>
+      <c r="C66" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="48" t="n">
+        <f aca="false">IFERROR(C66/B66,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="49" t="n">
+        <f aca="false">IFERROR(C67/B67,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="49" t="n">
+        <f aca="false">IFERROR(C68/B68,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -28030,40 +28023,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F1" s="51" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="161">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -383,12 +383,6 @@
     <t xml:space="preserve">560535</t>
   </si>
   <si>
-    <t xml:space="preserve">ZZ Test Batch Deck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">999003</t>
-  </si>
-  <si>
     <t xml:space="preserve">639396</t>
   </si>
   <si>
@@ -474,15 +468,6 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZZTestAlex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763449</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -25796,7 +25781,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -25898,8 +25883,8 @@
         <v>28</v>
       </c>
       <c r="B7" s="48" t="n">
-        <f aca="false">AVERAGE(B8:B18)</f>
-        <v>3.23983585858586</v>
+        <f aca="false">AVERAGE(B8:B17)</f>
+        <v>3.28381944444444</v>
       </c>
       <c r="C7" s="46"/>
     </row>
@@ -26068,153 +26053,155 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="48" t="n">
+        <f aca="false">AVERAGE(B19:B32)</f>
+        <v>3.31464285714286</v>
+      </c>
+      <c r="C18" s="46"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
+        <v>2.4</v>
+      </c>
+      <c r="C19" s="46"/>
+      <c r="D19" s="49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E19" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
-        <v>2.8</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="49" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="48" t="n">
-        <f aca="false">AVERAGE(B20:B33)</f>
-        <v>3.31464285714286</v>
-      </c>
-      <c r="C19" s="46"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="49" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
-        <v>2.6</v>
+        <v>3.57402777777778</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
-        <v>3.57402777777778</v>
+        <v>3.6</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
-        <v>2.9</v>
-      </c>
-      <c r="C24" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D24" s="49" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C25" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="C25" s="46"/>
       <c r="D25" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>124</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="49" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
-        <v>2.6</v>
-      </c>
-      <c r="C27" s="46"/>
+        <v>3.59875</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>124</v>
+      </c>
       <c r="D27" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E27" s="47" t="s">
         <v>125</v>
@@ -26222,592 +26209,532 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
-        <v>3.59875</v>
-      </c>
-      <c r="C28" s="46" t="s">
+        <v>3.94083333333333</v>
+      </c>
+      <c r="C28" s="46"/>
+      <c r="D28" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E28" s="47" t="s">
         <v>126</v>
-      </c>
-      <c r="D28" s="49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>3.94083333333333</v>
+        <v>3.65388888888889</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="49" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="49" t="n">
+        <v>46</v>
+      </c>
+      <c r="B30" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
-        <v>3.65388888888889</v>
+        <v>3.95583333333333</v>
       </c>
       <c r="C30" s="46"/>
-      <c r="D30" s="49" t="n">
-        <v>3.7</v>
+      <c r="D30" s="50" t="n">
+        <v>4</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B31" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
-        <v>3.95583333333333</v>
+        <v>2.94666666666667</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="50" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B32" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
-        <v>2.94666666666667</v>
-      </c>
-      <c r="C32" s="46"/>
+        <v>3.935</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>130</v>
+      </c>
       <c r="D32" s="50" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E32" s="47" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
-        <v>3.935</v>
-      </c>
-      <c r="C33" s="46" t="s">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="48" t="n">
+        <f aca="false">AVERAGE(B34:B44)</f>
+        <v>3.26275505050505</v>
+      </c>
+      <c r="C33" s="46"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
+        <v>3.5</v>
+      </c>
+      <c r="C34" s="46"/>
+      <c r="D34" s="49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E34" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="50" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E33" s="47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="48" t="n">
-        <f aca="false">AVERAGE(B35:B45)</f>
-        <v>3.26275505050505</v>
-      </c>
-      <c r="C34" s="46"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
-        <v>3.5</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C35" s="46"/>
       <c r="D35" s="49" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.43088888888889</v>
+        <v>3.7</v>
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="49" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="49" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>2.6</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C38" s="46"/>
       <c r="D38" s="49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>3.77816666666667</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>2.59388888888889</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C40" s="46"/>
       <c r="D40" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>3.23902777777778</v>
+        <v>2.6</v>
       </c>
       <c r="C41" s="46"/>
       <c r="D41" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>2.6</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E42" s="47" t="s">
-        <v>141</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>3.58416666666667</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>2.94083333333333</v>
+        <v>3.92333333333333</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
-        <v>3.92333333333333</v>
+      <c r="A45" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">AVERAGE(B46:B50)</f>
+        <v>3.2865</v>
       </c>
       <c r="C45" s="46"/>
-      <c r="D45" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E45" s="47" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="48" t="n">
-        <f aca="false">AVERAGE(B47:B51)</f>
-        <v>3.2865</v>
-      </c>
-      <c r="C46" s="46"/>
+      <c r="A46" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
+        <v>3.6</v>
+      </c>
+      <c r="C46" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.6</v>
+        <v>3.33761111111111</v>
       </c>
       <c r="C47" s="46" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D47" s="49" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.33761111111111</v>
-      </c>
-      <c r="C48" s="46" t="s">
-        <v>126</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C48" s="46"/>
       <c r="D48" s="49" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C49" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C49" s="46" t="s">
+        <v>130</v>
+      </c>
       <c r="D49" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C50" s="46" t="s">
-        <v>132</v>
-      </c>
+        <v>2.39488888888889</v>
+      </c>
+      <c r="C50" s="46"/>
       <c r="D50" s="49" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
-        <v>2.39488888888889</v>
+      <c r="A51" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="48" t="n">
+        <f aca="false">AVERAGE(B52:B56)</f>
+        <v>3.42807</v>
       </c>
       <c r="C51" s="46"/>
-      <c r="D51" s="49" t="n">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="48" t="n">
-        <f aca="false">AVERAGE(B53:B57)</f>
-        <v>3.42807</v>
+      <c r="A52" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
+        <v>3.6</v>
       </c>
       <c r="C52" s="46"/>
+      <c r="D52" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="C53" s="46"/>
       <c r="D53" s="49" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="C54" s="46"/>
       <c r="D54" s="49" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="C55" s="46"/>
       <c r="D55" s="49" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.3</v>
+        <v>3.74035</v>
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="49" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
-        <v>3.74035</v>
+      <c r="A57" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="48" t="n">
+        <f aca="false">AVERAGE(B58:B59)</f>
+        <v>3.05</v>
       </c>
       <c r="C57" s="46"/>
-      <c r="D57" s="49" t="n">
-        <v>3.7</v>
-      </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="48" t="n">
-        <f aca="false">AVERAGE(B59:B60)</f>
-        <v>3.05</v>
+      <c r="A58" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
+        <v>2.7</v>
       </c>
       <c r="C58" s="46"/>
+      <c r="D58" s="49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E58" s="47" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="49" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60" s="49" t="n">
+        <v>84</v>
+      </c>
+      <c r="B60" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="C60" s="46"/>
-      <c r="D60" s="49" t="n">
-        <v>3.4</v>
+      <c r="D60" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
-        <v>1</v>
+      <c r="A61" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">AVERAGE(B62:B63)</f>
+        <v>2.25194444444444</v>
       </c>
       <c r="C61" s="46"/>
-      <c r="D61" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="47" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">AVERAGE(B63:B64)</f>
-        <v>2.25194444444444</v>
+      <c r="A62" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
+        <v>2.30388888888889</v>
       </c>
       <c r="C62" s="46"/>
+      <c r="D62" s="49" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>2.30388888888889</v>
+        <v>2.2</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="49" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="E63" s="47" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
-        <v>2.2</v>
-      </c>
-      <c r="C64" s="46"/>
+        <v>2.43069444444444</v>
+      </c>
       <c r="D64" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E64" s="47" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B65" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
-        <v>2.43069444444444</v>
-      </c>
-      <c r="D65" s="49" t="n">
         <v>2.4</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="B66" s="48" t="n">
-        <f aca="false">AVERAGE(B67:B68)</f>
-        <v>3.1</v>
-      </c>
-      <c r="C66" s="46"/>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAlex")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="49" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E67" s="47" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="B68" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAlex")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
-        <v>3</v>
-      </c>
-      <c r="C68" s="46"/>
-      <c r="D68" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="E68" s="47" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -26826,7 +26753,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26837,16 +26764,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27122,42 +27049,42 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="49" t="n">
+      <c r="A18" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
+        <v>12</v>
+      </c>
+      <c r="C18" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>5</v>
+      </c>
+      <c r="D18" s="48" t="n">
         <f aca="false">IFERROR(C18/B18,0)</f>
-        <v>0</v>
+        <v>0.416666666666667</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19)</f>
-        <v>12</v>
-      </c>
-      <c r="C19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>5</v>
-      </c>
-      <c r="D19" s="48" t="n">
+      <c r="A19" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="49" t="n">
         <f aca="false">IFERROR(C19/B19,0)</f>
-        <v>0.416666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -27174,11 +27101,11 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27191,11 +27118,11 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27208,7 +27135,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
@@ -27225,7 +27152,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
@@ -27242,7 +27169,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
@@ -27259,7 +27186,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
@@ -27276,11 +27203,11 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27293,7 +27220,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
@@ -27301,122 +27228,122 @@
       </c>
       <c r="C28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="49" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="49" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="B30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="49" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="49" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="49" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
-        <v>1</v>
-      </c>
-      <c r="C33" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
-      </c>
-      <c r="D33" s="49" t="n">
+      <c r="A33" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
+        <v>11</v>
+      </c>
+      <c r="C33" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D33" s="48" t="n">
         <f aca="false">IFERROR(C33/B33,0)</f>
-        <v>1</v>
+        <v>0.272727272727273</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34)</f>
-        <v>11</v>
-      </c>
-      <c r="C34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D34" s="48" t="n">
+      <c r="A34" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="49" t="n">
         <f aca="false">IFERROR(C34/B34,0)</f>
-        <v>0.272727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27429,11 +27356,11 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27446,7 +27373,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
@@ -27463,24 +27390,24 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="49" t="n">
         <f aca="false">IFERROR(C38/B38,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
@@ -27488,20 +27415,20 @@
       </c>
       <c r="C39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="49" t="n">
         <f aca="false">IFERROR(C39/B39,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27514,11 +27441,11 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27531,11 +27458,11 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27548,7 +27475,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
@@ -27556,16 +27483,16 @@
       </c>
       <c r="C43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="49" t="n">
         <f aca="false">IFERROR(C43/B43,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
@@ -27581,46 +27508,46 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
-        <v>2</v>
-      </c>
-      <c r="C45" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
-      </c>
-      <c r="D45" s="49" t="n">
+      <c r="A45" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
+        <v>2</v>
+      </c>
+      <c r="C45" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="48" t="n">
         <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46)</f>
-        <v>2</v>
-      </c>
-      <c r="C46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="48" t="n">
+      <c r="A46" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="49" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27633,11 +27560,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27650,7 +27577,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
@@ -27667,11 +27594,11 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27683,42 +27610,42 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="49" t="n">
+      <c r="A51" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="48" t="n">
         <f aca="false">IFERROR(C51/B51,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52)</f>
-        <v>1</v>
-      </c>
-      <c r="C52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="48" t="n">
+      <c r="A52" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
+        <v>0</v>
+      </c>
+      <c r="C52" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="49" t="n">
         <f aca="false">IFERROR(C52/B52,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -27735,7 +27662,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -27752,7 +27679,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
@@ -27769,11 +27696,11 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27785,42 +27712,42 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
-        <v>1</v>
-      </c>
-      <c r="C57" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="49" t="n">
+      <c r="A57" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
+        <v>0</v>
+      </c>
+      <c r="C57" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="48" t="n">
         <f aca="false">IFERROR(C57/B57,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58)</f>
-        <v>0</v>
-      </c>
-      <c r="C58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="48" t="n">
+      <c r="A58" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
+        <v>0</v>
+      </c>
+      <c r="C58" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49" t="n">
         <f aca="false">IFERROR(C58/B58,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
@@ -27837,7 +27764,7 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B60" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
@@ -27853,46 +27780,46 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
-        <v>0</v>
-      </c>
-      <c r="C61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="49" t="n">
+      <c r="A61" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+        <v>4</v>
+      </c>
+      <c r="C61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="48" t="n">
         <f aca="false">IFERROR(C61/B61,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62)</f>
-        <v>4</v>
-      </c>
-      <c r="C62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="48" t="n">
+      <c r="A62" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
+        <v>3</v>
+      </c>
+      <c r="C62" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="49" t="n">
         <f aca="false">IFERROR(C62/B62,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27905,11 +27832,11 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27917,74 +27844,6 @@
       </c>
       <c r="D64" s="49" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B65" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
-        <v>1</v>
-      </c>
-      <c r="C65" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D65" s="49" t="n">
-        <f aca="false">IFERROR(C65/B65,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="47" t="s">
-        <v>148</v>
-      </c>
-      <c r="B66" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
-        <v>0</v>
-      </c>
-      <c r="C66" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="48" t="n">
-        <f aca="false">IFERROR(C66/B66,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="49" t="n">
-        <f aca="false">IFERROR(C67/B67,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="B68" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
-        <v>0</v>
-      </c>
-      <c r="C68" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAlex",'Game Log Season 3'!$D$3:$D$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="49" t="n">
-        <f aca="false">IFERROR(C68/B68,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -28023,40 +27882,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="H1" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="I1" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="J1" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="E1" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="F1" s="51" t="s">
+      <c r="K1" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="L1" s="51" t="s">
         <v>160</v>
-      </c>
-      <c r="H1" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="I1" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="J1" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="K1" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="L1" s="51" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="163">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t xml:space="preserve">560535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZZ Test Workflow Deck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">999004</t>
   </si>
   <si>
     <t xml:space="preserve">639396</t>
@@ -25781,7 +25787,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -25883,8 +25889,8 @@
         <v>28</v>
       </c>
       <c r="B7" s="48" t="n">
-        <f aca="false">AVERAGE(B8:B17)</f>
-        <v>3.28381944444444</v>
+        <f aca="false">AVERAGE(B8:B18)</f>
+        <v>3.22165404040404</v>
       </c>
       <c r="C7" s="46"/>
     </row>
@@ -26053,155 +26059,153 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
+        <v>2.6</v>
+      </c>
+      <c r="C18" s="46"/>
+      <c r="D18" s="49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="48" t="n">
-        <f aca="false">AVERAGE(B19:B32)</f>
+      <c r="B19" s="48" t="n">
+        <f aca="false">AVERAGE(B20:B33)</f>
         <v>3.31464285714286</v>
       </c>
-      <c r="C18" s="46"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
-        <v>2.4</v>
-      </c>
       <c r="C19" s="46"/>
-      <c r="D19" s="49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="49" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
-        <v>3.57402777777778</v>
+        <v>2.6</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
-        <v>3.6</v>
+        <v>3.57402777777778</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="49" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="C24" s="46"/>
       <c r="D24" s="49" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
-        <v>2.8</v>
-      </c>
-      <c r="C25" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D25" s="49" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>123</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
-        <v>3.59875</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>124</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="C27" s="46"/>
       <c r="D27" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E27" s="47" t="s">
         <v>125</v>
@@ -26209,531 +26213,549 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
-        <v>3.94083333333333</v>
-      </c>
-      <c r="C28" s="46"/>
+        <v>3.59875</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>126</v>
+      </c>
       <c r="D28" s="49" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>3.65388888888889</v>
+        <v>3.94083333333333</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="49" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="50" t="n">
+        <v>90</v>
+      </c>
+      <c r="B30" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
-        <v>3.95583333333333</v>
+        <v>3.65388888888889</v>
       </c>
       <c r="C30" s="46"/>
-      <c r="D30" s="50" t="n">
-        <v>4</v>
+      <c r="D30" s="49" t="n">
+        <v>3.7</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B31" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
-        <v>2.94666666666667</v>
+        <v>3.95583333333333</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="50" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B32" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
-        <v>3.935</v>
-      </c>
-      <c r="C32" s="46" t="s">
-        <v>130</v>
-      </c>
+        <v>2.94666666666667</v>
+      </c>
+      <c r="C32" s="46"/>
       <c r="D32" s="50" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="E32" s="47" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="47" t="s">
+    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
+        <v>3.935</v>
+      </c>
+      <c r="C33" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" s="50" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E33" s="47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="48" t="n">
-        <f aca="false">AVERAGE(B34:B44)</f>
+      <c r="B34" s="48" t="n">
+        <f aca="false">AVERAGE(B35:B45)</f>
         <v>3.26275505050505</v>
       </c>
-      <c r="C33" s="46"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
-        <v>3.5</v>
-      </c>
       <c r="C34" s="46"/>
-      <c r="D34" s="49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E34" s="47" t="s">
-        <v>132</v>
-      </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
-        <v>3.43088888888889</v>
+        <v>3.5</v>
       </c>
       <c r="C35" s="46"/>
       <c r="D35" s="49" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.7</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="49" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="49" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>3.77816666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C38" s="46"/>
       <c r="D38" s="49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>2.59388888888889</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>3.23902777777778</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C40" s="46"/>
       <c r="D40" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>2.6</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C41" s="46"/>
       <c r="D41" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>3.58416666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>2.94083333333333</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E43" s="47" t="s">
-        <v>140</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>3.92333333333333</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
+        <v>3.92333333333333</v>
+      </c>
+      <c r="C45" s="46"/>
+      <c r="D45" s="49" t="n">
         <v>3.9</v>
       </c>
-      <c r="E44" s="47" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="s">
+      <c r="E45" s="47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="48" t="n">
-        <f aca="false">AVERAGE(B46:B50)</f>
+      <c r="B46" s="48" t="n">
+        <f aca="false">AVERAGE(B47:B51)</f>
         <v>3.2865</v>
       </c>
-      <c r="C45" s="46"/>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
-        <v>3.6</v>
-      </c>
-      <c r="C46" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" s="49" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="C46" s="46"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.33761111111111</v>
+        <v>3.6</v>
       </c>
       <c r="C47" s="46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D47" s="49" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C48" s="46"/>
+        <v>3.33761111111111</v>
+      </c>
+      <c r="C48" s="46" t="s">
+        <v>126</v>
+      </c>
       <c r="D48" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C49" s="46" t="s">
-        <v>130</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C49" s="46"/>
       <c r="D49" s="49" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C50" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" s="49" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
         <v>2.39488888888889</v>
       </c>
-      <c r="C50" s="46"/>
-      <c r="D50" s="49" t="n">
+      <c r="C51" s="46"/>
+      <c r="D51" s="49" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47" t="s">
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="48" t="n">
-        <f aca="false">AVERAGE(B52:B56)</f>
+      <c r="B52" s="48" t="n">
+        <f aca="false">AVERAGE(B53:B57)</f>
         <v>3.42807</v>
       </c>
-      <c r="C51" s="46"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
-        <v>3.6</v>
-      </c>
       <c r="C52" s="46"/>
-      <c r="D52" s="49" t="n">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="C53" s="46"/>
       <c r="D53" s="49" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="C54" s="46"/>
       <c r="D54" s="49" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="C55" s="46"/>
       <c r="D55" s="49" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.74035</v>
+        <v>3.3</v>
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="49" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
+        <v>3.74035</v>
+      </c>
+      <c r="C57" s="46"/>
+      <c r="D57" s="49" t="n">
         <v>3.7</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="s">
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="48" t="n">
-        <f aca="false">AVERAGE(B58:B59)</f>
+      <c r="B58" s="48" t="n">
+        <f aca="false">AVERAGE(B59:B60)</f>
         <v>3.05</v>
       </c>
-      <c r="C57" s="46"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
-        <v>2.7</v>
-      </c>
       <c r="C58" s="46"/>
-      <c r="D58" s="49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E58" s="47" t="s">
-        <v>142</v>
-      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="49" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
+        <v>3.4</v>
+      </c>
+      <c r="C60" s="46"/>
+      <c r="D60" s="49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E60" s="47" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B60" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>1</v>
-      </c>
-      <c r="C60" s="46"/>
-      <c r="D60" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="47" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
+      <c r="B61" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
+        <v>1</v>
+      </c>
+      <c r="C61" s="46"/>
+      <c r="D61" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="47" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">AVERAGE(B62:B63)</f>
+      <c r="B62" s="48" t="n">
+        <f aca="false">AVERAGE(B63:B64)</f>
         <v>2.25194444444444</v>
       </c>
-      <c r="C61" s="46"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
-        <v>2.30388888888889</v>
-      </c>
       <c r="C62" s="46"/>
-      <c r="D62" s="49" t="n">
-        <v>2.5</v>
-      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>2.2</v>
+        <v>2.30388888888889</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E63" s="47" t="s">
-        <v>145</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
+        <v>2.2</v>
+      </c>
+      <c r="C64" s="46"/>
+      <c r="D64" s="49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E64" s="47" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
         <v>2.43069444444444</v>
       </c>
-      <c r="D64" s="49" t="n">
+      <c r="D65" s="49" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -26753,7 +26775,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26764,16 +26786,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27049,42 +27071,42 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
+      <c r="A18" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="49" t="n">
+        <f aca="false">IFERROR(C18/B18,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
+      <c r="B19" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19)</f>
         <v>12</v>
       </c>
-      <c r="C18" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+      <c r="C19" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>5</v>
       </c>
-      <c r="D18" s="48" t="n">
-        <f aca="false">IFERROR(C18/B18,0)</f>
+      <c r="D19" s="48" t="n">
+        <f aca="false">IFERROR(C19/B19,0)</f>
         <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D19" s="49" t="n">
-        <f aca="false">IFERROR(C19/B19,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -27101,11 +27123,11 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27118,11 +27140,11 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27135,7 +27157,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
@@ -27152,7 +27174,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
@@ -27169,7 +27191,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
@@ -27186,7 +27208,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
@@ -27203,11 +27225,11 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27220,7 +27242,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
@@ -27228,122 +27250,122 @@
       </c>
       <c r="C28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="49" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="49" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="B30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="49" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" s="49" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="49" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
+        <v>1</v>
+      </c>
+      <c r="C33" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D33" s="49" t="n">
+        <f aca="false">IFERROR(C33/B33,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
+      <c r="B34" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34)</f>
         <v>11</v>
       </c>
-      <c r="C33" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D33" s="48" t="n">
-        <f aca="false">IFERROR(C33/B33,0)</f>
+      <c r="C34" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D34" s="48" t="n">
+        <f aca="false">IFERROR(C34/B34,0)</f>
         <v>0.272727272727273</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
-        <v>0</v>
-      </c>
-      <c r="C34" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D34" s="49" t="n">
-        <f aca="false">IFERROR(C34/B34,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27356,11 +27378,11 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27373,7 +27395,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
@@ -27390,24 +27412,24 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="49" t="n">
         <f aca="false">IFERROR(C38/B38,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
@@ -27415,20 +27437,20 @@
       </c>
       <c r="C39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39" s="49" t="n">
         <f aca="false">IFERROR(C39/B39,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27441,11 +27463,11 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27458,11 +27480,11 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27475,7 +27497,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
@@ -27483,16 +27505,16 @@
       </c>
       <c r="C43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="49" t="n">
         <f aca="false">IFERROR(C43/B43,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
@@ -27508,46 +27530,46 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="s">
+      <c r="A45" s="49" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
+        <v>2</v>
+      </c>
+      <c r="C45" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="49" t="n">
+        <f aca="false">IFERROR(C45/B45,0)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
-        <v>2</v>
-      </c>
-      <c r="C45" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="48" t="n">
-        <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
-        <v>0</v>
-      </c>
-      <c r="C46" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="49" t="n">
+      <c r="B46" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46)</f>
+        <v>2</v>
+      </c>
+      <c r="C46" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="48" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27560,11 +27582,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27577,7 +27599,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
@@ -27594,11 +27616,11 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27610,42 +27632,42 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47" t="s">
+      <c r="A51" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="49" t="n">
+        <f aca="false">IFERROR(C51/B51,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="48" t="n">
-        <f aca="false">IFERROR(C51/B51,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
-        <v>0</v>
-      </c>
-      <c r="C52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="49" t="n">
+      <c r="B52" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52)</f>
+        <v>1</v>
+      </c>
+      <c r="C52" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="48" t="n">
         <f aca="false">IFERROR(C52/B52,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -27662,7 +27684,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -27679,7 +27701,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
@@ -27696,11 +27718,11 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27712,42 +27734,42 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="s">
+      <c r="A57" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
+        <v>1</v>
+      </c>
+      <c r="C57" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="49" t="n">
+        <f aca="false">IFERROR(C57/B57,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
-        <v>0</v>
-      </c>
-      <c r="C57" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="48" t="n">
-        <f aca="false">IFERROR(C57/B57,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
-        <v>0</v>
-      </c>
-      <c r="C58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="49" t="n">
+      <c r="B58" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58)</f>
+        <v>0</v>
+      </c>
+      <c r="C58" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="48" t="n">
         <f aca="false">IFERROR(C58/B58,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
@@ -27764,7 +27786,7 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B60" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
@@ -27780,46 +27802,46 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
+      <c r="A61" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="49" t="n">
+        <f aca="false">IFERROR(C61/B61,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+      <c r="B62" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62)</f>
         <v>4</v>
       </c>
-      <c r="C61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="48" t="n">
-        <f aca="false">IFERROR(C61/B61,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
-        <v>3</v>
-      </c>
-      <c r="C62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="49" t="n">
+      <c r="C62" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="48" t="n">
         <f aca="false">IFERROR(C62/B62,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27832,11 +27854,11 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27844,6 +27866,23 @@
       </c>
       <c r="D64" s="49" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
+        <v>1</v>
+      </c>
+      <c r="C65" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="49" t="n">
+        <f aca="false">IFERROR(C65/B65,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -27882,40 +27921,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B1" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>149</v>
-      </c>
       <c r="F1" s="51" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="161">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -381,12 +381,6 @@
   </si>
   <si>
     <t xml:space="preserve">560535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZZ Test Workflow Deck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">999004</t>
   </si>
   <si>
     <t xml:space="preserve">639396</t>
@@ -25787,7 +25781,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -25889,8 +25883,8 @@
         <v>28</v>
       </c>
       <c r="B7" s="48" t="n">
-        <f aca="false">AVERAGE(B8:B18)</f>
-        <v>3.22165404040404</v>
+        <f aca="false">AVERAGE(B8:B17)</f>
+        <v>3.28381944444444</v>
       </c>
       <c r="C7" s="46"/>
     </row>
@@ -26059,153 +26053,155 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="48" t="n">
+        <f aca="false">AVERAGE(B19:B32)</f>
+        <v>3.31464285714286</v>
+      </c>
+      <c r="C18" s="46"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
+        <v>2.4</v>
+      </c>
+      <c r="C19" s="46"/>
+      <c r="D19" s="49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E19" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
-        <v>2.6</v>
-      </c>
-      <c r="C18" s="46"/>
-      <c r="D18" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="48" t="n">
-        <f aca="false">AVERAGE(B20:B33)</f>
-        <v>3.31464285714286</v>
-      </c>
-      <c r="C19" s="46"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="49" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
-        <v>2.6</v>
+        <v>3.57402777777778</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
-        <v>3.57402777777778</v>
+        <v>3.6</v>
       </c>
       <c r="C22" s="46"/>
       <c r="D22" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
-        <v>2.9</v>
-      </c>
-      <c r="C24" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D24" s="49" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C25" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="C25" s="46"/>
       <c r="D25" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E25" s="47" t="s">
-        <v>124</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="49" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
-        <v>2.6</v>
-      </c>
-      <c r="C27" s="46"/>
+        <v>3.59875</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>124</v>
+      </c>
       <c r="D27" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E27" s="47" t="s">
         <v>125</v>
@@ -26213,549 +26209,531 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
-        <v>3.59875</v>
-      </c>
-      <c r="C28" s="46" t="s">
+        <v>3.94083333333333</v>
+      </c>
+      <c r="C28" s="46"/>
+      <c r="D28" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E28" s="47" t="s">
         <v>126</v>
-      </c>
-      <c r="D28" s="49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>3.94083333333333</v>
+        <v>3.65388888888889</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="49" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="49" t="n">
+        <v>46</v>
+      </c>
+      <c r="B30" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
-        <v>3.65388888888889</v>
+        <v>3.95583333333333</v>
       </c>
       <c r="C30" s="46"/>
-      <c r="D30" s="49" t="n">
-        <v>3.7</v>
+      <c r="D30" s="50" t="n">
+        <v>4</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B31" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
-        <v>3.95583333333333</v>
+        <v>2.94666666666667</v>
       </c>
       <c r="C31" s="46"/>
       <c r="D31" s="50" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B32" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
-        <v>2.94666666666667</v>
-      </c>
-      <c r="C32" s="46"/>
+        <v>3.935</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>130</v>
+      </c>
       <c r="D32" s="50" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E32" s="47" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
-        <v>3.935</v>
-      </c>
-      <c r="C33" s="46" t="s">
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="48" t="n">
+        <f aca="false">AVERAGE(B34:B44)</f>
+        <v>3.26275505050505</v>
+      </c>
+      <c r="C33" s="46"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
+        <v>3.5</v>
+      </c>
+      <c r="C34" s="46"/>
+      <c r="D34" s="49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E34" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="50" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E33" s="47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="48" t="n">
-        <f aca="false">AVERAGE(B35:B45)</f>
-        <v>3.26275505050505</v>
-      </c>
-      <c r="C34" s="46"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
-        <v>3.5</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C35" s="46"/>
       <c r="D35" s="49" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.43088888888889</v>
+        <v>3.7</v>
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="49" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="49" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>2.6</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C38" s="46"/>
       <c r="D38" s="49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>3.77816666666667</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>2.59388888888889</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C40" s="46"/>
       <c r="D40" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>3.23902777777778</v>
+        <v>2.6</v>
       </c>
       <c r="C41" s="46"/>
       <c r="D41" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>2.6</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E42" s="47" t="s">
-        <v>141</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>3.58416666666667</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>2.94083333333333</v>
+        <v>3.92333333333333</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
-        <v>3.92333333333333</v>
+      <c r="A45" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">AVERAGE(B46:B50)</f>
+        <v>3.2865</v>
       </c>
       <c r="C45" s="46"/>
-      <c r="D45" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E45" s="47" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="48" t="n">
-        <f aca="false">AVERAGE(B47:B51)</f>
-        <v>3.2865</v>
-      </c>
-      <c r="C46" s="46"/>
+      <c r="A46" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
+        <v>3.6</v>
+      </c>
+      <c r="C46" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="D46" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.6</v>
+        <v>3.33761111111111</v>
       </c>
       <c r="C47" s="46" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D47" s="49" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.33761111111111</v>
-      </c>
-      <c r="C48" s="46" t="s">
-        <v>126</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C48" s="46"/>
       <c r="D48" s="49" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C49" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C49" s="46" t="s">
+        <v>130</v>
+      </c>
       <c r="D49" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C50" s="46" t="s">
-        <v>132</v>
-      </c>
+        <v>2.39488888888889</v>
+      </c>
+      <c r="C50" s="46"/>
       <c r="D50" s="49" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
-        <v>2.39488888888889</v>
+      <c r="A51" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="48" t="n">
+        <f aca="false">AVERAGE(B52:B56)</f>
+        <v>3.42807</v>
       </c>
       <c r="C51" s="46"/>
-      <c r="D51" s="49" t="n">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="48" t="n">
-        <f aca="false">AVERAGE(B53:B57)</f>
-        <v>3.42807</v>
+      <c r="A52" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
+        <v>3.6</v>
       </c>
       <c r="C52" s="46"/>
+      <c r="D52" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="C53" s="46"/>
       <c r="D53" s="49" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="C54" s="46"/>
       <c r="D54" s="49" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="C55" s="46"/>
       <c r="D55" s="49" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.3</v>
+        <v>3.74035</v>
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="49" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
-        <v>3.74035</v>
+      <c r="A57" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="48" t="n">
+        <f aca="false">AVERAGE(B58:B59)</f>
+        <v>3.05</v>
       </c>
       <c r="C57" s="46"/>
-      <c r="D57" s="49" t="n">
-        <v>3.7</v>
-      </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="48" t="n">
-        <f aca="false">AVERAGE(B59:B60)</f>
-        <v>3.05</v>
+      <c r="A58" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
+        <v>2.7</v>
       </c>
       <c r="C58" s="46"/>
+      <c r="D58" s="49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E58" s="47" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="49" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="E59" s="47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60" s="49" t="n">
+        <v>84</v>
+      </c>
+      <c r="B60" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="C60" s="46"/>
-      <c r="D60" s="49" t="n">
-        <v>3.4</v>
+      <c r="D60" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
-        <v>1</v>
+      <c r="A61" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">AVERAGE(B62:B63)</f>
+        <v>2.25194444444444</v>
       </c>
       <c r="C61" s="46"/>
-      <c r="D61" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="47" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">AVERAGE(B63:B64)</f>
-        <v>2.25194444444444</v>
+      <c r="A62" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
+        <v>2.30388888888889</v>
       </c>
       <c r="C62" s="46"/>
+      <c r="D62" s="49" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>2.30388888888889</v>
+        <v>2.2</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="49" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="E63" s="47" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
-        <v>2.2</v>
-      </c>
-      <c r="C64" s="46"/>
+        <v>2.43069444444444</v>
+      </c>
       <c r="D64" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E64" s="47" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B65" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
-        <v>2.43069444444444</v>
-      </c>
-      <c r="D65" s="49" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -26775,7 +26753,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26786,16 +26764,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="D1" s="45" t="s">
         <v>149</v>
-      </c>
-      <c r="C1" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27071,42 +27049,42 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="49" t="n">
+      <c r="A18" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
+        <v>12</v>
+      </c>
+      <c r="C18" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>5</v>
+      </c>
+      <c r="D18" s="48" t="n">
         <f aca="false">IFERROR(C18/B18,0)</f>
-        <v>0</v>
+        <v>0.416666666666667</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19)</f>
-        <v>12</v>
-      </c>
-      <c r="C19" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>5</v>
-      </c>
-      <c r="D19" s="48" t="n">
+      <c r="A19" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="49" t="n">
         <f aca="false">IFERROR(C19/B19,0)</f>
-        <v>0.416666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -27123,11 +27101,11 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27140,11 +27118,11 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27157,7 +27135,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
@@ -27174,7 +27152,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
@@ -27191,7 +27169,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
@@ -27208,7 +27186,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
@@ -27225,11 +27203,11 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27242,7 +27220,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
@@ -27250,122 +27228,122 @@
       </c>
       <c r="C28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="49" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="49" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="B30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="49" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="49" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D32" s="49" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
-        <v>1</v>
-      </c>
-      <c r="C33" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
-      </c>
-      <c r="D33" s="49" t="n">
+      <c r="A33" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
+        <v>11</v>
+      </c>
+      <c r="C33" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D33" s="48" t="n">
         <f aca="false">IFERROR(C33/B33,0)</f>
-        <v>1</v>
+        <v>0.272727272727273</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34)</f>
-        <v>11</v>
-      </c>
-      <c r="C34" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D34" s="48" t="n">
+      <c r="A34" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="49" t="n">
         <f aca="false">IFERROR(C34/B34,0)</f>
-        <v>0.272727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27378,11 +27356,11 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27395,7 +27373,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
@@ -27412,24 +27390,24 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="49" t="n">
         <f aca="false">IFERROR(C38/B38,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
@@ -27437,20 +27415,20 @@
       </c>
       <c r="C39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="49" t="n">
         <f aca="false">IFERROR(C39/B39,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27463,11 +27441,11 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27480,11 +27458,11 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27497,7 +27475,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
@@ -27505,16 +27483,16 @@
       </c>
       <c r="C43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" s="49" t="n">
         <f aca="false">IFERROR(C43/B43,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
@@ -27530,46 +27508,46 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="49" t="s">
-        <v>97</v>
-      </c>
-      <c r="B45" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
-        <v>2</v>
-      </c>
-      <c r="C45" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
-      </c>
-      <c r="D45" s="49" t="n">
+      <c r="A45" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
+        <v>2</v>
+      </c>
+      <c r="C45" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="48" t="n">
         <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46)</f>
-        <v>2</v>
-      </c>
-      <c r="C46" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D46" s="48" t="n">
+      <c r="A46" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="49" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27582,11 +27560,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27599,7 +27577,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
@@ -27616,11 +27594,11 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27632,42 +27610,42 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="49" t="n">
+      <c r="A51" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
+        <v>1</v>
+      </c>
+      <c r="C51" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="48" t="n">
         <f aca="false">IFERROR(C51/B51,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52)</f>
-        <v>1</v>
-      </c>
-      <c r="C52" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D52" s="48" t="n">
+      <c r="A52" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
+        <v>0</v>
+      </c>
+      <c r="C52" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="49" t="n">
         <f aca="false">IFERROR(C52/B52,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -27684,7 +27662,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -27701,7 +27679,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
@@ -27718,11 +27696,11 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27734,42 +27712,42 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
-        <v>1</v>
-      </c>
-      <c r="C57" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="49" t="n">
+      <c r="A57" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
+        <v>0</v>
+      </c>
+      <c r="C57" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="48" t="n">
         <f aca="false">IFERROR(C57/B57,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58)</f>
-        <v>0</v>
-      </c>
-      <c r="C58" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D58" s="48" t="n">
+      <c r="A58" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B58" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
+        <v>0</v>
+      </c>
+      <c r="C58" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="49" t="n">
         <f aca="false">IFERROR(C58/B58,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
@@ -27786,7 +27764,7 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B60" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
@@ -27802,46 +27780,46 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
-        <v>0</v>
-      </c>
-      <c r="C61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="49" t="n">
+      <c r="A61" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+        <v>4</v>
+      </c>
+      <c r="C61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="48" t="n">
         <f aca="false">IFERROR(C61/B61,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62)</f>
-        <v>4</v>
-      </c>
-      <c r="C62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="48" t="n">
+      <c r="A62" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B62" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
+        <v>3</v>
+      </c>
+      <c r="C62" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="49" t="n">
         <f aca="false">IFERROR(C62/B62,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27854,11 +27832,11 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27866,23 +27844,6 @@
       </c>
       <c r="D64" s="49" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B65" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
-        <v>1</v>
-      </c>
-      <c r="C65" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D65" s="49" t="n">
-        <f aca="false">IFERROR(C65/B65,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -27921,40 +27882,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="D1" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="E1" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="G1" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="E1" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="51" t="s">
+      <c r="H1" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="I1" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="J1" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="K1" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="L1" s="51" t="s">
         <v>160</v>
-      </c>
-      <c r="K1" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="L1" s="51" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="164">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -468,6 +468,15 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZZTestAutoDeploy3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Commander Auto 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">999007</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -25781,7 +25790,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -26735,6 +26744,32 @@
       </c>
       <c r="D64" s="49" t="n">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="48" t="n">
+        <f aca="false">AVERAGE(B66:B66)</f>
+        <v>3</v>
+      </c>
+      <c r="C65" s="46"/>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="B66" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAutoDeploy3")*('Game Log Season 3'!$D$3:$D$1000=A66)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D66)</f>
+        <v>3</v>
+      </c>
+      <c r="C66" s="46"/>
+      <c r="D66" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" s="47" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -26753,7 +26788,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26764,16 +26799,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27844,6 +27879,40 @@
       </c>
       <c r="D64" s="49" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A65)</f>
+        <v>0</v>
+      </c>
+      <c r="C65" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="48" t="n">
+        <f aca="false">IFERROR(C65/B65,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="B66" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAutoDeploy3",'Game Log Season 3'!$D$3:$D$1000,A66)</f>
+        <v>0</v>
+      </c>
+      <c r="C66" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAutoDeploy3",'Game Log Season 3'!$D$3:$D$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="49" t="n">
+        <f aca="false">IFERROR(C66/B66,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -27882,40 +27951,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C1" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>149</v>
-      </c>
       <c r="F1" s="51" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="161">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -468,15 +468,6 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZZTestAutoDeploy3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Commander Auto 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">999007</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -25790,7 +25781,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -26744,32 +26735,6 @@
       </c>
       <c r="D64" s="49" t="n">
         <v>2.4</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="B65" s="48" t="n">
-        <f aca="false">AVERAGE(B66:B66)</f>
-        <v>3</v>
-      </c>
-      <c r="C65" s="46"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="B66" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="ZZTestAutoDeploy3")*('Game Log Season 3'!$D$3:$D$1000=A66)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D66)</f>
-        <v>3</v>
-      </c>
-      <c r="C66" s="46"/>
-      <c r="D66" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" s="47" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -26788,7 +26753,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26799,16 +26764,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" s="45" t="s">
         <v>149</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>150</v>
-      </c>
-      <c r="C1" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27879,40 +27844,6 @@
       </c>
       <c r="D64" s="49" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="B65" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A65)</f>
-        <v>0</v>
-      </c>
-      <c r="C65" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D65" s="48" t="n">
-        <f aca="false">IFERROR(C65/B65,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="49" t="s">
-        <v>147</v>
-      </c>
-      <c r="B66" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAutoDeploy3",'Game Log Season 3'!$D$3:$D$1000,A66)</f>
-        <v>0</v>
-      </c>
-      <c r="C66" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"ZZTestAutoDeploy3",'Game Log Season 3'!$D$3:$D$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="49" t="n">
-        <f aca="false">IFERROR(C66/B66,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -27951,40 +27882,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="E1" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="G1" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="H1" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="E1" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="F1" s="51" t="s">
+      <c r="I1" s="51" t="s">
         <v>157</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="J1" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="K1" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="L1" s="51" t="s">
         <v>160</v>
-      </c>
-      <c r="J1" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="K1" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="L1" s="51" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="164">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -426,6 +426,15 @@
   </si>
   <si>
     <t xml:space="preserve">566515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toph, the First Metalbender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">795075</t>
   </si>
   <si>
     <t xml:space="preserve">560264</t>
@@ -25781,7 +25790,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -26057,8 +26066,8 @@
         <v>30</v>
       </c>
       <c r="B18" s="48" t="n">
-        <f aca="false">AVERAGE(B19:B32)</f>
-        <v>3.31464285714286</v>
+        <f aca="false">AVERAGE(B19:B34)</f>
+        <v>3.2128125</v>
       </c>
       <c r="C18" s="46"/>
     </row>
@@ -26290,450 +26299,482 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="48" t="n">
-        <f aca="false">AVERAGE(B34:B44)</f>
-        <v>3.26275505050505</v>
+      <c r="A33" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
+        <v>3</v>
       </c>
       <c r="C33" s="46"/>
+      <c r="D33" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="47" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="B34" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
-        <v>3.5</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
+        <v>2</v>
       </c>
       <c r="C34" s="46"/>
       <c r="D34" s="49" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
-        <v>3.43088888888889</v>
+      <c r="A35" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="48" t="n">
+        <f aca="false">AVERAGE(B36:B46)</f>
+        <v>3.26275505050505</v>
       </c>
       <c r="C35" s="46"/>
-      <c r="D35" s="49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E35" s="47" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="49" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>2.6</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="49" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>3.77816666666667</v>
+        <v>3.7</v>
       </c>
       <c r="C38" s="46"/>
       <c r="D38" s="49" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>2.59388888888889</v>
+        <v>2.6</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
         <v>2.6</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>3.23902777777778</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C40" s="46"/>
       <c r="D40" s="49" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>2.6</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C41" s="46"/>
       <c r="D41" s="49" t="n">
         <v>2.6</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>3.58416666666667</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
         <v>3.6</v>
       </c>
+      <c r="E42" s="47" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>2.94083333333333</v>
+        <v>2.6</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>3.92333333333333</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E44" s="47" t="s">
-        <v>141</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B45" s="48" t="n">
-        <f aca="false">AVERAGE(B46:B50)</f>
-        <v>3.2865</v>
+      <c r="A45" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
+        <v>2.94083333333333</v>
       </c>
       <c r="C45" s="46"/>
+      <c r="D45" s="49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E45" s="47" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B46" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
-        <v>3.6</v>
-      </c>
-      <c r="C46" s="46" t="s">
-        <v>124</v>
-      </c>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
+        <v>3.92333333333333</v>
+      </c>
+      <c r="C46" s="46"/>
       <c r="D46" s="49" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
+      </c>
+      <c r="E46" s="47" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.33761111111111</v>
-      </c>
-      <c r="C47" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="D47" s="49" t="n">
-        <v>3.3</v>
-      </c>
+      <c r="A47" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="48" t="n">
+        <f aca="false">AVERAGE(B48:B52)</f>
+        <v>3.2865</v>
+      </c>
+      <c r="C47" s="46"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C48" s="46"/>
+        <v>3.6</v>
+      </c>
+      <c r="C48" s="46" t="s">
+        <v>124</v>
+      </c>
       <c r="D48" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.9</v>
+        <v>3.33761111111111</v>
       </c>
       <c r="C49" s="46" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D49" s="49" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
-        <v>2.39488888888889</v>
+        <v>3.2</v>
       </c>
       <c r="C50" s="46"/>
       <c r="D50" s="49" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="48" t="n">
-        <f aca="false">AVERAGE(B52:B56)</f>
-        <v>3.42807</v>
-      </c>
-      <c r="C51" s="46"/>
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C51" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="D51" s="49" t="n">
+        <v>3.9</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="B52" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
-        <v>3.6</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
+        <v>2.39488888888889</v>
       </c>
       <c r="C52" s="46"/>
       <c r="D52" s="49" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.8</v>
+      <c r="A53" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="48" t="n">
+        <f aca="false">AVERAGE(B54:B58)</f>
+        <v>3.42807</v>
       </c>
       <c r="C53" s="46"/>
-      <c r="D53" s="49" t="n">
-        <v>3.8</v>
-      </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="C54" s="46"/>
       <c r="D54" s="49" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="C55" s="46"/>
       <c r="D55" s="49" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.74035</v>
+        <v>2.7</v>
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="49" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B57" s="48" t="n">
-        <f aca="false">AVERAGE(B58:B59)</f>
-        <v>3.05</v>
+      <c r="A57" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
+        <v>3.3</v>
       </c>
       <c r="C57" s="46"/>
+      <c r="D57" s="49" t="n">
+        <v>3.3</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="B58" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
-        <v>2.7</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
+        <v>3.74035</v>
       </c>
       <c r="C58" s="46"/>
       <c r="D58" s="49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E58" s="47" t="s">
-        <v>142</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>3.4</v>
+      <c r="A59" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="48" t="n">
+        <f aca="false">AVERAGE(B60:B61)</f>
+        <v>3.05</v>
       </c>
       <c r="C59" s="46"/>
-      <c r="D59" s="49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E59" s="47" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B60" s="50" t="n">
+        <v>33</v>
+      </c>
+      <c r="B60" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="C60" s="46"/>
-      <c r="D60" s="50" t="n">
-        <v>1</v>
+      <c r="D60" s="49" t="n">
+        <v>2.7</v>
       </c>
       <c r="E60" s="47" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">AVERAGE(B62:B63)</f>
-        <v>2.25194444444444</v>
+      <c r="A61" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
+        <v>3.4</v>
       </c>
       <c r="C61" s="46"/>
+      <c r="D61" s="49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E61" s="47" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
-        <v>2.30388888888889</v>
+        <v>84</v>
+      </c>
+      <c r="B62" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
+        <v>1</v>
       </c>
       <c r="C62" s="46"/>
-      <c r="D62" s="49" t="n">
-        <v>2.5</v>
+      <c r="D62" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="B63" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>2.2</v>
+      <c r="A63" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B63" s="48" t="n">
+        <f aca="false">AVERAGE(B64:B65)</f>
+        <v>2.25194444444444</v>
       </c>
       <c r="C63" s="46"/>
-      <c r="D63" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E63" s="47" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
+        <v>2.30388888888889</v>
+      </c>
+      <c r="C64" s="46"/>
+      <c r="D64" s="49" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
+        <v>2.2</v>
+      </c>
+      <c r="C65" s="46"/>
+      <c r="D65" s="49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E65" s="47" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A66)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D66)</f>
         <v>2.43069444444444</v>
       </c>
-      <c r="D64" s="49" t="n">
+      <c r="D66" s="49" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -26753,7 +26794,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26764,16 +26805,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27304,32 +27345,32 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33)</f>
-        <v>11</v>
-      </c>
-      <c r="C33" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D33" s="48" t="n">
+      <c r="A33" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
+        <v>0</v>
+      </c>
+      <c r="C33" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="49" t="n">
         <f aca="false">IFERROR(C33/B33,0)</f>
-        <v>0.272727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="B34" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
         <v>0</v>
       </c>
       <c r="C34" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D34" s="49" t="n">
@@ -27338,25 +27379,25 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
-        <v>1</v>
-      </c>
-      <c r="C35" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D35" s="49" t="n">
+      <c r="A35" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A35)</f>
+        <v>11</v>
+      </c>
+      <c r="C35" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D35" s="48" t="n">
         <f aca="false">IFERROR(C35/B35,0)</f>
-        <v>0</v>
+        <v>0.272727272727273</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -27373,11 +27414,11 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27390,28 +27431,28 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="49" t="n">
         <f aca="false">IFERROR(C38/B38,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27424,28 +27465,28 @@
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="49" t="n">
         <f aca="false">IFERROR(C40/B40,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27458,7 +27499,7 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
@@ -27475,24 +27516,24 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="49" t="n">
         <f aca="false">IFERROR(C43/B43,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
@@ -27500,67 +27541,67 @@
       </c>
       <c r="C44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="49" t="n">
         <f aca="false">IFERROR(C44/B44,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
+        <v>2</v>
+      </c>
+      <c r="C45" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="49" t="n">
+        <f aca="false">IFERROR(C45/B45,0)</f>
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B45" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45)</f>
-        <v>2</v>
-      </c>
-      <c r="C45" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="48" t="n">
-        <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B46" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
+        <v>2</v>
       </c>
       <c r="C46" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
       </c>
       <c r="D46" s="49" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>1</v>
-      </c>
-      <c r="C47" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="49" t="n">
+      <c r="A47" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A47)</f>
+        <v>2</v>
+      </c>
+      <c r="C47" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="48" t="n">
         <f aca="false">IFERROR(C47/B47,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
@@ -27577,11 +27618,11 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27594,11 +27635,11 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27610,32 +27651,32 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51)</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D51" s="48" t="n">
+      <c r="A51" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
+        <v>0</v>
+      </c>
+      <c r="C51" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="49" t="n">
         <f aca="false">IFERROR(C51/B51,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="B52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
+        <v>1</v>
       </c>
       <c r="C52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D52" s="49" t="n">
@@ -27644,25 +27685,25 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
-        <v>0</v>
-      </c>
-      <c r="C53" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A53,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D53" s="49" t="n">
+      <c r="A53" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A53)</f>
+        <v>1</v>
+      </c>
+      <c r="C53" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A53,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D53" s="48" t="n">
         <f aca="false">IFERROR(C53/B53,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -27679,7 +27720,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B55" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
@@ -27696,11 +27737,11 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27712,32 +27753,32 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B57" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57)</f>
-        <v>0</v>
-      </c>
-      <c r="C57" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D57" s="48" t="n">
+      <c r="A57" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
+        <v>0</v>
+      </c>
+      <c r="C57" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="49" t="n">
         <f aca="false">IFERROR(C57/B57,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="B58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
+        <v>1</v>
       </c>
       <c r="C58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D58" s="49" t="n">
@@ -27746,25 +27787,25 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
-        <v>0</v>
-      </c>
-      <c r="C59" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A59,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D59" s="49" t="n">
+      <c r="A59" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A59)</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A59,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="48" t="n">
         <f aca="false">IFERROR(C59/B59,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="B60" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
@@ -27780,32 +27821,32 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
-        <v>4</v>
-      </c>
-      <c r="C61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="48" t="n">
+      <c r="A61" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="49" t="n">
         <f aca="false">IFERROR(C61/B61,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
+        <v>0</v>
       </c>
       <c r="C62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D62" s="49" t="n">
@@ -27814,29 +27855,29 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="B63" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
-        <v>0</v>
-      </c>
-      <c r="C63" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D63" s="49" t="n">
+      <c r="A63" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B63" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A63)</f>
+        <v>4</v>
+      </c>
+      <c r="C63" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="48" t="n">
         <f aca="false">IFERROR(C63/B63,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27844,6 +27885,40 @@
       </c>
       <c r="D64" s="49" t="n">
         <f aca="false">IFERROR(C64/B64,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B65" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
+        <v>0</v>
+      </c>
+      <c r="C65" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D65" s="49" t="n">
+        <f aca="false">IFERROR(C65/B65,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A66)</f>
+        <v>1</v>
+      </c>
+      <c r="C66" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="49" t="n">
+        <f aca="false">IFERROR(C66/B66,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -27882,40 +27957,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C1" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="51" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>149</v>
-      </c>
       <c r="F1" s="51" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="196">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -350,6 +350,12 @@
     <t xml:space="preserve">648625</t>
   </si>
   <si>
+    <t xml:space="preserve">Katara, the Fearless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797189</t>
+  </si>
+  <si>
     <t xml:space="preserve">626865</t>
   </si>
   <si>
@@ -381,6 +387,24 @@
   </si>
   <si>
     <t xml:space="preserve">560535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toph, Hardheaded Teacher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">796808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eshki, Temur's Roar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">737114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sokka, Tenacious Tactician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">741945</t>
   </si>
   <si>
     <t xml:space="preserve">639396</t>
@@ -437,6 +461,18 @@
     <t xml:space="preserve">795075</t>
   </si>
   <si>
+    <t xml:space="preserve">Tidus, Yuna's Guardian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">560459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michelangelo, the Heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">743883</t>
+  </si>
+  <si>
     <t xml:space="preserve">560264</t>
   </si>
   <si>
@@ -467,6 +503,21 @@
     <t xml:space="preserve">744134</t>
   </si>
   <si>
+    <t xml:space="preserve">Atraxa, Praetors' Voice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">560265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">560266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krenko, Mob Boss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744135</t>
+  </si>
+  <si>
     <t xml:space="preserve">595027</t>
   </si>
   <si>
@@ -477,6 +528,51 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiccup_The_Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam, Loyal Attendant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avatar Aang // Aang, Master of Elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763460</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -25790,7 +25886,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -25819,8 +25915,8 @@
         <v>26</v>
       </c>
       <c r="B2" s="48" t="n">
-        <f aca="false">AVERAGE(B3:B6)</f>
-        <v>2.72288194444444</v>
+        <f aca="false">AVERAGE(B3:B7)</f>
+        <v>2.95830555555556</v>
       </c>
       <c r="C2" s="46"/>
     </row>
@@ -25888,894 +25984,1240 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="48" t="n">
-        <f aca="false">AVERAGE(B8:B17)</f>
-        <v>3.28381944444444</v>
-      </c>
-      <c r="C7" s="46"/>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A8)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D8)</f>
-        <v>3.83916666666667</v>
+      <c r="B8" s="48" t="n">
+        <f aca="false">AVERAGE(B9:B21)</f>
+        <v>3.42601495726496</v>
       </c>
       <c r="C8" s="46"/>
-      <c r="D8" s="49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B9" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A9)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D9)</f>
-        <v>3.9</v>
+        <v>3.83916666666667</v>
       </c>
       <c r="C9" s="46"/>
       <c r="D9" s="49" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="49" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B10" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A10)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D10)</f>
-        <v>3.4</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>108</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="C10" s="46"/>
       <c r="D10" s="49" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="E10" s="47" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B11" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A11)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D11)</f>
-        <v>2.6</v>
-      </c>
-      <c r="C11" s="46"/>
+        <v>3.4</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>110</v>
+      </c>
       <c r="D11" s="49" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="49" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B12" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A12)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D12)</f>
-        <v>3.5</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="C12" s="46"/>
       <c r="D12" s="49" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B13" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A13)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D13)</f>
-        <v>2.65388888888889</v>
-      </c>
-      <c r="C13" s="46"/>
+        <v>3.5</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D13" s="49" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B14" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A14)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D14)</f>
-        <v>2.6</v>
+        <v>2.65388888888889</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="49" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A15)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D15)</f>
-        <v>3.91083333333333</v>
+        <v>2.6</v>
       </c>
       <c r="C15" s="46"/>
       <c r="D15" s="49" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="B16" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A16)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D16)</f>
-        <v>2.94083333333333</v>
+        <v>3.91083333333333</v>
       </c>
       <c r="C16" s="46"/>
       <c r="D16" s="49" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B17" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A17)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D17)</f>
-        <v>3.49347222222222</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C17" s="46"/>
       <c r="D17" s="49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A18)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D18)</f>
+        <v>3.49347222222222</v>
+      </c>
+      <c r="C18" s="46"/>
+      <c r="D18" s="49" t="n">
         <v>3.5</v>
       </c>
-      <c r="E17" s="47" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="48" t="n">
-        <f aca="false">AVERAGE(B19:B34)</f>
-        <v>3.2128125</v>
-      </c>
-      <c r="C18" s="46"/>
+      <c r="E18" s="47" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="B19" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
-        <v>2.4</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
+        <v>3.9</v>
       </c>
       <c r="C19" s="46"/>
       <c r="D19" s="49" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="B20" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
-        <v>2.6</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
+        <v>3.7</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="49" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="B21" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
-        <v>3.57402777777778</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
+        <v>4.1</v>
       </c>
       <c r="C21" s="46"/>
       <c r="D21" s="49" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A22)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D22)</f>
-        <v>3.6</v>
+      <c r="A22" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="48" t="n">
+        <f aca="false">AVERAGE(B23:B40)</f>
+        <v>3.28916666666667</v>
       </c>
       <c r="C22" s="46"/>
-      <c r="D22" s="49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>120</v>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A23)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D23)</f>
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="C23" s="46"/>
       <c r="D23" s="49" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="C24" s="46"/>
       <c r="D24" s="49" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
-        <v>2.8</v>
+        <v>3.57402777777778</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="49" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
-        <v>3.59875</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>124</v>
-      </c>
+        <v>2.9</v>
+      </c>
+      <c r="C27" s="46"/>
       <c r="D27" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
-        <v>3.94083333333333</v>
-      </c>
-      <c r="C28" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D28" s="49" t="n">
         <v>3.9</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>3.65388888888889</v>
+        <v>2.8</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="49" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E29" s="47" t="s">
-        <v>127</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="50" t="n">
+        <v>81</v>
+      </c>
+      <c r="B30" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
-        <v>3.95583333333333</v>
+        <v>2.6</v>
       </c>
       <c r="C30" s="46"/>
-      <c r="D30" s="50" t="n">
-        <v>4</v>
+      <c r="D30" s="49" t="n">
+        <v>2.6</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" s="50" t="n">
+        <v>83</v>
+      </c>
+      <c r="B31" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
-        <v>2.94666666666667</v>
-      </c>
-      <c r="C31" s="46"/>
-      <c r="D31" s="50" t="n">
-        <v>2.9</v>
+        <v>3.59875</v>
+      </c>
+      <c r="C31" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D31" s="49" t="n">
+        <v>3.6</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B32" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
-        <v>3.935</v>
-      </c>
-      <c r="C32" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="D32" s="50" t="n">
+        <v>3.94083333333333</v>
+      </c>
+      <c r="C32" s="46"/>
+      <c r="D32" s="49" t="n">
         <v>3.9</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="49" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B33" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
-        <v>3</v>
+        <v>3.65388888888889</v>
       </c>
       <c r="C33" s="46"/>
       <c r="D33" s="49" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B34" s="49" t="n">
+        <v>46</v>
+      </c>
+      <c r="B34" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
-        <v>2</v>
+        <v>3.95583333333333</v>
       </c>
       <c r="C34" s="46"/>
-      <c r="D34" s="49" t="n">
-        <v>2</v>
+      <c r="D34" s="50" t="n">
+        <v>4</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="48" t="n">
-        <f aca="false">AVERAGE(B36:B46)</f>
-        <v>3.26275505050505</v>
+      <c r="A35" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
+        <v>2.94666666666667</v>
       </c>
       <c r="C35" s="46"/>
-    </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D35" s="50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.5</v>
-      </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="49" t="n">
-        <v>3.5</v>
+        <v>40</v>
+      </c>
+      <c r="B36" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
+        <v>3.935</v>
+      </c>
+      <c r="C36" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="D36" s="50" t="n">
+        <v>3.9</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="B37" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>3.43088888888889</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
+        <v>3</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="49" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="B38" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>3.7</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
+        <v>2</v>
       </c>
       <c r="C38" s="46"/>
       <c r="D38" s="49" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="B39" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>2.6</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
+        <v>3.9</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="B40" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>3.77816666666667</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
+        <v>3.9</v>
       </c>
       <c r="C40" s="46"/>
       <c r="D40" s="49" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>2.59388888888889</v>
+      <c r="A41" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="48" t="n">
+        <f aca="false">AVERAGE(B42:B55)</f>
+        <v>3.33502182539683</v>
       </c>
       <c r="C41" s="46"/>
-      <c r="D41" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E41" s="47" t="s">
-        <v>140</v>
-      </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>3.23902777777778</v>
+        <v>3.5</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>2.6</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>3.58416666666667</v>
+        <v>3.7</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="B45" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
-        <v>2.94083333333333</v>
+        <v>2.6</v>
       </c>
       <c r="C45" s="46"/>
       <c r="D45" s="49" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="B46" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
-        <v>3.92333333333333</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C46" s="46"/>
       <c r="D46" s="49" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" s="48" t="n">
-        <f aca="false">AVERAGE(B48:B52)</f>
-        <v>3.2865</v>
+      <c r="A47" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
+        <v>2.59388888888889</v>
       </c>
       <c r="C47" s="46"/>
+      <c r="D47" s="49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E47" s="47" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B48" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.6</v>
-      </c>
-      <c r="C48" s="46" t="s">
-        <v>124</v>
-      </c>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
+        <v>3.23902777777778</v>
+      </c>
+      <c r="C48" s="46"/>
       <c r="D48" s="49" t="n">
         <v>3.6</v>
       </c>
+      <c r="E48" s="47" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="B49" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.33761111111111</v>
-      </c>
-      <c r="C49" s="46" t="s">
-        <v>124</v>
-      </c>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
+        <v>2.6</v>
+      </c>
+      <c r="C49" s="46"/>
       <c r="D49" s="49" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
+      </c>
+      <c r="E49" s="47" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B50" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
-        <v>3.2</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
+        <v>3.58416666666667</v>
       </c>
       <c r="C50" s="46"/>
       <c r="D50" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B51" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C51" s="46" t="s">
-        <v>130</v>
-      </c>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
+        <v>2.94083333333333</v>
+      </c>
+      <c r="C51" s="46"/>
       <c r="D51" s="49" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="E51" s="47" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B52" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
-        <v>2.39488888888889</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
+        <v>3.92333333333333</v>
       </c>
       <c r="C52" s="46"/>
       <c r="D52" s="49" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
+      </c>
+      <c r="E52" s="47" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="48" t="n">
-        <f aca="false">AVERAGE(B54:B58)</f>
-        <v>3.42807</v>
+      <c r="A53" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B53" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
+        <v>3.7</v>
       </c>
       <c r="C53" s="46"/>
+      <c r="D53" s="49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E53" s="47" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B54" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>3.6</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
+        <v>3.2</v>
       </c>
       <c r="C54" s="46"/>
       <c r="D54" s="49" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
+      </c>
+      <c r="E54" s="47" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="B55" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>3.8</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
+        <v>3.9</v>
       </c>
       <c r="C55" s="46"/>
       <c r="D55" s="49" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
+      </c>
+      <c r="E55" s="47" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="B56" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>2.7</v>
+      <c r="A56" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="48" t="n">
+        <f aca="false">AVERAGE(B57:B61)</f>
+        <v>3.2865</v>
       </c>
       <c r="C56" s="46"/>
-      <c r="D56" s="49" t="n">
-        <v>2.7</v>
-      </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B57" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
-        <v>3.3</v>
-      </c>
-      <c r="C57" s="46"/>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
+        <v>3.6</v>
+      </c>
+      <c r="C57" s="46" t="s">
+        <v>132</v>
+      </c>
       <c r="D57" s="49" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B58" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
-        <v>3.74035</v>
-      </c>
-      <c r="C58" s="46"/>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
+        <v>3.33761111111111</v>
+      </c>
+      <c r="C58" s="46" t="s">
+        <v>132</v>
+      </c>
       <c r="D58" s="49" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59" s="48" t="n">
-        <f aca="false">AVERAGE(B60:B61)</f>
-        <v>3.05</v>
+      <c r="A59" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
+        <v>3.2</v>
       </c>
       <c r="C59" s="46"/>
-    </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D59" s="49" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B60" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>2.7</v>
-      </c>
-      <c r="C60" s="46"/>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C60" s="46" t="s">
+        <v>138</v>
+      </c>
       <c r="D60" s="49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E60" s="47" t="s">
-        <v>145</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="49" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="B61" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
-        <v>3.4</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
+        <v>2.39488888888889</v>
       </c>
       <c r="C61" s="46"/>
       <c r="D61" s="49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E61" s="47" t="s">
-        <v>146</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B62" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
-        <v>1</v>
+      <c r="A62" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="48" t="n">
+        <f aca="false">AVERAGE(B63:B67)</f>
+        <v>3.42807</v>
       </c>
       <c r="C62" s="46"/>
-      <c r="D62" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="47" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B63" s="48" t="n">
-        <f aca="false">AVERAGE(B64:B65)</f>
-        <v>2.25194444444444</v>
+      <c r="A63" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B63" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
+        <v>3.6</v>
       </c>
       <c r="C63" s="46"/>
+      <c r="D63" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B64" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
-        <v>2.30388888888889</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
+        <v>3.8</v>
       </c>
       <c r="C64" s="46"/>
       <c r="D64" s="49" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B65" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
-        <v>2.2</v>
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
+        <v>2.7</v>
       </c>
       <c r="C65" s="46"/>
       <c r="D65" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E65" s="47" t="s">
-        <v>148</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A66)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D66)</f>
+        <v>3.3</v>
+      </c>
+      <c r="C66" s="46"/>
+      <c r="D66" s="49" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
+        <v>3.74035</v>
+      </c>
+      <c r="C67" s="46"/>
+      <c r="D67" s="49" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" s="48" t="n">
+        <f aca="false">AVERAGE(B69:B70)</f>
+        <v>3.05</v>
+      </c>
+      <c r="C68" s="46"/>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A69)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D69)</f>
+        <v>2.7</v>
+      </c>
+      <c r="C69" s="46"/>
+      <c r="D69" s="49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E69" s="47" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A70)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D70)</f>
+        <v>3.4</v>
+      </c>
+      <c r="C70" s="46"/>
+      <c r="D70" s="49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A71)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D71)</f>
+        <v>1</v>
+      </c>
+      <c r="C71" s="46"/>
+      <c r="D71" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="47" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B72" s="48" t="n">
+        <f aca="false">AVERAGE(B73:B74)</f>
+        <v>2.25194444444444</v>
+      </c>
+      <c r="C72" s="46"/>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A73)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D73)</f>
+        <v>2.30388888888889</v>
+      </c>
+      <c r="C73" s="46"/>
+      <c r="D73" s="49" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A74)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D74)</f>
+        <v>2.2</v>
+      </c>
+      <c r="C74" s="46"/>
+      <c r="D74" s="49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E74" s="47" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="B66" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A66)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D66)</f>
+      <c r="B75" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A75)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D75)</f>
         <v>2.43069444444444</v>
       </c>
-      <c r="D66" s="49" t="n">
+      <c r="D75" s="49" t="n">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="48" t="n">
+        <f aca="false">AVERAGE(B77:B88)</f>
+        <v>3.88333333333333</v>
+      </c>
+      <c r="C76" s="46"/>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A77)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D77)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C77" s="46"/>
+      <c r="D77" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E77" s="47" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A78)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D78)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C78" s="46"/>
+      <c r="D78" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E78" s="47" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="49" t="s">
+        <v>169</v>
+      </c>
+      <c r="B79" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A79)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D79)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C79" s="46"/>
+      <c r="D79" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E79" s="47" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="B80" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A80)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D80)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C80" s="46"/>
+      <c r="D80" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E80" s="47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="B81" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A81)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D81)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C81" s="46"/>
+      <c r="D81" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E81" s="47" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A82)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D82)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C82" s="46"/>
+      <c r="D82" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E82" s="47" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A83)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D83)</f>
+        <v>3.7</v>
+      </c>
+      <c r="C83" s="46"/>
+      <c r="D83" s="49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E83" s="47" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B84" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A84)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D84)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C84" s="46"/>
+      <c r="D84" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E84" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="B85" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A85)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D85)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C85" s="46"/>
+      <c r="D85" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E85" s="47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B86" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A86)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D86)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C86" s="46"/>
+      <c r="D86" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E86" s="47" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B87" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A87)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D87)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C87" s="46"/>
+      <c r="D87" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E87" s="47" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A88)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D88)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C88" s="46"/>
+      <c r="D88" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E88" s="47" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -26794,7 +27236,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26805,16 +27247,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26903,59 +27345,59 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7)</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="49" t="n">
+        <f aca="false">IFERROR(C7/B7,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7)</f>
+      <c r="B8" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8)</f>
         <v>14</v>
       </c>
-      <c r="C7" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A7,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+      <c r="C8" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>4</v>
       </c>
-      <c r="D7" s="48" t="n">
-        <f aca="false">IFERROR(C7/B7,0)</f>
+      <c r="D8" s="48" t="n">
+        <f aca="false">IFERROR(C8/B8,0)</f>
         <v>0.285714285714286</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8)</f>
-        <v>4</v>
-      </c>
-      <c r="C8" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
-      </c>
-      <c r="D8" s="49" t="n">
-        <f aca="false">IFERROR(C8/B8,0)</f>
-        <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="49" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B9" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C9" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A9,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="49" t="n">
         <f aca="false">IFERROR(C9/B9,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="49" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B10" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A10)</f>
@@ -26972,7 +27414,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="49" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B11" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A11)</f>
@@ -26989,7 +27431,7 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="49" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B12" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A12)</f>
@@ -27006,11 +27448,11 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="49" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="B13" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A13,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27023,11 +27465,11 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="49" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="B14" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C14" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A14,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27040,28 +27482,28 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="49" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B15" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A15,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="49" t="n">
         <f aca="false">IFERROR(C15/B15,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="49" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="B16" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C16" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A16,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27069,53 +27511,53 @@
       </c>
       <c r="D16" s="49" t="n">
         <f aca="false">IFERROR(C16/B16,0)</f>
-        <v>0.166666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="49" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B17" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C17" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="49" t="n">
         <f aca="false">IFERROR(C17/B17,0)</f>
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18)</f>
-        <v>12</v>
-      </c>
-      <c r="C18" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>5</v>
-      </c>
-      <c r="D18" s="48" t="n">
+      <c r="A18" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18)</f>
+        <v>1</v>
+      </c>
+      <c r="C18" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A18,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="49" t="n">
         <f aca="false">IFERROR(C18/B18,0)</f>
-        <v>0.416666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="B19" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
         <v>0</v>
       </c>
       <c r="C19" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A19,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D19" s="49" t="n">
@@ -27125,14 +27567,14 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="B20" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
         <v>0</v>
       </c>
       <c r="C20" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A20,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A20,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D20" s="49" t="n">
@@ -27142,14 +27584,14 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="B21" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
+        <v>0</v>
       </c>
       <c r="C21" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A21,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D21" s="49" t="n">
@@ -27158,25 +27600,25 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22)</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="49" t="n">
+      <c r="A22" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A22)</f>
+        <v>12</v>
+      </c>
+      <c r="C22" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>5</v>
+      </c>
+      <c r="D22" s="48" t="n">
         <f aca="false">IFERROR(C22/B22,0)</f>
-        <v>0</v>
+        <v>0.416666666666667</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B23" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A23)</f>
@@ -27193,7 +27635,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
@@ -27210,11 +27652,11 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27227,7 +27669,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
@@ -27244,11 +27686,11 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27261,28 +27703,28 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="49" t="n">
         <f aca="false">IFERROR(C28/B28,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27295,41 +27737,41 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="49" t="n">
         <f aca="false">IFERROR(C30/B30,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D31" s="49" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
-        <v>0.666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
@@ -27346,11 +27788,11 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="49" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="B33" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C33" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27363,65 +27805,65 @@
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="B34" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="49" t="n">
         <f aca="false">IFERROR(C34/B34,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A35)</f>
-        <v>11</v>
-      </c>
-      <c r="C35" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D35" s="48" t="n">
+      <c r="A35" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
+        <v>3</v>
+      </c>
+      <c r="C35" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>2</v>
+      </c>
+      <c r="D35" s="49" t="n">
         <f aca="false">IFERROR(C35/B35,0)</f>
-        <v>0.272727272727273</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B36" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
+        <v>1</v>
       </c>
       <c r="C36" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
       </c>
       <c r="D36" s="49" t="n">
         <f aca="false">IFERROR(C36/B36,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="B37" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
+        <v>0</v>
       </c>
       <c r="C37" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A37,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A37,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D37" s="49" t="n">
@@ -27431,14 +27873,14 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="B38" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
         <v>0</v>
       </c>
       <c r="C38" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D38" s="49" t="n">
@@ -27448,14 +27890,14 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="B39" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
         <v>0</v>
       </c>
       <c r="C39" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D39" s="49" t="n">
@@ -27465,45 +27907,45 @@
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="49" t="s">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="B40" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
+        <v>0</v>
       </c>
       <c r="C40" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
       </c>
       <c r="D40" s="49" t="n">
         <f aca="false">IFERROR(C40/B40,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="B41" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>1</v>
-      </c>
-      <c r="C41" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D41" s="49" t="n">
+      <c r="A41" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B41" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A41)</f>
+        <v>11</v>
+      </c>
+      <c r="C41" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D41" s="48" t="n">
         <f aca="false">IFERROR(C41/B41,0)</f>
-        <v>0</v>
+        <v>0.272727272727273</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27516,11 +27958,11 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27533,11 +27975,11 @@
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27550,28 +27992,28 @@
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="B45" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C45" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="49" t="n">
         <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="B46" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27579,36 +28021,36 @@
       </c>
       <c r="D46" s="49" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B47" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A47)</f>
-        <v>2</v>
-      </c>
-      <c r="C47" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="48" t="n">
+      <c r="A47" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
+        <v>1</v>
+      </c>
+      <c r="C47" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="49" t="n">
         <f aca="false">IFERROR(C47/B47,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B48" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
+        <v>2</v>
       </c>
       <c r="C48" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D48" s="49" t="n">
@@ -27618,14 +28060,14 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="B49" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
+        <v>0</v>
       </c>
       <c r="C49" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A49,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A49,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D49" s="49" t="n">
@@ -27635,14 +28077,14 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B50" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
+        <v>2</v>
       </c>
       <c r="C50" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D50" s="49" t="n">
@@ -27652,65 +28094,65 @@
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B51" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
+        <v>2</v>
       </c>
       <c r="C51" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
       </c>
       <c r="D51" s="49" t="n">
         <f aca="false">IFERROR(C51/B51,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
+        <v>2</v>
       </c>
       <c r="C52" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>1</v>
       </c>
       <c r="D52" s="49" t="n">
         <f aca="false">IFERROR(C52/B52,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A53)</f>
-        <v>1</v>
-      </c>
-      <c r="C53" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A53,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D53" s="48" t="n">
+      <c r="A53" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B53" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
+        <v>0</v>
+      </c>
+      <c r="C53" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A53,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D53" s="49" t="n">
         <f aca="false">IFERROR(C53/B53,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B54" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
         <v>0</v>
       </c>
       <c r="C54" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A54,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D54" s="49" t="n">
@@ -27720,14 +28162,14 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="49" t="s">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="B55" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
         <v>0</v>
       </c>
       <c r="C55" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D55" s="49" t="n">
@@ -27736,32 +28178,32 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="B56" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>0</v>
-      </c>
-      <c r="C56" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D56" s="49" t="n">
+      <c r="A56" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A56)</f>
+        <v>2</v>
+      </c>
+      <c r="C56" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="48" t="n">
         <f aca="false">IFERROR(C56/B56,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B57" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
         <v>0</v>
       </c>
       <c r="C57" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D57" s="49" t="n">
@@ -27771,14 +28213,14 @@
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
         <v>1</v>
       </c>
       <c r="C58" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D58" s="49" t="n">
@@ -27787,32 +28229,32 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A59)</f>
-        <v>0</v>
-      </c>
-      <c r="C59" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A59,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D59" s="48" t="n">
+      <c r="A59" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A59,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="49" t="n">
         <f aca="false">IFERROR(C59/B59,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B60" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
         <v>0</v>
       </c>
       <c r="C60" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A60,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A60,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D60" s="49" t="n">
@@ -27822,14 +28264,14 @@
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="49" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="B61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
+        <v>1</v>
       </c>
       <c r="C61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D61" s="49" t="n">
@@ -27838,49 +28280,49 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
-        <v>0</v>
-      </c>
-      <c r="C62" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="49" t="n">
+      <c r="A62" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62)</f>
+        <v>1</v>
+      </c>
+      <c r="C62" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="48" t="n">
         <f aca="false">IFERROR(C62/B62,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B63" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A63)</f>
-        <v>4</v>
-      </c>
-      <c r="C63" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D63" s="48" t="n">
+      <c r="A63" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B63" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
+        <v>0</v>
+      </c>
+      <c r="C63" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A63,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D63" s="49" t="n">
         <f aca="false">IFERROR(C63/B63,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B64" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
+        <v>0</v>
       </c>
       <c r="C64" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A64,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D64" s="49" t="n">
@@ -27890,14 +28332,14 @@
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B65" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
         <v>0</v>
       </c>
       <c r="C65" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D65" s="49" t="n">
@@ -27907,18 +28349,392 @@
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="49" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="B66" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A66)</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A66)</f>
+        <v>0</v>
       </c>
       <c r="C66" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
         <v>0</v>
       </c>
       <c r="D66" s="49" t="n">
         <f aca="false">IFERROR(C66/B66,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B67" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
+        <v>1</v>
+      </c>
+      <c r="C67" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="49" t="n">
+        <f aca="false">IFERROR(C67/B67,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B68" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A68)</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="48" t="n">
+        <f aca="false">IFERROR(C68/B68,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A69)</f>
+        <v>0</v>
+      </c>
+      <c r="C69" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A69,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D69" s="49" t="n">
+        <f aca="false">IFERROR(C69/B69,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A70)</f>
+        <v>0</v>
+      </c>
+      <c r="C70" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A70,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D70" s="49" t="n">
+        <f aca="false">IFERROR(C70/B70,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A71)</f>
+        <v>0</v>
+      </c>
+      <c r="C71" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A71,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D71" s="49" t="n">
+        <f aca="false">IFERROR(C71/B71,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B72" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A72)</f>
+        <v>4</v>
+      </c>
+      <c r="C72" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A72,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="48" t="n">
+        <f aca="false">IFERROR(C72/B72,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A73)</f>
+        <v>3</v>
+      </c>
+      <c r="C73" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A73,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="49" t="n">
+        <f aca="false">IFERROR(C73/B73,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="B74" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A74)</f>
+        <v>0</v>
+      </c>
+      <c r="C74" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A74,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="49" t="n">
+        <f aca="false">IFERROR(C74/B74,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B75" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A75)</f>
+        <v>1</v>
+      </c>
+      <c r="C75" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A75,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D75" s="49" t="n">
+        <f aca="false">IFERROR(C75/B75,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A76)</f>
+        <v>0</v>
+      </c>
+      <c r="C76" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A76,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D76" s="48" t="n">
+        <f aca="false">IFERROR(C76/B76,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A77)</f>
+        <v>0</v>
+      </c>
+      <c r="C77" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A77,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D77" s="49" t="n">
+        <f aca="false">IFERROR(C77/B77,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78)</f>
+        <v>0</v>
+      </c>
+      <c r="C78" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D78" s="49" t="n">
+        <f aca="false">IFERROR(C78/B78,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="49" t="s">
+        <v>169</v>
+      </c>
+      <c r="B79" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A79)</f>
+        <v>0</v>
+      </c>
+      <c r="C79" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A79,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D79" s="49" t="n">
+        <f aca="false">IFERROR(C79/B79,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="B80" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A80)</f>
+        <v>0</v>
+      </c>
+      <c r="C80" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A80,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D80" s="49" t="n">
+        <f aca="false">IFERROR(C80/B80,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="B81" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A81)</f>
+        <v>0</v>
+      </c>
+      <c r="C81" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A81,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D81" s="49" t="n">
+        <f aca="false">IFERROR(C81/B81,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A82)</f>
+        <v>0</v>
+      </c>
+      <c r="C82" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A82,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D82" s="49" t="n">
+        <f aca="false">IFERROR(C82/B82,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B83" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A83)</f>
+        <v>0</v>
+      </c>
+      <c r="C83" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A83,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D83" s="49" t="n">
+        <f aca="false">IFERROR(C83/B83,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B84" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84)</f>
+        <v>0</v>
+      </c>
+      <c r="C84" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="49" t="n">
+        <f aca="false">IFERROR(C84/B84,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="B85" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A85)</f>
+        <v>0</v>
+      </c>
+      <c r="C85" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A85,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="49" t="n">
+        <f aca="false">IFERROR(C85/B85,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B86" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86)</f>
+        <v>0</v>
+      </c>
+      <c r="C86" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D86" s="49" t="n">
+        <f aca="false">IFERROR(C86/B86,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="B87" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A87)</f>
+        <v>0</v>
+      </c>
+      <c r="C87" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A87,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D87" s="49" t="n">
+        <f aca="false">IFERROR(C87/B87,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B88" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A88)</f>
+        <v>0</v>
+      </c>
+      <c r="C88" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A88,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D88" s="49" t="n">
+        <f aca="false">IFERROR(C88/B88,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -27957,40 +28773,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="F1" s="51" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25886,7 +25886,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -26226,7 +26226,7 @@
         <v>30</v>
       </c>
       <c r="B22" s="48" t="n">
-        <f aca="false">AVERAGE(B23:B40)</f>
+        <f aca="false">AVERAGE(B23:B39)</f>
         <v>3.28916666666667</v>
       </c>
       <c r="C22" s="46"/>
@@ -26249,250 +26249,250 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A24)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D24)</f>
-        <v>2.6</v>
+        <v>3.57402777777778</v>
       </c>
       <c r="C24" s="46"/>
       <c r="D24" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A25)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D25)</f>
-        <v>3.57402777777778</v>
+        <v>3.6</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A26)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D26)</f>
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="C26" s="46"/>
       <c r="D26" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A27)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D27)</f>
-        <v>2.9</v>
-      </c>
-      <c r="C27" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>103</v>
+      </c>
       <c r="D27" s="49" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A28)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D28)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C28" s="46" t="s">
-        <v>103</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="C28" s="46"/>
       <c r="D28" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E28" s="47" t="s">
-        <v>130</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="C29" s="46"/>
       <c r="D29" s="49" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B30" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A30)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D30)</f>
-        <v>2.6</v>
-      </c>
-      <c r="C30" s="46"/>
+        <v>3.59875</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>132</v>
+      </c>
       <c r="D30" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A31)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D31)</f>
-        <v>3.59875</v>
-      </c>
-      <c r="C31" s="46" t="s">
-        <v>132</v>
-      </c>
+        <v>3.94083333333333</v>
+      </c>
+      <c r="C31" s="46"/>
       <c r="D31" s="49" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A32)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D32)</f>
-        <v>3.94083333333333</v>
+        <v>3.65388888888889</v>
       </c>
       <c r="C32" s="46"/>
       <c r="D32" s="49" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="49" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" s="49" t="n">
+        <v>46</v>
+      </c>
+      <c r="B33" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A33)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D33)</f>
-        <v>3.65388888888889</v>
+        <v>3.95583333333333</v>
       </c>
       <c r="C33" s="46"/>
-      <c r="D33" s="49" t="n">
-        <v>3.7</v>
+      <c r="D33" s="50" t="n">
+        <v>4</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B34" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A34)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D34)</f>
-        <v>3.95583333333333</v>
+        <v>2.94666666666667</v>
       </c>
       <c r="C34" s="46"/>
       <c r="D34" s="50" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B35" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A35)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D35)</f>
-        <v>2.94666666666667</v>
-      </c>
-      <c r="C35" s="46"/>
+        <v>3.935</v>
+      </c>
+      <c r="C35" s="46" t="s">
+        <v>138</v>
+      </c>
       <c r="D35" s="50" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="50" t="n">
+        <v>140</v>
+      </c>
+      <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
-        <v>3.935</v>
-      </c>
-      <c r="C36" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="D36" s="50" t="n">
-        <v>3.9</v>
+        <v>3</v>
+      </c>
+      <c r="C36" s="46"/>
+      <c r="D36" s="49" t="n">
+        <v>3</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A37)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D37)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" s="46"/>
       <c r="D37" s="49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="C38" s="46"/>
       <c r="D38" s="49" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
@@ -26503,534 +26503,534 @@
         <v>3.9</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="B40" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>3.9</v>
+      <c r="A40" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="48" t="n">
+        <f aca="false">AVERAGE(B41:B54)</f>
+        <v>3.33502182539683</v>
       </c>
       <c r="C40" s="46"/>
-      <c r="D40" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E40" s="47" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="48" t="n">
-        <f aca="false">AVERAGE(B42:B55)</f>
-        <v>3.33502182539683</v>
+      <c r="A41" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
+        <v>3.5</v>
       </c>
       <c r="C41" s="46"/>
+      <c r="D41" s="49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E41" s="47" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>3.5</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>3.43088888888889</v>
+        <v>3.7</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B45" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
-        <v>2.6</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C45" s="46"/>
       <c r="D45" s="49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B46" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
-        <v>3.77816666666667</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C46" s="46"/>
       <c r="D46" s="49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>2.59388888888889</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C47" s="46"/>
       <c r="D47" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.23902777777778</v>
+        <v>2.6</v>
       </c>
       <c r="C48" s="46"/>
       <c r="D48" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>2.6</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C49" s="46"/>
       <c r="D49" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E49" s="47" t="s">
-        <v>154</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
-        <v>3.58416666666667</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C50" s="46"/>
       <c r="D50" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
+      </c>
+      <c r="E50" s="47" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B51" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
-        <v>2.94083333333333</v>
+        <v>3.92333333333333</v>
       </c>
       <c r="C51" s="46"/>
       <c r="D51" s="49" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E51" s="47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
-        <v>3.92333333333333</v>
+        <v>3.7</v>
       </c>
       <c r="C52" s="46"/>
       <c r="D52" s="49" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="C53" s="46"/>
       <c r="D53" s="49" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="C54" s="46"/>
       <c r="D54" s="49" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="B55" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>3.9</v>
+      <c r="A55" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="48" t="n">
+        <f aca="false">AVERAGE(B56:B60)</f>
+        <v>3.2865</v>
       </c>
       <c r="C55" s="46"/>
-      <c r="D55" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E55" s="47" t="s">
-        <v>161</v>
-      </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56" s="48" t="n">
-        <f aca="false">AVERAGE(B57:B61)</f>
-        <v>3.2865</v>
-      </c>
-      <c r="C56" s="46"/>
+      <c r="A56" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
+        <v>3.6</v>
+      </c>
+      <c r="C56" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D56" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B57" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
-        <v>3.6</v>
+        <v>3.33761111111111</v>
       </c>
       <c r="C57" s="46" t="s">
         <v>132</v>
       </c>
       <c r="D57" s="49" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B58" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
-        <v>3.33761111111111</v>
-      </c>
-      <c r="C58" s="46" t="s">
-        <v>132</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C58" s="46"/>
       <c r="D58" s="49" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C59" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C59" s="46" t="s">
+        <v>138</v>
+      </c>
       <c r="D59" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B60" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C60" s="46" t="s">
-        <v>138</v>
-      </c>
+        <v>2.39488888888889</v>
+      </c>
+      <c r="C60" s="46"/>
       <c r="D60" s="49" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B61" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
-        <v>2.39488888888889</v>
+      <c r="A61" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">AVERAGE(B62:B66)</f>
+        <v>3.42807</v>
       </c>
       <c r="C61" s="46"/>
-      <c r="D61" s="49" t="n">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">AVERAGE(B63:B67)</f>
-        <v>3.42807</v>
+      <c r="A62" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B62" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
+        <v>3.6</v>
       </c>
       <c r="C62" s="46"/>
+      <c r="D62" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="49" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="C64" s="46"/>
       <c r="D64" s="49" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B65" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="C65" s="46"/>
       <c r="D65" s="49" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A66)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D66)</f>
-        <v>3.3</v>
+        <v>3.74035</v>
       </c>
       <c r="C66" s="46"/>
       <c r="D66" s="49" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
-        <v>3.74035</v>
+      <c r="A67" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" s="48" t="n">
+        <f aca="false">AVERAGE(B68:B69)</f>
+        <v>3.05</v>
       </c>
       <c r="C67" s="46"/>
-      <c r="D67" s="49" t="n">
-        <v>3.7</v>
-      </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B68" s="48" t="n">
-        <f aca="false">AVERAGE(B69:B70)</f>
-        <v>3.05</v>
+      <c r="A68" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
+        <v>2.7</v>
       </c>
       <c r="C68" s="46"/>
+      <c r="D68" s="49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E68" s="47" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B69" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A69)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D69)</f>
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="C69" s="46"/>
       <c r="D69" s="49" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B70" s="49" t="n">
+        <v>84</v>
+      </c>
+      <c r="B70" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A70)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D70)</f>
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="C70" s="46"/>
-      <c r="D70" s="49" t="n">
-        <v>3.4</v>
+      <c r="D70" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B71" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A71)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D71)</f>
-        <v>1</v>
+      <c r="A71" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B71" s="48" t="n">
+        <f aca="false">AVERAGE(B72:B73)</f>
+        <v>2.25194444444444</v>
       </c>
       <c r="C71" s="46"/>
-      <c r="D71" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="47" t="s">
-        <v>164</v>
-      </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B72" s="48" t="n">
-        <f aca="false">AVERAGE(B73:B74)</f>
-        <v>2.25194444444444</v>
+      <c r="A72" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A72)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D72)</f>
+        <v>2.30388888888889</v>
       </c>
       <c r="C72" s="46"/>
+      <c r="D72" s="49" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B73" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A73)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D73)</f>
-        <v>2.30388888888889</v>
+        <v>2.2</v>
       </c>
       <c r="C73" s="46"/>
       <c r="D73" s="49" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="E73" s="47" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B74" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A74)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D74)</f>
-        <v>2.2</v>
-      </c>
-      <c r="C74" s="46"/>
+        <v>2.43069444444444</v>
+      </c>
       <c r="D74" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E74" s="47" t="s">
-        <v>165</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B75" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A75)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D75)</f>
-        <v>2.43069444444444</v>
-      </c>
-      <c r="D75" s="49" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="A75" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" s="48" t="n">
+        <f aca="false">AVERAGE(B76:B87)</f>
+        <v>3.88333333333333</v>
+      </c>
+      <c r="C75" s="46"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="B76" s="48" t="n">
-        <f aca="false">AVERAGE(B77:B88)</f>
-        <v>3.88333333333333</v>
+      <c r="A76" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A76)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D76)</f>
+        <v>3.9</v>
       </c>
       <c r="C76" s="46"/>
+      <c r="D76" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E76" s="47" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="49" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B77" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A77)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D77)</f>
@@ -27041,12 +27041,12 @@
         <v>3.9</v>
       </c>
       <c r="E77" s="47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="49" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="B78" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A78)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D78)</f>
@@ -27057,12 +27057,12 @@
         <v>3.9</v>
       </c>
       <c r="E78" s="47" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="49" t="s">
-        <v>169</v>
+        <v>119</v>
       </c>
       <c r="B79" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A79)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D79)</f>
@@ -27073,12 +27073,12 @@
         <v>3.9</v>
       </c>
       <c r="E79" s="47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="49" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="B80" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A80)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D80)</f>
@@ -27089,12 +27089,12 @@
         <v>3.9</v>
       </c>
       <c r="E80" s="47" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="49" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B81" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A81)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D81)</f>
@@ -27105,44 +27105,44 @@
         <v>3.9</v>
       </c>
       <c r="E81" s="47" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="49" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B82" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A82)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D82)</f>
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="C82" s="46"/>
       <c r="D82" s="49" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E82" s="47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="49" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="B83" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A83)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D83)</f>
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="C83" s="46"/>
       <c r="D83" s="49" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="E83" s="47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="49" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="B84" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A84)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D84)</f>
@@ -27153,12 +27153,12 @@
         <v>3.9</v>
       </c>
       <c r="E84" s="47" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="49" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="B85" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A85)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D85)</f>
@@ -27169,12 +27169,12 @@
         <v>3.9</v>
       </c>
       <c r="E85" s="47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="49" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="B86" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A86)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D86)</f>
@@ -27185,12 +27185,12 @@
         <v>3.9</v>
       </c>
       <c r="E86" s="47" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="49" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="B87" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A87)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D87)</f>
@@ -27201,22 +27201,6 @@
         <v>3.9</v>
       </c>
       <c r="E87" s="47" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="B88" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A88)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D88)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C88" s="46"/>
-      <c r="D88" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E88" s="47" t="s">
         <v>180</v>
       </c>
     </row>
@@ -27236,7 +27220,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -27635,11 +27619,11 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="49" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B24" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A24,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27652,11 +27636,11 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A25,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27669,7 +27653,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="49" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B26" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A26)</f>
@@ -27686,7 +27670,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="49" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B27" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A27)</f>
@@ -27703,7 +27687,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="49" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B28" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A28)</f>
@@ -27720,7 +27704,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="49" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
@@ -27737,11 +27721,11 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="49" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A30,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27754,7 +27738,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="49" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31)</f>
@@ -27762,101 +27746,101 @@
       </c>
       <c r="C31" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A31,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" s="49" t="n">
         <f aca="false">IFERROR(C31/B31,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="49" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="B32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C32" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A32,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="49" t="n">
         <f aca="false">IFERROR(C32/B32,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="49" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="B33" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A33,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="49" t="n">
         <f aca="false">IFERROR(C33/B33,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="49" t="s">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B34" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A34)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A34,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="49" t="n">
         <f aca="false">IFERROR(C34/B34,0)</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A35)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A35,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="49" t="n">
         <f aca="false">IFERROR(C35/B35,0)</f>
-        <v>0.666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="49" t="n">
         <f aca="false">IFERROR(C36/B36,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="49" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="B37" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A37)</f>
@@ -27873,7 +27857,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -27890,7 +27874,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
@@ -27906,46 +27890,46 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="B40" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>0</v>
-      </c>
-      <c r="C40" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="49" t="n">
+      <c r="A40" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A40)</f>
+        <v>11</v>
+      </c>
+      <c r="C40" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D40" s="48" t="n">
         <f aca="false">IFERROR(C40/B40,0)</f>
-        <v>0</v>
+        <v>0.272727272727273</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A41)</f>
-        <v>11</v>
-      </c>
-      <c r="C41" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D41" s="48" t="n">
+      <c r="A41" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
+        <v>0</v>
+      </c>
+      <c r="C41" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="49" t="n">
         <f aca="false">IFERROR(C41/B41,0)</f>
-        <v>0.272727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27958,11 +27942,11 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27975,7 +27959,7 @@
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
@@ -27992,24 +27976,24 @@
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B45" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" s="49" t="n">
         <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B46" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
@@ -28017,20 +28001,20 @@
       </c>
       <c r="C46" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" s="49" t="n">
         <f aca="false">IFERROR(C46/B46,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28043,11 +28027,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28060,11 +28044,11 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A49,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28077,7 +28061,7 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
@@ -28085,16 +28069,16 @@
       </c>
       <c r="C50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A50,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50" s="49" t="n">
         <f aca="false">IFERROR(C50/B50,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B51" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
@@ -28111,24 +28095,24 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C52" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52" s="49" t="n">
         <f aca="false">IFERROR(C52/B52,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -28145,7 +28129,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>43</v>
+        <v>160</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28161,46 +28145,46 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="B55" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
-        <v>0</v>
-      </c>
-      <c r="C55" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D55" s="49" t="n">
+      <c r="A55" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B55" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A55)</f>
+        <v>2</v>
+      </c>
+      <c r="C55" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="48" t="n">
         <f aca="false">IFERROR(C55/B55,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B56" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A56)</f>
-        <v>2</v>
-      </c>
-      <c r="C56" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D56" s="48" t="n">
+      <c r="A56" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B56" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
+        <v>0</v>
+      </c>
+      <c r="C56" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="49" t="n">
         <f aca="false">IFERROR(C56/B56,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B57" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28213,11 +28197,11 @@
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B58" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A58,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28230,7 +28214,7 @@
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
@@ -28247,11 +28231,11 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B60" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A60,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28263,42 +28247,42 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
-        <v>1</v>
-      </c>
-      <c r="C61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="49" t="n">
+      <c r="A61" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+        <v>1</v>
+      </c>
+      <c r="C61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="48" t="n">
         <f aca="false">IFERROR(C61/B61,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62)</f>
-        <v>1</v>
-      </c>
-      <c r="C62" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D62" s="48" t="n">
+      <c r="A62" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B62" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
+        <v>0</v>
+      </c>
+      <c r="C62" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A62,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="49" t="n">
         <f aca="false">IFERROR(C62/B62,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
@@ -28315,7 +28299,7 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
@@ -28332,7 +28316,7 @@
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B65" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
@@ -28349,11 +28333,11 @@
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A66)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28365,42 +28349,42 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B67" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
-        <v>1</v>
-      </c>
-      <c r="C67" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="49" t="n">
+      <c r="A67" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B67" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A67)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="48" t="n">
         <f aca="false">IFERROR(C67/B67,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B68" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A68)</f>
-        <v>0</v>
-      </c>
-      <c r="C68" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="48" t="n">
+      <c r="A68" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
+        <v>0</v>
+      </c>
+      <c r="C68" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A68,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D68" s="49" t="n">
         <f aca="false">IFERROR(C68/B68,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B69" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A69)</f>
@@ -28417,7 +28401,7 @@
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="49" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B70" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A70)</f>
@@ -28433,46 +28417,46 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B71" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A71)</f>
-        <v>0</v>
-      </c>
-      <c r="C71" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A71,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D71" s="49" t="n">
+      <c r="A71" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B71" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A71)</f>
+        <v>4</v>
+      </c>
+      <c r="C71" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A71,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D71" s="48" t="n">
         <f aca="false">IFERROR(C71/B71,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B72" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A72)</f>
-        <v>4</v>
-      </c>
-      <c r="C72" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A72,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D72" s="48" t="n">
+      <c r="A72" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B72" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A72)</f>
+        <v>3</v>
+      </c>
+      <c r="C72" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A72,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="49" t="n">
         <f aca="false">IFERROR(C72/B72,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B73" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A73)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C73" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A73,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28485,11 +28469,11 @@
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B74" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A74)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A74,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28501,42 +28485,42 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B75" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A75)</f>
-        <v>1</v>
-      </c>
-      <c r="C75" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A75,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D75" s="49" t="n">
+      <c r="A75" s="47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B75" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A75)</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A75,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D75" s="48" t="n">
         <f aca="false">IFERROR(C75/B75,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="B76" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A76)</f>
-        <v>0</v>
-      </c>
-      <c r="C76" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A76,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="48" t="n">
+      <c r="A76" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A76)</f>
+        <v>0</v>
+      </c>
+      <c r="C76" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A76,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D76" s="49" t="n">
         <f aca="false">IFERROR(C76/B76,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="49" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B77" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A77)</f>
@@ -28553,7 +28537,7 @@
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="49" t="s">
-        <v>48</v>
+        <v>169</v>
       </c>
       <c r="B78" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78)</f>
@@ -28570,7 +28554,7 @@
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="49" t="s">
-        <v>169</v>
+        <v>119</v>
       </c>
       <c r="B79" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A79)</f>
@@ -28587,7 +28571,7 @@
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="49" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="B80" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A80)</f>
@@ -28604,7 +28588,7 @@
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="49" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="B81" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A81)</f>
@@ -28621,7 +28605,7 @@
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="49" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B82" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A82)</f>
@@ -28638,7 +28622,7 @@
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="49" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="B83" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A83)</f>
@@ -28655,7 +28639,7 @@
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="49" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="B84" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84)</f>
@@ -28672,7 +28656,7 @@
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="49" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="B85" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A85)</f>
@@ -28689,7 +28673,7 @@
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="49" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="B86" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86)</f>
@@ -28706,7 +28690,7 @@
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="49" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="B87" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A87)</f>
@@ -28718,23 +28702,6 @@
       </c>
       <c r="D87" s="49" t="n">
         <f aca="false">IFERROR(C87/B87,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="B88" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A88)</f>
-        <v>0</v>
-      </c>
-      <c r="C88" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A88,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D88" s="49" t="n">
-        <f aca="false">IFERROR(C88/B88,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="195">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -408,9 +408,6 @@
   </si>
   <si>
     <t xml:space="preserve">639396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">614175</t>
   </si>
   <si>
     <t xml:space="preserve">560454</t>
@@ -26227,7 +26224,7 @@
       </c>
       <c r="B22" s="48" t="n">
         <f aca="false">AVERAGE(B23:B39)</f>
-        <v>3.28916666666667</v>
+        <v>3.32970588235294</v>
       </c>
       <c r="C22" s="46"/>
     </row>
@@ -26260,7 +26257,7 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26276,7 +26273,7 @@
         <v>3.6</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26292,7 +26289,7 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26310,7 +26307,7 @@
         <v>3.9</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26339,7 +26336,7 @@
         <v>2.6</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26351,13 +26348,13 @@
         <v>3.59875</v>
       </c>
       <c r="C30" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D30" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26373,7 +26370,7 @@
         <v>3.9</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26389,7 +26386,7 @@
         <v>3.7</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26405,7 +26402,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26421,7 +26418,7 @@
         <v>2.9</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26433,18 +26430,18 @@
         <v>3.935</v>
       </c>
       <c r="C35" s="46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D35" s="50" t="n">
         <v>3.9</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
@@ -26455,7 +26452,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26471,12 +26468,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
@@ -26487,12 +26484,12 @@
         <v>3.9</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
@@ -26503,7 +26500,7 @@
         <v>3.9</v>
       </c>
       <c r="E39" s="47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26529,7 +26526,7 @@
         <v>3.5</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26545,7 +26542,7 @@
         <v>3.4</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26561,7 +26558,7 @@
         <v>3.7</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26577,7 +26574,7 @@
         <v>2.6</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26593,7 +26590,7 @@
         <v>3.8</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26609,7 +26606,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26625,7 +26622,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26641,7 +26638,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26670,7 +26667,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26686,12 +26683,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -26702,7 +26699,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26718,12 +26715,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -26734,7 +26731,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26756,7 +26753,7 @@
         <v>3.6</v>
       </c>
       <c r="C56" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D56" s="49" t="n">
         <v>3.6</v>
@@ -26771,7 +26768,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C57" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D57" s="49" t="n">
         <v>3.3</v>
@@ -26799,7 +26796,7 @@
         <v>3.9</v>
       </c>
       <c r="C59" s="46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D59" s="49" t="n">
         <v>3.9</v>
@@ -26916,7 +26913,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26932,7 +26929,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26948,7 +26945,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26987,7 +26984,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27004,7 +27001,7 @@
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="47" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B75" s="48" t="n">
         <f aca="false">AVERAGE(B76:B87)</f>
@@ -27025,7 +27022,7 @@
         <v>3.9</v>
       </c>
       <c r="E76" s="47" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27041,12 +27038,12 @@
         <v>3.9</v>
       </c>
       <c r="E77" s="47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="49" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B78" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A78)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D78)</f>
@@ -27057,7 +27054,7 @@
         <v>3.9</v>
       </c>
       <c r="E78" s="47" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27073,7 +27070,7 @@
         <v>3.9</v>
       </c>
       <c r="E79" s="47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27089,7 +27086,7 @@
         <v>3.9</v>
       </c>
       <c r="E80" s="47" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27105,7 +27102,7 @@
         <v>3.9</v>
       </c>
       <c r="E81" s="47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27121,7 +27118,7 @@
         <v>3.7</v>
       </c>
       <c r="E82" s="47" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27137,12 +27134,12 @@
         <v>3.9</v>
       </c>
       <c r="E83" s="47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B84" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A84)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D84)</f>
@@ -27153,7 +27150,7 @@
         <v>3.9</v>
       </c>
       <c r="E84" s="47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27169,12 +27166,12 @@
         <v>3.9</v>
       </c>
       <c r="E85" s="47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B86" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A86)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D86)</f>
@@ -27185,7 +27182,7 @@
         <v>3.9</v>
       </c>
       <c r="E86" s="47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27201,7 +27198,7 @@
         <v>3.9</v>
       </c>
       <c r="E87" s="47" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -27231,16 +27228,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="C1" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="D1" s="45" t="s">
         <v>183</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27823,7 +27820,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -27857,7 +27854,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -27874,7 +27871,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="49" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
@@ -28095,7 +28092,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -28129,7 +28126,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28486,7 +28483,7 @@
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="47" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B75" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A75)</f>
@@ -28537,7 +28534,7 @@
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="49" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B78" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78)</f>
@@ -28639,7 +28636,7 @@
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B84" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84)</f>
@@ -28673,7 +28670,7 @@
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B86" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86)</f>
@@ -28740,40 +28737,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="51" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="C1" s="51" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="D1" s="51" t="s">
         <v>187</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="E1" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="F1" s="51" t="s">
         <v>188</v>
       </c>
-      <c r="E1" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="F1" s="51" t="s">
+      <c r="G1" s="51" t="s">
         <v>189</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="H1" s="51" t="s">
         <v>190</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="I1" s="51" t="s">
         <v>191</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="J1" s="51" t="s">
         <v>192</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="K1" s="51" t="s">
         <v>193</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="L1" s="51" t="s">
         <v>194</v>
-      </c>
-      <c r="L1" s="51" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25883,7 +25883,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -26997,208 +26997,6 @@
       </c>
       <c r="D74" s="49" t="n">
         <v>2.4</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" s="48" t="n">
-        <f aca="false">AVERAGE(B76:B87)</f>
-        <v>3.88333333333333</v>
-      </c>
-      <c r="C75" s="46"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A76)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D76)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C76" s="46"/>
-      <c r="D76" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E76" s="47" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B77" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A77)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D77)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C77" s="46"/>
-      <c r="D77" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E77" s="47" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="B78" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A78)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D78)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C78" s="46"/>
-      <c r="D78" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E78" s="47" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="B79" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A79)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D79)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C79" s="46"/>
-      <c r="D79" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E79" s="47" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B80" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A80)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D80)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C80" s="46"/>
-      <c r="D80" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E80" s="47" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="B81" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A81)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D81)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C81" s="46"/>
-      <c r="D81" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E81" s="47" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="B82" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A82)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D82)</f>
-        <v>3.7</v>
-      </c>
-      <c r="C82" s="46"/>
-      <c r="D82" s="49" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E82" s="47" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="B83" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A83)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D83)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C83" s="46"/>
-      <c r="D83" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E83" s="47" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="B84" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A84)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D84)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C84" s="46"/>
-      <c r="D84" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E84" s="47" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="B85" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A85)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D85)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C85" s="46"/>
-      <c r="D85" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E85" s="47" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="B86" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A86)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D86)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C86" s="46"/>
-      <c r="D86" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E86" s="47" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="B87" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A87)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D87)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C87" s="46"/>
-      <c r="D87" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E87" s="47" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -27217,7 +27015,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -28478,227 +28276,6 @@
       </c>
       <c r="D74" s="49" t="n">
         <f aca="false">IFERROR(C74/B74,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A75)</f>
-        <v>0</v>
-      </c>
-      <c r="C75" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A75,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D75" s="48" t="n">
-        <f aca="false">IFERROR(C75/B75,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A76)</f>
-        <v>0</v>
-      </c>
-      <c r="C76" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A76,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="49" t="n">
-        <f aca="false">IFERROR(C76/B76,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B77" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A77)</f>
-        <v>0</v>
-      </c>
-      <c r="C77" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A77,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D77" s="49" t="n">
-        <f aca="false">IFERROR(C77/B77,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="B78" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78)</f>
-        <v>0</v>
-      </c>
-      <c r="C78" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D78" s="49" t="n">
-        <f aca="false">IFERROR(C78/B78,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="B79" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A79)</f>
-        <v>0</v>
-      </c>
-      <c r="C79" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A79,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D79" s="49" t="n">
-        <f aca="false">IFERROR(C79/B79,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B80" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A80)</f>
-        <v>0</v>
-      </c>
-      <c r="C80" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A80,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D80" s="49" t="n">
-        <f aca="false">IFERROR(C80/B80,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="B81" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A81)</f>
-        <v>0</v>
-      </c>
-      <c r="C81" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A81,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D81" s="49" t="n">
-        <f aca="false">IFERROR(C81/B81,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="B82" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A82)</f>
-        <v>0</v>
-      </c>
-      <c r="C82" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A82,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D82" s="49" t="n">
-        <f aca="false">IFERROR(C82/B82,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="B83" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A83)</f>
-        <v>0</v>
-      </c>
-      <c r="C83" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A83,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D83" s="49" t="n">
-        <f aca="false">IFERROR(C83/B83,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="B84" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84)</f>
-        <v>0</v>
-      </c>
-      <c r="C84" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D84" s="49" t="n">
-        <f aca="false">IFERROR(C84/B84,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="B85" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A85)</f>
-        <v>0</v>
-      </c>
-      <c r="C85" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A85,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="49" t="n">
-        <f aca="false">IFERROR(C85/B85,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="B86" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86)</f>
-        <v>0</v>
-      </c>
-      <c r="C86" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D86" s="49" t="n">
-        <f aca="false">IFERROR(C86/B86,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="B87" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A87)</f>
-        <v>0</v>
-      </c>
-      <c r="C87" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A87,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D87" s="49" t="n">
-        <f aca="false">IFERROR(C87/B87,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="180">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -525,51 +525,6 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiccup_The_Hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam, Loyal Attendant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avatar Aang // Aang, Master of Elements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763460</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -27026,16 +26981,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28314,40 +28269,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="F1" s="51" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="195">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -525,6 +525,51 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiccup_The_Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam, Loyal Attendant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avatar Aang // Aang, Master of Elements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">763460</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -25838,7 +25883,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -26952,6 +26997,208 @@
       </c>
       <c r="D74" s="49" t="n">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="48" t="n">
+        <f aca="false">AVERAGE(B76:B87)</f>
+        <v>3.88333333333333</v>
+      </c>
+      <c r="C75" s="46"/>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A76)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D76)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C76" s="46"/>
+      <c r="D76" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E76" s="47" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A77)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D77)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C77" s="46"/>
+      <c r="D77" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E77" s="47" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="B78" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A78)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D78)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C78" s="46"/>
+      <c r="D78" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E78" s="47" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="B79" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A79)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D79)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C79" s="46"/>
+      <c r="D79" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E79" s="47" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A80)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D80)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C80" s="46"/>
+      <c r="D80" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E80" s="47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A81)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D81)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C81" s="46"/>
+      <c r="D81" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E81" s="47" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A82)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D82)</f>
+        <v>3.7</v>
+      </c>
+      <c r="C82" s="46"/>
+      <c r="D82" s="49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E82" s="47" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B83" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A83)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D83)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C83" s="46"/>
+      <c r="D83" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E83" s="47" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A84)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D84)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C84" s="46"/>
+      <c r="D84" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E84" s="47" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B85" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A85)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D85)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C85" s="46"/>
+      <c r="D85" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E85" s="47" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="B86" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A86)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D86)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C86" s="46"/>
+      <c r="D86" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E86" s="47" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A87)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D87)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C87" s="46"/>
+      <c r="D87" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E87" s="47" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -26970,7 +27217,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26981,16 +27228,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28231,6 +28478,227 @@
       </c>
       <c r="D74" s="49" t="n">
         <f aca="false">IFERROR(C74/B74,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="B75" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A75)</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A75,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D75" s="48" t="n">
+        <f aca="false">IFERROR(C75/B75,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A76)</f>
+        <v>0</v>
+      </c>
+      <c r="C76" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A76,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D76" s="49" t="n">
+        <f aca="false">IFERROR(C76/B76,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B77" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A77)</f>
+        <v>0</v>
+      </c>
+      <c r="C77" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A77,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D77" s="49" t="n">
+        <f aca="false">IFERROR(C77/B77,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="B78" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78)</f>
+        <v>0</v>
+      </c>
+      <c r="C78" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D78" s="49" t="n">
+        <f aca="false">IFERROR(C78/B78,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="49" t="s">
+        <v>119</v>
+      </c>
+      <c r="B79" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A79)</f>
+        <v>0</v>
+      </c>
+      <c r="C79" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A79,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D79" s="49" t="n">
+        <f aca="false">IFERROR(C79/B79,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A80)</f>
+        <v>0</v>
+      </c>
+      <c r="C80" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A80,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D80" s="49" t="n">
+        <f aca="false">IFERROR(C80/B80,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A81)</f>
+        <v>0</v>
+      </c>
+      <c r="C81" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A81,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D81" s="49" t="n">
+        <f aca="false">IFERROR(C81/B81,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A82)</f>
+        <v>0</v>
+      </c>
+      <c r="C82" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A82,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D82" s="49" t="n">
+        <f aca="false">IFERROR(C82/B82,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B83" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A83)</f>
+        <v>0</v>
+      </c>
+      <c r="C83" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A83,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D83" s="49" t="n">
+        <f aca="false">IFERROR(C83/B83,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84)</f>
+        <v>0</v>
+      </c>
+      <c r="C84" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="49" t="n">
+        <f aca="false">IFERROR(C84/B84,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B85" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A85)</f>
+        <v>0</v>
+      </c>
+      <c r="C85" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A85,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="49" t="n">
+        <f aca="false">IFERROR(C85/B85,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="49" t="s">
+        <v>156</v>
+      </c>
+      <c r="B86" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86)</f>
+        <v>0</v>
+      </c>
+      <c r="C86" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D86" s="49" t="n">
+        <f aca="false">IFERROR(C86/B86,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="B87" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A87)</f>
+        <v>0</v>
+      </c>
+      <c r="C87" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A87,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D87" s="49" t="n">
+        <f aca="false">IFERROR(C87/B87,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -28269,40 +28737,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="F1" s="51" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25883,7 +25883,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -26223,7 +26223,7 @@
         <v>30</v>
       </c>
       <c r="B22" s="48" t="n">
-        <f aca="false">AVERAGE(B23:B39)</f>
+        <f aca="false">AVERAGE(B23:B38)</f>
         <v>3.32970588235294</v>
       </c>
       <c r="C22" s="46"/>
@@ -26488,717 +26488,499 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="B39" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>3.9</v>
+      <c r="A39" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="48" t="n">
+        <f aca="false">AVERAGE(B40:B53)</f>
+        <v>3.33502182539683</v>
       </c>
       <c r="C39" s="46"/>
-      <c r="D39" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E39" s="47" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="48" t="n">
-        <f aca="false">AVERAGE(B41:B54)</f>
-        <v>3.33502182539683</v>
+      <c r="A40" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
+        <v>3.5</v>
       </c>
       <c r="C40" s="46"/>
+      <c r="D40" s="49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E40" s="47" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>3.5</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C41" s="46"/>
       <c r="D41" s="49" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>3.43088888888889</v>
+        <v>3.7</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>2.6</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B45" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
-        <v>3.77816666666667</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C45" s="46"/>
       <c r="D45" s="49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B46" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
-        <v>2.59388888888889</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C46" s="46"/>
       <c r="D46" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.23902777777778</v>
+        <v>2.6</v>
       </c>
       <c r="C47" s="46"/>
       <c r="D47" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>2.6</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C48" s="46"/>
       <c r="D48" s="49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E48" s="47" t="s">
-        <v>153</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>3.58416666666667</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C49" s="46"/>
       <c r="D49" s="49" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
+      </c>
+      <c r="E49" s="47" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
-        <v>2.94083333333333</v>
+        <v>3.92333333333333</v>
       </c>
       <c r="C50" s="46"/>
       <c r="D50" s="49" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="B51" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
-        <v>3.92333333333333</v>
+        <v>3.7</v>
       </c>
       <c r="C51" s="46"/>
       <c r="D51" s="49" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="E51" s="47" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="C52" s="46"/>
       <c r="D52" s="49" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="C53" s="46"/>
       <c r="D53" s="49" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="B54" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
-        <v>3.9</v>
+      <c r="A54" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" s="48" t="n">
+        <f aca="false">AVERAGE(B55:B59)</f>
+        <v>3.2865</v>
       </c>
       <c r="C54" s="46"/>
-      <c r="D54" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E54" s="47" t="s">
-        <v>160</v>
-      </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" s="48" t="n">
-        <f aca="false">AVERAGE(B56:B60)</f>
-        <v>3.2865</v>
-      </c>
-      <c r="C55" s="46"/>
+      <c r="A55" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
+        <v>3.6</v>
+      </c>
+      <c r="C55" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="D55" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.6</v>
+        <v>3.33761111111111</v>
       </c>
       <c r="C56" s="46" t="s">
         <v>131</v>
       </c>
       <c r="D56" s="49" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B57" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
-        <v>3.33761111111111</v>
-      </c>
-      <c r="C57" s="46" t="s">
-        <v>131</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C57" s="46"/>
       <c r="D57" s="49" t="n">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B58" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C58" s="46"/>
+        <v>3.9</v>
+      </c>
+      <c r="C58" s="46" t="s">
+        <v>137</v>
+      </c>
       <c r="D58" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C59" s="46" t="s">
-        <v>137</v>
-      </c>
+        <v>2.39488888888889</v>
+      </c>
+      <c r="C59" s="46"/>
       <c r="D59" s="49" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B60" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
-        <v>2.39488888888889</v>
+      <c r="A60" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="48" t="n">
+        <f aca="false">AVERAGE(B61:B65)</f>
+        <v>3.42807</v>
       </c>
       <c r="C60" s="46"/>
-      <c r="D60" s="49" t="n">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">AVERAGE(B62:B66)</f>
-        <v>3.42807</v>
+      <c r="A61" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B61" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
+        <v>3.6</v>
       </c>
       <c r="C61" s="46"/>
+      <c r="D61" s="49" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B62" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="C62" s="46"/>
       <c r="D62" s="49" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="49" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="C64" s="46"/>
       <c r="D64" s="49" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
-        <v>3.3</v>
+        <v>3.74035</v>
       </c>
       <c r="C65" s="46"/>
       <c r="D65" s="49" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B66" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A66)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D66)</f>
-        <v>3.74035</v>
+      <c r="A66" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" s="48" t="n">
+        <f aca="false">AVERAGE(B67:B68)</f>
+        <v>3.05</v>
       </c>
       <c r="C66" s="46"/>
-      <c r="D66" s="49" t="n">
-        <v>3.7</v>
-      </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="48" t="n">
-        <f aca="false">AVERAGE(B68:B69)</f>
-        <v>3.05</v>
+      <c r="A67" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
+        <v>2.7</v>
       </c>
       <c r="C67" s="46"/>
+      <c r="D67" s="49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E67" s="47" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B68" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="C68" s="46"/>
       <c r="D68" s="49" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69" s="49" t="n">
+        <v>84</v>
+      </c>
+      <c r="B69" s="50" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A69)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D69)</f>
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="C69" s="46"/>
-      <c r="D69" s="49" t="n">
-        <v>3.4</v>
+      <c r="D69" s="50" t="n">
+        <v>1</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B70" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A70)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D70)</f>
-        <v>1</v>
+      <c r="A70" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B70" s="48" t="n">
+        <f aca="false">AVERAGE(B71:B72)</f>
+        <v>2.25194444444444</v>
       </c>
       <c r="C70" s="46"/>
-      <c r="D70" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="47" t="s">
-        <v>163</v>
-      </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B71" s="48" t="n">
-        <f aca="false">AVERAGE(B72:B73)</f>
-        <v>2.25194444444444</v>
+      <c r="A71" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A71)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D71)</f>
+        <v>2.30388888888889</v>
       </c>
       <c r="C71" s="46"/>
+      <c r="D71" s="49" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B72" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A72)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D72)</f>
-        <v>2.30388888888889</v>
+        <v>2.2</v>
       </c>
       <c r="C72" s="46"/>
       <c r="D72" s="49" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="E72" s="47" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B73" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A73)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D73)</f>
-        <v>2.2</v>
-      </c>
-      <c r="C73" s="46"/>
+        <v>2.43069444444444</v>
+      </c>
       <c r="D73" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E73" s="47" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B74" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A74)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D74)</f>
-        <v>2.43069444444444</v>
-      </c>
-      <c r="D74" s="49" t="n">
         <v>2.4</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" s="48" t="n">
-        <f aca="false">AVERAGE(B76:B87)</f>
-        <v>3.88333333333333</v>
-      </c>
-      <c r="C75" s="46"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A76)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D76)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C76" s="46"/>
-      <c r="D76" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E76" s="47" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B77" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A77)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D77)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C77" s="46"/>
-      <c r="D77" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E77" s="47" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="B78" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A78)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D78)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C78" s="46"/>
-      <c r="D78" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E78" s="47" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="B79" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A79)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D79)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C79" s="46"/>
-      <c r="D79" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E79" s="47" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B80" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A80)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D80)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C80" s="46"/>
-      <c r="D80" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E80" s="47" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="B81" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A81)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D81)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C81" s="46"/>
-      <c r="D81" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E81" s="47" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="B82" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A82)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D82)</f>
-        <v>3.7</v>
-      </c>
-      <c r="C82" s="46"/>
-      <c r="D82" s="49" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E82" s="47" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="B83" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A83)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D83)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C83" s="46"/>
-      <c r="D83" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E83" s="47" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="B84" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A84)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D84)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C84" s="46"/>
-      <c r="D84" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E84" s="47" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="B85" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A85)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D85)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C85" s="46"/>
-      <c r="D85" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E85" s="47" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="B86" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A86)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D86)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C86" s="46"/>
-      <c r="D86" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E86" s="47" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="B87" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Hiccup_The_Hero")*('Game Log Season 3'!$D$3:$D$1000=A87)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D87)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C87" s="46"/>
-      <c r="D87" s="49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E87" s="47" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -27217,7 +26999,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -27870,46 +27652,46 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="B39" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
-        <v>0</v>
-      </c>
-      <c r="C39" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="49" t="n">
+      <c r="A39" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A39)</f>
+        <v>11</v>
+      </c>
+      <c r="C39" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D39" s="48" t="n">
         <f aca="false">IFERROR(C39/B39,0)</f>
-        <v>0</v>
+        <v>0.272727272727273</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A40)</f>
-        <v>11</v>
-      </c>
-      <c r="C40" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D40" s="48" t="n">
+      <c r="A40" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="49" t="n">
         <f aca="false">IFERROR(C40/B40,0)</f>
-        <v>0.272727272727273</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27922,11 +27704,11 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27939,7 +27721,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
@@ -27956,24 +27738,24 @@
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" s="49" t="n">
         <f aca="false">IFERROR(C44/B44,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="B45" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
@@ -27981,20 +27763,20 @@
       </c>
       <c r="C45" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" s="49" t="n">
         <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="B46" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28007,11 +27789,11 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28024,11 +27806,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28041,7 +27823,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
@@ -28049,16 +27831,16 @@
       </c>
       <c r="C49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A49,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" s="49" t="n">
         <f aca="false">IFERROR(C49/B49,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
@@ -28075,24 +27857,24 @@
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="B51" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C51" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" s="49" t="n">
         <f aca="false">IFERROR(C51/B51,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -28109,7 +27891,7 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -28125,46 +27907,46 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="B54" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
-        <v>0</v>
-      </c>
-      <c r="C54" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D54" s="49" t="n">
+      <c r="A54" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="B54" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A54)</f>
+        <v>2</v>
+      </c>
+      <c r="C54" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A54,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="48" t="n">
         <f aca="false">IFERROR(C54/B54,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A55)</f>
-        <v>2</v>
-      </c>
-      <c r="C55" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D55" s="48" t="n">
+      <c r="A55" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
+        <v>0</v>
+      </c>
+      <c r="C55" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="49" t="n">
         <f aca="false">IFERROR(C55/B55,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28177,11 +27959,11 @@
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B57" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28194,7 +27976,7 @@
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B58" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
@@ -28211,11 +27993,11 @@
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A59,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28227,42 +28009,42 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B60" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
-        <v>1</v>
-      </c>
-      <c r="C60" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A60,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D60" s="49" t="n">
+      <c r="A60" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A60)</f>
+        <v>1</v>
+      </c>
+      <c r="C60" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A60,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="48" t="n">
         <f aca="false">IFERROR(C60/B60,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
-        <v>1</v>
-      </c>
-      <c r="C61" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="48" t="n">
+      <c r="A61" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
+        <v>0</v>
+      </c>
+      <c r="C61" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="49" t="n">
         <f aca="false">IFERROR(C61/B61,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="B62" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
@@ -28279,7 +28061,7 @@
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
@@ -28296,7 +28078,7 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
@@ -28313,11 +28095,11 @@
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28329,42 +28111,42 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B66" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A66)</f>
-        <v>1</v>
-      </c>
-      <c r="C66" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="49" t="n">
+      <c r="A66" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B66" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
+        <v>0</v>
+      </c>
+      <c r="C66" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="48" t="n">
         <f aca="false">IFERROR(C66/B66,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A67)</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="48" t="n">
+      <c r="A67" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="49" t="n">
         <f aca="false">IFERROR(C67/B67,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="49" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B68" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
@@ -28381,7 +28163,7 @@
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="49" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B69" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A69)</f>
@@ -28397,46 +28179,46 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B70" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A70)</f>
-        <v>0</v>
-      </c>
-      <c r="C70" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A70,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D70" s="49" t="n">
+      <c r="A70" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B70" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A70)</f>
+        <v>4</v>
+      </c>
+      <c r="C70" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A70,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D70" s="48" t="n">
         <f aca="false">IFERROR(C70/B70,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="B71" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A71)</f>
-        <v>4</v>
-      </c>
-      <c r="C71" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A71,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D71" s="48" t="n">
+      <c r="A71" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A71)</f>
+        <v>3</v>
+      </c>
+      <c r="C71" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A71,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D71" s="49" t="n">
         <f aca="false">IFERROR(C71/B71,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B72" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A72)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C72" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A72,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28449,11 +28231,11 @@
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="49" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B73" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A73)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A73,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28461,244 +28243,6 @@
       </c>
       <c r="D73" s="49" t="n">
         <f aca="false">IFERROR(C73/B73,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="49" t="s">
-        <v>96</v>
-      </c>
-      <c r="B74" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A74)</f>
-        <v>1</v>
-      </c>
-      <c r="C74" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A74,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="49" t="n">
-        <f aca="false">IFERROR(C74/B74,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="47" t="s">
-        <v>165</v>
-      </c>
-      <c r="B75" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A75)</f>
-        <v>0</v>
-      </c>
-      <c r="C75" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A75,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D75" s="48" t="n">
-        <f aca="false">IFERROR(C75/B75,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A76)</f>
-        <v>0</v>
-      </c>
-      <c r="C76" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A76,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="49" t="n">
-        <f aca="false">IFERROR(C76/B76,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="B77" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A77)</f>
-        <v>0</v>
-      </c>
-      <c r="C77" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A77,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D77" s="49" t="n">
-        <f aca="false">IFERROR(C77/B77,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="B78" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78)</f>
-        <v>0</v>
-      </c>
-      <c r="C78" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A78,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D78" s="49" t="n">
-        <f aca="false">IFERROR(C78/B78,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="49" t="s">
-        <v>119</v>
-      </c>
-      <c r="B79" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A79)</f>
-        <v>0</v>
-      </c>
-      <c r="C79" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A79,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D79" s="49" t="n">
-        <f aca="false">IFERROR(C79/B79,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="B80" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A80)</f>
-        <v>0</v>
-      </c>
-      <c r="C80" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A80,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D80" s="49" t="n">
-        <f aca="false">IFERROR(C80/B80,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="B81" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A81)</f>
-        <v>0</v>
-      </c>
-      <c r="C81" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A81,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D81" s="49" t="n">
-        <f aca="false">IFERROR(C81/B81,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="B82" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A82)</f>
-        <v>0</v>
-      </c>
-      <c r="C82" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A82,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D82" s="49" t="n">
-        <f aca="false">IFERROR(C82/B82,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="B83" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A83)</f>
-        <v>0</v>
-      </c>
-      <c r="C83" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A83,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D83" s="49" t="n">
-        <f aca="false">IFERROR(C83/B83,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="B84" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84)</f>
-        <v>0</v>
-      </c>
-      <c r="C84" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A84,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D84" s="49" t="n">
-        <f aca="false">IFERROR(C84/B84,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="B85" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A85)</f>
-        <v>0</v>
-      </c>
-      <c r="C85" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A85,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D85" s="49" t="n">
-        <f aca="false">IFERROR(C85/B85,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="49" t="s">
-        <v>156</v>
-      </c>
-      <c r="B86" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86)</f>
-        <v>0</v>
-      </c>
-      <c r="C86" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A86,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D86" s="49" t="n">
-        <f aca="false">IFERROR(C86/B86,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="B87" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A87)</f>
-        <v>0</v>
-      </c>
-      <c r="C87" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Hiccup_The_Hero",'Game Log Season 3'!$D$3:$D$1000,A87,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D87" s="49" t="n">
-        <f aca="false">IFERROR(C87/B87,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="178">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -464,12 +464,6 @@
     <t xml:space="preserve">560459</t>
   </si>
   <si>
-    <t xml:space="preserve">Michelangelo, the Heart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">743883</t>
-  </si>
-  <si>
     <t xml:space="preserve">560264</t>
   </si>
   <si>
@@ -525,51 +519,6 @@
   </si>
   <si>
     <t xml:space="preserve">576574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hiccup_The_Hero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam, Loyal Attendant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avatar Aang // Aang, Master of Elements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">763460</t>
   </si>
   <si>
     <t xml:space="preserve">Player / Deck</t>
@@ -26224,7 +26173,7 @@
       </c>
       <c r="B22" s="48" t="n">
         <f aca="false">AVERAGE(B23:B38)</f>
-        <v>3.32970588235294</v>
+        <v>3.2940625</v>
       </c>
       <c r="C22" s="46"/>
     </row>
@@ -26510,7 +26459,7 @@
         <v>3.5</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26526,7 +26475,7 @@
         <v>3.4</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26542,7 +26491,7 @@
         <v>3.7</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26558,7 +26507,7 @@
         <v>2.6</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26574,7 +26523,7 @@
         <v>3.8</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26590,7 +26539,7 @@
         <v>2.6</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26606,7 +26555,7 @@
         <v>3.6</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26622,7 +26571,7 @@
         <v>2.6</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26651,7 +26600,7 @@
         <v>2.9</v>
       </c>
       <c r="E49" s="47" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26667,12 +26616,12 @@
         <v>3.9</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B51" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
@@ -26683,7 +26632,7 @@
         <v>3.7</v>
       </c>
       <c r="E51" s="47" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26699,12 +26648,12 @@
         <v>3.2</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
@@ -26715,7 +26664,7 @@
         <v>3.9</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26897,7 +26846,7 @@
         <v>2.7</v>
       </c>
       <c r="E67" s="47" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26913,7 +26862,7 @@
         <v>3.4</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26929,7 +26878,7 @@
         <v>1</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26968,7 +26917,7 @@
         <v>2.2</v>
       </c>
       <c r="E72" s="47" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27010,16 +26959,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27857,7 +27806,7 @@
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B51" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
@@ -27891,7 +27840,7 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -28281,40 +28230,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="B1" s="51" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="E1" s="51" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="F1" s="51" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="180">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -462,6 +462,12 @@
   </si>
   <si>
     <t xml:space="preserve">560459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonardo, the Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">614175</t>
   </si>
   <si>
     <t xml:space="preserve">560264</t>
@@ -25832,7 +25838,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.33"/>
@@ -26172,8 +26178,8 @@
         <v>30</v>
       </c>
       <c r="B22" s="48" t="n">
-        <f aca="false">AVERAGE(B23:B38)</f>
-        <v>3.2940625</v>
+        <f aca="false">AVERAGE(B23:B39)</f>
+        <v>3.30029411764706</v>
       </c>
       <c r="C22" s="46"/>
     </row>
@@ -26437,199 +26443,199 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="47" t="s">
+      <c r="A39" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
+        <v>3.4</v>
+      </c>
+      <c r="C39" s="46"/>
+      <c r="D39" s="49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E39" s="47" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="48" t="n">
-        <f aca="false">AVERAGE(B40:B53)</f>
+      <c r="B40" s="48" t="n">
+        <f aca="false">AVERAGE(B41:B54)</f>
         <v>3.33502182539683</v>
       </c>
-      <c r="C39" s="46"/>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A40)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D40)</f>
-        <v>3.5</v>
-      </c>
       <c r="C40" s="46"/>
-      <c r="D40" s="49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E40" s="47" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A41)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D41)</f>
-        <v>3.43088888888889</v>
+        <v>3.5</v>
       </c>
       <c r="C41" s="46"/>
       <c r="D41" s="49" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E41" s="47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A42)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D42)</f>
-        <v>3.7</v>
+        <v>3.43088888888889</v>
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="49" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A43)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D43)</f>
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="C43" s="46"/>
       <c r="D43" s="49" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="E43" s="47" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A44)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D44)</f>
-        <v>3.77816666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C44" s="46"/>
       <c r="D44" s="49" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B45" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
-        <v>2.59388888888889</v>
+        <v>3.77816666666667</v>
       </c>
       <c r="C45" s="46"/>
       <c r="D45" s="49" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B46" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A46)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D46)</f>
-        <v>3.23902777777778</v>
+        <v>2.59388888888889</v>
       </c>
       <c r="C46" s="46"/>
       <c r="D46" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>2.6</v>
+        <v>3.23902777777778</v>
       </c>
       <c r="C47" s="46"/>
       <c r="D47" s="49" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A48)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D48)</f>
-        <v>3.58416666666667</v>
+        <v>2.6</v>
       </c>
       <c r="C48" s="46"/>
       <c r="D48" s="49" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
+      </c>
+      <c r="E48" s="47" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A49)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D49)</f>
-        <v>2.94083333333333</v>
+        <v>3.58416666666667</v>
       </c>
       <c r="C49" s="46"/>
       <c r="D49" s="49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E49" s="47" t="s">
-        <v>152</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A50)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D50)</f>
-        <v>3.92333333333333</v>
+        <v>2.94083333333333</v>
       </c>
       <c r="C50" s="46"/>
       <c r="D50" s="49" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="B51" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A51)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D51)</f>
-        <v>3.7</v>
+        <v>3.92333333333333</v>
       </c>
       <c r="C51" s="46"/>
       <c r="D51" s="49" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="E51" s="47" t="s">
         <v>155</v>
@@ -26637,298 +26643,314 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="C52" s="46"/>
       <c r="D52" s="49" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A53)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D53)</f>
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="C53" s="46"/>
       <c r="D53" s="49" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="E53" s="47" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="47" t="s">
+      <c r="A54" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C54" s="46"/>
+      <c r="D54" s="49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E54" s="47" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B54" s="48" t="n">
-        <f aca="false">AVERAGE(B55:B59)</f>
+      <c r="B55" s="48" t="n">
+        <f aca="false">AVERAGE(B56:B60)</f>
         <v>3.2865</v>
       </c>
-      <c r="C54" s="46"/>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B55" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A55)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D55)</f>
-        <v>3.6</v>
-      </c>
-      <c r="C55" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="D55" s="49" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="C55" s="46"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A56)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D56)</f>
-        <v>3.33761111111111</v>
+        <v>3.6</v>
       </c>
       <c r="C56" s="46" t="s">
         <v>131</v>
       </c>
       <c r="D56" s="49" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B57" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A57)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D57)</f>
-        <v>3.2</v>
-      </c>
-      <c r="C57" s="46"/>
+        <v>3.33761111111111</v>
+      </c>
+      <c r="C57" s="46" t="s">
+        <v>131</v>
+      </c>
       <c r="D57" s="49" t="n">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B58" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A58)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D58)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C58" s="46" t="s">
-        <v>137</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="C58" s="46"/>
       <c r="D58" s="49" t="n">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A59)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D59)</f>
+        <v>3.9</v>
+      </c>
+      <c r="C59" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D59" s="49" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B60" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Kristy")*('Game Log Season 3'!$D$3:$D$1000=A60)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D60)</f>
         <v>2.39488888888889</v>
       </c>
-      <c r="C59" s="46"/>
-      <c r="D59" s="49" t="n">
+      <c r="C60" s="46"/>
+      <c r="D60" s="49" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="47" t="s">
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="48" t="n">
-        <f aca="false">AVERAGE(B61:B65)</f>
+      <c r="B61" s="48" t="n">
+        <f aca="false">AVERAGE(B62:B66)</f>
         <v>3.42807</v>
       </c>
-      <c r="C60" s="46"/>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B61" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A61)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D61)</f>
-        <v>3.6</v>
-      </c>
       <c r="C61" s="46"/>
-      <c r="D61" s="49" t="n">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B62" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A62)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D62)</f>
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="C62" s="46"/>
       <c r="D62" s="49" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A63)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D63)</f>
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="C63" s="46"/>
       <c r="D63" s="49" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A64)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D64)</f>
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="C64" s="46"/>
       <c r="D64" s="49" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A65)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D65)</f>
-        <v>3.74035</v>
+        <v>3.3</v>
       </c>
       <c r="C65" s="46"/>
       <c r="D65" s="49" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B66" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Joseph")*('Game Log Season 3'!$D$3:$D$1000=A66)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D66)</f>
+        <v>3.74035</v>
+      </c>
+      <c r="C66" s="46"/>
+      <c r="D66" s="49" t="n">
         <v>3.7</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="47" t="s">
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B66" s="48" t="n">
-        <f aca="false">AVERAGE(B67:B68)</f>
+      <c r="B67" s="48" t="n">
+        <f aca="false">AVERAGE(B68:B69)</f>
         <v>3.05</v>
       </c>
-      <c r="C66" s="46"/>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B67" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A67)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D67)</f>
-        <v>2.7</v>
-      </c>
       <c r="C67" s="46"/>
-      <c r="D67" s="49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E67" s="47" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="49" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B68" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A68)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D68)</f>
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="C68" s="46"/>
       <c r="D68" s="49" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A69)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D69)</f>
+        <v>3.4</v>
+      </c>
+      <c r="C69" s="46"/>
+      <c r="D69" s="49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E69" s="47" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B69" s="50" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A69)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D69)</f>
-        <v>1</v>
-      </c>
-      <c r="C69" s="46"/>
-      <c r="D69" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="47" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="47" t="s">
+      <c r="B70" s="50" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Red")*('Game Log Season 3'!$D$3:$D$1000=A70)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D70)</f>
+        <v>1</v>
+      </c>
+      <c r="C70" s="46"/>
+      <c r="D70" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B70" s="48" t="n">
-        <f aca="false">AVERAGE(B71:B72)</f>
+      <c r="B71" s="48" t="n">
+        <f aca="false">AVERAGE(B72:B73)</f>
         <v>2.25194444444444</v>
       </c>
-      <c r="C70" s="46"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B71" s="49" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A71)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D71)</f>
-        <v>2.30388888888889</v>
-      </c>
       <c r="C71" s="46"/>
-      <c r="D71" s="49" t="n">
-        <v>2.5</v>
-      </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="49" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B72" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A72)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D72)</f>
-        <v>2.2</v>
+        <v>2.30388888888889</v>
       </c>
       <c r="C72" s="46"/>
       <c r="D72" s="49" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E72" s="47" t="s">
-        <v>162</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B73" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A73)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D73)</f>
+        <v>2.2</v>
+      </c>
+      <c r="C73" s="46"/>
+      <c r="D73" s="49" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E73" s="47" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="49" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Michelle")*('Game Log Season 3'!$D$3:$D$1000=A74)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D74)</f>
         <v>2.43069444444444</v>
       </c>
-      <c r="D73" s="49" t="n">
+      <c r="D74" s="49" t="n">
         <v>2.4</v>
       </c>
     </row>
@@ -26948,7 +26970,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.89"/>
@@ -26959,16 +26981,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27601,46 +27623,46 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="47" t="s">
+      <c r="A39" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39)</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="49" t="n">
+        <f aca="false">IFERROR(C39/B39,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A39)</f>
+      <c r="B40" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A40)</f>
         <v>11</v>
       </c>
-      <c r="C39" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A39,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>3</v>
-      </c>
-      <c r="D39" s="48" t="n">
-        <f aca="false">IFERROR(C39/B39,0)</f>
+      <c r="C40" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>3</v>
+      </c>
+      <c r="D40" s="48" t="n">
+        <f aca="false">IFERROR(C40/B40,0)</f>
         <v>0.272727272727273</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40)</f>
-        <v>0</v>
-      </c>
-      <c r="C40" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="49" t="n">
-        <f aca="false">IFERROR(C40/B40,0)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="49" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A41,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27653,11 +27675,11 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="49" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="B42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A42,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27670,7 +27692,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="49" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B43" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A43)</f>
@@ -27687,24 +27709,24 @@
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="49" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="B44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A44,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="49" t="n">
         <f aca="false">IFERROR(C44/B44,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B45" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45)</f>
@@ -27712,20 +27734,20 @@
       </c>
       <c r="C45" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A45,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" s="49" t="n">
         <f aca="false">IFERROR(C45/B45,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="49" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="B46" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A46,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27738,11 +27760,11 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="49" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="B47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C47" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27755,11 +27777,11 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A48)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C48" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A48,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27772,7 +27794,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A49)</f>
@@ -27780,16 +27802,16 @@
       </c>
       <c r="C49" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A49,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" s="49" t="n">
         <f aca="false">IFERROR(C49/B49,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="49" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B50" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A50)</f>
@@ -27806,24 +27828,24 @@
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="49" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="B51" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A51)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C51" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A51,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51" s="49" t="n">
         <f aca="false">IFERROR(C51/B51,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -27840,7 +27862,7 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="49" t="s">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="B53" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A53)</f>
@@ -27856,46 +27878,46 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="47" t="s">
+      <c r="A54" s="49" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
+        <v>0</v>
+      </c>
+      <c r="C54" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="49" t="n">
+        <f aca="false">IFERROR(C54/B54,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B54" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A54)</f>
-        <v>2</v>
-      </c>
-      <c r="C54" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A54,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D54" s="48" t="n">
-        <f aca="false">IFERROR(C54/B54,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B55" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A55)</f>
-        <v>0</v>
-      </c>
-      <c r="C55" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D55" s="49" t="n">
+      <c r="B55" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A55)</f>
+        <v>2</v>
+      </c>
+      <c r="C55" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A55,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="48" t="n">
         <f aca="false">IFERROR(C55/B55,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="49" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A56)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A56,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27908,11 +27930,11 @@
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="49" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="B57" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A57)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A57,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27925,7 +27947,7 @@
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="49" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B58" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A58)</f>
@@ -27942,11 +27964,11 @@
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A59)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A59,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27958,42 +27980,42 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="47" t="s">
+      <c r="A60" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="B60" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A60)</f>
+        <v>1</v>
+      </c>
+      <c r="C60" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Kristy",'Game Log Season 3'!$D$3:$D$1000,A60,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="49" t="n">
+        <f aca="false">IFERROR(C60/B60,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A60)</f>
-        <v>1</v>
-      </c>
-      <c r="C60" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A60,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D60" s="48" t="n">
-        <f aca="false">IFERROR(C60/B60,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="B61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A61)</f>
-        <v>0</v>
-      </c>
-      <c r="C61" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D61" s="49" t="n">
+      <c r="B61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61)</f>
+        <v>1</v>
+      </c>
+      <c r="C61" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A61,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D61" s="48" t="n">
         <f aca="false">IFERROR(C61/B61,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="49" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B62" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A62)</f>
@@ -28010,7 +28032,7 @@
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B63" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A63)</f>
@@ -28027,7 +28049,7 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B64" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A64)</f>
@@ -28044,11 +28066,11 @@
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="49" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A65)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A65,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28060,42 +28082,42 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="47" t="s">
+      <c r="A66" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="B66" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A66)</f>
+        <v>1</v>
+      </c>
+      <c r="C66" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Joseph",'Game Log Season 3'!$D$3:$D$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="49" t="n">
+        <f aca="false">IFERROR(C66/B66,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="B66" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66)</f>
-        <v>0</v>
-      </c>
-      <c r="C66" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A66,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D66" s="48" t="n">
-        <f aca="false">IFERROR(C66/B66,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="49" t="s">
-        <v>33</v>
-      </c>
-      <c r="B67" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A67)</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D67" s="49" t="n">
+      <c r="B67" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A67)</f>
+        <v>0</v>
+      </c>
+      <c r="C67" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A67,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="48" t="n">
         <f aca="false">IFERROR(C67/B67,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="49" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="B68" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A68)</f>
@@ -28112,7 +28134,7 @@
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="49" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B69" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A69)</f>
@@ -28128,46 +28150,46 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="47" t="s">
+      <c r="A70" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A70)</f>
+        <v>0</v>
+      </c>
+      <c r="C70" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Red",'Game Log Season 3'!$D$3:$D$1000,A70,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D70" s="49" t="n">
+        <f aca="false">IFERROR(C70/B70,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="B70" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A70)</f>
+      <c r="B71" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A71)</f>
         <v>4</v>
       </c>
-      <c r="C70" s="48" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A70,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D70" s="48" t="n">
-        <f aca="false">IFERROR(C70/B70,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="B71" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A71)</f>
-        <v>3</v>
-      </c>
-      <c r="C71" s="49" t="n">
-        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A71,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D71" s="49" t="n">
+      <c r="C71" s="48" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A71,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D71" s="48" t="n">
         <f aca="false">IFERROR(C71/B71,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="49" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="B72" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A72)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C72" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A72,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28180,11 +28202,11 @@
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="49" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="B73" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A73)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C73" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A73,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28192,6 +28214,23 @@
       </c>
       <c r="D73" s="49" t="n">
         <f aca="false">IFERROR(C73/B73,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="49" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A74)</f>
+        <v>1</v>
+      </c>
+      <c r="C74" s="49" t="n">
+        <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Michelle",'Game Log Season 3'!$D$3:$D$1000,A74,'Game Log Season 3'!$F$3:$F$1000,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="49" t="n">
+        <f aca="false">IFERROR(C74/B74,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -28230,40 +28269,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B1" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="E1" s="51" t="s">
         <v>168</v>
       </c>
-      <c r="C1" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>166</v>
-      </c>
       <c r="F1" s="51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25943,9 +25943,13 @@
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
         <v>3.9</v>
       </c>
-      <c r="C7" s="46"/>
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>*Bracket 2</t>
+        </is>
+      </c>
       <c r="D7" s="49" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="E7" s="47" t="s">
         <v>107</v>
@@ -26165,9 +26169,13 @@
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
         <v>4.1</v>
       </c>
-      <c r="C21" s="46"/>
+      <c r="C21" s="46" t="inlineStr">
+        <is>
+          <t>*Bracket 3</t>
+        </is>
+      </c>
       <c r="D21" s="49" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="47" t="s">
         <v>124</v>
@@ -26443,8 +26451,10 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="s">
-        <v>144</v>
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>Leonardo, the Balance/Michelangelo, the Heart</t>
+        </is>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
@@ -26452,7 +26462,7 @@
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="E39" s="47" t="s">
         <v>145</v>
@@ -27623,8 +27633,10 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="s">
-        <v>144</v>
+      <c r="A39" s="49" t="inlineStr">
+        <is>
+          <t>Leonardo, the Balance/Michelangelo, the Heart</t>
+        </is>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39)</f>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="180">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -353,6 +353,9 @@
     <t xml:space="preserve">Katara, the Fearless</t>
   </si>
   <si>
+    <t xml:space="preserve">*Bracket 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">797189</t>
   </si>
   <si>
@@ -404,6 +407,9 @@
     <t xml:space="preserve">Sokka, Tenacious Tactician</t>
   </si>
   <si>
+    <t xml:space="preserve">*Bracket 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">741945</t>
   </si>
   <si>
@@ -423,9 +429,6 @@
   </si>
   <si>
     <t xml:space="preserve">671540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Bracket 3</t>
   </si>
   <si>
     <t xml:space="preserve">677158</t>
@@ -462,9 +465,6 @@
   </si>
   <si>
     <t xml:space="preserve">560459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leonardo, the Balance</t>
   </si>
   <si>
     <t xml:space="preserve">614175</t>
@@ -25868,7 +25868,7 @@
       </c>
       <c r="B2" s="48" t="n">
         <f aca="false">AVERAGE(B3:B7)</f>
-        <v>2.95830555555556</v>
+        <v>2.57830555555556</v>
       </c>
       <c r="C2" s="46"/>
     </row>
@@ -25941,18 +25941,16 @@
       </c>
       <c r="B7" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
-        <v>3.9</v>
-      </c>
-      <c r="C7" s="46" t="inlineStr">
-        <is>
-          <t>*Bracket 2</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>107</v>
       </c>
       <c r="D7" s="49" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25961,7 +25959,7 @@
       </c>
       <c r="B8" s="48" t="n">
         <f aca="false">AVERAGE(B9:B21)</f>
-        <v>3.42601495726496</v>
+        <v>3.34139957264957</v>
       </c>
       <c r="C8" s="46"/>
     </row>
@@ -25978,7 +25976,7 @@
         <v>3.8</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25994,7 +25992,7 @@
         <v>3.9</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26006,13 +26004,13 @@
         <v>3.4</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D11" s="49" t="n">
         <v>3.4</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26028,7 +26026,7 @@
         <v>2.6</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26046,7 +26044,7 @@
         <v>3.5</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26062,7 +26060,7 @@
         <v>2.7</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26078,7 +26076,7 @@
         <v>2.6</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26094,7 +26092,7 @@
         <v>3.9</v>
       </c>
       <c r="E16" s="47" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26110,7 +26108,7 @@
         <v>2.3</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26126,12 +26124,12 @@
         <v>3.5</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B19" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
@@ -26142,12 +26140,12 @@
         <v>3.9</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
@@ -26158,27 +26156,25 @@
         <v>3.7</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A21)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D21)</f>
-        <v>4.1</v>
-      </c>
-      <c r="C21" s="46" t="inlineStr">
-        <is>
-          <t>*Bracket 3</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C21" s="46" t="s">
+        <v>125</v>
       </c>
       <c r="D21" s="49" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26187,7 +26183,7 @@
       </c>
       <c r="B22" s="48" t="n">
         <f aca="false">AVERAGE(B23:B39)</f>
-        <v>3.30029411764706</v>
+        <v>3.25323529411765</v>
       </c>
       <c r="C22" s="46"/>
     </row>
@@ -26204,7 +26200,7 @@
         <v>2.4</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26220,7 +26216,7 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="47" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26236,7 +26232,7 @@
         <v>3.6</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26252,7 +26248,7 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26270,7 +26266,7 @@
         <v>3.9</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26299,7 +26295,7 @@
         <v>2.6</v>
       </c>
       <c r="E29" s="47" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26311,13 +26307,13 @@
         <v>3.59875</v>
       </c>
       <c r="C30" s="46" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D30" s="49" t="n">
         <v>3.6</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26333,7 +26329,7 @@
         <v>3.9</v>
       </c>
       <c r="E31" s="47" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26349,7 +26345,7 @@
         <v>3.7</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26365,7 +26361,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26381,7 +26377,7 @@
         <v>2.9</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26393,18 +26389,18 @@
         <v>3.935</v>
       </c>
       <c r="C35" s="46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D35" s="50" t="n">
         <v>3.9</v>
       </c>
       <c r="E35" s="47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
@@ -26415,7 +26411,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26431,12 +26427,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
@@ -26447,18 +26443,16 @@
         <v>3.9</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="inlineStr">
-        <is>
-          <t>Leonardo, the Balance/Michelangelo, the Heart</t>
-        </is>
+      <c r="A39" s="49" t="s">
+        <v>66</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A39)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D39)</f>
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="C39" s="46"/>
       <c r="D39" s="49" t="n">
@@ -26718,7 +26712,7 @@
         <v>3.6</v>
       </c>
       <c r="C56" s="46" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D56" s="49" t="n">
         <v>3.6</v>
@@ -26733,7 +26727,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C57" s="46" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D57" s="49" t="n">
         <v>3.3</v>
@@ -26761,7 +26755,7 @@
         <v>3.9</v>
       </c>
       <c r="C59" s="46" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D59" s="49" t="n">
         <v>3.9</v>
@@ -27294,7 +27288,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B19" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
@@ -27311,7 +27305,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B20" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -27328,7 +27322,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B21" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A21)</f>
@@ -27583,7 +27577,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="49" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B36" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -27617,7 +27611,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -27633,10 +27627,8 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="49" t="inlineStr">
-        <is>
-          <t>Leonardo, the Balance/Michelangelo, the Heart</t>
-        </is>
+      <c r="A39" s="49" t="s">
+        <v>66</v>
       </c>
       <c r="B39" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A39)</f>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -26544,7 +26544,11 @@
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
         <v>3.77816666666667</v>
       </c>
-      <c r="C45" s="46"/>
+      <c r="C45" s="46" t="inlineStr">
+        <is>
+          <t>*Bracket 4</t>
+        </is>
+      </c>
       <c r="D45" s="49" t="n">
         <v>3.8</v>
       </c>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="181">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -480,6 +480,9 @@
   </si>
   <si>
     <t xml:space="preserve">601032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*Bracket 4</t>
   </si>
   <si>
     <t xml:space="preserve">560261</t>
@@ -26544,16 +26547,14 @@
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
         <v>3.77816666666667</v>
       </c>
-      <c r="C45" s="46" t="inlineStr">
-        <is>
-          <t>*Bracket 4</t>
-        </is>
+      <c r="C45" s="46" t="s">
+        <v>150</v>
       </c>
       <c r="D45" s="49" t="n">
         <v>3.8</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26569,7 +26570,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26585,7 +26586,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26601,7 +26602,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26630,7 +26631,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26646,12 +26647,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -26662,7 +26663,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26678,12 +26679,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -26694,7 +26695,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26876,7 +26877,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26892,7 +26893,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26908,7 +26909,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26947,7 +26948,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26989,16 +26990,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="45" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27853,7 +27854,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -27887,7 +27888,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28277,40 +28278,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" s="51" t="s">
         <v>169</v>
       </c>
-      <c r="B1" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="E1" s="51" t="s">
-        <v>168</v>
-      </c>
       <c r="F1" s="51" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G1" s="51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H1" s="51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I1" s="51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J1" s="51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K1" s="51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L1" s="51" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -26547,9 +26547,7 @@
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A45)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D45)</f>
         <v>3.77816666666667</v>
       </c>
-      <c r="C45" s="46" t="s">
-        <v>150</v>
-      </c>
+      <c r="C45" s="46"/>
       <c r="D45" s="49" t="n">
         <v>3.8</v>
       </c>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="180">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -480,9 +480,6 @@
   </si>
   <si>
     <t xml:space="preserve">601032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Bracket 4</t>
   </si>
   <si>
     <t xml:space="preserve">560261</t>
@@ -26552,7 +26549,7 @@
         <v>3.8</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26568,7 +26565,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26584,7 +26581,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26600,7 +26597,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26629,7 +26626,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26645,12 +26642,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -26661,7 +26658,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26677,12 +26674,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -26693,7 +26690,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26875,7 +26872,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26891,7 +26888,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26907,7 +26904,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26946,7 +26943,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26988,16 +26985,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="C1" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="D1" s="45" t="s">
         <v>168</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -27852,7 +27849,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B52" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -27886,7 +27883,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B54" s="49" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28276,40 +28273,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="C1" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="D1" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="E1" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="E1" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="F1" s="51" t="s">
+      <c r="G1" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="H1" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="H1" s="51" t="s">
+      <c r="I1" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="J1" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="J1" s="51" t="s">
+      <c r="K1" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="K1" s="51" t="s">
+      <c r="L1" s="51" t="s">
         <v>179</v>
-      </c>
-      <c r="L1" s="51" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="186">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -336,6 +336,18 @@
   </si>
   <si>
     <t xml:space="preserve">Arna Kennerüd, Skycaptain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestPlayer1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Commander A (THROWAWAY TEST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestPlayer2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Commander B (THROWAWAY TEST)</t>
   </si>
   <si>
     <t xml:space="preserve">Decks</t>
@@ -21284,7 +21296,7 @@
         <f aca="false">((O3*0.3)+(Q3*0.175)+(R3*0.175)+(U3*0.175)+((1-V3)*0.175))+W3</f>
         <v>2.51261111111111</v>
       </c>
-      <c r="Y3" s="0" t="n">
+      <c r="Y3" s="1" t="n">
         <v>767378</v>
       </c>
     </row>
@@ -21370,7 +21382,7 @@
         <f aca="false">((O4*0.3)+(Q4*0.175)+(R4*0.175)+(U4*0.175)+((1-V4)*0.175))+W4</f>
         <v>3.68761111111111</v>
       </c>
-      <c r="Y4" s="0" t="n">
+      <c r="Y4" s="1" t="n">
         <v>767378</v>
       </c>
     </row>
@@ -21456,7 +21468,7 @@
         <f aca="false">((O5*0.3)+(Q5*0.175)+(R5*0.175)+(U5*0.175)+((1-V5)*0.175))+W5</f>
         <v>2.68761111111111</v>
       </c>
-      <c r="Y5" s="0" t="n">
+      <c r="Y5" s="1" t="n">
         <v>767378</v>
       </c>
     </row>
@@ -21542,7 +21554,7 @@
         <f aca="false">((O6*0.3)+(Q6*0.175)+(R6*0.175)+(U6*0.175)+((1-V6)*0.175))+W6</f>
         <v>3.77816666666667</v>
       </c>
-      <c r="Y6" s="0" t="n">
+      <c r="Y6" s="1" t="n">
         <v>767378</v>
       </c>
     </row>
@@ -21628,7 +21640,7 @@
         <f aca="false">((O7*0.3)+(Q7*0.175)+(R7*0.175)+(U7*0.175)+((1-V7)*0.175))+W7</f>
         <v>3.33761111111111</v>
       </c>
-      <c r="Y7" s="0" t="n">
+      <c r="Y7" s="1" t="n">
         <v>767378</v>
       </c>
     </row>
@@ -21714,7 +21726,7 @@
         <f aca="false">((O8*0.3)+(Q8*0.175)+(R8*0.175)+(U8*0.175)+((1-V8)*0.175))+W8</f>
         <v>3.95583333333333</v>
       </c>
-      <c r="Y8" s="0" t="n">
+      <c r="Y8" s="1" t="n">
         <v>773832</v>
       </c>
     </row>
@@ -21800,7 +21812,7 @@
         <f aca="false">((O9*0.3)+(Q9*0.175)+(R9*0.175)+(U9*0.175)+((1-V9)*0.175))+W9</f>
         <v>2.66888888888889</v>
       </c>
-      <c r="Y9" s="0" t="n">
+      <c r="Y9" s="1" t="n">
         <v>773832</v>
       </c>
     </row>
@@ -21886,7 +21898,7 @@
         <f aca="false">((O10*0.3)+(Q10*0.175)+(R10*0.175)+(U10*0.175)+((1-V10)*0.175))+W10</f>
         <v>2.49388888888889</v>
       </c>
-      <c r="Y10" s="0" t="n">
+      <c r="Y10" s="1" t="n">
         <v>773832</v>
       </c>
     </row>
@@ -21972,7 +21984,7 @@
         <f aca="false">((O11*0.3)+(Q11*0.175)+(R11*0.175)+(U11*0.175)+((1-V11)*0.175))+W11</f>
         <v>3.31888888888889</v>
       </c>
-      <c r="Y11" s="0" t="n">
+      <c r="Y11" s="1" t="n">
         <v>773832</v>
       </c>
     </row>
@@ -22058,7 +22070,7 @@
         <f aca="false">((O12*0.3)+(Q12*0.175)+(R12*0.175)+(U12*0.175)+((1-V12)*0.175))+W12</f>
         <v>2.86</v>
       </c>
-      <c r="Y12" s="0" t="n">
+      <c r="Y12" s="1" t="n">
         <v>774108</v>
       </c>
     </row>
@@ -22144,7 +22156,7 @@
         <f aca="false">((O13*0.3)+(Q13*0.175)+(R13*0.175)+(U13*0.175)+((1-V13)*0.175))+W13</f>
         <v>3.3575</v>
       </c>
-      <c r="Y13" s="0" t="n">
+      <c r="Y13" s="1" t="n">
         <v>774108</v>
       </c>
     </row>
@@ -22230,7 +22242,7 @@
         <f aca="false">((O14*0.3)+(Q14*0.175)+(R14*0.175)+(U14*0.175)+((1-V14)*0.175))+W14</f>
         <v>2.47138888888889</v>
       </c>
-      <c r="Y14" s="0" t="n">
+      <c r="Y14" s="1" t="n">
         <v>774108</v>
       </c>
     </row>
@@ -22316,7 +22328,7 @@
         <f aca="false">((O15*0.3)+(Q15*0.175)+(R15*0.175)+(U15*0.175)+((1-V15)*0.175))+W15</f>
         <v>3.57402777777778</v>
       </c>
-      <c r="Y15" s="0" t="n">
+      <c r="Y15" s="1" t="n">
         <v>774108</v>
       </c>
     </row>
@@ -22402,7 +22414,7 @@
         <f aca="false">((O16*0.3)+(Q16*0.175)+(R16*0.175)+(U16*0.175)+((1-V16)*0.175))+W16</f>
         <v>3.94083333333333</v>
       </c>
-      <c r="Y16" s="0" t="n">
+      <c r="Y16" s="1" t="n">
         <v>774418</v>
       </c>
     </row>
@@ -22488,7 +22500,7 @@
         <f aca="false">((O17*0.3)+(Q17*0.175)+(R17*0.175)+(U17*0.175)+((1-V17)*0.175))+W17</f>
         <v>2.30388888888889</v>
       </c>
-      <c r="Y17" s="0" t="n">
+      <c r="Y17" s="1" t="n">
         <v>774418</v>
       </c>
     </row>
@@ -22574,7 +22586,7 @@
         <f aca="false">((O18*0.3)+(Q18*0.175)+(R18*0.175)+(U18*0.175)+((1-V18)*0.175))+W18</f>
         <v>2.30388888888889</v>
       </c>
-      <c r="Y18" s="0" t="n">
+      <c r="Y18" s="1" t="n">
         <v>774418</v>
       </c>
     </row>
@@ -22660,7 +22672,7 @@
         <f aca="false">((O19*0.3)+(Q19*0.175)+(R19*0.175)+(U19*0.175)+((1-V19)*0.175))+W19</f>
         <v>2.7725</v>
       </c>
-      <c r="Y19" s="0" t="n">
+      <c r="Y19" s="1" t="n">
         <v>787397</v>
       </c>
     </row>
@@ -22746,7 +22758,7 @@
         <f aca="false">((O20*0.3)+(Q20*0.175)+(R20*0.175)+(U20*0.175)+((1-V20)*0.175))+W20</f>
         <v>3.66055555555556</v>
       </c>
-      <c r="Y20" s="0" t="n">
+      <c r="Y20" s="1" t="n">
         <v>787397</v>
       </c>
     </row>
@@ -22832,7 +22844,7 @@
         <f aca="false">((O21*0.3)+(Q21*0.175)+(R21*0.175)+(U21*0.175)+((1-V21)*0.175))+W21</f>
         <v>3.58305555555556</v>
       </c>
-      <c r="Y21" s="0" t="n">
+      <c r="Y21" s="1" t="n">
         <v>787397</v>
       </c>
     </row>
@@ -22918,7 +22930,7 @@
         <f aca="false">((O22*0.3)+(Q22*0.175)+(R22*0.175)+(U22*0.175)+((1-V22)*0.175))+W22</f>
         <v>2.59833333333333</v>
       </c>
-      <c r="Y22" s="0" t="n">
+      <c r="Y22" s="1" t="n">
         <v>787397</v>
       </c>
     </row>
@@ -23004,7 +23016,7 @@
         <f aca="false">((O23*0.3)+(Q23*0.175)+(R23*0.175)+(U23*0.175)+((1-V23)*0.175))+W23</f>
         <v>2.887</v>
       </c>
-      <c r="Y23" s="0" t="n">
+      <c r="Y23" s="1" t="n">
         <v>823975</v>
       </c>
     </row>
@@ -23090,7 +23102,7 @@
         <f aca="false">((O24*0.3)+(Q24*0.175)+(R24*0.175)+(U24*0.175)+((1-V24)*0.175))+W24</f>
         <v>3.74035</v>
       </c>
-      <c r="Y24" s="0" t="n">
+      <c r="Y24" s="1" t="n">
         <v>823975</v>
       </c>
     </row>
@@ -23176,7 +23188,7 @@
         <f aca="false">((O25*0.3)+(Q25*0.175)+(R25*0.175)+(U25*0.175)+((1-V25)*0.175))+W25</f>
         <v>2.46688888888889</v>
       </c>
-      <c r="Y25" s="0" t="n">
+      <c r="Y25" s="1" t="n">
         <v>823975</v>
       </c>
     </row>
@@ -23262,7 +23274,7 @@
         <f aca="false">((O26*0.3)+(Q26*0.175)+(R26*0.175)+(U26*0.175)+((1-V26)*0.175))+W26</f>
         <v>3.43088888888889</v>
       </c>
-      <c r="Y26" s="0" t="n">
+      <c r="Y26" s="1" t="n">
         <v>823975</v>
       </c>
     </row>
@@ -23348,7 +23360,7 @@
         <f aca="false">((O27*0.3)+(Q27*0.175)+(R27*0.175)+(U27*0.175)+((1-V27)*0.175))+W27</f>
         <v>2.39488888888889</v>
       </c>
-      <c r="Y27" s="0" t="n">
+      <c r="Y27" s="1" t="n">
         <v>823975</v>
       </c>
     </row>
@@ -23434,7 +23446,7 @@
         <f aca="false">((O28*0.3)+(Q28*0.175)+(R28*0.175)+(U28*0.175)+((1-V28)*0.175))+W28</f>
         <v>3.91083333333333</v>
       </c>
-      <c r="Y28" s="0" t="n">
+      <c r="Y28" s="1" t="n">
         <v>824881</v>
       </c>
     </row>
@@ -23520,7 +23532,7 @@
         <f aca="false">((O29*0.3)+(Q29*0.175)+(R29*0.175)+(U29*0.175)+((1-V29)*0.175))+W29</f>
         <v>2.70263888888889</v>
       </c>
-      <c r="Y29" s="0" t="n">
+      <c r="Y29" s="1" t="n">
         <v>824881</v>
       </c>
     </row>
@@ -23606,7 +23618,7 @@
         <f aca="false">((O30*0.3)+(Q30*0.175)+(R30*0.175)+(U30*0.175)+((1-V30)*0.175))+W30</f>
         <v>3.49388888888889</v>
       </c>
-      <c r="Y30" s="0" t="n">
+      <c r="Y30" s="1" t="n">
         <v>824881</v>
       </c>
     </row>
@@ -23692,7 +23704,7 @@
         <f aca="false">((O31*0.3)+(Q31*0.175)+(R31*0.175)+(U31*0.175)+((1-V31)*0.175))+W31</f>
         <v>2.40388888888889</v>
       </c>
-      <c r="Y31" s="0" t="n">
+      <c r="Y31" s="1" t="n">
         <v>824881</v>
       </c>
     </row>
@@ -23778,7 +23790,7 @@
         <f aca="false">((O32*0.3)+(Q32*0.175)+(R32*0.175)+(U32*0.175)+((1-V32)*0.175))+W32</f>
         <v>3.935</v>
       </c>
-      <c r="Y32" s="0" t="n">
+      <c r="Y32" s="1" t="n">
         <v>848075</v>
       </c>
     </row>
@@ -23864,7 +23876,7 @@
         <f aca="false">((O33*0.3)+(Q33*0.175)+(R33*0.175)+(U33*0.175)+((1-V33)*0.175))+W33</f>
         <v>2.48375</v>
       </c>
-      <c r="Y33" s="0" t="n">
+      <c r="Y33" s="1" t="n">
         <v>848075</v>
       </c>
     </row>
@@ -23950,7 +23962,7 @@
         <f aca="false">((O34*0.3)+(Q34*0.175)+(R34*0.175)+(U34*0.175)+((1-V34)*0.175))+W34</f>
         <v>2.59388888888889</v>
       </c>
-      <c r="Y34" s="0" t="n">
+      <c r="Y34" s="1" t="n">
         <v>848075</v>
       </c>
     </row>
@@ -24036,7 +24048,7 @@
         <f aca="false">((O35*0.3)+(Q35*0.175)+(R35*0.175)+(U35*0.175)+((1-V35)*0.175))+W35</f>
         <v>3.83916666666667</v>
       </c>
-      <c r="Y35" s="0" t="n">
+      <c r="Y35" s="1" t="n">
         <v>862064</v>
       </c>
     </row>
@@ -24122,7 +24134,7 @@
         <f aca="false">((O36*0.3)+(Q36*0.175)+(R36*0.175)+(U36*0.175)+((1-V36)*0.175))+W36</f>
         <v>3.60569444444444</v>
       </c>
-      <c r="Y36" s="0" t="n">
+      <c r="Y36" s="1" t="n">
         <v>862064</v>
       </c>
     </row>
@@ -24208,7 +24220,7 @@
         <f aca="false">((O37*0.3)+(Q37*0.175)+(R37*0.175)+(U37*0.175)+((1-V37)*0.175))+W37</f>
         <v>2.28486111111111</v>
       </c>
-      <c r="Y37" s="0" t="n">
+      <c r="Y37" s="1" t="n">
         <v>862064</v>
       </c>
     </row>
@@ -24294,7 +24306,7 @@
         <f aca="false">((O38*0.3)+(Q38*0.175)+(R38*0.175)+(U38*0.175)+((1-V38)*0.175))+W38</f>
         <v>2.43069444444444</v>
       </c>
-      <c r="Y38" s="0" t="n">
+      <c r="Y38" s="1" t="n">
         <v>862064</v>
       </c>
     </row>
@@ -24380,7 +24392,7 @@
         <f aca="false">((O39*0.3)+(Q39*0.175)+(R39*0.175)+(U39*0.175)+((1-V39)*0.175))+W39</f>
         <v>3.935</v>
       </c>
-      <c r="Y39" s="0" t="n">
+      <c r="Y39" s="1" t="n">
         <v>863208</v>
       </c>
     </row>
@@ -24466,7 +24478,7 @@
         <f aca="false">((O40*0.3)+(Q40*0.175)+(R40*0.175)+(U40*0.175)+((1-V40)*0.175))+W40</f>
         <v>2.48375</v>
       </c>
-      <c r="Y40" s="0" t="n">
+      <c r="Y40" s="1" t="n">
         <v>863208</v>
       </c>
     </row>
@@ -24552,7 +24564,7 @@
         <f aca="false">((O41*0.3)+(Q41*0.175)+(R41*0.175)+(U41*0.175)+((1-V41)*0.175))+W41</f>
         <v>3.30875</v>
       </c>
-      <c r="Y41" s="0" t="n">
+      <c r="Y41" s="1" t="n">
         <v>863208</v>
       </c>
     </row>
@@ -24638,7 +24650,7 @@
         <f aca="false">((O42*0.3)+(Q42*0.175)+(R42*0.175)+(U42*0.175)+((1-V42)*0.175))+W42</f>
         <v>2.94083333333333</v>
       </c>
-      <c r="Y42" s="0" t="n">
+      <c r="Y42" s="1" t="n">
         <v>868917</v>
       </c>
     </row>
@@ -24724,7 +24736,7 @@
         <f aca="false">((O43*0.3)+(Q43*0.175)+(R43*0.175)+(U43*0.175)+((1-V43)*0.175))+W43</f>
         <v>2.65388888888889</v>
       </c>
-      <c r="Y43" s="0" t="n">
+      <c r="Y43" s="1" t="n">
         <v>868917</v>
       </c>
     </row>
@@ -24810,7 +24822,7 @@
         <f aca="false">((O44*0.3)+(Q44*0.175)+(R44*0.175)+(U44*0.175)+((1-V44)*0.175))+W44</f>
         <v>3.65388888888889</v>
       </c>
-      <c r="Y44" s="0" t="n">
+      <c r="Y44" s="1" t="n">
         <v>868917</v>
       </c>
     </row>
@@ -24896,7 +24908,7 @@
         <f aca="false">((O45*0.3)+(Q45*0.175)+(R45*0.175)+(U45*0.175)+((1-V45)*0.175))+W45</f>
         <v>2.94666666666667</v>
       </c>
-      <c r="Y45" s="0" t="n">
+      <c r="Y45" s="1" t="n">
         <v>869357</v>
       </c>
     </row>
@@ -24982,7 +24994,7 @@
         <f aca="false">((O46*0.3)+(Q46*0.175)+(R46*0.175)+(U46*0.175)+((1-V46)*0.175))+W46</f>
         <v>2.29902777777778</v>
       </c>
-      <c r="Y46" s="0" t="n">
+      <c r="Y46" s="1" t="n">
         <v>869357</v>
       </c>
     </row>
@@ -25068,7 +25080,7 @@
         <f aca="false">((O47*0.3)+(Q47*0.175)+(R47*0.175)+(U47*0.175)+((1-V47)*0.175))+W47</f>
         <v>3.58416666666667</v>
       </c>
-      <c r="Y47" s="0" t="n">
+      <c r="Y47" s="1" t="n">
         <v>869357</v>
       </c>
     </row>
@@ -25154,7 +25166,7 @@
         <f aca="false">((O48*0.3)+(Q48*0.175)+(R48*0.175)+(U48*0.175)+((1-V48)*0.175))+W48</f>
         <v>3.92333333333333</v>
       </c>
-      <c r="Y48" s="0" t="n">
+      <c r="Y48" s="1" t="n">
         <v>869611</v>
       </c>
     </row>
@@ -25240,7 +25252,7 @@
         <f aca="false">((O49*0.3)+(Q49*0.175)+(R49*0.175)+(U49*0.175)+((1-V49)*0.175))+W49</f>
         <v>3.49347222222222</v>
       </c>
-      <c r="Y49" s="0" t="n">
+      <c r="Y49" s="1" t="n">
         <v>869611</v>
       </c>
     </row>
@@ -25326,7 +25338,7 @@
         <f aca="false">((O50*0.3)+(Q50*0.175)+(R50*0.175)+(U50*0.175)+((1-V50)*0.175))+W50</f>
         <v>3.59875</v>
       </c>
-      <c r="Y50" s="0" t="n">
+      <c r="Y50" s="1" t="n">
         <v>869611</v>
       </c>
     </row>
@@ -25412,7 +25424,7 @@
         <f aca="false">((O51*0.3)+(Q51*0.175)+(R51*0.175)+(U51*0.175)+((1-V51)*0.175))+W51</f>
         <v>2.94083333333333</v>
       </c>
-      <c r="Y51" s="0" t="n">
+      <c r="Y51" s="1" t="n">
         <v>913140</v>
       </c>
     </row>
@@ -25498,7 +25510,7 @@
         <f aca="false">((O52*0.3)+(Q52*0.175)+(R52*0.175)+(U52*0.175)+((1-V52)*0.175))+W52</f>
         <v>2.30388888888889</v>
       </c>
-      <c r="Y52" s="0" t="n">
+      <c r="Y52" s="1" t="n">
         <v>913140</v>
       </c>
     </row>
@@ -25584,7 +25596,7 @@
         <f aca="false">((O53*0.3)+(Q53*0.175)+(R53*0.175)+(U53*0.175)+((1-V53)*0.175))+W53</f>
         <v>3.23902777777778</v>
       </c>
-      <c r="Y53" s="0" t="n">
+      <c r="Y53" s="1" t="n">
         <v>913140</v>
       </c>
     </row>
@@ -25670,7 +25682,7 @@
         <f aca="false">((O54*0.3)+(Q54*0.175)+(R54*0.175)+(U54*0.175)+((1-V54)*0.175))+W54</f>
         <v>3.67861111111111</v>
       </c>
-      <c r="Y54" s="0" t="n">
+      <c r="Y54" s="1" t="n">
         <v>944159</v>
       </c>
     </row>
@@ -25756,7 +25768,7 @@
         <f aca="false">((O55*0.3)+(Q55*0.175)+(R55*0.175)+(U55*0.175)+((1-V55)*0.175))+W55</f>
         <v>2.32125</v>
       </c>
-      <c r="Y55" s="0" t="n">
+      <c r="Y55" s="1" t="n">
         <v>944159</v>
       </c>
     </row>
@@ -25842,7 +25854,7 @@
         <f aca="false">((O56*0.3)+(Q56*0.175)+(R56*0.175)+(U56*0.175)+((1-V56)*0.175))+W56</f>
         <v>2.89916666666667</v>
       </c>
-      <c r="Y56" s="0" t="n">
+      <c r="Y56" s="1" t="n">
         <v>944159</v>
       </c>
     </row>
@@ -25928,21 +25940,181 @@
         <f aca="false">((O57*0.3)+(Q57*0.175)+(R57*0.175)+(U57*0.175)+((1-V57)*0.175))+W57</f>
         <v>2.48111111111111</v>
       </c>
-      <c r="Y57" s="0" t="n">
+      <c r="Y57" s="1" t="n">
         <v>944159</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="40"/>
-      <c r="E58" s="15"/>
-      <c r="M58" s="17"/>
-      <c r="X58" s="15"/>
+      <c r="A58" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B58" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <f aca="false">F58-(1/H58)</f>
+        <v>0.5</v>
+      </c>
+      <c r="K58" s="22" t="n">
+        <f aca="false">((I58-((H58-1)/H58))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <f aca="false">E58-((E59)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <f aca="false">0.5+(L58*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N58" s="22" t="n">
+        <f aca="false">((H58-(G58-1))/H58)*(IF(I58&lt;&gt;0,(I58+H58)/H58,1))</f>
+        <v>1</v>
+      </c>
+      <c r="O58" s="26" t="n">
+        <f aca="false">(N58-(1/6))/(10/6)</f>
+        <v>0.5</v>
+      </c>
+      <c r="P58" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" s="26" t="n">
+        <f aca="false">IF(F58=1,(((1-((P58-3)/15))*0.5)+0.5),((P58/18)*0.5))</f>
+        <v>0.766666666666667</v>
+      </c>
+      <c r="R58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="26" t="n">
+        <f aca="false">IFERROR(T58/S58, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V58" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X58" s="15" t="n">
+        <f aca="false">((O58*0.3)+(Q58*0.175)+(R58*0.175)+(U58*0.175)+((1-V58)*0.175))+W58</f>
+        <v>3.63416666666667</v>
+      </c>
+      <c r="Y58" s="1" t="n">
+        <v>999999999</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="40"/>
-      <c r="E59" s="15"/>
-      <c r="M59" s="17"/>
-      <c r="X59" s="15"/>
+      <c r="A59" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B59" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="22" t="n">
+        <f aca="false">F59-(1/H59)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="K59" s="22" t="n">
+        <f aca="false">((I59-((H59-1)/H59))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L59" s="22" t="n">
+        <f aca="false">E59-((E58)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="17" t="n">
+        <f aca="false">0.5+(L59*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N59" s="22" t="n">
+        <f aca="false">((H59-(G59-1))/H59)*(IF(I59&lt;&gt;0,(I59+H59)/H59,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="O59" s="26" t="n">
+        <f aca="false">(N59-(1/6))/(10/6)</f>
+        <v>0.2</v>
+      </c>
+      <c r="P59" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" s="26" t="n">
+        <f aca="false">IF(F59=1,(((1-((P59-3)/15))*0.5)+0.5),((P59/18)*0.5))</f>
+        <v>0.277777777777778</v>
+      </c>
+      <c r="R59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="26" t="n">
+        <f aca="false">IFERROR(T59/S59, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X59" s="15" t="n">
+        <f aca="false">((O59*0.3)+(Q59*0.175)+(R59*0.175)+(U59*0.175)+((1-V59)*0.175))+W59</f>
+        <v>3.45861111111111</v>
+      </c>
+      <c r="Y59" s="1" t="n">
+        <v>999999999</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="40"/>
@@ -26324,17 +26496,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C1" s="45"/>
       <c r="D1" s="44" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26360,7 +26532,7 @@
         <v>2.4</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26372,13 +26544,13 @@
         <v>3.7</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D4" s="48" t="n">
         <v>3.7</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26394,7 +26566,7 @@
         <v>2.3</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26419,13 +26591,13 @@
         <v>2.89916666666667</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D7" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26451,7 +26623,7 @@
         <v>3.8</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26467,7 +26639,7 @@
         <v>3.9</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26479,13 +26651,13 @@
         <v>3.4</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" s="48" t="n">
         <v>3.4</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26501,7 +26673,7 @@
         <v>2.6</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26513,13 +26685,13 @@
         <v>3.5</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D13" s="48" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26535,7 +26707,7 @@
         <v>2.7</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26551,7 +26723,7 @@
         <v>2.6</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26567,7 +26739,7 @@
         <v>3.9</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26583,7 +26755,7 @@
         <v>2.3</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26599,12 +26771,12 @@
         <v>3.5</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
@@ -26615,12 +26787,12 @@
         <v>3.9</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
@@ -26631,7 +26803,7 @@
         <v>3.7</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26643,13 +26815,13 @@
         <v>3.67861111111111</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D21" s="48" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26675,7 +26847,7 @@
         <v>2.4</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26691,7 +26863,7 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26707,7 +26879,7 @@
         <v>3.6</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26723,7 +26895,7 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26735,13 +26907,13 @@
         <v>3.9</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D27" s="48" t="n">
         <v>3.9</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26770,7 +26942,7 @@
         <v>2.6</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26782,13 +26954,13 @@
         <v>3.59875</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D30" s="48" t="n">
         <v>3.6</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26804,7 +26976,7 @@
         <v>3.9</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26820,7 +26992,7 @@
         <v>3.7</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26836,7 +27008,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26852,7 +27024,7 @@
         <v>2.9</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26864,18 +27036,18 @@
         <v>3.935</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D35" s="49" t="n">
         <v>3.9</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
@@ -26886,7 +27058,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26902,12 +27074,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
@@ -26918,7 +27090,7 @@
         <v>3.9</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26934,7 +27106,7 @@
         <v>2.6</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26960,7 +27132,7 @@
         <v>3.5</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26976,7 +27148,7 @@
         <v>3.4</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26992,7 +27164,7 @@
         <v>3.7</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27008,7 +27180,7 @@
         <v>2.6</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27024,7 +27196,7 @@
         <v>3.8</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27040,7 +27212,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27056,7 +27228,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27072,7 +27244,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27101,7 +27273,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27117,12 +27289,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -27133,7 +27305,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27149,12 +27321,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -27165,7 +27337,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27187,7 +27359,7 @@
         <v>3.6</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D56" s="48" t="n">
         <v>3.6</v>
@@ -27202,7 +27374,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D57" s="48" t="n">
         <v>3.3</v>
@@ -27230,7 +27402,7 @@
         <v>3.9</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D59" s="48" t="n">
         <v>3.9</v>
@@ -27347,7 +27519,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27363,7 +27535,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27379,7 +27551,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27418,7 +27590,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27460,16 +27632,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27763,7 +27935,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
@@ -27780,7 +27952,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -28052,7 +28224,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -28086,7 +28258,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -28324,7 +28496,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -28358,7 +28530,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28748,40 +28920,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D1" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="50" t="s">
-        <v>170</v>
-      </c>
       <c r="F1" s="50" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H1" s="50" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I1" s="50" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K1" s="50" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L1" s="50" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="188">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t xml:space="preserve">Test Commander B (THROWAWAY TEST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Commander C (THROWAWAY TEST 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Commander D (THROWAWAY TEST 2)</t>
   </si>
   <si>
     <t xml:space="preserve">Decks</t>
@@ -26117,16 +26123,176 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="40"/>
-      <c r="E60" s="15"/>
-      <c r="M60" s="17"/>
-      <c r="X60" s="15"/>
+      <c r="A60" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B60" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="22" t="n">
+        <f aca="false">F60-(1/H60)</f>
+        <v>0.5</v>
+      </c>
+      <c r="K60" s="22" t="n">
+        <f aca="false">((I60-((H60-1)/H60))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L60" s="22" t="n">
+        <f aca="false">E60-((E61)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="17" t="n">
+        <f aca="false">0.5+(L60*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N60" s="22" t="n">
+        <f aca="false">((H60-(G60-1))/H60)*(IF(I60&lt;&gt;0,(I60+H60)/H60,1))</f>
+        <v>1</v>
+      </c>
+      <c r="O60" s="26" t="n">
+        <f aca="false">(N60-(1/6))/(10/6)</f>
+        <v>0.5</v>
+      </c>
+      <c r="P60" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" s="26" t="n">
+        <f aca="false">IF(F60=1,(((1-((P60-3)/15))*0.5)+0.5),((P60/18)*0.5))</f>
+        <v>0.766666666666667</v>
+      </c>
+      <c r="R60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="26" t="n">
+        <f aca="false">IFERROR(T60/S60, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X60" s="15" t="n">
+        <f aca="false">((O60*0.3)+(Q60*0.175)+(R60*0.175)+(U60*0.175)+((1-V60)*0.175))+W60</f>
+        <v>3.63416666666667</v>
+      </c>
+      <c r="Y60" s="1" t="n">
+        <v>999999998</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="40"/>
-      <c r="E61" s="15"/>
-      <c r="M61" s="17"/>
-      <c r="X61" s="15"/>
+      <c r="A61" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B61" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="22" t="n">
+        <f aca="false">F61-(1/H61)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="K61" s="22" t="n">
+        <f aca="false">((I61-((H61-1)/H61))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L61" s="22" t="n">
+        <f aca="false">E61-((E60)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="17" t="n">
+        <f aca="false">0.5+(L61*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N61" s="22" t="n">
+        <f aca="false">((H61-(G61-1))/H61)*(IF(I61&lt;&gt;0,(I61+H61)/H61,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="O61" s="26" t="n">
+        <f aca="false">(N61-(1/6))/(10/6)</f>
+        <v>0.2</v>
+      </c>
+      <c r="P61" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" s="26" t="n">
+        <f aca="false">IF(F61=1,(((1-((P61-3)/15))*0.5)+0.5),((P61/18)*0.5))</f>
+        <v>0.277777777777778</v>
+      </c>
+      <c r="R61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="26" t="n">
+        <f aca="false">IFERROR(T61/S61, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V61" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X61" s="15" t="n">
+        <f aca="false">((O61*0.3)+(Q61*0.175)+(R61*0.175)+(U61*0.175)+((1-V61)*0.175))+W61</f>
+        <v>3.45861111111111</v>
+      </c>
+      <c r="Y61" s="1" t="n">
+        <v>999999998</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="40"/>
@@ -26496,17 +26662,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C1" s="45"/>
       <c r="D1" s="44" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26532,7 +26698,7 @@
         <v>2.4</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26544,13 +26710,13 @@
         <v>3.7</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D4" s="48" t="n">
         <v>3.7</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26566,7 +26732,7 @@
         <v>2.3</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26591,13 +26757,13 @@
         <v>2.89916666666667</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D7" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26623,7 +26789,7 @@
         <v>3.8</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26639,7 +26805,7 @@
         <v>3.9</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26651,13 +26817,13 @@
         <v>3.4</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D11" s="48" t="n">
         <v>3.4</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26673,7 +26839,7 @@
         <v>2.6</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26685,13 +26851,13 @@
         <v>3.5</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D13" s="48" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26707,7 +26873,7 @@
         <v>2.7</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26723,7 +26889,7 @@
         <v>2.6</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26739,7 +26905,7 @@
         <v>3.9</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26755,7 +26921,7 @@
         <v>2.3</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26771,12 +26937,12 @@
         <v>3.5</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
@@ -26787,12 +26953,12 @@
         <v>3.9</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
@@ -26803,7 +26969,7 @@
         <v>3.7</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26815,13 +26981,13 @@
         <v>3.67861111111111</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D21" s="48" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26847,7 +27013,7 @@
         <v>2.4</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26863,7 +27029,7 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26879,7 +27045,7 @@
         <v>3.6</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26895,7 +27061,7 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26907,13 +27073,13 @@
         <v>3.9</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D27" s="48" t="n">
         <v>3.9</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26942,7 +27108,7 @@
         <v>2.6</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26954,13 +27120,13 @@
         <v>3.59875</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" s="48" t="n">
         <v>3.6</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26976,7 +27142,7 @@
         <v>3.9</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26992,7 +27158,7 @@
         <v>3.7</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27008,7 +27174,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27024,7 +27190,7 @@
         <v>2.9</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27036,18 +27202,18 @@
         <v>3.935</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D35" s="49" t="n">
         <v>3.9</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
@@ -27058,7 +27224,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27074,12 +27240,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
@@ -27090,7 +27256,7 @@
         <v>3.9</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27106,7 +27272,7 @@
         <v>2.6</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27132,7 +27298,7 @@
         <v>3.5</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27148,7 +27314,7 @@
         <v>3.4</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27164,7 +27330,7 @@
         <v>3.7</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27180,7 +27346,7 @@
         <v>2.6</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27196,7 +27362,7 @@
         <v>3.8</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27212,7 +27378,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27228,7 +27394,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27244,7 +27410,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27273,7 +27439,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27289,12 +27455,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -27305,7 +27471,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27321,12 +27487,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -27337,7 +27503,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27359,7 +27525,7 @@
         <v>3.6</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D56" s="48" t="n">
         <v>3.6</v>
@@ -27374,7 +27540,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D57" s="48" t="n">
         <v>3.3</v>
@@ -27402,7 +27568,7 @@
         <v>3.9</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D59" s="48" t="n">
         <v>3.9</v>
@@ -27519,7 +27685,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27535,7 +27701,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27551,7 +27717,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27590,7 +27756,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27632,16 +27798,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27935,7 +28101,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
@@ -27952,7 +28118,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -28224,7 +28390,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -28258,7 +28424,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -28496,7 +28662,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -28530,7 +28696,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28920,40 +29086,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B1" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="D1" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="E1" s="50" t="s">
-        <v>174</v>
-      </c>
       <c r="F1" s="50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H1" s="50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I1" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K1" s="50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L1" s="50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="186">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -336,6 +336,18 @@
   </si>
   <si>
     <t xml:space="preserve">Arna Kennerüd, Skycaptain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestPlayer1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Commander E (THROWAWAY TEST 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestPlayer2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Commander F (THROWAWAY TEST 3)</t>
   </si>
   <si>
     <t xml:space="preserve">Decks</t>
@@ -25933,58 +25945,176 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="40"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="22"/>
-      <c r="O58" s="26"/>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="26"/>
-      <c r="R58" s="22"/>
-      <c r="S58" s="22"/>
-      <c r="T58" s="22"/>
-      <c r="U58" s="26"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="24"/>
-      <c r="X58" s="15"/>
-      <c r="Y58" s="1"/>
+      <c r="A58" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B58" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <f aca="false">F58-(1/H58)</f>
+        <v>0.5</v>
+      </c>
+      <c r="K58" s="22" t="n">
+        <f aca="false">((I58-((H58-1)/H58))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <f aca="false">E58-((E59)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <f aca="false">0.5+(L58*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N58" s="22" t="n">
+        <f aca="false">((H58-(G58-1))/H58)*(IF(I58&lt;&gt;0,(I58+H58)/H58,1))</f>
+        <v>1</v>
+      </c>
+      <c r="O58" s="26" t="n">
+        <f aca="false">(N58-(1/6))/(10/6)</f>
+        <v>0.5</v>
+      </c>
+      <c r="P58" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" s="26" t="n">
+        <f aca="false">IF(F58=1,(((1-((P58-3)/15))*0.5)+0.5),((P58/18)*0.5))</f>
+        <v>0.766666666666667</v>
+      </c>
+      <c r="R58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="26" t="n">
+        <f aca="false">IFERROR(T58/S58, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V58" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X58" s="15" t="n">
+        <f aca="false">((O58*0.3)+(Q58*0.175)+(R58*0.175)+(U58*0.175)+((1-V58)*0.175))+W58</f>
+        <v>3.63416666666667</v>
+      </c>
+      <c r="Y58" s="1" t="n">
+        <v>999999997</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="40"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="22"/>
-      <c r="O59" s="26"/>
-      <c r="P59" s="22"/>
-      <c r="Q59" s="26"/>
-      <c r="R59" s="22"/>
-      <c r="S59" s="22"/>
-      <c r="T59" s="22"/>
-      <c r="U59" s="26"/>
-      <c r="V59" s="27"/>
-      <c r="W59" s="24"/>
-      <c r="X59" s="15"/>
-      <c r="Y59" s="1"/>
+      <c r="A59" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B59" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="22" t="n">
+        <f aca="false">F59-(1/H59)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="K59" s="22" t="n">
+        <f aca="false">((I59-((H59-1)/H59))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L59" s="22" t="n">
+        <f aca="false">E59-((E58)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="17" t="n">
+        <f aca="false">0.5+(L59*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N59" s="22" t="n">
+        <f aca="false">((H59-(G59-1))/H59)*(IF(I59&lt;&gt;0,(I59+H59)/H59,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="O59" s="26" t="n">
+        <f aca="false">(N59-(1/6))/(10/6)</f>
+        <v>0.2</v>
+      </c>
+      <c r="P59" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" s="26" t="n">
+        <f aca="false">IF(F59=1,(((1-((P59-3)/15))*0.5)+0.5),((P59/18)*0.5))</f>
+        <v>0.277777777777778</v>
+      </c>
+      <c r="R59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="26" t="n">
+        <f aca="false">IFERROR(T59/S59, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X59" s="15" t="n">
+        <f aca="false">((O59*0.3)+(Q59*0.175)+(R59*0.175)+(U59*0.175)+((1-V59)*0.175))+W59</f>
+        <v>3.45861111111111</v>
+      </c>
+      <c r="Y59" s="1" t="n">
+        <v>999999997</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="40"/>
@@ -26408,17 +26538,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C1" s="45"/>
       <c r="D1" s="44" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26444,7 +26574,7 @@
         <v>2.4</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26456,13 +26586,13 @@
         <v>3.7</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D4" s="48" t="n">
         <v>3.7</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26478,7 +26608,7 @@
         <v>2.3</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26503,13 +26633,13 @@
         <v>2.89916666666667</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D7" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26535,7 +26665,7 @@
         <v>3.8</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26551,7 +26681,7 @@
         <v>3.9</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26563,13 +26693,13 @@
         <v>3.4</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" s="48" t="n">
         <v>3.4</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26585,7 +26715,7 @@
         <v>2.6</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26597,13 +26727,13 @@
         <v>3.5</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D13" s="48" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26619,7 +26749,7 @@
         <v>2.7</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26635,7 +26765,7 @@
         <v>2.6</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26651,7 +26781,7 @@
         <v>3.9</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26667,7 +26797,7 @@
         <v>2.3</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26683,12 +26813,12 @@
         <v>3.5</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
@@ -26699,12 +26829,12 @@
         <v>3.9</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
@@ -26715,7 +26845,7 @@
         <v>3.7</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26727,13 +26857,13 @@
         <v>3.67861111111111</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D21" s="48" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26759,7 +26889,7 @@
         <v>2.4</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26775,7 +26905,7 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26791,7 +26921,7 @@
         <v>3.6</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26807,7 +26937,7 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26819,13 +26949,13 @@
         <v>3.9</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D27" s="48" t="n">
         <v>3.9</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26854,7 +26984,7 @@
         <v>2.6</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26866,13 +26996,13 @@
         <v>3.59875</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D30" s="48" t="n">
         <v>3.6</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26888,7 +27018,7 @@
         <v>3.9</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26904,7 +27034,7 @@
         <v>3.7</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26920,7 +27050,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26936,7 +27066,7 @@
         <v>2.9</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26948,18 +27078,18 @@
         <v>3.935</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D35" s="49" t="n">
         <v>3.9</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
@@ -26970,7 +27100,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26986,12 +27116,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
@@ -27002,7 +27132,7 @@
         <v>3.9</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27018,7 +27148,7 @@
         <v>2.6</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27044,7 +27174,7 @@
         <v>3.5</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27060,7 +27190,7 @@
         <v>3.4</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27076,7 +27206,7 @@
         <v>3.7</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27092,7 +27222,7 @@
         <v>2.6</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27108,7 +27238,7 @@
         <v>3.8</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27124,7 +27254,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27140,7 +27270,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27156,7 +27286,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27185,7 +27315,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27201,12 +27331,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -27217,7 +27347,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27233,12 +27363,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -27249,7 +27379,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27271,7 +27401,7 @@
         <v>3.6</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D56" s="48" t="n">
         <v>3.6</v>
@@ -27286,7 +27416,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D57" s="48" t="n">
         <v>3.3</v>
@@ -27314,7 +27444,7 @@
         <v>3.9</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D59" s="48" t="n">
         <v>3.9</v>
@@ -27431,7 +27561,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27447,7 +27577,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27463,7 +27593,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27502,7 +27632,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27544,16 +27674,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27847,7 +27977,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
@@ -27864,7 +27994,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -28136,7 +28266,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -28170,7 +28300,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -28408,7 +28538,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -28442,7 +28572,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28832,40 +28962,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D1" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="50" t="s">
-        <v>170</v>
-      </c>
       <c r="F1" s="50" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H1" s="50" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I1" s="50" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K1" s="50" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L1" s="50" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="186">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -336,6 +336,18 @@
   </si>
   <si>
     <t xml:space="preserve">Arna Kennerüd, Skycaptain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestPlayer1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test G (THROWAWAY 4a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestPlayer2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test H (THROWAWAY 4a)</t>
   </si>
   <si>
     <t xml:space="preserve">Decks</t>
@@ -25933,58 +25945,176 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="40"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="22"/>
-      <c r="O58" s="26"/>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="26"/>
-      <c r="R58" s="22"/>
-      <c r="S58" s="22"/>
-      <c r="T58" s="22"/>
-      <c r="U58" s="26"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="24"/>
-      <c r="X58" s="15"/>
-      <c r="Y58" s="1"/>
+      <c r="A58" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B58" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <f aca="false">F58-(1/H58)</f>
+        <v>0.5</v>
+      </c>
+      <c r="K58" s="22" t="n">
+        <f aca="false">((I58-((H58-1)/H58))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <f aca="false">E58-((E59)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <f aca="false">0.5+(L58*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N58" s="22" t="n">
+        <f aca="false">((H58-(G58-1))/H58)*(IF(I58&lt;&gt;0,(I58+H58)/H58,1))</f>
+        <v>1</v>
+      </c>
+      <c r="O58" s="26" t="n">
+        <f aca="false">(N58-(1/6))/(10/6)</f>
+        <v>0.5</v>
+      </c>
+      <c r="P58" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" s="26" t="n">
+        <f aca="false">IF(F58=1,(((1-((P58-3)/15))*0.5)+0.5),((P58/18)*0.5))</f>
+        <v>0.766666666666667</v>
+      </c>
+      <c r="R58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="26" t="n">
+        <f aca="false">IFERROR(T58/S58, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V58" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X58" s="15" t="n">
+        <f aca="false">((O58*0.3)+(Q58*0.175)+(R58*0.175)+(U58*0.175)+((1-V58)*0.175))+W58</f>
+        <v>3.63416666666667</v>
+      </c>
+      <c r="Y58" s="1" t="n">
+        <v>999999996</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="40"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="22"/>
-      <c r="O59" s="26"/>
-      <c r="P59" s="22"/>
-      <c r="Q59" s="26"/>
-      <c r="R59" s="22"/>
-      <c r="S59" s="22"/>
-      <c r="T59" s="22"/>
-      <c r="U59" s="26"/>
-      <c r="V59" s="27"/>
-      <c r="W59" s="24"/>
-      <c r="X59" s="15"/>
-      <c r="Y59" s="1"/>
+      <c r="A59" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B59" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="22" t="n">
+        <f aca="false">F59-(1/H59)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="K59" s="22" t="n">
+        <f aca="false">((I59-((H59-1)/H59))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L59" s="22" t="n">
+        <f aca="false">E59-((E58)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="17" t="n">
+        <f aca="false">0.5+(L59*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N59" s="22" t="n">
+        <f aca="false">((H59-(G59-1))/H59)*(IF(I59&lt;&gt;0,(I59+H59)/H59,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="O59" s="26" t="n">
+        <f aca="false">(N59-(1/6))/(10/6)</f>
+        <v>0.2</v>
+      </c>
+      <c r="P59" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" s="26" t="n">
+        <f aca="false">IF(F59=1,(((1-((P59-3)/15))*0.5)+0.5),((P59/18)*0.5))</f>
+        <v>0.277777777777778</v>
+      </c>
+      <c r="R59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="26" t="n">
+        <f aca="false">IFERROR(T59/S59, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X59" s="15" t="n">
+        <f aca="false">((O59*0.3)+(Q59*0.175)+(R59*0.175)+(U59*0.175)+((1-V59)*0.175))+W59</f>
+        <v>3.45861111111111</v>
+      </c>
+      <c r="Y59" s="1" t="n">
+        <v>999999996</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="40"/>
@@ -26408,17 +26538,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C1" s="45"/>
       <c r="D1" s="44" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26444,7 +26574,7 @@
         <v>2.4</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26456,13 +26586,13 @@
         <v>3.7</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D4" s="48" t="n">
         <v>3.7</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26478,7 +26608,7 @@
         <v>2.3</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26503,13 +26633,13 @@
         <v>2.89916666666667</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D7" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26535,7 +26665,7 @@
         <v>3.8</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26551,7 +26681,7 @@
         <v>3.9</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26563,13 +26693,13 @@
         <v>3.4</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" s="48" t="n">
         <v>3.4</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26585,7 +26715,7 @@
         <v>2.6</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26597,13 +26727,13 @@
         <v>3.5</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D13" s="48" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26619,7 +26749,7 @@
         <v>2.7</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26635,7 +26765,7 @@
         <v>2.6</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26651,7 +26781,7 @@
         <v>3.9</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26667,7 +26797,7 @@
         <v>2.3</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26683,12 +26813,12 @@
         <v>3.5</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
@@ -26699,12 +26829,12 @@
         <v>3.9</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
@@ -26715,7 +26845,7 @@
         <v>3.7</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26727,13 +26857,13 @@
         <v>3.67861111111111</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D21" s="48" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26759,7 +26889,7 @@
         <v>2.4</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26775,7 +26905,7 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26791,7 +26921,7 @@
         <v>3.6</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26807,7 +26937,7 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26819,13 +26949,13 @@
         <v>3.9</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D27" s="48" t="n">
         <v>3.9</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26854,7 +26984,7 @@
         <v>2.6</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26866,13 +26996,13 @@
         <v>3.59875</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D30" s="48" t="n">
         <v>3.6</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26888,7 +27018,7 @@
         <v>3.9</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26904,7 +27034,7 @@
         <v>3.7</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26920,7 +27050,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26936,7 +27066,7 @@
         <v>2.9</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26948,18 +27078,18 @@
         <v>3.935</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D35" s="49" t="n">
         <v>3.9</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
@@ -26970,7 +27100,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26986,12 +27116,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
@@ -27002,7 +27132,7 @@
         <v>3.9</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27018,7 +27148,7 @@
         <v>2.6</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27044,7 +27174,7 @@
         <v>3.5</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27060,7 +27190,7 @@
         <v>3.4</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27076,7 +27206,7 @@
         <v>3.7</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27092,7 +27222,7 @@
         <v>2.6</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27108,7 +27238,7 @@
         <v>3.8</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27124,7 +27254,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27140,7 +27270,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27156,7 +27286,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27185,7 +27315,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27201,12 +27331,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -27217,7 +27347,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27233,12 +27363,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -27249,7 +27379,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27271,7 +27401,7 @@
         <v>3.6</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D56" s="48" t="n">
         <v>3.6</v>
@@ -27286,7 +27416,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D57" s="48" t="n">
         <v>3.3</v>
@@ -27314,7 +27444,7 @@
         <v>3.9</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D59" s="48" t="n">
         <v>3.9</v>
@@ -27431,7 +27561,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27447,7 +27577,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27463,7 +27593,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27502,7 +27632,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27544,16 +27674,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27847,7 +27977,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
@@ -27864,7 +27994,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -28136,7 +28266,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -28170,7 +28300,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -28408,7 +28538,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -28442,7 +28572,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28832,40 +28962,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D1" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="50" t="s">
-        <v>170</v>
-      </c>
       <c r="F1" s="50" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H1" s="50" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I1" s="50" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K1" s="50" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L1" s="50" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="188">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t xml:space="preserve">Test H (THROWAWAY 4a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test I (THROWAWAY 4b)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test J (THROWAWAY 4b)</t>
   </si>
   <si>
     <t xml:space="preserve">Decks</t>
@@ -26117,58 +26123,176 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="40"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="22"/>
-      <c r="L60" s="22"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="22"/>
-      <c r="O60" s="26"/>
-      <c r="P60" s="22"/>
-      <c r="Q60" s="26"/>
-      <c r="R60" s="22"/>
-      <c r="S60" s="22"/>
-      <c r="T60" s="22"/>
-      <c r="U60" s="26"/>
-      <c r="V60" s="27"/>
-      <c r="W60" s="24"/>
-      <c r="X60" s="15"/>
-      <c r="Y60" s="1"/>
+      <c r="A60" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B60" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="22" t="n">
+        <f aca="false">F60-(1/H60)</f>
+        <v>0.5</v>
+      </c>
+      <c r="K60" s="22" t="n">
+        <f aca="false">((I60-((H60-1)/H60))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L60" s="22" t="n">
+        <f aca="false">E60-((E61)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="17" t="n">
+        <f aca="false">0.5+(L60*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N60" s="22" t="n">
+        <f aca="false">((H60-(G60-1))/H60)*(IF(I60&lt;&gt;0,(I60+H60)/H60,1))</f>
+        <v>1</v>
+      </c>
+      <c r="O60" s="26" t="n">
+        <f aca="false">(N60-(1/6))/(10/6)</f>
+        <v>0.5</v>
+      </c>
+      <c r="P60" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q60" s="26" t="n">
+        <f aca="false">IF(F60=1,(((1-((P60-3)/15))*0.5)+0.5),((P60/18)*0.5))</f>
+        <v>0.766666666666667</v>
+      </c>
+      <c r="R60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="26" t="n">
+        <f aca="false">IFERROR(T60/S60, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X60" s="15" t="n">
+        <f aca="false">((O60*0.3)+(Q60*0.175)+(R60*0.175)+(U60*0.175)+((1-V60)*0.175))+W60</f>
+        <v>3.63416666666667</v>
+      </c>
+      <c r="Y60" s="1" t="n">
+        <v>999999995</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="40"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="26"/>
-      <c r="R61" s="22"/>
-      <c r="S61" s="22"/>
-      <c r="T61" s="22"/>
-      <c r="U61" s="26"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="24"/>
-      <c r="X61" s="15"/>
-      <c r="Y61" s="1"/>
+      <c r="A61" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B61" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="22" t="n">
+        <f aca="false">F61-(1/H61)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="K61" s="22" t="n">
+        <f aca="false">((I61-((H61-1)/H61))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L61" s="22" t="n">
+        <f aca="false">E61-((E60)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M61" s="17" t="n">
+        <f aca="false">0.5+(L61*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N61" s="22" t="n">
+        <f aca="false">((H61-(G61-1))/H61)*(IF(I61&lt;&gt;0,(I61+H61)/H61,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="O61" s="26" t="n">
+        <f aca="false">(N61-(1/6))/(10/6)</f>
+        <v>0.2</v>
+      </c>
+      <c r="P61" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q61" s="26" t="n">
+        <f aca="false">IF(F61=1,(((1-((P61-3)/15))*0.5)+0.5),((P61/18)*0.5))</f>
+        <v>0.277777777777778</v>
+      </c>
+      <c r="R61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="26" t="n">
+        <f aca="false">IFERROR(T61/S61, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V61" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X61" s="15" t="n">
+        <f aca="false">((O61*0.3)+(Q61*0.175)+(R61*0.175)+(U61*0.175)+((1-V61)*0.175))+W61</f>
+        <v>3.45861111111111</v>
+      </c>
+      <c r="Y61" s="1" t="n">
+        <v>999999995</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="40"/>
@@ -26538,17 +26662,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C1" s="45"/>
       <c r="D1" s="44" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26574,7 +26698,7 @@
         <v>2.4</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26586,13 +26710,13 @@
         <v>3.7</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D4" s="48" t="n">
         <v>3.7</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26608,7 +26732,7 @@
         <v>2.3</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26633,13 +26757,13 @@
         <v>2.89916666666667</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D7" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26665,7 +26789,7 @@
         <v>3.8</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26681,7 +26805,7 @@
         <v>3.9</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26693,13 +26817,13 @@
         <v>3.4</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D11" s="48" t="n">
         <v>3.4</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26715,7 +26839,7 @@
         <v>2.6</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26727,13 +26851,13 @@
         <v>3.5</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D13" s="48" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26749,7 +26873,7 @@
         <v>2.7</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26765,7 +26889,7 @@
         <v>2.6</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26781,7 +26905,7 @@
         <v>3.9</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26797,7 +26921,7 @@
         <v>2.3</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26813,12 +26937,12 @@
         <v>3.5</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
@@ -26829,12 +26953,12 @@
         <v>3.9</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
@@ -26845,7 +26969,7 @@
         <v>3.7</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26857,13 +26981,13 @@
         <v>3.67861111111111</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D21" s="48" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26889,7 +27013,7 @@
         <v>2.4</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26905,7 +27029,7 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26921,7 +27045,7 @@
         <v>3.6</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26937,7 +27061,7 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26949,13 +27073,13 @@
         <v>3.9</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D27" s="48" t="n">
         <v>3.9</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26984,7 +27108,7 @@
         <v>2.6</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26996,13 +27120,13 @@
         <v>3.59875</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D30" s="48" t="n">
         <v>3.6</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27018,7 +27142,7 @@
         <v>3.9</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27034,7 +27158,7 @@
         <v>3.7</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27050,7 +27174,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27066,7 +27190,7 @@
         <v>2.9</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27078,18 +27202,18 @@
         <v>3.935</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D35" s="49" t="n">
         <v>3.9</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
@@ -27100,7 +27224,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27116,12 +27240,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
@@ -27132,7 +27256,7 @@
         <v>3.9</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27148,7 +27272,7 @@
         <v>2.6</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27174,7 +27298,7 @@
         <v>3.5</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27190,7 +27314,7 @@
         <v>3.4</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27206,7 +27330,7 @@
         <v>3.7</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27222,7 +27346,7 @@
         <v>2.6</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27238,7 +27362,7 @@
         <v>3.8</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27254,7 +27378,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27270,7 +27394,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27286,7 +27410,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27315,7 +27439,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27331,12 +27455,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -27347,7 +27471,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27363,12 +27487,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -27379,7 +27503,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27401,7 +27525,7 @@
         <v>3.6</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D56" s="48" t="n">
         <v>3.6</v>
@@ -27416,7 +27540,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D57" s="48" t="n">
         <v>3.3</v>
@@ -27444,7 +27568,7 @@
         <v>3.9</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D59" s="48" t="n">
         <v>3.9</v>
@@ -27561,7 +27685,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27577,7 +27701,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27593,7 +27717,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27632,7 +27756,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27674,16 +27798,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27977,7 +28101,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
@@ -27994,7 +28118,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -28266,7 +28390,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -28300,7 +28424,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -28538,7 +28662,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -28572,7 +28696,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28962,40 +29086,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B1" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="D1" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="E1" s="50" t="s">
-        <v>174</v>
-      </c>
       <c r="F1" s="50" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H1" s="50" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I1" s="50" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K1" s="50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L1" s="50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="186">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -336,6 +336,18 @@
   </si>
   <si>
     <t xml:space="preserve">Arna Kennerüd, Skycaptain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestPlayer1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test K (THROWAWAY ARCHIVE TEST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestPlayer2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test L (THROWAWAY ARCHIVE TEST)</t>
   </si>
   <si>
     <t xml:space="preserve">Decks</t>
@@ -25933,58 +25945,176 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="40"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="22"/>
-      <c r="O58" s="26"/>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="26"/>
-      <c r="R58" s="22"/>
-      <c r="S58" s="22"/>
-      <c r="T58" s="22"/>
-      <c r="U58" s="26"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="24"/>
-      <c r="X58" s="15"/>
-      <c r="Y58" s="1"/>
+      <c r="A58" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B58" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <f aca="false">F58-(1/H58)</f>
+        <v>0.5</v>
+      </c>
+      <c r="K58" s="22" t="n">
+        <f aca="false">((I58-((H58-1)/H58))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <f aca="false">E58-((E59)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <f aca="false">0.5+(L58*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N58" s="22" t="n">
+        <f aca="false">((H58-(G58-1))/H58)*(IF(I58&lt;&gt;0,(I58+H58)/H58,1))</f>
+        <v>1</v>
+      </c>
+      <c r="O58" s="26" t="n">
+        <f aca="false">(N58-(1/6))/(10/6)</f>
+        <v>0.5</v>
+      </c>
+      <c r="P58" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q58" s="26" t="n">
+        <f aca="false">IF(F58=1,(((1-((P58-3)/15))*0.5)+0.5),((P58/18)*0.5))</f>
+        <v>0.766666666666667</v>
+      </c>
+      <c r="R58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="26" t="n">
+        <f aca="false">IFERROR(T58/S58, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V58" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X58" s="15" t="n">
+        <f aca="false">((O58*0.3)+(Q58*0.175)+(R58*0.175)+(U58*0.175)+((1-V58)*0.175))+W58</f>
+        <v>3.63416666666667</v>
+      </c>
+      <c r="Y58" s="1" t="n">
+        <v>999999994</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="40"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="22"/>
-      <c r="O59" s="26"/>
-      <c r="P59" s="22"/>
-      <c r="Q59" s="26"/>
-      <c r="R59" s="22"/>
-      <c r="S59" s="22"/>
-      <c r="T59" s="22"/>
-      <c r="U59" s="26"/>
-      <c r="V59" s="27"/>
-      <c r="W59" s="24"/>
-      <c r="X59" s="15"/>
-      <c r="Y59" s="1"/>
+      <c r="A59" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B59" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="22" t="n">
+        <f aca="false">F59-(1/H59)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="K59" s="22" t="n">
+        <f aca="false">((I59-((H59-1)/H59))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="L59" s="22" t="n">
+        <f aca="false">E59-((E58)/1)</f>
+        <v>0</v>
+      </c>
+      <c r="M59" s="17" t="n">
+        <f aca="false">0.5+(L59*0.09)</f>
+        <v>0.5</v>
+      </c>
+      <c r="N59" s="22" t="n">
+        <f aca="false">((H59-(G59-1))/H59)*(IF(I59&lt;&gt;0,(I59+H59)/H59,1))</f>
+        <v>0.5</v>
+      </c>
+      <c r="O59" s="26" t="n">
+        <f aca="false">(N59-(1/6))/(10/6)</f>
+        <v>0.2</v>
+      </c>
+      <c r="P59" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q59" s="26" t="n">
+        <f aca="false">IF(F59=1,(((1-((P59-3)/15))*0.5)+0.5),((P59/18)*0.5))</f>
+        <v>0.277777777777778</v>
+      </c>
+      <c r="R59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="26" t="n">
+        <f aca="false">IFERROR(T59/S59, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X59" s="15" t="n">
+        <f aca="false">((O59*0.3)+(Q59*0.175)+(R59*0.175)+(U59*0.175)+((1-V59)*0.175))+W59</f>
+        <v>3.45861111111111</v>
+      </c>
+      <c r="Y59" s="1" t="n">
+        <v>999999994</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="40"/>
@@ -26408,17 +26538,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C1" s="45"/>
       <c r="D1" s="44" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26444,7 +26574,7 @@
         <v>2.4</v>
       </c>
       <c r="E3" s="46" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26456,13 +26586,13 @@
         <v>3.7</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D4" s="48" t="n">
         <v>3.7</v>
       </c>
       <c r="E4" s="46" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26478,7 +26608,7 @@
         <v>2.3</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26503,13 +26633,13 @@
         <v>2.89916666666667</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D7" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26535,7 +26665,7 @@
         <v>3.8</v>
       </c>
       <c r="E9" s="46" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26551,7 +26681,7 @@
         <v>3.9</v>
       </c>
       <c r="E10" s="46" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26563,13 +26693,13 @@
         <v>3.4</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" s="48" t="n">
         <v>3.4</v>
       </c>
       <c r="E11" s="46" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26585,7 +26715,7 @@
         <v>2.6</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26597,13 +26727,13 @@
         <v>3.5</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D13" s="48" t="n">
         <v>3.5</v>
       </c>
       <c r="E13" s="46" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26619,7 +26749,7 @@
         <v>2.7</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26635,7 +26765,7 @@
         <v>2.6</v>
       </c>
       <c r="E15" s="46" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26651,7 +26781,7 @@
         <v>3.9</v>
       </c>
       <c r="E16" s="46" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26667,7 +26797,7 @@
         <v>2.3</v>
       </c>
       <c r="E17" s="46" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26683,12 +26813,12 @@
         <v>3.5</v>
       </c>
       <c r="E18" s="46" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A19)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D19)</f>
@@ -26699,12 +26829,12 @@
         <v>3.9</v>
       </c>
       <c r="E19" s="46" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A20)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D20)</f>
@@ -26715,7 +26845,7 @@
         <v>3.7</v>
       </c>
       <c r="E20" s="46" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26727,13 +26857,13 @@
         <v>3.67861111111111</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D21" s="48" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="46" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26759,7 +26889,7 @@
         <v>2.4</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26775,7 +26905,7 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26791,7 +26921,7 @@
         <v>3.6</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26807,7 +26937,7 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26819,13 +26949,13 @@
         <v>3.9</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D27" s="48" t="n">
         <v>3.9</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26854,7 +26984,7 @@
         <v>2.6</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26866,13 +26996,13 @@
         <v>3.59875</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D30" s="48" t="n">
         <v>3.6</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26888,7 +27018,7 @@
         <v>3.9</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26904,7 +27034,7 @@
         <v>3.7</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26920,7 +27050,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26936,7 +27066,7 @@
         <v>2.9</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26948,18 +27078,18 @@
         <v>3.935</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D35" s="49" t="n">
         <v>3.9</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
@@ -26970,7 +27100,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26986,12 +27116,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
@@ -27002,7 +27132,7 @@
         <v>3.9</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27018,7 +27148,7 @@
         <v>2.6</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27044,7 +27174,7 @@
         <v>3.5</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27060,7 +27190,7 @@
         <v>3.4</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27076,7 +27206,7 @@
         <v>3.7</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27092,7 +27222,7 @@
         <v>2.6</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27108,7 +27238,7 @@
         <v>3.8</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27124,7 +27254,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27140,7 +27270,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27156,7 +27286,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27185,7 +27315,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27201,12 +27331,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -27217,7 +27347,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27233,12 +27363,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -27249,7 +27379,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27271,7 +27401,7 @@
         <v>3.6</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D56" s="48" t="n">
         <v>3.6</v>
@@ -27286,7 +27416,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D57" s="48" t="n">
         <v>3.3</v>
@@ -27314,7 +27444,7 @@
         <v>3.9</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D59" s="48" t="n">
         <v>3.9</v>
@@ -27431,7 +27561,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27447,7 +27577,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27463,7 +27593,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27502,7 +27632,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27544,16 +27674,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B1" s="44" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27847,7 +27977,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="48" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B19" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A19)</f>
@@ -27864,7 +27994,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="48" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B20" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A20)</f>
@@ -28136,7 +28266,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -28170,7 +28300,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -28408,7 +28538,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -28442,7 +28572,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -28832,40 +28962,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D1" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E1" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="50" t="s">
-        <v>170</v>
-      </c>
       <c r="F1" s="50" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H1" s="50" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I1" s="50" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J1" s="50" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="K1" s="50" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L1" s="50" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="181">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -25930,112 +25930,348 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="40"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="22"/>
-      <c r="O58" s="26"/>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="26"/>
-      <c r="R58" s="22"/>
-      <c r="S58" s="22"/>
-      <c r="T58" s="22"/>
-      <c r="U58" s="26"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="24"/>
-      <c r="X58" s="15"/>
-      <c r="Y58" s="1"/>
+      <c r="A58" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B58" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>2.30388888888889</v>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="22" t="n">
+        <f aca="false">F58-(1/H58)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="K58" s="22" t="n">
+        <f aca="false">((I58-((H58-1)/H58))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0166666666666667</v>
+      </c>
+      <c r="L58" s="22" t="n">
+        <f aca="false">E58-((E59+E60+E61)/3)</f>
+        <v>-0.62273148148148</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <f aca="false">0.5+(L58*0.09)</f>
+        <v>0.443954166666667</v>
+      </c>
+      <c r="N58" s="22" t="n">
+        <f aca="false">((H58-(G58-1))/H58)*(IF(I58&lt;&gt;0,(I58+H58)/H58,1))</f>
+        <v>0.75</v>
+      </c>
+      <c r="O58" s="26" t="n">
+        <f aca="false">(N58-(1/6))/(10/6)</f>
+        <v>0.35</v>
+      </c>
+      <c r="P58" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q58" s="26" t="n">
+        <f aca="false">IF(F58=1,(((1-((P58-3)/15))*0.5)+0.5),((P58/18)*0.5))</f>
+        <v>0.25</v>
+      </c>
+      <c r="R58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="26" t="n">
+        <f aca="false">IFERROR(T58/S58, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V58" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="X58" s="15" t="n">
+        <f aca="false">((O58*0.3)+(Q58*0.175)+(R58*0.175)+(U58*0.175)+((1-V58)*0.175))+W58</f>
+        <v>2.32375</v>
+      </c>
+      <c r="Y58" s="1" t="n">
+        <v>945272</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="40"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="22"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="22"/>
-      <c r="O59" s="26"/>
-      <c r="P59" s="22"/>
-      <c r="Q59" s="26"/>
-      <c r="R59" s="22"/>
-      <c r="S59" s="22"/>
-      <c r="T59" s="22"/>
-      <c r="U59" s="26"/>
-      <c r="V59" s="27"/>
-      <c r="W59" s="24"/>
-      <c r="X59" s="15"/>
-      <c r="Y59" s="1"/>
+      <c r="A59" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B59" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C59" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>2.94083333333333</v>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H59" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="22" t="n">
+        <f aca="false">F59-(1/H59)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="K59" s="22" t="n">
+        <f aca="false">((I59-((H59-1)/H59))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.0166666666666667</v>
+      </c>
+      <c r="L59" s="22" t="n">
+        <f aca="false">E59-((E58+E60+E61)/3)</f>
+        <v>0.226527777777773</v>
+      </c>
+      <c r="M59" s="17" t="n">
+        <f aca="false">0.5+(L59*0.09)</f>
+        <v>0.5203875</v>
+      </c>
+      <c r="N59" s="22" t="n">
+        <f aca="false">((H59-(G59-1))/H59)*(IF(I59&lt;&gt;0,(I59+H59)/H59,1))</f>
+        <v>0.25</v>
+      </c>
+      <c r="O59" s="26" t="n">
+        <f aca="false">(N59-(1/6))/(10/6)</f>
+        <v>0.05</v>
+      </c>
+      <c r="P59" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="26" t="n">
+        <f aca="false">IF(F59=1,(((1-((P59-3)/15))*0.5)+0.5),((P59/18)*0.5))</f>
+        <v>0.222222222222222</v>
+      </c>
+      <c r="R59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="26" t="n">
+        <f aca="false">IFERROR(T59/S59, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V59" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="X59" s="15" t="n">
+        <f aca="false">((O59*0.3)+(Q59*0.175)+(R59*0.175)+(U59*0.175)+((1-V59)*0.175))+W59</f>
+        <v>2.22888888888889</v>
+      </c>
+      <c r="Y59" s="1" t="n">
+        <v>945272</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="40"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="22"/>
-      <c r="H60" s="22"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="22"/>
-      <c r="L60" s="22"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="22"/>
-      <c r="O60" s="26"/>
-      <c r="P60" s="22"/>
-      <c r="Q60" s="26"/>
-      <c r="R60" s="22"/>
-      <c r="S60" s="22"/>
-      <c r="T60" s="22"/>
-      <c r="U60" s="26"/>
-      <c r="V60" s="27"/>
-      <c r="W60" s="24"/>
-      <c r="X60" s="15"/>
-      <c r="Y60" s="1"/>
+      <c r="A60" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B60" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C60" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F60" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I60" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J60" s="22" t="n">
+        <f aca="false">F60-(1/H60)</f>
+        <v>0.75</v>
+      </c>
+      <c r="K60" s="22" t="n">
+        <f aca="false">((I60-((H60-1)/H60))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.416666666666667</v>
+      </c>
+      <c r="L60" s="22" t="n">
+        <f aca="false">E60-((E58+E59+E61)/3)</f>
+        <v>-0.227916666666667</v>
+      </c>
+      <c r="M60" s="17" t="n">
+        <f aca="false">0.5+(L60*0.09)</f>
+        <v>0.4794875</v>
+      </c>
+      <c r="N60" s="22" t="n">
+        <f aca="false">((H60-(G60-1))/H60)*(IF(I60&lt;&gt;0,(I60+H60)/H60,1))</f>
+        <v>1.5</v>
+      </c>
+      <c r="O60" s="26" t="n">
+        <f aca="false">(N60-(1/6))/(10/6)</f>
+        <v>0.8</v>
+      </c>
+      <c r="P60" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q60" s="26" t="n">
+        <f aca="false">IF(F60=1,(((1-((P60-3)/15))*0.5)+0.5),((P60/18)*0.5))</f>
+        <v>0.8</v>
+      </c>
+      <c r="R60" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="26" t="n">
+        <f aca="false">IFERROR(T60/S60, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="X60" s="15" t="n">
+        <f aca="false">((O60*0.3)+(Q60*0.175)+(R60*0.175)+(U60*0.175)+((1-V60)*0.175))+W60</f>
+        <v>2.905</v>
+      </c>
+      <c r="Y60" s="1" t="n">
+        <v>945272</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="40"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="15"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="22"/>
-      <c r="H61" s="22"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="17"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="26"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="26"/>
-      <c r="R61" s="22"/>
-      <c r="S61" s="22"/>
-      <c r="T61" s="22"/>
-      <c r="U61" s="26"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="24"/>
-      <c r="X61" s="15"/>
-      <c r="Y61" s="1"/>
+      <c r="A61" s="40" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B61" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="C61" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>3.23902777777778</v>
+      </c>
+      <c r="F61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I61" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="22" t="n">
+        <f aca="false">F61-(1/H61)</f>
+        <v>-0.25</v>
+      </c>
+      <c r="K61" s="22" t="n">
+        <f aca="false">((I61-((H61-1)/H61))-(-5/6))/((5-(5/6))-(-5/6))</f>
+        <v>0.216666666666667</v>
+      </c>
+      <c r="L61" s="22" t="n">
+        <f aca="false">E61-((E58+E59+E60)/3)</f>
+        <v>0.624120370370374</v>
+      </c>
+      <c r="M61" s="17" t="n">
+        <f aca="false">0.5+(L61*0.09)</f>
+        <v>0.556170833333334</v>
+      </c>
+      <c r="N61" s="22" t="n">
+        <f aca="false">((H61-(G61-1))/H61)*(IF(I61&lt;&gt;0,(I61+H61)/H61,1))</f>
+        <v>0.625</v>
+      </c>
+      <c r="O61" s="26" t="n">
+        <f aca="false">(N61-(1/6))/(10/6)</f>
+        <v>0.275</v>
+      </c>
+      <c r="P61" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q61" s="26" t="n">
+        <f aca="false">IF(F61=1,(((1-((P61-3)/15))*0.5)+0.5),((P61/18)*0.5))</f>
+        <v>0.222222222222222</v>
+      </c>
+      <c r="R61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="26" t="n">
+        <f aca="false">IFERROR(T61/S61, 1)</f>
+        <v>1</v>
+      </c>
+      <c r="V61" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X61" s="15" t="n">
+        <f aca="false">((O61*0.3)+(Q61*0.175)+(R61*0.175)+(U61*0.175)+((1-V61)*0.175))+W61</f>
+        <v>3.47138888888889</v>
+      </c>
+      <c r="Y61" s="1" t="n">
+        <v>945272</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="40"/>
@@ -26424,7 +26660,7 @@
       </c>
       <c r="B2" s="47" t="n">
         <f aca="false">AVERAGE(B3:B7)</f>
-        <v>2.75813888888889</v>
+        <v>2.76211111111111</v>
       </c>
       <c r="C2" s="45"/>
     </row>
@@ -26468,7 +26704,7 @@
       </c>
       <c r="B5" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A5)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D5)</f>
-        <v>2.30388888888889</v>
+        <v>2.32375</v>
       </c>
       <c r="C5" s="45"/>
       <c r="D5" s="48" t="n">
@@ -26515,7 +26751,7 @@
       </c>
       <c r="B8" s="47" t="n">
         <f aca="false">AVERAGE(B9:B21)</f>
-        <v>3.39360042735043</v>
+        <v>3.33883547008547</v>
       </c>
       <c r="C8" s="45"/>
     </row>
@@ -26657,7 +26893,7 @@
       </c>
       <c r="B17" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Manny")*('Game Log Season 3'!$D$3:$D$1000=A17)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D17)</f>
-        <v>2.94083333333333</v>
+        <v>2.22888888888889</v>
       </c>
       <c r="C17" s="45"/>
       <c r="D17" s="48" t="n">
@@ -26739,7 +26975,7 @@
       </c>
       <c r="B22" s="47" t="n">
         <f aca="false">AVERAGE(B23:B39)</f>
-        <v>3.21919117647059</v>
+        <v>3.23713235294118</v>
       </c>
       <c r="C22" s="45"/>
     </row>
@@ -26844,7 +27080,7 @@
       </c>
       <c r="B29" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A29)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D29)</f>
-        <v>2.6</v>
+        <v>2.905</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="48" t="n">
@@ -27024,7 +27260,7 @@
       </c>
       <c r="B40" s="47" t="n">
         <f aca="false">AVERAGE(B41:B54)</f>
-        <v>3.30218452380952</v>
+        <v>3.31878174603175</v>
       </c>
       <c r="C40" s="45"/>
     </row>
@@ -27130,7 +27366,7 @@
       </c>
       <c r="B47" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A47)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D47)</f>
-        <v>3.23902777777778</v>
+        <v>3.47138888888889</v>
       </c>
       <c r="C47" s="45"/>
       <c r="D47" s="48" t="n">
@@ -27559,7 +27795,7 @@
       </c>
       <c r="B2" s="47" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A2)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="47" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A2,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27567,7 +27803,7 @@
       </c>
       <c r="D2" s="47" t="n">
         <f aca="false">IFERROR(C2/B2,0)</f>
-        <v>0.375</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27610,7 +27846,7 @@
       </c>
       <c r="B5" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A5)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Becca",'Game Log Season 3'!$D$3:$D$1000,A5,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27618,7 +27854,7 @@
       </c>
       <c r="D5" s="48" t="n">
         <f aca="false">IFERROR(C5/B5,0)</f>
-        <v>0.333333333333333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27661,7 +27897,7 @@
       </c>
       <c r="B8" s="47" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="47" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A8,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27669,7 +27905,7 @@
       </c>
       <c r="D8" s="47" t="n">
         <f aca="false">IFERROR(C8/B8,0)</f>
-        <v>0.266666666666667</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27814,7 +28050,7 @@
       </c>
       <c r="B17" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Manny",'Game Log Season 3'!$D$3:$D$1000,A17,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -27822,7 +28058,7 @@
       </c>
       <c r="D17" s="48" t="n">
         <f aca="false">IFERROR(C17/B17,0)</f>
-        <v>0.166666666666667</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27899,15 +28135,15 @@
       </c>
       <c r="B22" s="47" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A22)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C22" s="47" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A22,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" s="47" t="n">
         <f aca="false">IFERROR(C22/B22,0)</f>
-        <v>0.384615384615385</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28018,15 +28254,15 @@
       </c>
       <c r="B29" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A29,'Game Log Season 3'!$F$3:$F$1000,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="48" t="n">
         <f aca="false">IFERROR(C29/B29,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28205,7 +28441,7 @@
       </c>
       <c r="B40" s="47" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A40)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C40" s="47" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,A40,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28213,7 +28449,7 @@
       </c>
       <c r="D40" s="47" t="n">
         <f aca="false">IFERROR(C40/B40,0)</f>
-        <v>0.25</v>
+        <v>0.230769230769231</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28324,7 +28560,7 @@
       </c>
       <c r="B47" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A47,'Game Log Season 3'!$F$3:$F$1000,1)</f>
@@ -28871,11 +29107,11 @@
       </c>
       <c r="B2" s="17" t="n">
         <f aca="false">(H2*0.3)+(I2*0.2)+(L2*0.5)</f>
-        <v>0.343487739096919</v>
+        <v>0.382160342472996</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
@@ -28883,11 +29119,11 @@
       </c>
       <c r="E2" s="17" t="n">
         <f aca="false">IFERROR(C2/(C2+D2),0)</f>
-        <v>0.384615384615385</v>
+        <v>0.428571428571429</v>
       </c>
       <c r="F2" s="1" t="n">
         <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="G2" s="1" t="n">
         <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D2,0)</f>
@@ -28895,15 +29131,15 @@
       </c>
       <c r="H2" s="17" t="n">
         <f aca="false">IFERROR(F2/(F2+G2),0)</f>
-        <v>0.376325088339223</v>
+        <v>0.422258592471359</v>
       </c>
       <c r="I2" s="17" t="n">
         <f aca="false">IF(C2&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.221538461538462</v>
+        <v>0.23547619047619</v>
       </c>
       <c r="J2" s="1" t="n">
         <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C2, 0)</f>
-        <v>5.01575</v>
+        <v>6.0362625</v>
       </c>
       <c r="K2" s="1" t="n">
         <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Mateo", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D2, 0)</f>
@@ -28911,7 +29147,7 @@
       </c>
       <c r="L2" s="17" t="n">
         <f aca="false">IFERROR(J2/(J2+K2),0)</f>
-        <v>0.37256504057492</v>
+        <v>0.4167750532727</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28920,7 +29156,7 @@
       </c>
       <c r="B3" s="17" t="n">
         <f aca="false">(H3*0.3)+(I3*0.2)+(L3*0.5)</f>
-        <v>0.23225483051281</v>
+        <v>0.217200151257559</v>
       </c>
       <c r="C3" s="1" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28928,11 +29164,11 @@
       </c>
       <c r="D3" s="1" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="17" t="n">
         <f aca="false">IFERROR(C3/(C3+D3),0)</f>
-        <v>0.25</v>
+        <v>0.230769230769231</v>
       </c>
       <c r="F3" s="1" t="n">
         <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28940,15 +29176,15 @@
       </c>
       <c r="G3" s="1" t="n">
         <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D3,0)</f>
-        <v>6.46666666666667</v>
+        <v>7.21666666666667</v>
       </c>
       <c r="H3" s="17" t="n">
         <f aca="false">IFERROR(F3/(F3+G3),0)</f>
-        <v>0.248062015503876</v>
+        <v>0.228163992869875</v>
       </c>
       <c r="I3" s="17" t="n">
         <f aca="false">IF(C3&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.19</v>
+        <v>0.192051282051282</v>
       </c>
       <c r="J3" s="1" t="n">
         <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C3, 0)</f>
@@ -28956,11 +29192,11 @@
       </c>
       <c r="K3" s="1" t="n">
         <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Ryan", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D3, 0)</f>
-        <v>9.3315</v>
+        <v>10.3876708333333</v>
       </c>
       <c r="L3" s="17" t="n">
         <f aca="false">IFERROR(J3/(J3+K3),0)</f>
-        <v>0.239672451723295</v>
+        <v>0.220681393972681</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28969,7 +29205,7 @@
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">(H4*0.3)+(I4*0.2)+(L4*0.5)</f>
-        <v>0.339791965801515</v>
+        <v>0.303396021322759</v>
       </c>
       <c r="C4" s="1" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28977,11 +29213,11 @@
       </c>
       <c r="D4" s="1" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="17" t="n">
         <f aca="false">IFERROR(C4/(C4+D4),0)</f>
-        <v>0.375</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="F4" s="1" t="n">
         <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -28989,15 +29225,15 @@
       </c>
       <c r="G4" s="1" t="n">
         <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D4,0)</f>
-        <v>3.63333333333333</v>
+        <v>4.38333333333333</v>
       </c>
       <c r="H4" s="17" t="n">
         <f aca="false">IFERROR(F4/(F4+G4),0)</f>
-        <v>0.38243626062323</v>
+        <v>0.339195979899497</v>
       </c>
       <c r="I4" s="17" t="n">
         <f aca="false">IF(C4&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.119583333333333</v>
+        <v>0.108148148148148</v>
       </c>
       <c r="J4" s="1" t="n">
         <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C4, 0)</f>
@@ -29005,11 +29241,11 @@
       </c>
       <c r="K4" s="1" t="n">
         <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Becca", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D4, 0)</f>
-        <v>4.805</v>
+        <v>5.74895416666667</v>
       </c>
       <c r="L4" s="17" t="n">
         <f aca="false">IFERROR(J4/(J4+K4),0)</f>
-        <v>0.402288841895758</v>
+        <v>0.360015195446561</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29018,7 +29254,7 @@
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">(H5*0.3)+(I5*0.2)+(L5*0.5)</f>
-        <v>0.241609619679882</v>
+        <v>0.226064167519965</v>
       </c>
       <c r="C5" s="1" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -29026,11 +29262,11 @@
       </c>
       <c r="D5" s="1" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="17" t="n">
         <f aca="false">IFERROR(C5/(C5+D5),0)</f>
-        <v>0.266666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="F5" s="1" t="n">
         <f aca="false">SUMIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)</f>
@@ -29038,15 +29274,15 @@
       </c>
       <c r="G5" s="1" t="n">
         <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$J$3:$J$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)*-1))*D5,0)</f>
-        <v>7.93333333333333</v>
+        <v>8.68333333333333</v>
       </c>
       <c r="H5" s="17" t="n">
         <f aca="false">IFERROR(F5/(F5+G5),0)</f>
-        <v>0.263157894736842</v>
+        <v>0.246020260492041</v>
       </c>
       <c r="I5" s="17" t="n">
         <f aca="false">IF(C5&lt;&gt;0,AVERAGEIF('Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$K$3:$K$126),0)</f>
-        <v>0.156444444444444</v>
+        <v>0.147708333333333</v>
       </c>
       <c r="J5" s="1" t="n">
         <f aca="false">IFERROR((1-(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 1)-0.5))*C5, 0)</f>
@@ -29054,11 +29290,11 @@
       </c>
       <c r="K5" s="1" t="n">
         <f aca="false">IFERROR((1+(AVERAGEIFS('Game Log Season 3'!$M$3:$M$126, 'Game Log Season 3'!$C$3:$C$126, "Manny", 'Game Log Season 3'!$F$3:$F$126, 0)-0.5))*D5, 0)</f>
-        <v>10.664</v>
+        <v>11.6843875</v>
       </c>
       <c r="L5" s="17" t="n">
         <f aca="false">IFERROR(J5/(J5+K5),0)</f>
-        <v>0.26274672473988</v>
+        <v>0.245432845411373</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -25833,7 +25833,7 @@
         <v>0</v>
       </c>
       <c r="W56" s="24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X56" s="15" t="n">
         <f aca="false">((O56*0.3)+(Q56*0.175)+(R56*0.175)+(U56*0.175)+((1-V56)*0.175))+W56</f>
@@ -26735,8 +26735,10 @@
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
         <v>2.89916666666667</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>109</v>
+      <c r="C7" s="45" t="inlineStr">
+        <is>
+          <t>*Bracket 3</t>
+        </is>
       </c>
       <c r="D7" s="48" t="n">
         <v>2</v>

--- a/deck-strength.xlsx
+++ b/deck-strength.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="180">
   <si>
     <t xml:space="preserve">Base Game Info</t>
   </si>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">648625</t>
   </si>
   <si>
-    <t xml:space="preserve">*Bracket 2</t>
+    <t xml:space="preserve">*Bracket 3</t>
   </si>
   <si>
     <t xml:space="preserve">797189</t>
@@ -408,9 +408,6 @@
   </si>
   <si>
     <t xml:space="preserve">737114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Bracket 3</t>
   </si>
   <si>
     <t xml:space="preserve">741945</t>
@@ -887,203 +884,203 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -25837,7 +25834,7 @@
       </c>
       <c r="X56" s="15" t="n">
         <f aca="false">((O56*0.3)+(Q56*0.175)+(R56*0.175)+(U56*0.175)+((1-V56)*0.175))+W56</f>
-        <v>2.89916666666667</v>
+        <v>3.89916666666667</v>
       </c>
       <c r="Y56" s="1" t="n">
         <v>944159</v>
@@ -26660,7 +26657,7 @@
       </c>
       <c r="B2" s="47" t="n">
         <f aca="false">AVERAGE(B3:B7)</f>
-        <v>2.76211111111111</v>
+        <v>2.96211111111111</v>
       </c>
       <c r="C2" s="45"/>
     </row>
@@ -26733,12 +26730,10 @@
       </c>
       <c r="B7" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Becca")*('Game Log Season 3'!$D$3:$D$1000=A7)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D7)</f>
-        <v>2.89916666666667</v>
-      </c>
-      <c r="C7" s="45" t="inlineStr">
-        <is>
-          <t>*Bracket 3</t>
-        </is>
+        <v>3.89916666666667</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>109</v>
       </c>
       <c r="D7" s="48" t="n">
         <v>2</v>
@@ -26962,13 +26957,13 @@
         <v>3.67861111111111</v>
       </c>
       <c r="C21" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="46" t="s">
         <v>126</v>
-      </c>
-      <c r="D21" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" s="46" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26994,7 +26989,7 @@
         <v>2.4</v>
       </c>
       <c r="E23" s="46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27010,7 +27005,7 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27026,7 +27021,7 @@
         <v>3.6</v>
       </c>
       <c r="E25" s="46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27042,7 +27037,7 @@
         <v>2.9</v>
       </c>
       <c r="E26" s="46" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27060,7 +27055,7 @@
         <v>3.9</v>
       </c>
       <c r="E27" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27089,7 +27084,7 @@
         <v>2.6</v>
       </c>
       <c r="E29" s="46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27101,13 +27096,13 @@
         <v>3.59875</v>
       </c>
       <c r="C30" s="45" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D30" s="48" t="n">
         <v>3.6</v>
       </c>
       <c r="E30" s="46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27123,7 +27118,7 @@
         <v>3.9</v>
       </c>
       <c r="E31" s="46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27139,7 +27134,7 @@
         <v>3.7</v>
       </c>
       <c r="E32" s="46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27155,7 +27150,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27171,7 +27166,7 @@
         <v>2.9</v>
       </c>
       <c r="E34" s="46" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27183,18 +27178,18 @@
         <v>3.935</v>
       </c>
       <c r="C35" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D35" s="49" t="n">
         <v>3.9</v>
       </c>
       <c r="E35" s="46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A36)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D36)</f>
@@ -27205,7 +27200,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27221,12 +27216,12 @@
         <v>2</v>
       </c>
       <c r="E37" s="46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Mateo")*('Game Log Season 3'!$D$3:$D$1000=A38)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D38)</f>
@@ -27237,7 +27232,7 @@
         <v>3.9</v>
       </c>
       <c r="E38" s="46" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27253,7 +27248,7 @@
         <v>2.6</v>
       </c>
       <c r="E39" s="46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27279,7 +27274,7 @@
         <v>3.5</v>
       </c>
       <c r="E41" s="46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27295,7 +27290,7 @@
         <v>3.4</v>
       </c>
       <c r="E42" s="46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27311,7 +27306,7 @@
         <v>3.7</v>
       </c>
       <c r="E43" s="46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27327,7 +27322,7 @@
         <v>2.6</v>
       </c>
       <c r="E44" s="46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27343,7 +27338,7 @@
         <v>3.8</v>
       </c>
       <c r="E45" s="46" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27359,7 +27354,7 @@
         <v>2.6</v>
       </c>
       <c r="E46" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27375,7 +27370,7 @@
         <v>3.6</v>
       </c>
       <c r="E47" s="46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27391,7 +27386,7 @@
         <v>2.6</v>
       </c>
       <c r="E48" s="46" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27420,7 +27415,7 @@
         <v>2.9</v>
       </c>
       <c r="E50" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27436,12 +27431,12 @@
         <v>3.9</v>
       </c>
       <c r="E51" s="46" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A52)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D52)</f>
@@ -27452,7 +27447,7 @@
         <v>3.7</v>
       </c>
       <c r="E52" s="46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27468,12 +27463,12 @@
         <v>3.2</v>
       </c>
       <c r="E53" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(('Game Log Season 3'!$C$3:$C$1000="Ryan")*('Game Log Season 3'!$D$3:$D$1000=A54)*('Game Log Season 3'!$X$3:$X$1000&lt;&gt;"")),'Game Log Season 3'!$X$3:$X$1000), D54)</f>
@@ -27484,7 +27479,7 @@
         <v>3.9</v>
       </c>
       <c r="E54" s="46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27506,7 +27501,7 @@
         <v>3.6</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D56" s="48" t="n">
         <v>3.6</v>
@@ -27521,7 +27516,7 @@
         <v>3.33761111111111</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D57" s="48" t="n">
         <v>3.3</v>
@@ -27549,7 +27544,7 @@
         <v>3.9</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D59" s="48" t="n">
         <v>3.9</v>
@@ -27666,7 +27661,7 @@
         <v>2.7</v>
       </c>
       <c r="E68" s="46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27682,7 +27677,7 @@
         <v>3.4</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27698,7 +27693,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27737,7 +27732,7 @@
         <v>2.2</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27779,16 +27774,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="C1" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="D1" s="44" t="s">
         <v>168</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28371,7 +28366,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="48" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A36)</f>
@@ -28405,7 +28400,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="48" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B38" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Mateo",'Game Log Season 3'!$D$3:$D$1000,A38)</f>
@@ -28643,7 +28638,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B52" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A52)</f>
@@ -28677,7 +28672,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B54" s="48" t="n">
         <f aca="false">COUNTIFS('Game Log Season 3'!$C$3:$C$1000,"Ryan",'Game Log Season 3'!$D$3:$D$1000,A54)</f>
@@ -29067,40 +29062,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="C1" s="50" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="D1" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="E1" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1" s="50" t="s">
         <v>173</v>
       </c>
-      <c r="E1" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="F1" s="50" t="s">
+      <c r="G1" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="H1" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="H1" s="50" t="s">
+      <c r="I1" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="J1" s="50" t="s">
         <v>177</v>
       </c>
-      <c r="J1" s="50" t="s">
+      <c r="K1" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="L1" s="50" t="s">
         <v>179</v>
-      </c>
-      <c r="L1" s="50" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
